--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -2098,13 +2098,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46112.51244319444</v>
+        <v>46112.679109861114</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.51244314815</v>
+        <v>46112.67910981481</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.51823255787</v>
+        <v>46112.684899224536</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2147,13 +2147,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46112.51257668981</v>
+        <v>46112.679243356484</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.51257664352</v>
+        <v>46112.67924331018</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.5127128125</v>
+        <v>46112.67937947917</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2210,13 +2210,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46112.51258456019</v>
+        <v>46112.67925122685</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.512584537035</v>
+        <v>46112.67925120371</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.51271390046</v>
+        <v>46112.67938056713</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2273,13 +2273,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46112.512590729166</v>
+        <v>46112.67925739584</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.512590706014</v>
+        <v>46112.679257372685</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.512714641205</v>
+        <v>46112.67938130787</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2336,13 +2336,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46112.512596782406</v>
+        <v>46112.67926344907</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.51259677083</v>
+        <v>46112.6792634375</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.51271540509</v>
+        <v>46112.67938207176</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2399,13 +2399,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46112.51260584491</v>
+        <v>46112.679272511574</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.51260582176</v>
+        <v>46112.67927248843</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.51271681713</v>
+        <v>46112.679383483795</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2462,11 +2462,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46112.512449305555</v>
+        <v>46112.67911597222</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.72790445602</v>
+        <v>46134.894571122684</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2509,13 +2509,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46112.51261770833</v>
+        <v>46112.679284375</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.727895069445</v>
+        <v>46134.89456173611</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.72791310185</v>
+        <v>46134.894579768516</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2574,11 +2574,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46112.51262674769</v>
+        <v>46112.67929341435</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46112.51271876157</v>
+        <v>46112.679385428244</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2637,11 +2637,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46112.51263542824</v>
+        <v>46112.67930209491</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46112.57621241898</v>
+        <v>46112.74287908565</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2690,11 +2690,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46112.51264354167</v>
+        <v>46112.67931020833</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46112.576934282406</v>
+        <v>46112.74360094908</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2743,11 +2743,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46112.51265068287</v>
+        <v>46112.67931734954</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46112.57731502315</v>
+        <v>46112.74398168981</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2796,11 +2796,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46112.512658182866</v>
+        <v>46112.67932484954</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46112.577250497685</v>
+        <v>46112.74391716435</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2849,13 +2849,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46112.5124543287</v>
+        <v>46112.679120995366</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.576852453705</v>
+        <v>46114.74351912037</v>
       </c>
       <c r="D17" s="8">
-        <v>46118.382188020834</v>
+        <v>46118.5488546875</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2900,13 +2900,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46112.51266609954</v>
+        <v>46112.6793327662</v>
       </c>
       <c r="C18" s="5">
-        <v>46113.64149030093</v>
+        <v>46113.80815696759</v>
       </c>
       <c r="D18" s="5">
-        <v>46113.97976787037</v>
+        <v>46114.14643453703</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2965,13 +2965,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46112.51267491898</v>
+        <v>46112.67934158565</v>
       </c>
       <c r="C19" s="8">
-        <v>46113.64152197917</v>
+        <v>46113.80818864584</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.001939525464</v>
+        <v>46121.16860619213</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -3030,13 +3030,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46112.512683865745</v>
+        <v>46112.6793505324</v>
       </c>
       <c r="C20" s="5">
-        <v>46113.64158159722</v>
+        <v>46113.808248263886</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.00193938657</v>
+        <v>46121.16860605324</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -3095,13 +3095,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46112.51269375</v>
+        <v>46112.67936041667</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.5768353125</v>
+        <v>46114.74350197917</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.00193940972</v>
+        <v>46121.16860607639</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3160,13 +3160,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46112.5127040625</v>
+        <v>46112.679370729165</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.641615659726</v>
+        <v>46113.80828232639</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.00193939815</v>
+        <v>46121.16860606481</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3225,11 +3225,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46112.51246052083</v>
+        <v>46112.6791271875</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.378926053236</v>
+        <v>46135.54559271991</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3274,13 +3274,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46112.51275108797</v>
+        <v>46112.679417754625</v>
       </c>
       <c r="C24" s="5">
-        <v>46113.64167752315</v>
+        <v>46113.80834418982</v>
       </c>
       <c r="D24" s="5">
-        <v>46115.97324016204</v>
+        <v>46116.1399068287</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3339,13 +3339,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46112.512763437495</v>
+        <v>46112.67943010417</v>
       </c>
       <c r="C25" s="8">
-        <v>46113.641691261575</v>
+        <v>46113.80835792824</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.01996149306</v>
+        <v>46123.18662815972</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3404,13 +3404,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46112.5127737963</v>
+        <v>46112.67944046296</v>
       </c>
       <c r="C26" s="5">
-        <v>46113.64171145833</v>
+        <v>46113.808378125</v>
       </c>
       <c r="D26" s="5">
-        <v>46123.01996138888</v>
+        <v>46123.186628055555</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3469,13 +3469,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46112.51278568287</v>
+        <v>46112.679452349534</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.3789077199</v>
+        <v>46135.545574386575</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.3791616088</v>
+        <v>46135.54582827546</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3534,11 +3534,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46112.51279622685</v>
+        <v>46112.67946289352</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46185.03691783565</v>
+        <v>46185.20358450232</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3597,13 +3597,13 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46112.512811469904</v>
+        <v>46112.679478136575</v>
       </c>
       <c r="C29" s="8">
-        <v>46113.64174697916</v>
+        <v>46113.808413645835</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.01996229167</v>
+        <v>46123.186628958334</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3662,11 +3662,11 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46112.512821365744</v>
+        <v>46112.67948803241</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46185.03691782407</v>
+        <v>46185.20358449074</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3725,13 +3725,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46112.51283033565</v>
+        <v>46112.67949700232</v>
       </c>
       <c r="C31" s="8">
-        <v>46113.64180048611</v>
+        <v>46113.808467152776</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.019961516206</v>
+        <v>46123.18662818287</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3790,11 +3790,11 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46112.512468402776</v>
+        <v>46112.67913506944</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.70107769676</v>
+        <v>46154.86774436342</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3837,11 +3837,11 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46112.51283943287</v>
+        <v>46112.679506099536</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46182.511818217594</v>
+        <v>46182.67848488426</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3900,13 +3900,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46112.51284900463</v>
+        <v>46112.6795156713</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.51181258102</v>
+        <v>46182.67847924768</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.51181427084</v>
+        <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3965,11 +3965,11 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46112.51285855324</v>
+        <v>46112.67952521991</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.51181939815</v>
+        <v>46182.67848606482</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -4028,11 +4028,11 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46112.512867812504</v>
+        <v>46112.67953447917</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.690974791665</v>
+        <v>46169.85764145834</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -4091,11 +4091,11 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46112.51287643518</v>
+        <v>46112.679543101855</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46169.691055752315</v>
+        <v>46169.85772241898</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -4154,11 +4154,11 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46112.51288542824</v>
+        <v>46112.67955209491</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.6910919213</v>
+        <v>46169.85775858797</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -4215,11 +4215,11 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46112.512938252316</v>
+        <v>46112.67960491898</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46183.022532048606</v>
+        <v>46183.18919871528</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -4278,13 +4278,13 @@
         <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46112.51294784722</v>
+        <v>46112.679614513894</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.5115599537</v>
+        <v>46182.678226620366</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.511561238425</v>
+        <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -4343,11 +4343,11 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46112.51295690972</v>
+        <v>46112.67962357639</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46182.51156645833</v>
+        <v>46182.678233125</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -4406,11 +4406,11 @@
         <v>152</v>
       </c>
       <c r="B42" s="5">
-        <v>46112.51296591436</v>
+        <v>46112.679632581014</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.51145549769</v>
+        <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>153</v>
@@ -4469,13 +4469,13 @@
         <v>155</v>
       </c>
       <c r="B43" s="8">
-        <v>46112.5129746875</v>
+        <v>46112.67964135417</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.511448171295</v>
+        <v>46182.67811483797</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.51145045139</v>
+        <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>156</v>
@@ -4534,11 +4534,11 @@
         <v>158</v>
       </c>
       <c r="B44" s="5">
-        <v>46112.512987187496</v>
+        <v>46112.67965385417</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.51145657407</v>
+        <v>46182.67812324074</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>159</v>
@@ -4597,13 +4597,13 @@
         <v>161</v>
       </c>
       <c r="B45" s="8">
-        <v>46112.51299570602</v>
+        <v>46112.679662372684</v>
       </c>
       <c r="C45" s="8">
-        <v>46155.726274988425</v>
+        <v>46155.8929416551</v>
       </c>
       <c r="D45" s="8">
-        <v>46182.51145737269</v>
+        <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>162</v>
@@ -4662,11 +4662,11 @@
         <v>164</v>
       </c>
       <c r="B46" s="5">
-        <v>46112.51300423611</v>
+        <v>46112.67967090278</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.690259490744</v>
+        <v>46169.85692615741</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4725,11 +4725,11 @@
         <v>169</v>
       </c>
       <c r="B47" s="8">
-        <v>46112.51301306713</v>
+        <v>46112.679679733796</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.690210381945</v>
+        <v>46169.856877048616</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4788,11 +4788,11 @@
         <v>171</v>
       </c>
       <c r="B48" s="5">
-        <v>46112.51302189815</v>
+        <v>46112.679688564815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.69023289352</v>
+        <v>46169.85689956018</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4851,13 +4851,13 @@
         <v>174</v>
       </c>
       <c r="B49" s="8">
-        <v>46112.51303165509</v>
+        <v>46112.679698321765</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.70106975695</v>
+        <v>46154.86773642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.70108104167</v>
+        <v>46154.86774770833</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -4916,13 +4916,13 @@
         <v>177</v>
       </c>
       <c r="B50" s="5">
-        <v>46112.51303997685</v>
+        <v>46112.67970664352</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.70082611111</v>
+        <v>46154.867492777776</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.70082777778</v>
+        <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>178</v>
@@ -4971,13 +4971,13 @@
         <v>180</v>
       </c>
       <c r="B51" s="8">
-        <v>46112.51304803241</v>
+        <v>46112.67971469907</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.7010562963</v>
+        <v>46154.86772296297</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.701057638886</v>
+        <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>181</v>
@@ -5026,11 +5026,11 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46112.51305577546</v>
+        <v>46112.67972244213</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46181.566355358795</v>
+        <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5089,11 +5089,11 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46112.51306508102</v>
+        <v>46112.67973174769</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.6904224537</v>
+        <v>46169.85708912037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>117</v>
@@ -5148,11 +5148,11 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46112.513109594904</v>
+        <v>46112.679776261575</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46181.566355902774</v>
+        <v>46181.733022569446</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -5201,13 +5201,13 @@
         <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46112.51312052083</v>
+        <v>46112.6797871875</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.52637825231</v>
+        <v>46182.69304491898</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.526389363426</v>
+        <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>195</v>
@@ -5266,13 +5266,13 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46112.51312832176</v>
+        <v>46112.67979498843</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.50735290509</v>
+        <v>46182.67401957176</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.50735489583</v>
+        <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -5321,13 +5321,13 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46112.51313431713</v>
+        <v>46112.679800983795</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.52636532407</v>
+        <v>46182.69303199074</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.526366875</v>
+        <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5376,11 +5376,11 @@
         <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46112.51314059028</v>
+        <v>46112.67980725694</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.4768471412</v>
+        <v>46162.64351380787</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>204</v>
@@ -5425,13 +5425,13 @@
         <v>206</v>
       </c>
       <c r="B59" s="8">
-        <v>46112.51314456019</v>
+        <v>46112.67981122685</v>
       </c>
       <c r="C59" s="8">
-        <v>46155.38365375</v>
+        <v>46155.55032041667</v>
       </c>
       <c r="D59" s="8">
-        <v>46155.38366818287</v>
+        <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>207</v>
@@ -5490,13 +5490,13 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.55900234954</v>
+        <v>46114.7256690162</v>
       </c>
       <c r="C60" s="5">
-        <v>46155.38283228009</v>
+        <v>46155.549498946755</v>
       </c>
       <c r="D60" s="5">
-        <v>46157.76145039352</v>
+        <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5545,13 +5545,13 @@
         <v>217</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.55919216435</v>
+        <v>46114.72585883102</v>
       </c>
       <c r="C61" s="8">
-        <v>46155.38284497685</v>
+        <v>46155.54951164352</v>
       </c>
       <c r="D61" s="8">
-        <v>46157.763175127315</v>
+        <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>218</v>
@@ -5600,13 +5600,13 @@
         <v>220</v>
       </c>
       <c r="B62" s="5">
-        <v>46114.559363113425</v>
+        <v>46114.7260297801</v>
       </c>
       <c r="C62" s="5">
-        <v>46155.38290252315</v>
+        <v>46155.54956918981</v>
       </c>
       <c r="D62" s="5">
-        <v>46155.38290398148</v>
+        <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>221</v>
@@ -5655,13 +5655,13 @@
         <v>223</v>
       </c>
       <c r="B63" s="8">
-        <v>46112.513158518515</v>
+        <v>46112.67982518519</v>
       </c>
       <c r="C63" s="8">
-        <v>46162.47682798612</v>
+        <v>46162.64349465277</v>
       </c>
       <c r="D63" s="8">
-        <v>46182.03449976852</v>
+        <v>46182.20116643519</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5720,13 +5720,13 @@
         <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.56278202546</v>
+        <v>46114.72944869213</v>
       </c>
       <c r="C64" s="5">
-        <v>46162.47679596065</v>
+        <v>46162.64346262731</v>
       </c>
       <c r="D64" s="5">
-        <v>46162.47679793982</v>
+        <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>213</v>
@@ -5775,13 +5775,13 @@
         <v>229</v>
       </c>
       <c r="B65" s="8">
-        <v>46114.56284165509</v>
+        <v>46114.72950832176</v>
       </c>
       <c r="C65" s="8">
-        <v>46162.4768038426</v>
+        <v>46162.643470509254</v>
       </c>
       <c r="D65" s="8">
-        <v>46162.47680546297</v>
+        <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>218</v>
@@ -5830,13 +5830,13 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.56289835648</v>
+        <v>46114.72956502315</v>
       </c>
       <c r="C66" s="5">
-        <v>46162.47681384259</v>
+        <v>46162.64348050926</v>
       </c>
       <c r="D66" s="5">
-        <v>46162.47681508102</v>
+        <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>221</v>
@@ -5885,13 +5885,13 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46112.513167129626</v>
+        <v>46112.6798337963</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.566344293984</v>
+        <v>46181.73301096065</v>
       </c>
       <c r="D67" s="8">
-        <v>46183.03786285879</v>
+        <v>46183.204529525465</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>108</v>
@@ -5950,13 +5950,13 @@
         <v>237</v>
       </c>
       <c r="B68" s="5">
-        <v>46114.562975381945</v>
+        <v>46114.72964204861</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.56631296297</v>
+        <v>46181.732979629625</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.56631502315</v>
+        <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>213</v>
@@ -6003,13 +6003,13 @@
         <v>238</v>
       </c>
       <c r="B69" s="8">
-        <v>46114.56307118056</v>
+        <v>46114.72973784722</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.566322303246</v>
+        <v>46181.7329889699</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.56632388889</v>
+        <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>218</v>
@@ -6056,13 +6056,13 @@
         <v>239</v>
       </c>
       <c r="B70" s="5">
-        <v>46114.56312274306</v>
+        <v>46114.72978940972</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.56633099537</v>
+        <v>46181.73299766204</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.56633236111</v>
+        <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>221</v>
@@ -6109,11 +6109,11 @@
         <v>240</v>
       </c>
       <c r="B71" s="8">
-        <v>46112.513180486116</v>
+        <v>46112.67984715277</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.38119627315</v>
+        <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>241</v>
@@ -6172,11 +6172,11 @@
         <v>245</v>
       </c>
       <c r="B72" s="5">
-        <v>46112.513187453704</v>
+        <v>46112.679854120375</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.38120070602</v>
+        <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>213</v>
@@ -6225,11 +6225,11 @@
         <v>247</v>
       </c>
       <c r="B73" s="8">
-        <v>46112.51319414352</v>
+        <v>46112.67986081018</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.381201516204</v>
+        <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>248</v>
@@ -6278,11 +6278,11 @@
         <v>250</v>
       </c>
       <c r="B74" s="5">
-        <v>46112.528609155095</v>
+        <v>46112.69527582176</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.38120229167</v>
+        <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>251</v>
@@ -6331,11 +6331,11 @@
         <v>254</v>
       </c>
       <c r="B75" s="8">
-        <v>46112.51320065973</v>
+        <v>46112.679867326384</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46118.38429747685</v>
+        <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>255</v>
@@ -6378,11 +6378,11 @@
         <v>257</v>
       </c>
       <c r="B76" s="5">
-        <v>46112.513203807874</v>
+        <v>46112.67987047454</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.38430252315</v>
+        <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>256</v>
@@ -6439,11 +6439,11 @@
         <v>261</v>
       </c>
       <c r="B77" s="8">
-        <v>46112.51321234954</v>
+        <v>46112.6798790162</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.57779443287</v>
+        <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>262</v>
@@ -6486,11 +6486,11 @@
         <v>264</v>
       </c>
       <c r="B78" s="5">
-        <v>46112.51321587963</v>
+        <v>46112.6798825463</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46177.041532812495</v>
+        <v>46177.208199479166</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>265</v>
@@ -6549,11 +6549,11 @@
         <v>269</v>
       </c>
       <c r="B79" s="8">
-        <v>46112.51322407408</v>
+        <v>46112.679890740736</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46179.00114486111</v>
+        <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>270</v>
@@ -6612,11 +6612,11 @@
         <v>272</v>
       </c>
       <c r="B80" s="5">
-        <v>46112.51323149305</v>
+        <v>46112.679898159724</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46118.370271203705</v>
+        <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>273</v>
@@ -6659,11 +6659,11 @@
         <v>275</v>
       </c>
       <c r="B81" s="8">
-        <v>46112.51323503473</v>
+        <v>46112.679901701384</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46118.369935509254</v>
+        <v>46118.536602175926</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>
@@ -6722,11 +6722,11 @@
         <v>280</v>
       </c>
       <c r="B82" s="5">
-        <v>46112.51324356481</v>
+        <v>46112.67991023148</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46118.37004333333</v>
+        <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>281</v>
@@ -6785,11 +6785,11 @@
         <v>282</v>
       </c>
       <c r="B83" s="8">
-        <v>46112.513294108794</v>
+        <v>46112.679960775466</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46181.56635840278</v>
+        <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>213</v>
@@ -6838,11 +6838,11 @@
         <v>285</v>
       </c>
       <c r="B84" s="5">
-        <v>46112.51330585648</v>
+        <v>46112.67997252315</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46181.56636319445</v>
+        <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>248</v>
@@ -6891,11 +6891,11 @@
         <v>287</v>
       </c>
       <c r="B85" s="8">
-        <v>46112.51646270833</v>
+        <v>46112.683129375</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46118.36979733796</v>
+        <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>251</v>
@@ -6944,11 +6944,11 @@
         <v>289</v>
       </c>
       <c r="B86" s="5">
-        <v>46112.51331552083</v>
+        <v>46112.6799821875</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.370731319446</v>
+        <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>290</v>
@@ -7007,11 +7007,11 @@
         <v>292</v>
       </c>
       <c r="B87" s="8">
-        <v>46112.513324988424</v>
+        <v>46112.679991655095</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46181.56635912037</v>
+        <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>213</v>
@@ -7060,11 +7060,11 @@
         <v>295</v>
       </c>
       <c r="B88" s="5">
-        <v>46112.513333993054</v>
+        <v>46112.68000065972</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46181.56635642362</v>
+        <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>248</v>
@@ -7113,11 +7113,11 @@
         <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46112.51887622685</v>
+        <v>46112.68554289352</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46118.370733310185</v>
+        <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>252</v>
@@ -7166,11 +7166,11 @@
         <v>300</v>
       </c>
       <c r="B90" s="5">
-        <v>46112.51334262731</v>
+        <v>46112.68000929398</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.38430175926</v>
+        <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>301</v>
@@ -7213,11 +7213,11 @@
         <v>303</v>
       </c>
       <c r="B91" s="8">
-        <v>46112.51334737269</v>
+        <v>46112.68001403935</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.0316921875</v>
+        <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>304</v>
@@ -7276,11 +7276,11 @@
         <v>306</v>
       </c>
       <c r="B92" s="5">
-        <v>46112.51335707176</v>
+        <v>46112.68002373843</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46118.385106875</v>
+        <v>46118.551773541665</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>57</v>
@@ -7339,11 +7339,11 @@
         <v>308</v>
       </c>
       <c r="B93" s="8">
-        <v>46112.51337078704</v>
+        <v>46112.680037453705</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46112.513543113426</v>
+        <v>46112.6802097801</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>309</v>
@@ -7402,11 +7402,11 @@
         <v>311</v>
       </c>
       <c r="B94" s="5">
-        <v>46112.51337990741</v>
+        <v>46112.680046574074</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46112.51360348379</v>
+        <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>312</v>
@@ -7465,11 +7465,11 @@
         <v>314</v>
       </c>
       <c r="B95" s="8">
-        <v>46112.51339332176</v>
+        <v>46112.68005998843</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46154.701074004624</v>
+        <v>46154.867740671296</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>315</v>
@@ -7528,11 +7528,11 @@
         <v>317</v>
       </c>
       <c r="B96" s="5">
-        <v>46112.51340157408</v>
+        <v>46112.68006824074</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46118.38429957176</v>
+        <v>46118.55096623843</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>318</v>
@@ -7589,11 +7589,11 @@
         <v>320</v>
       </c>
       <c r="B97" s="8">
-        <v>46112.51341141204</v>
+        <v>46112.6800780787</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46183.02253207176</v>
+        <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>321</v>
@@ -7652,11 +7652,11 @@
         <v>323</v>
       </c>
       <c r="B98" s="5">
-        <v>46112.513451516206</v>
+        <v>46112.68011818287</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46118.37341457176</v>
+        <v>46118.540081238425</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>324</v>
@@ -7699,11 +7699,11 @@
         <v>326</v>
       </c>
       <c r="B99" s="8">
-        <v>46112.513457696754</v>
+        <v>46112.680124363425</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46118.37427302083</v>
+        <v>46118.540939687504</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>327</v>
@@ -7762,11 +7762,11 @@
         <v>329</v>
       </c>
       <c r="B100" s="5">
-        <v>46112.51346640046</v>
+        <v>46112.68013306713</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.384298125005</v>
+        <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>213</v>
@@ -7815,11 +7815,11 @@
         <v>332</v>
       </c>
       <c r="B101" s="8">
-        <v>46112.51347578704</v>
+        <v>46112.680142453704</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.384299618054</v>
+        <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>248</v>
@@ -7868,11 +7868,11 @@
         <v>335</v>
       </c>
       <c r="B102" s="5">
-        <v>46112.52029046296</v>
+        <v>46112.68695712963</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46118.37427526621</v>
+        <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>252</v>
@@ -7921,11 +7921,11 @@
         <v>337</v>
       </c>
       <c r="B103" s="8">
-        <v>46112.51348563658</v>
+        <v>46112.68015230324</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.374608032405</v>
+        <v>46118.54127469908</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>338</v>
@@ -7984,11 +7984,11 @@
         <v>340</v>
       </c>
       <c r="B104" s="5">
-        <v>46112.51349394676</v>
+        <v>46112.680160613425</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46181.566359606484</v>
+        <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>213</v>
@@ -8037,11 +8037,11 @@
         <v>343</v>
       </c>
       <c r="B105" s="8">
-        <v>46112.513505462965</v>
+        <v>46112.68017212963</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46181.566357118056</v>
+        <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>248</v>
@@ -8090,11 +8090,11 @@
         <v>346</v>
       </c>
       <c r="B106" s="5">
-        <v>46112.52114252315</v>
+        <v>46112.68780918981</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.37460988426</v>
+        <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>252</v>
@@ -8143,11 +8143,11 @@
         <v>348</v>
       </c>
       <c r="B107" s="8">
-        <v>46112.5135159375</v>
+        <v>46112.68018260416</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.37478846065</v>
+        <v>46118.54145512731</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>349</v>
@@ -8206,11 +8206,11 @@
         <v>350</v>
       </c>
       <c r="B108" s="5">
-        <v>46112.51352381945</v>
+        <v>46112.680190486106</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46181.5663616088</v>
+        <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>213</v>
@@ -8259,11 +8259,11 @@
         <v>353</v>
       </c>
       <c r="B109" s="8">
-        <v>46112.513535081016</v>
+        <v>46112.68020174769</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46181.56636039352</v>
+        <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>248</v>
@@ -8312,11 +8312,11 @@
         <v>356</v>
       </c>
       <c r="B110" s="5">
-        <v>46112.52223030092</v>
+        <v>46112.68889696759</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46118.37478960648</v>
+        <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>252</v>
@@ -8365,11 +8365,11 @@
         <v>358</v>
       </c>
       <c r="B111" s="8">
-        <v>46112.51354650463</v>
+        <v>46112.6802131713</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46118.3749275463</v>
+        <v>46118.54159421296</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>359</v>
@@ -8428,11 +8428,11 @@
         <v>360</v>
       </c>
       <c r="B112" s="5">
-        <v>46112.51355444445</v>
+        <v>46112.680221111106</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46181.566360937504</v>
+        <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>213</v>
@@ -8481,11 +8481,11 @@
         <v>362</v>
       </c>
       <c r="B113" s="8">
-        <v>46112.51356582176</v>
+        <v>46112.68023248843</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46181.56636228009</v>
+        <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>248</v>
@@ -8534,11 +8534,11 @@
         <v>364</v>
       </c>
       <c r="B114" s="5">
-        <v>46112.52445456019</v>
+        <v>46112.69112122685</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46118.374930000005</v>
+        <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>251</v>
@@ -8587,11 +8587,11 @@
         <v>366</v>
       </c>
       <c r="B115" s="8">
-        <v>46112.51357737269</v>
+        <v>46112.68024403935</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46118.37509318287</v>
+        <v>46118.54175984954</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>367</v>
@@ -8650,11 +8650,11 @@
         <v>368</v>
       </c>
       <c r="B116" s="5">
-        <v>46112.51358561343</v>
+        <v>46112.68025228009</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46181.56635783565</v>
+        <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>213</v>
@@ -8703,11 +8703,11 @@
         <v>371</v>
       </c>
       <c r="B117" s="8">
-        <v>46112.51359768519</v>
+        <v>46112.68026435185</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46181.56636282407</v>
+        <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>248</v>
@@ -8756,11 +8756,11 @@
         <v>374</v>
       </c>
       <c r="B118" s="5">
-        <v>46112.52614829861</v>
+        <v>46112.69281496528</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46118.37508619213</v>
+        <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>252</v>
@@ -8809,11 +8809,11 @@
         <v>376</v>
       </c>
       <c r="B119" s="8">
-        <v>46112.51364833333</v>
+        <v>46112.680315000005</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46118.375211990744</v>
+        <v>46118.54187865741</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>377</v>
@@ -8872,11 +8872,11 @@
         <v>378</v>
       </c>
       <c r="B120" s="5">
-        <v>46112.51365986111</v>
+        <v>46112.68032652778</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46118.375212743056</v>
+        <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>213</v>
@@ -8923,11 +8923,11 @@
         <v>380</v>
       </c>
       <c r="B121" s="8">
-        <v>46112.513669409724</v>
+        <v>46112.68033607639</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46118.375213611114</v>
+        <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>248</v>
@@ -8974,11 +8974,11 @@
         <v>382</v>
       </c>
       <c r="B122" s="5">
-        <v>46112.5270869213</v>
+        <v>46112.69375358796</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46118.37521438657</v>
+        <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>252</v>
@@ -9025,11 +9025,11 @@
         <v>384</v>
       </c>
       <c r="B123" s="8">
-        <v>46112.51367827546</v>
+        <v>46112.68034494213</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46118.375342060186</v>
+        <v>46118.54200872685</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>385</v>
@@ -9086,11 +9086,11 @@
         <v>386</v>
       </c>
       <c r="B124" s="5">
-        <v>46112.51368667824</v>
+        <v>46112.680353344906</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46118.38119788194</v>
+        <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>213</v>
@@ -9137,11 +9137,11 @@
         <v>388</v>
       </c>
       <c r="B125" s="8">
-        <v>46112.513694803245</v>
+        <v>46112.6803614699</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46118.381196145834</v>
+        <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>248</v>
@@ -9188,11 +9188,11 @@
         <v>390</v>
       </c>
       <c r="B126" s="5">
-        <v>46112.528263541666</v>
+        <v>46112.69493020834</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46118.38119685186</v>
+        <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>252</v>
@@ -9239,11 +9239,11 @@
         <v>392</v>
       </c>
       <c r="B127" s="8">
-        <v>46112.51370282407</v>
+        <v>46112.68036949074</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46118.37611902777</v>
+        <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>393</v>
@@ -9286,11 +9286,11 @@
         <v>395</v>
       </c>
       <c r="B128" s="5">
-        <v>46112.51370762731</v>
+        <v>46112.68037429398</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46118.375693090275</v>
+        <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>396</v>
@@ -9349,11 +9349,11 @@
         <v>400</v>
       </c>
       <c r="B129" s="8">
-        <v>46112.51371667824</v>
+        <v>46112.68038334491</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46118.375693738424</v>
+        <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>213</v>
@@ -9400,11 +9400,11 @@
         <v>402</v>
       </c>
       <c r="B130" s="5">
-        <v>46112.51372454861</v>
+        <v>46112.68039121528</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46118.37569451389</v>
+        <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>248</v>
@@ -9451,11 +9451,11 @@
         <v>404</v>
       </c>
       <c r="B131" s="8">
-        <v>46112.53120728009</v>
+        <v>46112.69787394676</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46118.37569533565</v>
+        <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>251</v>
@@ -9502,11 +9502,11 @@
         <v>406</v>
       </c>
       <c r="B132" s="5">
-        <v>46112.51373324074</v>
+        <v>46112.6803999074</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46118.37569619213</v>
+        <v>46118.542362858796</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>56</v>
@@ -9553,11 +9553,11 @@
         <v>408</v>
       </c>
       <c r="B133" s="8">
-        <v>46112.51374471065</v>
+        <v>46112.68041137731</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46118.37569696759</v>
+        <v>46118.54236363426</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>60</v>
@@ -9604,11 +9604,11 @@
         <v>410</v>
       </c>
       <c r="B134" s="5">
-        <v>46112.51375236111</v>
+        <v>46112.680419027776</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46118.37569774306</v>
+        <v>46118.54236440972</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>63</v>
@@ -9655,11 +9655,11 @@
         <v>412</v>
       </c>
       <c r="B135" s="8">
-        <v>46112.51376033565</v>
+        <v>46112.68042700231</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46118.37569853009</v>
+        <v>46118.54236519676</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>66</v>
@@ -9706,11 +9706,11 @@
         <v>414</v>
       </c>
       <c r="B136" s="5">
-        <v>46112.51376799769</v>
+        <v>46112.68043466435</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46118.37569929398</v>
+        <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>322</v>
@@ -9757,11 +9757,11 @@
         <v>416</v>
       </c>
       <c r="B137" s="8">
-        <v>46112.51377549769</v>
+        <v>46112.68044216435</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46118.376586956016</v>
+        <v>46118.54325362269</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>417</v>
@@ -9820,11 +9820,11 @@
         <v>420</v>
       </c>
       <c r="B138" s="5">
-        <v>46112.51378354167</v>
+        <v>46112.68045020833</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46118.376425891205</v>
+        <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>213</v>
@@ -9873,11 +9873,11 @@
         <v>422</v>
       </c>
       <c r="B139" s="8">
-        <v>46112.51379094907</v>
+        <v>46112.680457615745</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46118.37642664352</v>
+        <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>248</v>
@@ -9926,11 +9926,11 @@
         <v>424</v>
       </c>
       <c r="B140" s="5">
-        <v>46112.5326671875</v>
+        <v>46112.699333854165</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46118.376474247685</v>
+        <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>252</v>
@@ -9979,11 +9979,11 @@
         <v>426</v>
       </c>
       <c r="B141" s="8">
-        <v>46112.51379863426</v>
+        <v>46112.68046530093</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46118.376428240736</v>
+        <v>46118.54309490741</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>56</v>
@@ -10032,11 +10032,11 @@
         <v>428</v>
       </c>
       <c r="B142" s="5">
-        <v>46112.51380609954</v>
+        <v>46112.6804727662</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46118.37642912037</v>
+        <v>46118.54309578704</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>60</v>
@@ -10085,11 +10085,11 @@
         <v>430</v>
       </c>
       <c r="B143" s="8">
-        <v>46112.51385761574</v>
+        <v>46112.680524282405</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46118.3764299537</v>
+        <v>46118.54309662037</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>63</v>
@@ -10138,11 +10138,11 @@
         <v>432</v>
       </c>
       <c r="B144" s="5">
-        <v>46112.51386880787</v>
+        <v>46112.68053547454</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46118.37643081018</v>
+        <v>46118.54309747685</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10191,11 +10191,11 @@
         <v>434</v>
       </c>
       <c r="B145" s="8">
-        <v>46112.51387761574</v>
+        <v>46112.68054428241</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46118.37643179398</v>
+        <v>46118.54309846065</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>435</v>
@@ -10244,11 +10244,11 @@
         <v>437</v>
       </c>
       <c r="B146" s="5">
-        <v>46112.51388608797</v>
+        <v>46112.68055275463</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46118.37690659722</v>
+        <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>438</v>
@@ -10305,11 +10305,11 @@
         <v>440</v>
       </c>
       <c r="B147" s="8">
-        <v>46112.513897199075</v>
+        <v>46112.68056386574</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46118.37690609954</v>
+        <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>213</v>
@@ -10358,11 +10358,11 @@
         <v>442</v>
       </c>
       <c r="B148" s="5">
-        <v>46112.513905011576</v>
+        <v>46112.68057167824</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46118.37690674768</v>
+        <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>248</v>
@@ -10411,11 +10411,11 @@
         <v>444</v>
       </c>
       <c r="B149" s="8">
-        <v>46112.53368842593</v>
+        <v>46112.70035509259</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46118.43840368056</v>
+        <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>252</v>
@@ -10464,11 +10464,11 @@
         <v>445</v>
       </c>
       <c r="B150" s="5">
-        <v>46112.5139128125</v>
+        <v>46112.680579479165</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46118.37690806713</v>
+        <v>46118.5435747338</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>56</v>
@@ -10517,11 +10517,11 @@
         <v>447</v>
       </c>
       <c r="B151" s="8">
-        <v>46112.51392055556</v>
+        <v>46112.68058722222</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46118.37690870371</v>
+        <v>46118.54357537037</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10570,11 +10570,11 @@
         <v>449</v>
       </c>
       <c r="B152" s="5">
-        <v>46112.51392856482</v>
+        <v>46112.68059523148</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46118.376909328705</v>
+        <v>46118.54357599537</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10623,11 +10623,11 @@
         <v>451</v>
       </c>
       <c r="B153" s="8">
-        <v>46112.51393680555</v>
+        <v>46112.680603472225</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46118.37690994213</v>
+        <v>46118.5435766088</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10676,11 +10676,11 @@
         <v>453</v>
       </c>
       <c r="B154" s="5">
-        <v>46112.51394438658</v>
+        <v>46112.68061105324</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46118.37691060185</v>
+        <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>454</v>
@@ -10729,11 +10729,11 @@
         <v>456</v>
       </c>
       <c r="B155" s="8">
-        <v>46112.51395211805</v>
+        <v>46112.680618784725</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46118.377256736116</v>
+        <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>457</v>
@@ -10792,11 +10792,11 @@
         <v>460</v>
       </c>
       <c r="B156" s="5">
-        <v>46112.513966886574</v>
+        <v>46112.680633553246</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46118.37717853009</v>
+        <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>213</v>
@@ -10845,11 +10845,11 @@
         <v>462</v>
       </c>
       <c r="B157" s="8">
-        <v>46112.51397584491</v>
+        <v>46112.68064251158</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46118.37717936342</v>
+        <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>248</v>
@@ -10898,11 +10898,11 @@
         <v>463</v>
       </c>
       <c r="B158" s="5">
-        <v>46112.514049143516</v>
+        <v>46112.68071581019</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46118.37718408565</v>
+        <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>435</v>
@@ -10951,11 +10951,11 @@
         <v>464</v>
       </c>
       <c r="B159" s="8">
-        <v>46112.572476319445</v>
+        <v>46112.739142986116</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46118.377185335645</v>
+        <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>252</v>
@@ -11004,11 +11004,11 @@
         <v>465</v>
       </c>
       <c r="B160" s="5">
-        <v>46112.51398341435</v>
+        <v>46112.68065008102</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46118.37718614584</v>
+        <v>46118.5438528125</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>56</v>
@@ -11057,11 +11057,11 @@
         <v>466</v>
       </c>
       <c r="B161" s="8">
-        <v>46112.513990810185</v>
+        <v>46112.680657476856</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46118.377186956015</v>
+        <v>46118.54385362269</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>60</v>
@@ -11110,11 +11110,11 @@
         <v>467</v>
       </c>
       <c r="B162" s="5">
-        <v>46112.514031377315</v>
+        <v>46112.68069804399</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46118.3771878125</v>
+        <v>46118.54385447917</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>66</v>
@@ -11163,11 +11163,11 @@
         <v>468</v>
       </c>
       <c r="B163" s="8">
-        <v>46112.514040821756</v>
+        <v>46112.68070748843</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46118.37718862269</v>
+        <v>46118.54385528935</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>63</v>
@@ -11216,11 +11216,11 @@
         <v>469</v>
       </c>
       <c r="B164" s="5">
-        <v>46112.514057106484</v>
+        <v>46112.68072377315</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46118.37611855324</v>
+        <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>470</v>
@@ -11263,11 +11263,11 @@
         <v>472</v>
       </c>
       <c r="B165" s="8">
-        <v>46112.51406148148</v>
+        <v>46112.680728148145</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46118.37735388889</v>
+        <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>473</v>
@@ -11326,11 +11326,11 @@
         <v>476</v>
       </c>
       <c r="B166" s="5">
-        <v>46112.51407065972</v>
+        <v>46112.68073732639</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46118.37743908565</v>
+        <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>477</v>
@@ -11389,11 +11389,11 @@
         <v>479</v>
       </c>
       <c r="B167" s="8">
-        <v>46112.51408033565</v>
+        <v>46112.68074700232</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46118.37611855324</v>
+        <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>480</v>
@@ -11438,11 +11438,11 @@
         <v>482</v>
       </c>
       <c r="B168" s="5">
-        <v>46112.5140847338</v>
+        <v>46112.68075140046</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46118.377544710645</v>
+        <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>483</v>
@@ -11501,11 +11501,11 @@
         <v>485</v>
       </c>
       <c r="B169" s="8">
-        <v>46112.51409322917</v>
+        <v>46112.68075989583</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46118.3776578588</v>
+        <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>486</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -5661,7 +5661,7 @@
         <v>46162.64349465277</v>
       </c>
       <c r="D63" s="8">
-        <v>46182.20116643519</v>
+        <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5708,8 +5708,8 @@
       <c r="S63" s="9">
         <v>1</v>
       </c>
-      <c r="T63" s="12" t="s">
-        <v>110</v>
+      <c r="T63" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>32</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -5891,7 +5891,7 @@
         <v>46181.73301096065</v>
       </c>
       <c r="D67" s="8">
-        <v>46183.204529525465</v>
+        <v>46191.201163958336</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>108</v>
@@ -5938,8 +5938,8 @@
       <c r="S67" s="9">
         <v>1</v>
       </c>
-      <c r="T67" s="12" t="s">
-        <v>110</v>
+      <c r="T67" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>32</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46185.20358450232</v>
+        <v>46192.176068368055</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46185.20358449074</v>
+        <v>46192.17606454861</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46154.86774436342</v>
+        <v>46191.89614340277</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3839,9 +3839,11 @@
       <c r="B33" s="8">
         <v>46112.679506099536</v>
       </c>
-      <c r="C33" s="9"/>
+      <c r="C33" s="8">
+        <v>46191.89613496528</v>
+      </c>
       <c r="D33" s="8">
-        <v>46182.67848488426</v>
+        <v>46191.8961546875</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3886,13 +3888,13 @@
         <v>46245</v>
       </c>
       <c r="S33" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="U33" s="10" t="s">
-        <v>54</v>
+      <c r="U33" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3967,9 +3969,11 @@
       <c r="B35" s="8">
         <v>46112.67952521991</v>
       </c>
-      <c r="C35" s="9"/>
+      <c r="C35" s="8">
+        <v>46191.89611988426</v>
+      </c>
       <c r="D35" s="8">
-        <v>46182.67848606482</v>
+        <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -4032,7 +4036,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.85764145834</v>
+        <v>46191.90378388889</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -4095,7 +4099,7 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46169.85772241898</v>
+        <v>46191.89674231481</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -4158,7 +4162,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.85775858797</v>
+        <v>46191.89674752315</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -7343,7 +7347,7 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46112.6802097801</v>
+        <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>309</v>
@@ -7393,8 +7397,8 @@
       <c r="T93" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="U93" s="10" t="s">
-        <v>54</v>
+      <c r="U93" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -4036,7 +4036,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46191.90378388889</v>
+        <v>46192.90906696759</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="486">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -341,9 +341,6 @@
   </si>
   <si>
     <t>Generación OC materiales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213886181474378</t>
@@ -3538,7 +3535,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46192.176068368055</v>
+        <v>46193.20103372685</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3585,8 +3582,8 @@
       <c r="S28" s="6">
         <v>0</v>
       </c>
-      <c r="T28" s="12" t="s">
-        <v>110</v>
+      <c r="T28" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U28" s="12" t="s">
         <v>90</v>
@@ -3594,7 +3591,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46112.679478136575</v>
@@ -3606,7 +3603,7 @@
         <v>46123.186628958334</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3639,7 +3636,7 @@
         <v>78</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3659,17 +3656,17 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5">
         <v>46112.67948803241</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46192.17606454861</v>
+        <v>46193.20103049769</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3699,10 +3696,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P30" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3713,8 +3710,8 @@
       <c r="S30" s="6">
         <v>0</v>
       </c>
-      <c r="T30" s="12" t="s">
-        <v>110</v>
+      <c r="T30" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U30" s="12" t="s">
         <v>90</v>
@@ -3722,7 +3719,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46112.67949700232</v>
@@ -3767,7 +3764,7 @@
         <v>85</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3787,7 +3784,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B32" s="5">
         <v>46112.67913506944</v>
@@ -3797,7 +3794,7 @@
         <v>46191.89614340277</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3821,7 +3818,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3834,7 +3831,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B33" s="8">
         <v>46112.679506099536</v>
@@ -3846,16 +3843,16 @@
         <v>46191.8961546875</v>
       </c>
       <c r="E33" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3873,13 +3870,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3899,7 +3896,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46112.6795156713</v>
@@ -3911,16 +3908,16 @@
         <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3938,13 +3935,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3964,7 +3961,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46112.67952521991</v>
@@ -3976,16 +3973,16 @@
         <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -4003,13 +4000,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -4029,7 +4026,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46112.67953447917</v>
@@ -4039,16 +4036,16 @@
         <v>46192.90906696759</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -4066,13 +4063,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -4092,7 +4089,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46112.679543101855</v>
@@ -4102,16 +4099,16 @@
         <v>46191.89674231481</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -4129,13 +4126,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>102</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4155,7 +4152,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46112.67955209491</v>
@@ -4165,16 +4162,16 @@
         <v>46191.89674752315</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4192,13 +4189,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4216,7 +4213,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46112.67960491898</v>
@@ -4226,16 +4223,16 @@
         <v>46183.18919871528</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4253,13 +4250,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4279,7 +4276,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46112.679614513894</v>
@@ -4291,16 +4288,16 @@
         <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4318,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4344,7 +4341,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46112.67962357639</v>
@@ -4354,16 +4351,16 @@
         <v>46182.678233125</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4381,13 +4378,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4407,7 +4404,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46112.679632581014</v>
@@ -4417,16 +4414,16 @@
         <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4444,13 +4441,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4470,7 +4467,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="8">
         <v>46112.67964135417</v>
@@ -4482,16 +4479,16 @@
         <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4509,13 +4506,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>92</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4535,7 +4532,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46112.67965385417</v>
@@ -4545,16 +4542,16 @@
         <v>46182.67812324074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4572,13 +4569,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4598,7 +4595,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B45" s="8">
         <v>46112.679662372684</v>
@@ -4610,16 +4607,16 @@
         <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4637,13 +4634,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4663,7 +4660,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46112.67967090278</v>
@@ -4673,16 +4670,16 @@
         <v>46169.85692615741</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4700,13 +4697,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4726,7 +4723,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4742,10 +4739,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4763,13 +4760,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4789,7 +4786,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4799,16 +4796,16 @@
         <v>46169.85689956018</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4826,13 +4823,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4852,7 +4849,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4864,16 +4861,16 @@
         <v>46154.86774770833</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4891,13 +4888,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4917,7 +4914,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4929,16 +4926,16 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4956,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4972,7 +4969,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4984,16 +4981,16 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -5011,13 +5008,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5027,7 +5024,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5037,16 +5034,16 @@
         <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5064,13 +5061,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -5090,7 +5087,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5100,16 +5097,16 @@
         <v>46169.85708912037</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5127,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5149,7 +5146,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5159,16 +5156,16 @@
         <v>46181.733022569446</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5186,13 +5183,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5202,7 +5199,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5214,16 +5211,16 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5241,10 +5238,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5267,7 +5264,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5279,16 +5276,16 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5306,13 +5303,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5322,7 +5319,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5334,16 +5331,16 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5361,13 +5358,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5377,7 +5374,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5387,7 +5384,7 @@
         <v>46162.64351380787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5411,7 +5408,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5426,7 +5423,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5438,16 +5435,16 @@
         <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5465,13 +5462,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5491,7 +5488,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5503,16 +5500,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5530,13 +5527,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5546,7 +5543,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5558,16 +5555,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5585,13 +5582,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5601,7 +5598,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5613,16 +5610,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5640,13 +5637,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5656,7 +5653,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5668,16 +5665,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5695,13 +5692,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5721,7 +5718,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5733,16 +5730,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5760,13 +5757,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5776,7 +5773,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5788,16 +5785,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5815,13 +5812,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5831,7 +5828,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5843,16 +5840,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5870,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5886,7 +5883,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5904,10 +5901,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5925,13 +5922,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5951,7 +5948,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5963,16 +5960,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5991,7 +5988,7 @@
         <v>108</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>108</v>
@@ -6004,7 +6001,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6016,16 +6013,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6044,7 +6041,7 @@
         <v>108</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>108</v>
@@ -6057,7 +6054,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6069,16 +6066,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6097,7 +6094,7 @@
         <v>108</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>108</v>
@@ -6110,7 +6107,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6120,16 +6117,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6147,10 +6144,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6173,7 +6170,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6183,16 +6180,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>243</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6210,13 +6207,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6226,7 +6223,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6236,16 +6233,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6263,13 +6260,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6279,7 +6276,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6289,16 +6286,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>243</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6316,13 +6313,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6332,7 +6329,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6342,7 +6339,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6366,7 +6363,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6379,7 +6376,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6389,16 +6386,16 @@
         <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6414,13 +6411,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6440,7 +6437,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6450,7 +6447,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6474,7 +6471,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6487,7 +6484,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6497,16 +6494,16 @@
         <v>46177.208199479166</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6524,13 +6521,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6550,7 +6547,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6560,16 +6557,16 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>259</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6587,13 +6584,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6613,7 +6610,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6623,7 +6620,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6647,7 +6644,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6660,7 +6657,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6670,16 +6667,16 @@
         <v>46118.536602175926</v>
       </c>
       <c r="E81" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6697,13 +6694,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6723,7 +6720,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6733,16 +6730,16 @@
         <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6760,13 +6757,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6786,7 +6783,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6796,16 +6793,16 @@
         <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6823,13 +6820,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6839,7 +6836,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6849,16 +6846,16 @@
         <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6876,13 +6873,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6892,7 +6889,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6902,16 +6899,16 @@
         <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6929,13 +6926,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6945,7 +6942,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6955,16 +6952,16 @@
         <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -6982,13 +6979,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7008,7 +7005,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7018,16 +7015,16 @@
         <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>259</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7045,13 +7042,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O87" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="P87" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>294</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7061,7 +7058,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7071,16 +7068,16 @@
         <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7098,13 +7095,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>296</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>297</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7114,7 +7111,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7124,16 +7121,16 @@
         <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>259</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7151,13 +7148,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7167,7 +7164,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7177,7 +7174,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7201,7 +7198,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7214,7 +7211,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7224,16 +7221,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7251,13 +7248,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7277,7 +7274,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7293,10 +7290,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7314,13 +7311,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7340,7 +7337,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7350,16 +7347,16 @@
         <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7377,13 +7374,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7403,7 +7400,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7413,16 +7410,16 @@
         <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7440,13 +7437,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7466,7 +7463,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
@@ -7476,16 +7473,16 @@
         <v>46154.867740671296</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7503,13 +7500,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7529,7 +7526,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7539,16 +7536,16 @@
         <v>46118.55096623843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7564,13 +7561,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7590,7 +7587,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7600,16 +7597,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7627,13 +7624,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7653,7 +7650,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7663,7 +7660,7 @@
         <v>46118.540081238425</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7687,7 +7684,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7700,7 +7697,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
@@ -7710,7 +7707,7 @@
         <v>46118.540939687504</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7737,13 +7734,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7763,7 +7760,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
@@ -7773,7 +7770,7 @@
         <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7800,13 +7797,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>331</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7816,7 +7813,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
@@ -7826,7 +7823,7 @@
         <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7853,13 +7850,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>334</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7869,7 +7866,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
@@ -7879,7 +7876,7 @@
         <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7906,13 +7903,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7922,7 +7919,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
@@ -7932,7 +7929,7 @@
         <v>46118.54127469908</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7959,13 +7956,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -7985,7 +7982,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
@@ -7995,7 +7992,7 @@
         <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8022,13 +8019,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>341</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>342</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8038,7 +8035,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
@@ -8048,7 +8045,7 @@
         <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8075,13 +8072,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O105" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="P105" s="9" t="s">
         <v>344</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>345</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8091,7 +8088,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
@@ -8101,7 +8098,7 @@
         <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8128,13 +8125,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8144,7 +8141,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
@@ -8154,7 +8151,7 @@
         <v>46118.54145512731</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8181,13 +8178,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8207,7 +8204,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
@@ -8217,7 +8214,7 @@
         <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8244,13 +8241,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O108" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8260,7 +8257,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
@@ -8270,7 +8267,7 @@
         <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8297,13 +8294,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O109" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="P109" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="P109" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8313,7 +8310,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
@@ -8323,7 +8320,7 @@
         <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8350,13 +8347,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8366,7 +8363,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
@@ -8376,7 +8373,7 @@
         <v>46118.54159421296</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8403,13 +8400,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8429,7 +8426,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
@@ -8439,7 +8436,7 @@
         <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8466,13 +8463,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8482,7 +8479,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
@@ -8492,7 +8489,7 @@
         <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8519,13 +8516,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8535,7 +8532,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
@@ -8545,7 +8542,7 @@
         <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8572,13 +8569,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8588,7 +8585,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
@@ -8598,7 +8595,7 @@
         <v>46118.54175984954</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8625,13 +8622,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8651,7 +8648,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
@@ -8661,7 +8658,7 @@
         <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8688,13 +8685,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O116" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="P116" s="6" t="s">
         <v>369</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>370</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8704,7 +8701,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
@@ -8714,7 +8711,7 @@
         <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8741,13 +8738,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O117" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="P117" s="9" t="s">
         <v>372</v>
-      </c>
-      <c r="P117" s="9" t="s">
-        <v>373</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8757,7 +8754,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
@@ -8767,7 +8764,7 @@
         <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8794,13 +8791,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8810,7 +8807,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
@@ -8820,7 +8817,7 @@
         <v>46118.54187865741</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8847,13 +8844,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8873,7 +8870,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
@@ -8883,7 +8880,7 @@
         <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8908,13 +8905,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8924,7 +8921,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
@@ -8934,7 +8931,7 @@
         <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8959,13 +8956,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8975,7 +8972,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
@@ -8985,7 +8982,7 @@
         <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9010,13 +9007,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9026,7 +9023,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
@@ -9036,7 +9033,7 @@
         <v>46118.54200872685</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9061,13 +9058,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9087,7 +9084,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B124" s="5">
         <v>46112.680353344906</v>
@@ -9097,7 +9094,7 @@
         <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9122,13 +9119,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9138,7 +9135,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B125" s="8">
         <v>46112.6803614699</v>
@@ -9148,7 +9145,7 @@
         <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9173,13 +9170,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9189,7 +9186,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B126" s="5">
         <v>46112.69493020834</v>
@@ -9199,7 +9196,7 @@
         <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9224,13 +9221,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9240,7 +9237,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B127" s="8">
         <v>46112.68036949074</v>
@@ -9250,7 +9247,7 @@
         <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9274,7 +9271,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9287,7 +9284,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B128" s="5">
         <v>46112.68037429398</v>
@@ -9297,16 +9294,16 @@
         <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G128" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="F128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G128" s="6" t="s">
+      <c r="H128" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I128" s="5">
         <v>46287</v>
@@ -9324,13 +9321,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q128" s="5">
         <v>46287</v>
@@ -9350,7 +9347,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B129" s="8">
         <v>46112.68038334491</v>
@@ -9360,16 +9357,16 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H129" s="9" t="s">
         <v>397</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>398</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9385,13 +9382,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9401,7 +9398,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B130" s="5">
         <v>46112.68039121528</v>
@@ -9411,16 +9408,16 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9436,13 +9433,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9452,7 +9449,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B131" s="8">
         <v>46112.69787394676</v>
@@ -9462,16 +9459,16 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>397</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>398</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9487,13 +9484,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9503,7 +9500,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B132" s="5">
         <v>46112.6803999074</v>
@@ -9519,10 +9516,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9538,13 +9535,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9554,7 +9551,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B133" s="8">
         <v>46112.68041137731</v>
@@ -9570,10 +9567,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>397</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>398</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9589,13 +9586,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9605,7 +9602,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B134" s="5">
         <v>46112.680419027776</v>
@@ -9621,10 +9618,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9640,13 +9637,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9656,7 +9653,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B135" s="8">
         <v>46112.68042700231</v>
@@ -9672,10 +9669,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>397</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>398</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9691,13 +9688,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9707,7 +9704,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B136" s="5">
         <v>46112.68043466435</v>
@@ -9717,16 +9714,16 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9742,13 +9739,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9758,7 +9755,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B137" s="8">
         <v>46112.68044216435</v>
@@ -9768,7 +9765,7 @@
         <v>46118.54325362269</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9795,13 +9792,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O137" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="P137" s="9" t="s">
         <v>418</v>
-      </c>
-      <c r="P137" s="9" t="s">
-        <v>419</v>
       </c>
       <c r="Q137" s="8">
         <v>46288</v>
@@ -9821,7 +9818,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B138" s="5">
         <v>46112.68045020833</v>
@@ -9831,7 +9828,7 @@
         <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9858,13 +9855,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9874,7 +9871,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B139" s="8">
         <v>46112.680457615745</v>
@@ -9884,7 +9881,7 @@
         <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9911,13 +9908,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9927,7 +9924,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B140" s="5">
         <v>46112.699333854165</v>
@@ -9937,7 +9934,7 @@
         <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9964,13 +9961,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9980,7 +9977,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B141" s="8">
         <v>46112.68046530093</v>
@@ -10017,13 +10014,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>56</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10033,7 +10030,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B142" s="5">
         <v>46112.6804727662</v>
@@ -10070,13 +10067,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10086,7 +10083,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B143" s="8">
         <v>46112.680524282405</v>
@@ -10123,13 +10120,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10139,7 +10136,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B144" s="5">
         <v>46112.68053547454</v>
@@ -10176,13 +10173,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10192,7 +10189,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B145" s="8">
         <v>46112.68054428241</v>
@@ -10202,7 +10199,7 @@
         <v>46118.54309846065</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10229,13 +10226,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10245,7 +10242,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B146" s="5">
         <v>46112.68055275463</v>
@@ -10255,16 +10252,16 @@
         <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10280,13 +10277,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q146" s="5">
         <v>46293</v>
@@ -10306,7 +10303,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B147" s="8">
         <v>46112.68056386574</v>
@@ -10316,16 +10313,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10343,13 +10340,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10359,7 +10356,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B148" s="5">
         <v>46112.68057167824</v>
@@ -10369,16 +10366,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10396,13 +10393,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10412,7 +10409,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B149" s="8">
         <v>46112.70035509259</v>
@@ -10422,16 +10419,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10449,13 +10446,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10465,7 +10462,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B150" s="5">
         <v>46112.680579479165</v>
@@ -10481,10 +10478,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10502,13 +10499,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10518,7 +10515,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B151" s="8">
         <v>46112.68058722222</v>
@@ -10534,10 +10531,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10555,13 +10552,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10571,7 +10568,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B152" s="5">
         <v>46112.68059523148</v>
@@ -10587,10 +10584,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10608,13 +10605,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10624,7 +10621,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B153" s="8">
         <v>46112.680603472225</v>
@@ -10640,10 +10637,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10661,13 +10658,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10677,7 +10674,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B154" s="5">
         <v>46112.68061105324</v>
@@ -10687,16 +10684,16 @@
         <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10714,13 +10711,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10730,7 +10727,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B155" s="8">
         <v>46112.680618784725</v>
@@ -10740,16 +10737,16 @@
         <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10767,13 +10764,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O155" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="P155" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="P155" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="Q155" s="8">
         <v>46294</v>
@@ -10793,7 +10790,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B156" s="5">
         <v>46112.680633553246</v>
@@ -10803,16 +10800,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10830,13 +10827,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10846,7 +10843,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B157" s="8">
         <v>46112.68064251158</v>
@@ -10856,16 +10853,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10883,13 +10880,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10899,7 +10896,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B158" s="5">
         <v>46112.68071581019</v>
@@ -10909,16 +10906,16 @@
         <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10936,13 +10933,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10952,7 +10949,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B159" s="8">
         <v>46112.739142986116</v>
@@ -10962,16 +10959,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H159" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -10989,10 +10986,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11005,7 +11002,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B160" s="5">
         <v>46112.68065008102</v>
@@ -11021,10 +11018,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11042,13 +11039,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11058,7 +11055,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B161" s="8">
         <v>46112.680657476856</v>
@@ -11074,10 +11071,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H161" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11095,13 +11092,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11111,7 +11108,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B162" s="5">
         <v>46112.68069804399</v>
@@ -11127,10 +11124,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11148,13 +11145,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11164,7 +11161,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B163" s="8">
         <v>46112.68070748843</v>
@@ -11180,10 +11177,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H163" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>
@@ -11201,13 +11198,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11217,7 +11214,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B164" s="5">
         <v>46112.68072377315</v>
@@ -11227,7 +11224,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>25</v>
@@ -11251,7 +11248,7 @@
         <v>26</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>26</v>
@@ -11264,7 +11261,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B165" s="8">
         <v>46112.680728148145</v>
@@ -11274,16 +11271,16 @@
         <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="F165" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G165" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="F165" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G165" s="9" t="s">
+      <c r="H165" s="9" t="s">
         <v>474</v>
-      </c>
-      <c r="H165" s="9" t="s">
-        <v>475</v>
       </c>
       <c r="I165" s="8">
         <v>46295</v>
@@ -11301,13 +11298,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Q165" s="8">
         <v>46295</v>
@@ -11327,7 +11324,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B166" s="5">
         <v>46112.68073732639</v>
@@ -11337,16 +11334,16 @@
         <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="H166" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="H166" s="6" t="s">
-        <v>475</v>
       </c>
       <c r="I166" s="5">
         <v>46295</v>
@@ -11364,13 +11361,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Q166" s="5">
         <v>46295</v>
@@ -11390,7 +11387,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B167" s="8">
         <v>46112.68074700232</v>
@@ -11400,7 +11397,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>25</v>
@@ -11424,7 +11421,7 @@
         <v>26</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>26</v>
@@ -11439,7 +11436,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B168" s="5">
         <v>46112.68075140046</v>
@@ -11449,16 +11446,16 @@
         <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="H168" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>475</v>
       </c>
       <c r="I168" s="5">
         <v>46295</v>
@@ -11476,13 +11473,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Q168" s="5">
         <v>46295</v>
@@ -11502,7 +11499,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B169" s="8">
         <v>46112.68075989583</v>
@@ -11512,16 +11509,16 @@
         <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="H169" s="9" t="s">
         <v>474</v>
-      </c>
-      <c r="H169" s="9" t="s">
-        <v>475</v>
       </c>
       <c r="I169" s="8">
         <v>46304</v>
@@ -11539,13 +11536,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q169" s="8">
         <v>46304</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46192.90906696759</v>
+        <v>46195.714815196756</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4094,9 +4094,11 @@
       <c r="B37" s="8">
         <v>46112.679543101855</v>
       </c>
-      <c r="C37" s="9"/>
+      <c r="C37" s="8">
+        <v>46195.68274940972</v>
+      </c>
       <c r="D37" s="8">
-        <v>46191.89674231481</v>
+        <v>46195.682751747685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -4159,7 +4161,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46191.89674752315</v>
+        <v>46195.7109980324</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -4220,7 +4222,7 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46183.18919871528</v>
+        <v>46195.71583903935</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4539,7 +4541,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.67812324074</v>
+        <v>46195.68193791667</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46182.678233125</v>
+        <v>46195.71615581018</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.68193791667</v>
+        <v>46195.71674362269</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46193.20103372685</v>
+        <v>46196.65421123843</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3580,13 +3580,13 @@
         <v>46192</v>
       </c>
       <c r="S28" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>90</v>
+      <c r="U28" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46195.714815196756</v>
+        <v>46196.634982337964</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.856877048616</v>
+        <v>46196.654216180556</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -4541,7 +4541,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46195.71674362269</v>
+        <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -2095,13 +2095,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46112.679109861114</v>
+        <v>46112.51244319444</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.67910981481</v>
+        <v>46112.51244314815</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.684899224536</v>
+        <v>46112.51823255787</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2144,13 +2144,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46112.679243356484</v>
+        <v>46112.51257668981</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.67924331018</v>
+        <v>46112.51257664352</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.67937947917</v>
+        <v>46112.5127128125</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2207,13 +2207,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46112.67925122685</v>
+        <v>46112.51258456019</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.67925120371</v>
+        <v>46112.512584537035</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.67938056713</v>
+        <v>46112.51271390046</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2270,13 +2270,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46112.67925739584</v>
+        <v>46112.512590729166</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.679257372685</v>
+        <v>46112.512590706014</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.67938130787</v>
+        <v>46112.512714641205</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2333,13 +2333,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46112.67926344907</v>
+        <v>46112.512596782406</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.6792634375</v>
+        <v>46112.51259677083</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.67938207176</v>
+        <v>46112.51271540509</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2396,13 +2396,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46112.679272511574</v>
+        <v>46112.51260584491</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.67927248843</v>
+        <v>46112.51260582176</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.679383483795</v>
+        <v>46112.51271681713</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2459,11 +2459,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46112.67911597222</v>
+        <v>46112.512449305555</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.894571122684</v>
+        <v>46134.72790445602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2506,13 +2506,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46112.679284375</v>
+        <v>46112.51261770833</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.89456173611</v>
+        <v>46134.727895069445</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.894579768516</v>
+        <v>46134.72791310185</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2571,11 +2571,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46112.67929341435</v>
+        <v>46112.51262674769</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46112.679385428244</v>
+        <v>46112.51271876157</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2634,11 +2634,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46112.67930209491</v>
+        <v>46112.51263542824</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46112.74287908565</v>
+        <v>46112.57621241898</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2687,11 +2687,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46112.67931020833</v>
+        <v>46112.51264354167</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46112.74360094908</v>
+        <v>46112.576934282406</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2740,11 +2740,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46112.67931734954</v>
+        <v>46112.51265068287</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46112.74398168981</v>
+        <v>46112.57731502315</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2793,11 +2793,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46112.67932484954</v>
+        <v>46112.512658182866</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46112.74391716435</v>
+        <v>46112.577250497685</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2846,13 +2846,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46112.679120995366</v>
+        <v>46112.5124543287</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.74351912037</v>
+        <v>46114.576852453705</v>
       </c>
       <c r="D17" s="8">
-        <v>46118.5488546875</v>
+        <v>46118.382188020834</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2897,13 +2897,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46112.6793327662</v>
+        <v>46112.51266609954</v>
       </c>
       <c r="C18" s="5">
-        <v>46113.80815696759</v>
+        <v>46113.64149030093</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.14643453703</v>
+        <v>46113.97976787037</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2962,13 +2962,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46112.67934158565</v>
+        <v>46112.51267491898</v>
       </c>
       <c r="C19" s="8">
-        <v>46113.80818864584</v>
+        <v>46113.64152197917</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.16860619213</v>
+        <v>46121.001939525464</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -3027,13 +3027,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46112.6793505324</v>
+        <v>46112.512683865745</v>
       </c>
       <c r="C20" s="5">
-        <v>46113.808248263886</v>
+        <v>46113.64158159722</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.16860605324</v>
+        <v>46121.00193938657</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -3092,13 +3092,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46112.67936041667</v>
+        <v>46112.51269375</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.74350197917</v>
+        <v>46114.5768353125</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.16860607639</v>
+        <v>46121.00193940972</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3157,13 +3157,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46112.679370729165</v>
+        <v>46112.5127040625</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.80828232639</v>
+        <v>46113.641615659726</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.16860606481</v>
+        <v>46121.00193939815</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3222,11 +3222,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46112.6791271875</v>
+        <v>46112.51246052083</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.54559271991</v>
+        <v>46135.378926053236</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3271,13 +3271,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46112.679417754625</v>
+        <v>46112.51275108797</v>
       </c>
       <c r="C24" s="5">
-        <v>46113.80834418982</v>
+        <v>46113.64167752315</v>
       </c>
       <c r="D24" s="5">
-        <v>46116.1399068287</v>
+        <v>46115.97324016204</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3336,13 +3336,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46112.67943010417</v>
+        <v>46112.512763437495</v>
       </c>
       <c r="C25" s="8">
-        <v>46113.80835792824</v>
+        <v>46113.641691261575</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.18662815972</v>
+        <v>46123.01996149306</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3401,13 +3401,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46112.67944046296</v>
+        <v>46112.5127737963</v>
       </c>
       <c r="C26" s="5">
-        <v>46113.808378125</v>
+        <v>46113.64171145833</v>
       </c>
       <c r="D26" s="5">
-        <v>46123.186628055555</v>
+        <v>46123.01996138888</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3466,13 +3466,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46112.679452349534</v>
+        <v>46112.51278568287</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.545574386575</v>
+        <v>46135.3789077199</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.54582827546</v>
+        <v>46135.3791616088</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3531,11 +3531,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46112.67946289352</v>
+        <v>46112.51279622685</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46196.65421123843</v>
+        <v>46196.48754457176</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3594,13 +3594,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46112.679478136575</v>
+        <v>46112.512811469904</v>
       </c>
       <c r="C29" s="8">
-        <v>46113.808413645835</v>
+        <v>46113.64174697916</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.186628958334</v>
+        <v>46123.01996229167</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3659,11 +3659,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46112.67948803241</v>
+        <v>46112.512821365744</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.20103049769</v>
+        <v>46193.034363831015</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3722,13 +3722,13 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46112.67949700232</v>
+        <v>46112.51283033565</v>
       </c>
       <c r="C31" s="8">
-        <v>46113.808467152776</v>
+        <v>46113.64180048611</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.18662818287</v>
+        <v>46123.019961516206</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3787,11 +3787,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46112.67913506944</v>
+        <v>46112.512468402776</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46191.89614340277</v>
+        <v>46191.729476736116</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3834,13 +3834,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46112.679506099536</v>
+        <v>46112.51283943287</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.89613496528</v>
+        <v>46191.72946829861</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.8961546875</v>
+        <v>46191.729488020836</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -3899,13 +3899,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46112.6795156713</v>
+        <v>46112.51284900463</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.67847924768</v>
+        <v>46182.51181258102</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.678480937495</v>
+        <v>46182.51181427084</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3964,13 +3964,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46112.67952521991</v>
+        <v>46112.51285855324</v>
       </c>
       <c r="C35" s="8">
-        <v>46191.89611988426</v>
+        <v>46191.72945321759</v>
       </c>
       <c r="D35" s="8">
-        <v>46191.89612179398</v>
+        <v>46191.729455127315</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -4029,11 +4029,11 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46112.67953447917</v>
+        <v>46112.512867812504</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46196.634982337964</v>
+        <v>46196.4683156713</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4092,13 +4092,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46112.679543101855</v>
+        <v>46112.51287643518</v>
       </c>
       <c r="C37" s="8">
-        <v>46195.68274940972</v>
+        <v>46195.51608274305</v>
       </c>
       <c r="D37" s="8">
-        <v>46195.682751747685</v>
+        <v>46195.51608508102</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -4157,11 +4157,11 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46112.67955209491</v>
+        <v>46112.51288542824</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.7109980324</v>
+        <v>46195.544331365745</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -4218,11 +4218,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46112.67960491898</v>
+        <v>46112.512938252316</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.71583903935</v>
+        <v>46195.54917237269</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4281,13 +4281,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46112.679614513894</v>
+        <v>46112.51294784722</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.678226620366</v>
+        <v>46182.5115599537</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.6782279051</v>
+        <v>46182.511561238425</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4346,11 +4346,11 @@
         <v>148</v>
       </c>
       <c r="B41" s="8">
-        <v>46112.67962357639</v>
+        <v>46112.51295690972</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46195.71615581018</v>
+        <v>46195.54948914352</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -4409,11 +4409,11 @@
         <v>151</v>
       </c>
       <c r="B42" s="5">
-        <v>46112.679632581014</v>
+        <v>46112.51296591436</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.67812216435</v>
+        <v>46182.51145549769</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>152</v>
@@ -4472,13 +4472,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="8">
-        <v>46112.67964135417</v>
+        <v>46112.5129746875</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.67811483797</v>
+        <v>46182.511448171295</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.678117118056</v>
+        <v>46182.51145045139</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>155</v>
@@ -4537,11 +4537,11 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46112.67965385417</v>
+        <v>46112.512987187496</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.72350310185</v>
+        <v>46196.556836435186</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4600,13 +4600,13 @@
         <v>160</v>
       </c>
       <c r="B45" s="8">
-        <v>46112.679662372684</v>
+        <v>46112.51299570602</v>
       </c>
       <c r="C45" s="8">
-        <v>46155.8929416551</v>
+        <v>46155.726274988425</v>
       </c>
       <c r="D45" s="8">
-        <v>46182.67812403935</v>
+        <v>46182.51145737269</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>161</v>
@@ -4665,11 +4665,11 @@
         <v>163</v>
       </c>
       <c r="B46" s="5">
-        <v>46112.67967090278</v>
+        <v>46112.51300423611</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.85692615741</v>
+        <v>46169.690259490744</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -4728,11 +4728,11 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46112.679679733796</v>
+        <v>46112.51301306713</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46196.654216180556</v>
+        <v>46196.487549513884</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4791,11 +4791,11 @@
         <v>170</v>
       </c>
       <c r="B48" s="5">
-        <v>46112.679688564815</v>
+        <v>46112.51302189815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.85689956018</v>
+        <v>46169.69023289352</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4854,13 +4854,13 @@
         <v>173</v>
       </c>
       <c r="B49" s="8">
-        <v>46112.679698321765</v>
+        <v>46112.51303165509</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.86773642361</v>
+        <v>46154.70106975695</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.86774770833</v>
+        <v>46154.70108104167</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>174</v>
@@ -4919,13 +4919,13 @@
         <v>176</v>
       </c>
       <c r="B50" s="5">
-        <v>46112.67970664352</v>
+        <v>46112.51303997685</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.867492777776</v>
+        <v>46154.70082611111</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.86749444444</v>
+        <v>46154.70082777778</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>177</v>
@@ -4974,13 +4974,13 @@
         <v>179</v>
       </c>
       <c r="B51" s="8">
-        <v>46112.67971469907</v>
+        <v>46112.51304803241</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.86772296297</v>
+        <v>46154.7010562963</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.86772430556</v>
+        <v>46154.701057638886</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>180</v>
@@ -5029,11 +5029,11 @@
         <v>182</v>
       </c>
       <c r="B52" s="5">
-        <v>46112.67972244213</v>
+        <v>46112.51305577546</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46181.733022025466</v>
+        <v>46181.566355358795</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>183</v>
@@ -5092,11 +5092,11 @@
         <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46112.67973174769</v>
+        <v>46112.51306508102</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.85708912037</v>
+        <v>46169.6904224537</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>116</v>
@@ -5151,11 +5151,11 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46112.679776261575</v>
+        <v>46112.513109594904</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46181.733022569446</v>
+        <v>46181.566355902774</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5204,13 +5204,13 @@
         <v>193</v>
       </c>
       <c r="B55" s="8">
-        <v>46112.6797871875</v>
+        <v>46112.51312052083</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.69304491898</v>
+        <v>46182.52637825231</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.6930560301</v>
+        <v>46182.526389363426</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>
@@ -5269,13 +5269,13 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46112.67979498843</v>
+        <v>46112.51312832176</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.67401957176</v>
+        <v>46182.50735290509</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.6740215625</v>
+        <v>46182.50735489583</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -5324,13 +5324,13 @@
         <v>199</v>
       </c>
       <c r="B57" s="8">
-        <v>46112.679800983795</v>
+        <v>46112.51313431713</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.69303199074</v>
+        <v>46182.52636532407</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.69303354167</v>
+        <v>46182.526366875</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5379,11 +5379,11 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46112.67980725694</v>
+        <v>46112.51314059028</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.64351380787</v>
+        <v>46162.4768471412</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>203</v>
@@ -5428,13 +5428,13 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46112.67981122685</v>
+        <v>46112.51314456019</v>
       </c>
       <c r="C59" s="8">
-        <v>46155.55032041667</v>
+        <v>46155.38365375</v>
       </c>
       <c r="D59" s="8">
-        <v>46155.55033484954</v>
+        <v>46155.38366818287</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>206</v>
@@ -5493,13 +5493,13 @@
         <v>211</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.7256690162</v>
+        <v>46114.55900234954</v>
       </c>
       <c r="C60" s="5">
-        <v>46155.549498946755</v>
+        <v>46155.38283228009</v>
       </c>
       <c r="D60" s="5">
-        <v>46157.92811706019</v>
+        <v>46157.76145039352</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>212</v>
@@ -5548,13 +5548,13 @@
         <v>216</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.72585883102</v>
+        <v>46114.55919216435</v>
       </c>
       <c r="C61" s="8">
-        <v>46155.54951164352</v>
+        <v>46155.38284497685</v>
       </c>
       <c r="D61" s="8">
-        <v>46157.929841793986</v>
+        <v>46157.763175127315</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>217</v>
@@ -5603,13 +5603,13 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46114.7260297801</v>
+        <v>46114.559363113425</v>
       </c>
       <c r="C62" s="5">
-        <v>46155.54956918981</v>
+        <v>46155.38290252315</v>
       </c>
       <c r="D62" s="5">
-        <v>46155.549570648145</v>
+        <v>46155.38290398148</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5658,13 +5658,13 @@
         <v>222</v>
       </c>
       <c r="B63" s="8">
-        <v>46112.67982518519</v>
+        <v>46112.513158518515</v>
       </c>
       <c r="C63" s="8">
-        <v>46162.64349465277</v>
+        <v>46162.47682798612</v>
       </c>
       <c r="D63" s="8">
-        <v>46190.17747758102</v>
+        <v>46190.01081091435</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>223</v>
@@ -5723,13 +5723,13 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.72944869213</v>
+        <v>46114.56278202546</v>
       </c>
       <c r="C64" s="5">
-        <v>46162.64346262731</v>
+        <v>46162.47679596065</v>
       </c>
       <c r="D64" s="5">
-        <v>46162.64346460648</v>
+        <v>46162.47679793982</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5778,13 +5778,13 @@
         <v>228</v>
       </c>
       <c r="B65" s="8">
-        <v>46114.72950832176</v>
+        <v>46114.56284165509</v>
       </c>
       <c r="C65" s="8">
-        <v>46162.643470509254</v>
+        <v>46162.4768038426</v>
       </c>
       <c r="D65" s="8">
-        <v>46162.643472129625</v>
+        <v>46162.47680546297</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>217</v>
@@ -5833,13 +5833,13 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.72956502315</v>
+        <v>46114.56289835648</v>
       </c>
       <c r="C66" s="5">
-        <v>46162.64348050926</v>
+        <v>46162.47681384259</v>
       </c>
       <c r="D66" s="5">
-        <v>46162.643481747684</v>
+        <v>46162.47681508102</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>220</v>
@@ -5888,13 +5888,13 @@
         <v>234</v>
       </c>
       <c r="B67" s="8">
-        <v>46112.6798337963</v>
+        <v>46112.513167129626</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.73301096065</v>
+        <v>46181.566344293984</v>
       </c>
       <c r="D67" s="8">
-        <v>46191.201163958336</v>
+        <v>46191.034497291665</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>108</v>
@@ -5953,13 +5953,13 @@
         <v>236</v>
       </c>
       <c r="B68" s="5">
-        <v>46114.72964204861</v>
+        <v>46114.562975381945</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.732979629625</v>
+        <v>46181.56631296297</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.73298168981</v>
+        <v>46181.56631502315</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>212</v>
@@ -6006,13 +6006,13 @@
         <v>237</v>
       </c>
       <c r="B69" s="8">
-        <v>46114.72973784722</v>
+        <v>46114.56307118056</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.7329889699</v>
+        <v>46181.566322303246</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.73299055555</v>
+        <v>46181.56632388889</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>217</v>
@@ -6059,13 +6059,13 @@
         <v>238</v>
       </c>
       <c r="B70" s="5">
-        <v>46114.72978940972</v>
+        <v>46114.56312274306</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.73299766204</v>
+        <v>46181.56633099537</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.73299902778</v>
+        <v>46181.56633236111</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>220</v>
@@ -6112,11 +6112,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46112.67984715277</v>
+        <v>46112.513180486116</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.54786293981</v>
+        <v>46118.38119627315</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>240</v>
@@ -6175,11 +6175,11 @@
         <v>244</v>
       </c>
       <c r="B72" s="5">
-        <v>46112.679854120375</v>
+        <v>46112.513187453704</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.54786737269</v>
+        <v>46118.38120070602</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>212</v>
@@ -6228,11 +6228,11 @@
         <v>246</v>
       </c>
       <c r="B73" s="8">
-        <v>46112.67986081018</v>
+        <v>46112.51319414352</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.54786818287</v>
+        <v>46118.381201516204</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>247</v>
@@ -6281,11 +6281,11 @@
         <v>249</v>
       </c>
       <c r="B74" s="5">
-        <v>46112.69527582176</v>
+        <v>46112.528609155095</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.54786895833</v>
+        <v>46118.38120229167</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>250</v>
@@ -6334,11 +6334,11 @@
         <v>253</v>
       </c>
       <c r="B75" s="8">
-        <v>46112.679867326384</v>
+        <v>46112.51320065973</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46118.55096414352</v>
+        <v>46118.38429747685</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>254</v>
@@ -6381,11 +6381,11 @@
         <v>256</v>
       </c>
       <c r="B76" s="5">
-        <v>46112.67987047454</v>
+        <v>46112.513203807874</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.55096918982</v>
+        <v>46118.38430252315</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>255</v>
@@ -6442,11 +6442,11 @@
         <v>260</v>
       </c>
       <c r="B77" s="8">
-        <v>46112.6798790162</v>
+        <v>46112.51321234954</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.74446109954</v>
+        <v>46114.57779443287</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>261</v>
@@ -6489,11 +6489,11 @@
         <v>263</v>
       </c>
       <c r="B78" s="5">
-        <v>46112.6798825463</v>
+        <v>46112.51321587963</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46177.208199479166</v>
+        <v>46177.041532812495</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>264</v>
@@ -6552,11 +6552,11 @@
         <v>268</v>
       </c>
       <c r="B79" s="8">
-        <v>46112.679890740736</v>
+        <v>46112.51322407408</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46179.167811527775</v>
+        <v>46179.00114486111</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>
@@ -6615,11 +6615,11 @@
         <v>271</v>
       </c>
       <c r="B80" s="5">
-        <v>46112.679898159724</v>
+        <v>46112.51323149305</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46118.53693787037</v>
+        <v>46118.370271203705</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>272</v>
@@ -6662,11 +6662,11 @@
         <v>274</v>
       </c>
       <c r="B81" s="8">
-        <v>46112.679901701384</v>
+        <v>46112.51323503473</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46118.536602175926</v>
+        <v>46118.369935509254</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>275</v>
@@ -6725,11 +6725,11 @@
         <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46112.67991023148</v>
+        <v>46112.51324356481</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46118.53671</v>
+        <v>46118.37004333333</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>280</v>
@@ -6788,11 +6788,11 @@
         <v>281</v>
       </c>
       <c r="B83" s="8">
-        <v>46112.679960775466</v>
+        <v>46112.513294108794</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46181.73302506944</v>
+        <v>46181.56635840278</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>212</v>
@@ -6841,11 +6841,11 @@
         <v>284</v>
       </c>
       <c r="B84" s="5">
-        <v>46112.67997252315</v>
+        <v>46112.51330585648</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46181.73302986111</v>
+        <v>46181.56636319445</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>247</v>
@@ -6894,11 +6894,11 @@
         <v>286</v>
       </c>
       <c r="B85" s="8">
-        <v>46112.683129375</v>
+        <v>46112.51646270833</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46118.53646400463</v>
+        <v>46118.36979733796</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>250</v>
@@ -6947,11 +6947,11 @@
         <v>288</v>
       </c>
       <c r="B86" s="5">
-        <v>46112.6799821875</v>
+        <v>46112.51331552083</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.53739798611</v>
+        <v>46118.370731319446</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>289</v>
@@ -7010,11 +7010,11 @@
         <v>291</v>
       </c>
       <c r="B87" s="8">
-        <v>46112.679991655095</v>
+        <v>46112.513324988424</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46181.733025787034</v>
+        <v>46181.56635912037</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>212</v>
@@ -7063,11 +7063,11 @@
         <v>294</v>
       </c>
       <c r="B88" s="5">
-        <v>46112.68000065972</v>
+        <v>46112.513333993054</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46181.73302309027</v>
+        <v>46181.56635642362</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>247</v>
@@ -7116,11 +7116,11 @@
         <v>297</v>
       </c>
       <c r="B89" s="8">
-        <v>46112.68554289352</v>
+        <v>46112.51887622685</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46118.53739997685</v>
+        <v>46118.370733310185</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>251</v>
@@ -7169,11 +7169,11 @@
         <v>299</v>
       </c>
       <c r="B90" s="5">
-        <v>46112.68000929398</v>
+        <v>46112.51334262731</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.55096842593</v>
+        <v>46118.38430175926</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>300</v>
@@ -7216,11 +7216,11 @@
         <v>302</v>
       </c>
       <c r="B91" s="8">
-        <v>46112.68001403935</v>
+        <v>46112.51334737269</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.19835885416</v>
+        <v>46185.0316921875</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>303</v>
@@ -7279,11 +7279,11 @@
         <v>305</v>
       </c>
       <c r="B92" s="5">
-        <v>46112.68002373843</v>
+        <v>46112.51335707176</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46118.551773541665</v>
+        <v>46118.385106875</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>57</v>
@@ -7342,11 +7342,11 @@
         <v>307</v>
       </c>
       <c r="B93" s="8">
-        <v>46112.680037453705</v>
+        <v>46112.51337078704</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46191.89613979167</v>
+        <v>46191.729473125</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>308</v>
@@ -7405,11 +7405,11 @@
         <v>310</v>
       </c>
       <c r="B94" s="5">
-        <v>46112.680046574074</v>
+        <v>46112.51337990741</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46112.680270150464</v>
+        <v>46112.51360348379</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>311</v>
@@ -7468,11 +7468,11 @@
         <v>313</v>
       </c>
       <c r="B95" s="8">
-        <v>46112.68005998843</v>
+        <v>46112.51339332176</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46154.867740671296</v>
+        <v>46154.701074004624</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>314</v>
@@ -7531,11 +7531,11 @@
         <v>316</v>
       </c>
       <c r="B96" s="5">
-        <v>46112.68006824074</v>
+        <v>46112.51340157408</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46118.55096623843</v>
+        <v>46118.38429957176</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>317</v>
@@ -7592,11 +7592,11 @@
         <v>319</v>
       </c>
       <c r="B97" s="8">
-        <v>46112.6800780787</v>
+        <v>46112.51341141204</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46183.18919873843</v>
+        <v>46183.02253207176</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>320</v>
@@ -7655,11 +7655,11 @@
         <v>322</v>
       </c>
       <c r="B98" s="5">
-        <v>46112.68011818287</v>
+        <v>46112.513451516206</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46118.540081238425</v>
+        <v>46118.37341457176</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>323</v>
@@ -7702,11 +7702,11 @@
         <v>325</v>
       </c>
       <c r="B99" s="8">
-        <v>46112.680124363425</v>
+        <v>46112.513457696754</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46118.540939687504</v>
+        <v>46118.37427302083</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>326</v>
@@ -7765,11 +7765,11 @@
         <v>328</v>
       </c>
       <c r="B100" s="5">
-        <v>46112.68013306713</v>
+        <v>46112.51346640046</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.55096479166</v>
+        <v>46118.384298125005</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>212</v>
@@ -7818,11 +7818,11 @@
         <v>331</v>
       </c>
       <c r="B101" s="8">
-        <v>46112.680142453704</v>
+        <v>46112.51347578704</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.55096628472</v>
+        <v>46118.384299618054</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>247</v>
@@ -7871,11 +7871,11 @@
         <v>334</v>
       </c>
       <c r="B102" s="5">
-        <v>46112.68695712963</v>
+        <v>46112.52029046296</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46118.54094193287</v>
+        <v>46118.37427526621</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>251</v>
@@ -7924,11 +7924,11 @@
         <v>336</v>
       </c>
       <c r="B103" s="8">
-        <v>46112.68015230324</v>
+        <v>46112.51348563658</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.54127469908</v>
+        <v>46118.374608032405</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>337</v>
@@ -7987,11 +7987,11 @@
         <v>339</v>
       </c>
       <c r="B104" s="5">
-        <v>46112.680160613425</v>
+        <v>46112.51349394676</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46181.73302627315</v>
+        <v>46181.566359606484</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>212</v>
@@ -8040,11 +8040,11 @@
         <v>342</v>
       </c>
       <c r="B105" s="8">
-        <v>46112.68017212963</v>
+        <v>46112.513505462965</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46181.73302378472</v>
+        <v>46181.566357118056</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>247</v>
@@ -8093,11 +8093,11 @@
         <v>345</v>
       </c>
       <c r="B106" s="5">
-        <v>46112.68780918981</v>
+        <v>46112.52114252315</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.541276550925</v>
+        <v>46118.37460988426</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>251</v>
@@ -8146,11 +8146,11 @@
         <v>347</v>
       </c>
       <c r="B107" s="8">
-        <v>46112.68018260416</v>
+        <v>46112.5135159375</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.54145512731</v>
+        <v>46118.37478846065</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>348</v>
@@ -8209,11 +8209,11 @@
         <v>349</v>
       </c>
       <c r="B108" s="5">
-        <v>46112.680190486106</v>
+        <v>46112.51352381945</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46181.73302827546</v>
+        <v>46181.5663616088</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>212</v>
@@ -8262,11 +8262,11 @@
         <v>352</v>
       </c>
       <c r="B109" s="8">
-        <v>46112.68020174769</v>
+        <v>46112.513535081016</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46181.73302706018</v>
+        <v>46181.56636039352</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>247</v>
@@ -8315,11 +8315,11 @@
         <v>355</v>
       </c>
       <c r="B110" s="5">
-        <v>46112.68889696759</v>
+        <v>46112.52223030092</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46118.541456273146</v>
+        <v>46118.37478960648</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>251</v>
@@ -8368,11 +8368,11 @@
         <v>357</v>
       </c>
       <c r="B111" s="8">
-        <v>46112.6802131713</v>
+        <v>46112.51354650463</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46118.54159421296</v>
+        <v>46118.3749275463</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>358</v>
@@ -8431,11 +8431,11 @@
         <v>359</v>
       </c>
       <c r="B112" s="5">
-        <v>46112.680221111106</v>
+        <v>46112.51355444445</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46181.73302760417</v>
+        <v>46181.566360937504</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>212</v>
@@ -8484,11 +8484,11 @@
         <v>361</v>
       </c>
       <c r="B113" s="8">
-        <v>46112.68023248843</v>
+        <v>46112.51356582176</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46181.733028946765</v>
+        <v>46181.56636228009</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>247</v>
@@ -8537,11 +8537,11 @@
         <v>363</v>
       </c>
       <c r="B114" s="5">
-        <v>46112.69112122685</v>
+        <v>46112.52445456019</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46118.54159666666</v>
+        <v>46118.374930000005</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>250</v>
@@ -8590,11 +8590,11 @@
         <v>365</v>
       </c>
       <c r="B115" s="8">
-        <v>46112.68024403935</v>
+        <v>46112.51357737269</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46118.54175984954</v>
+        <v>46118.37509318287</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>366</v>
@@ -8653,11 +8653,11 @@
         <v>367</v>
       </c>
       <c r="B116" s="5">
-        <v>46112.68025228009</v>
+        <v>46112.51358561343</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46181.73302450232</v>
+        <v>46181.56635783565</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>212</v>
@@ -8706,11 +8706,11 @@
         <v>370</v>
       </c>
       <c r="B117" s="8">
-        <v>46112.68026435185</v>
+        <v>46112.51359768519</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46181.733029490744</v>
+        <v>46181.56636282407</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>247</v>
@@ -8759,11 +8759,11 @@
         <v>373</v>
       </c>
       <c r="B118" s="5">
-        <v>46112.69281496528</v>
+        <v>46112.52614829861</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46118.5417528588</v>
+        <v>46118.37508619213</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>251</v>
@@ -8812,11 +8812,11 @@
         <v>375</v>
       </c>
       <c r="B119" s="8">
-        <v>46112.680315000005</v>
+        <v>46112.51364833333</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46118.54187865741</v>
+        <v>46118.375211990744</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>376</v>
@@ -8875,11 +8875,11 @@
         <v>377</v>
       </c>
       <c r="B120" s="5">
-        <v>46112.68032652778</v>
+        <v>46112.51365986111</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46118.54187940972</v>
+        <v>46118.375212743056</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>212</v>
@@ -8926,11 +8926,11 @@
         <v>379</v>
       </c>
       <c r="B121" s="8">
-        <v>46112.68033607639</v>
+        <v>46112.513669409724</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46118.54188027778</v>
+        <v>46118.375213611114</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>247</v>
@@ -8977,11 +8977,11 @@
         <v>381</v>
       </c>
       <c r="B122" s="5">
-        <v>46112.69375358796</v>
+        <v>46112.5270869213</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46118.54188105324</v>
+        <v>46118.37521438657</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>251</v>
@@ -9028,11 +9028,11 @@
         <v>383</v>
       </c>
       <c r="B123" s="8">
-        <v>46112.68034494213</v>
+        <v>46112.51367827546</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46118.54200872685</v>
+        <v>46118.375342060186</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>384</v>
@@ -9089,11 +9089,11 @@
         <v>385</v>
       </c>
       <c r="B124" s="5">
-        <v>46112.680353344906</v>
+        <v>46112.51368667824</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46118.547864548615</v>
+        <v>46118.38119788194</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>212</v>
@@ -9140,11 +9140,11 @@
         <v>387</v>
       </c>
       <c r="B125" s="8">
-        <v>46112.6803614699</v>
+        <v>46112.513694803245</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46118.5478628125</v>
+        <v>46118.381196145834</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>247</v>
@@ -9191,11 +9191,11 @@
         <v>389</v>
       </c>
       <c r="B126" s="5">
-        <v>46112.69493020834</v>
+        <v>46112.528263541666</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46118.54786351851</v>
+        <v>46118.38119685186</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>251</v>
@@ -9242,11 +9242,11 @@
         <v>391</v>
       </c>
       <c r="B127" s="8">
-        <v>46112.68036949074</v>
+        <v>46112.51370282407</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46118.542785694444</v>
+        <v>46118.37611902777</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>392</v>
@@ -9289,11 +9289,11 @@
         <v>394</v>
       </c>
       <c r="B128" s="5">
-        <v>46112.68037429398</v>
+        <v>46112.51370762731</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46118.542359756946</v>
+        <v>46118.375693090275</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>395</v>
@@ -9352,11 +9352,11 @@
         <v>399</v>
       </c>
       <c r="B129" s="8">
-        <v>46112.68038334491</v>
+        <v>46112.51371667824</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46118.54236040509</v>
+        <v>46118.375693738424</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>212</v>
@@ -9403,11 +9403,11 @@
         <v>401</v>
       </c>
       <c r="B130" s="5">
-        <v>46112.68039121528</v>
+        <v>46112.51372454861</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46118.54236118056</v>
+        <v>46118.37569451389</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>247</v>
@@ -9454,11 +9454,11 @@
         <v>403</v>
       </c>
       <c r="B131" s="8">
-        <v>46112.69787394676</v>
+        <v>46112.53120728009</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46118.542362002314</v>
+        <v>46118.37569533565</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>250</v>
@@ -9505,11 +9505,11 @@
         <v>405</v>
       </c>
       <c r="B132" s="5">
-        <v>46112.6803999074</v>
+        <v>46112.51373324074</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46118.542362858796</v>
+        <v>46118.37569619213</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>56</v>
@@ -9556,11 +9556,11 @@
         <v>407</v>
       </c>
       <c r="B133" s="8">
-        <v>46112.68041137731</v>
+        <v>46112.51374471065</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46118.54236363426</v>
+        <v>46118.37569696759</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>60</v>
@@ -9607,11 +9607,11 @@
         <v>409</v>
       </c>
       <c r="B134" s="5">
-        <v>46112.680419027776</v>
+        <v>46112.51375236111</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46118.54236440972</v>
+        <v>46118.37569774306</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>63</v>
@@ -9658,11 +9658,11 @@
         <v>411</v>
       </c>
       <c r="B135" s="8">
-        <v>46112.68042700231</v>
+        <v>46112.51376033565</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46118.54236519676</v>
+        <v>46118.37569853009</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>66</v>
@@ -9709,11 +9709,11 @@
         <v>413</v>
       </c>
       <c r="B136" s="5">
-        <v>46112.68043466435</v>
+        <v>46112.51376799769</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46118.542365960646</v>
+        <v>46118.37569929398</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>321</v>
@@ -9760,11 +9760,11 @@
         <v>415</v>
       </c>
       <c r="B137" s="8">
-        <v>46112.68044216435</v>
+        <v>46112.51377549769</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46118.54325362269</v>
+        <v>46118.376586956016</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>416</v>
@@ -9823,11 +9823,11 @@
         <v>419</v>
       </c>
       <c r="B138" s="5">
-        <v>46112.68045020833</v>
+        <v>46112.51378354167</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46118.54309255787</v>
+        <v>46118.376425891205</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>212</v>
@@ -9876,11 +9876,11 @@
         <v>421</v>
       </c>
       <c r="B139" s="8">
-        <v>46112.680457615745</v>
+        <v>46112.51379094907</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46118.54309331019</v>
+        <v>46118.37642664352</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>247</v>
@@ -9929,11 +9929,11 @@
         <v>423</v>
       </c>
       <c r="B140" s="5">
-        <v>46112.699333854165</v>
+        <v>46112.5326671875</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46118.54314091435</v>
+        <v>46118.376474247685</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>251</v>
@@ -9982,11 +9982,11 @@
         <v>425</v>
       </c>
       <c r="B141" s="8">
-        <v>46112.68046530093</v>
+        <v>46112.51379863426</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46118.54309490741</v>
+        <v>46118.376428240736</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>56</v>
@@ -10035,11 +10035,11 @@
         <v>427</v>
       </c>
       <c r="B142" s="5">
-        <v>46112.6804727662</v>
+        <v>46112.51380609954</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46118.54309578704</v>
+        <v>46118.37642912037</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>60</v>
@@ -10088,11 +10088,11 @@
         <v>429</v>
       </c>
       <c r="B143" s="8">
-        <v>46112.680524282405</v>
+        <v>46112.51385761574</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46118.54309662037</v>
+        <v>46118.3764299537</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>63</v>
@@ -10141,11 +10141,11 @@
         <v>431</v>
       </c>
       <c r="B144" s="5">
-        <v>46112.68053547454</v>
+        <v>46112.51386880787</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46118.54309747685</v>
+        <v>46118.37643081018</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10194,11 +10194,11 @@
         <v>433</v>
       </c>
       <c r="B145" s="8">
-        <v>46112.68054428241</v>
+        <v>46112.51387761574</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46118.54309846065</v>
+        <v>46118.37643179398</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>434</v>
@@ -10247,11 +10247,11 @@
         <v>436</v>
       </c>
       <c r="B146" s="5">
-        <v>46112.68055275463</v>
+        <v>46112.51388608797</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46118.54357326389</v>
+        <v>46118.37690659722</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>437</v>
@@ -10308,11 +10308,11 @@
         <v>439</v>
       </c>
       <c r="B147" s="8">
-        <v>46112.68056386574</v>
+        <v>46112.513897199075</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46118.543572766204</v>
+        <v>46118.37690609954</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>212</v>
@@ -10361,11 +10361,11 @@
         <v>441</v>
       </c>
       <c r="B148" s="5">
-        <v>46112.68057167824</v>
+        <v>46112.513905011576</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46118.543573414354</v>
+        <v>46118.37690674768</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>247</v>
@@ -10414,11 +10414,11 @@
         <v>443</v>
       </c>
       <c r="B149" s="8">
-        <v>46112.70035509259</v>
+        <v>46112.53368842593</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46118.60507034722</v>
+        <v>46118.43840368056</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>251</v>
@@ -10467,11 +10467,11 @@
         <v>444</v>
       </c>
       <c r="B150" s="5">
-        <v>46112.680579479165</v>
+        <v>46112.5139128125</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46118.5435747338</v>
+        <v>46118.37690806713</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>56</v>
@@ -10520,11 +10520,11 @@
         <v>446</v>
       </c>
       <c r="B151" s="8">
-        <v>46112.68058722222</v>
+        <v>46112.51392055556</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46118.54357537037</v>
+        <v>46118.37690870371</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10573,11 +10573,11 @@
         <v>448</v>
       </c>
       <c r="B152" s="5">
-        <v>46112.68059523148</v>
+        <v>46112.51392856482</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46118.54357599537</v>
+        <v>46118.376909328705</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10626,11 +10626,11 @@
         <v>450</v>
       </c>
       <c r="B153" s="8">
-        <v>46112.680603472225</v>
+        <v>46112.51393680555</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46118.5435766088</v>
+        <v>46118.37690994213</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10679,11 +10679,11 @@
         <v>452</v>
       </c>
       <c r="B154" s="5">
-        <v>46112.68061105324</v>
+        <v>46112.51394438658</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46118.543577268516</v>
+        <v>46118.37691060185</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>453</v>
@@ -10732,11 +10732,11 @@
         <v>455</v>
       </c>
       <c r="B155" s="8">
-        <v>46112.680618784725</v>
+        <v>46112.51395211805</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46118.54392340277</v>
+        <v>46118.377256736116</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>456</v>
@@ -10795,11 +10795,11 @@
         <v>459</v>
       </c>
       <c r="B156" s="5">
-        <v>46112.680633553246</v>
+        <v>46112.513966886574</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46118.543845196764</v>
+        <v>46118.37717853009</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>212</v>
@@ -10848,11 +10848,11 @@
         <v>461</v>
       </c>
       <c r="B157" s="8">
-        <v>46112.68064251158</v>
+        <v>46112.51397584491</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46118.543846030094</v>
+        <v>46118.37717936342</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>247</v>
@@ -10901,11 +10901,11 @@
         <v>462</v>
       </c>
       <c r="B158" s="5">
-        <v>46112.68071581019</v>
+        <v>46112.514049143516</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46118.543850752314</v>
+        <v>46118.37718408565</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>434</v>
@@ -10954,11 +10954,11 @@
         <v>463</v>
       </c>
       <c r="B159" s="8">
-        <v>46112.739142986116</v>
+        <v>46112.572476319445</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46118.543852002316</v>
+        <v>46118.377185335645</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>251</v>
@@ -11007,11 +11007,11 @@
         <v>464</v>
       </c>
       <c r="B160" s="5">
-        <v>46112.68065008102</v>
+        <v>46112.51398341435</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46118.5438528125</v>
+        <v>46118.37718614584</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>56</v>
@@ -11060,11 +11060,11 @@
         <v>465</v>
       </c>
       <c r="B161" s="8">
-        <v>46112.680657476856</v>
+        <v>46112.513990810185</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46118.54385362269</v>
+        <v>46118.377186956015</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>60</v>
@@ -11113,11 +11113,11 @@
         <v>466</v>
       </c>
       <c r="B162" s="5">
-        <v>46112.68069804399</v>
+        <v>46112.514031377315</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46118.54385447917</v>
+        <v>46118.3771878125</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>66</v>
@@ -11166,11 +11166,11 @@
         <v>467</v>
       </c>
       <c r="B163" s="8">
-        <v>46112.68070748843</v>
+        <v>46112.514040821756</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46118.54385528935</v>
+        <v>46118.37718862269</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>63</v>
@@ -11219,11 +11219,11 @@
         <v>468</v>
       </c>
       <c r="B164" s="5">
-        <v>46112.68072377315</v>
+        <v>46112.514057106484</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46118.54278521991</v>
+        <v>46118.37611855324</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>469</v>
@@ -11266,11 +11266,11 @@
         <v>471</v>
       </c>
       <c r="B165" s="8">
-        <v>46112.680728148145</v>
+        <v>46112.51406148148</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46118.54402055556</v>
+        <v>46118.37735388889</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>472</v>
@@ -11329,11 +11329,11 @@
         <v>475</v>
       </c>
       <c r="B166" s="5">
-        <v>46112.68073732639</v>
+        <v>46112.51407065972</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46118.54410575231</v>
+        <v>46118.37743908565</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>476</v>
@@ -11392,11 +11392,11 @@
         <v>478</v>
       </c>
       <c r="B167" s="8">
-        <v>46112.68074700232</v>
+        <v>46112.51408033565</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46118.54278521991</v>
+        <v>46118.37611855324</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>479</v>
@@ -11441,11 +11441,11 @@
         <v>481</v>
       </c>
       <c r="B168" s="5">
-        <v>46112.68075140046</v>
+        <v>46112.5140847338</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46118.54421137732</v>
+        <v>46118.377544710645</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>482</v>
@@ -11504,11 +11504,11 @@
         <v>484</v>
       </c>
       <c r="B169" s="8">
-        <v>46112.68075989583</v>
+        <v>46112.51409322917</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46118.544324525465</v>
+        <v>46118.3776578588</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>485</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -2095,13 +2095,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46112.51244319444</v>
+        <v>46112.679109861114</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.51244314815</v>
+        <v>46112.67910981481</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.51823255787</v>
+        <v>46112.684899224536</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2144,13 +2144,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46112.51257668981</v>
+        <v>46112.679243356484</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.51257664352</v>
+        <v>46112.67924331018</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.5127128125</v>
+        <v>46112.67937947917</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2207,13 +2207,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46112.51258456019</v>
+        <v>46112.67925122685</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.512584537035</v>
+        <v>46112.67925120371</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.51271390046</v>
+        <v>46112.67938056713</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2270,13 +2270,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46112.512590729166</v>
+        <v>46112.67925739584</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.512590706014</v>
+        <v>46112.679257372685</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.512714641205</v>
+        <v>46112.67938130787</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2333,13 +2333,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46112.512596782406</v>
+        <v>46112.67926344907</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.51259677083</v>
+        <v>46112.6792634375</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.51271540509</v>
+        <v>46112.67938207176</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2396,13 +2396,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46112.51260584491</v>
+        <v>46112.679272511574</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.51260582176</v>
+        <v>46112.67927248843</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.51271681713</v>
+        <v>46112.679383483795</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2459,11 +2459,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46112.512449305555</v>
+        <v>46112.67911597222</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.72790445602</v>
+        <v>46134.894571122684</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2506,13 +2506,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46112.51261770833</v>
+        <v>46112.679284375</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.727895069445</v>
+        <v>46134.89456173611</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.72791310185</v>
+        <v>46134.894579768516</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2571,11 +2571,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46112.51262674769</v>
+        <v>46112.67929341435</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46112.51271876157</v>
+        <v>46112.679385428244</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2634,11 +2634,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46112.51263542824</v>
+        <v>46112.67930209491</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46112.57621241898</v>
+        <v>46112.74287908565</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2687,11 +2687,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46112.51264354167</v>
+        <v>46112.67931020833</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46112.576934282406</v>
+        <v>46112.74360094908</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2740,11 +2740,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46112.51265068287</v>
+        <v>46112.67931734954</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46112.57731502315</v>
+        <v>46112.74398168981</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2793,11 +2793,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46112.512658182866</v>
+        <v>46112.67932484954</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46112.577250497685</v>
+        <v>46112.74391716435</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2846,13 +2846,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46112.5124543287</v>
+        <v>46112.679120995366</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.576852453705</v>
+        <v>46114.74351912037</v>
       </c>
       <c r="D17" s="8">
-        <v>46118.382188020834</v>
+        <v>46118.5488546875</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2897,13 +2897,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46112.51266609954</v>
+        <v>46112.6793327662</v>
       </c>
       <c r="C18" s="5">
-        <v>46113.64149030093</v>
+        <v>46113.80815696759</v>
       </c>
       <c r="D18" s="5">
-        <v>46113.97976787037</v>
+        <v>46114.14643453703</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2962,13 +2962,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46112.51267491898</v>
+        <v>46112.67934158565</v>
       </c>
       <c r="C19" s="8">
-        <v>46113.64152197917</v>
+        <v>46113.80818864584</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.001939525464</v>
+        <v>46121.16860619213</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -3027,13 +3027,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46112.512683865745</v>
+        <v>46112.6793505324</v>
       </c>
       <c r="C20" s="5">
-        <v>46113.64158159722</v>
+        <v>46113.808248263886</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.00193938657</v>
+        <v>46121.16860605324</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -3092,13 +3092,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46112.51269375</v>
+        <v>46112.67936041667</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.5768353125</v>
+        <v>46114.74350197917</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.00193940972</v>
+        <v>46121.16860607639</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3157,13 +3157,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46112.5127040625</v>
+        <v>46112.679370729165</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.641615659726</v>
+        <v>46113.80828232639</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.00193939815</v>
+        <v>46121.16860606481</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3222,11 +3222,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46112.51246052083</v>
+        <v>46112.6791271875</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.378926053236</v>
+        <v>46135.54559271991</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3271,13 +3271,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46112.51275108797</v>
+        <v>46112.679417754625</v>
       </c>
       <c r="C24" s="5">
-        <v>46113.64167752315</v>
+        <v>46113.80834418982</v>
       </c>
       <c r="D24" s="5">
-        <v>46115.97324016204</v>
+        <v>46116.1399068287</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3336,13 +3336,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46112.512763437495</v>
+        <v>46112.67943010417</v>
       </c>
       <c r="C25" s="8">
-        <v>46113.641691261575</v>
+        <v>46113.80835792824</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.01996149306</v>
+        <v>46123.18662815972</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3401,13 +3401,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46112.5127737963</v>
+        <v>46112.67944046296</v>
       </c>
       <c r="C26" s="5">
-        <v>46113.64171145833</v>
+        <v>46113.808378125</v>
       </c>
       <c r="D26" s="5">
-        <v>46123.01996138888</v>
+        <v>46123.186628055555</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3466,13 +3466,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46112.51278568287</v>
+        <v>46112.679452349534</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.3789077199</v>
+        <v>46135.545574386575</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.3791616088</v>
+        <v>46135.54582827546</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3531,11 +3531,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46112.51279622685</v>
+        <v>46112.67946289352</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46196.48754457176</v>
+        <v>46196.65421123843</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3594,13 +3594,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46112.512811469904</v>
+        <v>46112.679478136575</v>
       </c>
       <c r="C29" s="8">
-        <v>46113.64174697916</v>
+        <v>46113.808413645835</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.01996229167</v>
+        <v>46123.186628958334</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3659,11 +3659,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46112.512821365744</v>
+        <v>46112.67948803241</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.034363831015</v>
+        <v>46193.20103049769</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3722,13 +3722,13 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46112.51283033565</v>
+        <v>46112.67949700232</v>
       </c>
       <c r="C31" s="8">
-        <v>46113.64180048611</v>
+        <v>46113.808467152776</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.019961516206</v>
+        <v>46123.18662818287</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3787,11 +3787,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46112.512468402776</v>
+        <v>46112.67913506944</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46191.729476736116</v>
+        <v>46191.89614340277</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3834,13 +3834,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46112.51283943287</v>
+        <v>46112.679506099536</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.72946829861</v>
+        <v>46191.89613496528</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.729488020836</v>
+        <v>46191.8961546875</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -3899,13 +3899,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46112.51284900463</v>
+        <v>46112.6795156713</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.51181258102</v>
+        <v>46182.67847924768</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.51181427084</v>
+        <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3964,13 +3964,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46112.51285855324</v>
+        <v>46112.67952521991</v>
       </c>
       <c r="C35" s="8">
-        <v>46191.72945321759</v>
+        <v>46191.89611988426</v>
       </c>
       <c r="D35" s="8">
-        <v>46191.729455127315</v>
+        <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -4029,11 +4029,11 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46112.512867812504</v>
+        <v>46112.67953447917</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46196.4683156713</v>
+        <v>46196.634982337964</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4092,13 +4092,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46112.51287643518</v>
+        <v>46112.679543101855</v>
       </c>
       <c r="C37" s="8">
-        <v>46195.51608274305</v>
+        <v>46195.68274940972</v>
       </c>
       <c r="D37" s="8">
-        <v>46195.51608508102</v>
+        <v>46195.682751747685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -4157,11 +4157,11 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46112.51288542824</v>
+        <v>46112.67955209491</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.544331365745</v>
+        <v>46195.7109980324</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -4218,11 +4218,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46112.512938252316</v>
+        <v>46112.67960491898</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.54917237269</v>
+        <v>46195.71583903935</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4281,13 +4281,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46112.51294784722</v>
+        <v>46112.679614513894</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.5115599537</v>
+        <v>46182.678226620366</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.511561238425</v>
+        <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4346,11 +4346,11 @@
         <v>148</v>
       </c>
       <c r="B41" s="8">
-        <v>46112.51295690972</v>
+        <v>46112.67962357639</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46195.54948914352</v>
+        <v>46195.71615581018</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -4409,11 +4409,11 @@
         <v>151</v>
       </c>
       <c r="B42" s="5">
-        <v>46112.51296591436</v>
+        <v>46112.679632581014</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.51145549769</v>
+        <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>152</v>
@@ -4472,13 +4472,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="8">
-        <v>46112.5129746875</v>
+        <v>46112.67964135417</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.511448171295</v>
+        <v>46182.67811483797</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.51145045139</v>
+        <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>155</v>
@@ -4537,11 +4537,11 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46112.512987187496</v>
+        <v>46112.67965385417</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.556836435186</v>
+        <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4600,13 +4600,13 @@
         <v>160</v>
       </c>
       <c r="B45" s="8">
-        <v>46112.51299570602</v>
+        <v>46112.679662372684</v>
       </c>
       <c r="C45" s="8">
-        <v>46155.726274988425</v>
+        <v>46155.8929416551</v>
       </c>
       <c r="D45" s="8">
-        <v>46182.51145737269</v>
+        <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>161</v>
@@ -4665,11 +4665,11 @@
         <v>163</v>
       </c>
       <c r="B46" s="5">
-        <v>46112.51300423611</v>
+        <v>46112.67967090278</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.690259490744</v>
+        <v>46169.85692615741</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -4728,11 +4728,11 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46112.51301306713</v>
+        <v>46112.679679733796</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46196.487549513884</v>
+        <v>46196.654216180556</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4791,11 +4791,11 @@
         <v>170</v>
       </c>
       <c r="B48" s="5">
-        <v>46112.51302189815</v>
+        <v>46112.679688564815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.69023289352</v>
+        <v>46169.85689956018</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4854,13 +4854,13 @@
         <v>173</v>
       </c>
       <c r="B49" s="8">
-        <v>46112.51303165509</v>
+        <v>46112.679698321765</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.70106975695</v>
+        <v>46154.86773642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.70108104167</v>
+        <v>46154.86774770833</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>174</v>
@@ -4919,13 +4919,13 @@
         <v>176</v>
       </c>
       <c r="B50" s="5">
-        <v>46112.51303997685</v>
+        <v>46112.67970664352</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.70082611111</v>
+        <v>46154.867492777776</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.70082777778</v>
+        <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>177</v>
@@ -4974,13 +4974,13 @@
         <v>179</v>
       </c>
       <c r="B51" s="8">
-        <v>46112.51304803241</v>
+        <v>46112.67971469907</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.7010562963</v>
+        <v>46154.86772296297</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.701057638886</v>
+        <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>180</v>
@@ -5029,11 +5029,11 @@
         <v>182</v>
       </c>
       <c r="B52" s="5">
-        <v>46112.51305577546</v>
+        <v>46112.67972244213</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46181.566355358795</v>
+        <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>183</v>
@@ -5092,11 +5092,11 @@
         <v>187</v>
       </c>
       <c r="B53" s="8">
-        <v>46112.51306508102</v>
+        <v>46112.67973174769</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.6904224537</v>
+        <v>46169.85708912037</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>116</v>
@@ -5151,11 +5151,11 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46112.513109594904</v>
+        <v>46112.679776261575</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46181.566355902774</v>
+        <v>46181.733022569446</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -5204,13 +5204,13 @@
         <v>193</v>
       </c>
       <c r="B55" s="8">
-        <v>46112.51312052083</v>
+        <v>46112.6797871875</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.52637825231</v>
+        <v>46182.69304491898</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.526389363426</v>
+        <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>
@@ -5269,13 +5269,13 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46112.51312832176</v>
+        <v>46112.67979498843</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.50735290509</v>
+        <v>46182.67401957176</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.50735489583</v>
+        <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -5324,13 +5324,13 @@
         <v>199</v>
       </c>
       <c r="B57" s="8">
-        <v>46112.51313431713</v>
+        <v>46112.679800983795</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.52636532407</v>
+        <v>46182.69303199074</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.526366875</v>
+        <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>200</v>
@@ -5379,11 +5379,11 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46112.51314059028</v>
+        <v>46112.67980725694</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.4768471412</v>
+        <v>46162.64351380787</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>203</v>
@@ -5428,13 +5428,13 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46112.51314456019</v>
+        <v>46112.67981122685</v>
       </c>
       <c r="C59" s="8">
-        <v>46155.38365375</v>
+        <v>46155.55032041667</v>
       </c>
       <c r="D59" s="8">
-        <v>46155.38366818287</v>
+        <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>206</v>
@@ -5493,13 +5493,13 @@
         <v>211</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.55900234954</v>
+        <v>46114.7256690162</v>
       </c>
       <c r="C60" s="5">
-        <v>46155.38283228009</v>
+        <v>46155.549498946755</v>
       </c>
       <c r="D60" s="5">
-        <v>46157.76145039352</v>
+        <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>212</v>
@@ -5548,13 +5548,13 @@
         <v>216</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.55919216435</v>
+        <v>46114.72585883102</v>
       </c>
       <c r="C61" s="8">
-        <v>46155.38284497685</v>
+        <v>46155.54951164352</v>
       </c>
       <c r="D61" s="8">
-        <v>46157.763175127315</v>
+        <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>217</v>
@@ -5603,13 +5603,13 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46114.559363113425</v>
+        <v>46114.7260297801</v>
       </c>
       <c r="C62" s="5">
-        <v>46155.38290252315</v>
+        <v>46155.54956918981</v>
       </c>
       <c r="D62" s="5">
-        <v>46155.38290398148</v>
+        <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>220</v>
@@ -5658,13 +5658,13 @@
         <v>222</v>
       </c>
       <c r="B63" s="8">
-        <v>46112.513158518515</v>
+        <v>46112.67982518519</v>
       </c>
       <c r="C63" s="8">
-        <v>46162.47682798612</v>
+        <v>46162.64349465277</v>
       </c>
       <c r="D63" s="8">
-        <v>46190.01081091435</v>
+        <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>223</v>
@@ -5723,13 +5723,13 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.56278202546</v>
+        <v>46114.72944869213</v>
       </c>
       <c r="C64" s="5">
-        <v>46162.47679596065</v>
+        <v>46162.64346262731</v>
       </c>
       <c r="D64" s="5">
-        <v>46162.47679793982</v>
+        <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5778,13 +5778,13 @@
         <v>228</v>
       </c>
       <c r="B65" s="8">
-        <v>46114.56284165509</v>
+        <v>46114.72950832176</v>
       </c>
       <c r="C65" s="8">
-        <v>46162.4768038426</v>
+        <v>46162.643470509254</v>
       </c>
       <c r="D65" s="8">
-        <v>46162.47680546297</v>
+        <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>217</v>
@@ -5833,13 +5833,13 @@
         <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.56289835648</v>
+        <v>46114.72956502315</v>
       </c>
       <c r="C66" s="5">
-        <v>46162.47681384259</v>
+        <v>46162.64348050926</v>
       </c>
       <c r="D66" s="5">
-        <v>46162.47681508102</v>
+        <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>220</v>
@@ -5888,13 +5888,13 @@
         <v>234</v>
       </c>
       <c r="B67" s="8">
-        <v>46112.513167129626</v>
+        <v>46112.6798337963</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.566344293984</v>
+        <v>46181.73301096065</v>
       </c>
       <c r="D67" s="8">
-        <v>46191.034497291665</v>
+        <v>46191.201163958336</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>108</v>
@@ -5953,13 +5953,13 @@
         <v>236</v>
       </c>
       <c r="B68" s="5">
-        <v>46114.562975381945</v>
+        <v>46114.72964204861</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.56631296297</v>
+        <v>46181.732979629625</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.56631502315</v>
+        <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>212</v>
@@ -6006,13 +6006,13 @@
         <v>237</v>
       </c>
       <c r="B69" s="8">
-        <v>46114.56307118056</v>
+        <v>46114.72973784722</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.566322303246</v>
+        <v>46181.7329889699</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.56632388889</v>
+        <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>217</v>
@@ -6059,13 +6059,13 @@
         <v>238</v>
       </c>
       <c r="B70" s="5">
-        <v>46114.56312274306</v>
+        <v>46114.72978940972</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.56633099537</v>
+        <v>46181.73299766204</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.56633236111</v>
+        <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>220</v>
@@ -6112,11 +6112,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="8">
-        <v>46112.513180486116</v>
+        <v>46112.67984715277</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.38119627315</v>
+        <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>240</v>
@@ -6175,11 +6175,11 @@
         <v>244</v>
       </c>
       <c r="B72" s="5">
-        <v>46112.513187453704</v>
+        <v>46112.679854120375</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.38120070602</v>
+        <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>212</v>
@@ -6228,11 +6228,11 @@
         <v>246</v>
       </c>
       <c r="B73" s="8">
-        <v>46112.51319414352</v>
+        <v>46112.67986081018</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.381201516204</v>
+        <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>247</v>
@@ -6281,11 +6281,11 @@
         <v>249</v>
       </c>
       <c r="B74" s="5">
-        <v>46112.528609155095</v>
+        <v>46112.69527582176</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.38120229167</v>
+        <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>250</v>
@@ -6334,11 +6334,11 @@
         <v>253</v>
       </c>
       <c r="B75" s="8">
-        <v>46112.51320065973</v>
+        <v>46112.679867326384</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46118.38429747685</v>
+        <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>254</v>
@@ -6381,11 +6381,11 @@
         <v>256</v>
       </c>
       <c r="B76" s="5">
-        <v>46112.513203807874</v>
+        <v>46112.67987047454</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.38430252315</v>
+        <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>255</v>
@@ -6442,11 +6442,11 @@
         <v>260</v>
       </c>
       <c r="B77" s="8">
-        <v>46112.51321234954</v>
+        <v>46112.6798790162</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.57779443287</v>
+        <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>261</v>
@@ -6489,11 +6489,11 @@
         <v>263</v>
       </c>
       <c r="B78" s="5">
-        <v>46112.51321587963</v>
+        <v>46112.6798825463</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46177.041532812495</v>
+        <v>46177.208199479166</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>264</v>
@@ -6552,11 +6552,11 @@
         <v>268</v>
       </c>
       <c r="B79" s="8">
-        <v>46112.51322407408</v>
+        <v>46112.679890740736</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46179.00114486111</v>
+        <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>
@@ -6615,11 +6615,11 @@
         <v>271</v>
       </c>
       <c r="B80" s="5">
-        <v>46112.51323149305</v>
+        <v>46112.679898159724</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46118.370271203705</v>
+        <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>272</v>
@@ -6662,11 +6662,11 @@
         <v>274</v>
       </c>
       <c r="B81" s="8">
-        <v>46112.51323503473</v>
+        <v>46112.679901701384</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46118.369935509254</v>
+        <v>46118.536602175926</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>275</v>
@@ -6725,11 +6725,11 @@
         <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46112.51324356481</v>
+        <v>46112.67991023148</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46118.37004333333</v>
+        <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>280</v>
@@ -6788,11 +6788,11 @@
         <v>281</v>
       </c>
       <c r="B83" s="8">
-        <v>46112.513294108794</v>
+        <v>46112.679960775466</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46181.56635840278</v>
+        <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>212</v>
@@ -6841,11 +6841,11 @@
         <v>284</v>
       </c>
       <c r="B84" s="5">
-        <v>46112.51330585648</v>
+        <v>46112.67997252315</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46181.56636319445</v>
+        <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>247</v>
@@ -6894,11 +6894,11 @@
         <v>286</v>
       </c>
       <c r="B85" s="8">
-        <v>46112.51646270833</v>
+        <v>46112.683129375</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46118.36979733796</v>
+        <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>250</v>
@@ -6947,11 +6947,11 @@
         <v>288</v>
       </c>
       <c r="B86" s="5">
-        <v>46112.51331552083</v>
+        <v>46112.6799821875</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.370731319446</v>
+        <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>289</v>
@@ -7010,11 +7010,11 @@
         <v>291</v>
       </c>
       <c r="B87" s="8">
-        <v>46112.513324988424</v>
+        <v>46112.679991655095</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46181.56635912037</v>
+        <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>212</v>
@@ -7063,11 +7063,11 @@
         <v>294</v>
       </c>
       <c r="B88" s="5">
-        <v>46112.513333993054</v>
+        <v>46112.68000065972</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46181.56635642362</v>
+        <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>247</v>
@@ -7116,11 +7116,11 @@
         <v>297</v>
       </c>
       <c r="B89" s="8">
-        <v>46112.51887622685</v>
+        <v>46112.68554289352</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46118.370733310185</v>
+        <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>251</v>
@@ -7169,11 +7169,11 @@
         <v>299</v>
       </c>
       <c r="B90" s="5">
-        <v>46112.51334262731</v>
+        <v>46112.68000929398</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.38430175926</v>
+        <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>300</v>
@@ -7216,11 +7216,11 @@
         <v>302</v>
       </c>
       <c r="B91" s="8">
-        <v>46112.51334737269</v>
+        <v>46112.68001403935</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.0316921875</v>
+        <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>303</v>
@@ -7279,11 +7279,11 @@
         <v>305</v>
       </c>
       <c r="B92" s="5">
-        <v>46112.51335707176</v>
+        <v>46112.68002373843</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46118.385106875</v>
+        <v>46118.551773541665</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>57</v>
@@ -7342,11 +7342,11 @@
         <v>307</v>
       </c>
       <c r="B93" s="8">
-        <v>46112.51337078704</v>
+        <v>46112.680037453705</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46191.729473125</v>
+        <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>308</v>
@@ -7405,11 +7405,11 @@
         <v>310</v>
       </c>
       <c r="B94" s="5">
-        <v>46112.51337990741</v>
+        <v>46112.680046574074</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46112.51360348379</v>
+        <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>311</v>
@@ -7468,11 +7468,11 @@
         <v>313</v>
       </c>
       <c r="B95" s="8">
-        <v>46112.51339332176</v>
+        <v>46112.68005998843</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46154.701074004624</v>
+        <v>46154.867740671296</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>314</v>
@@ -7531,11 +7531,11 @@
         <v>316</v>
       </c>
       <c r="B96" s="5">
-        <v>46112.51340157408</v>
+        <v>46112.68006824074</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46118.38429957176</v>
+        <v>46118.55096623843</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>317</v>
@@ -7592,11 +7592,11 @@
         <v>319</v>
       </c>
       <c r="B97" s="8">
-        <v>46112.51341141204</v>
+        <v>46112.6800780787</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46183.02253207176</v>
+        <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>320</v>
@@ -7655,11 +7655,11 @@
         <v>322</v>
       </c>
       <c r="B98" s="5">
-        <v>46112.513451516206</v>
+        <v>46112.68011818287</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46118.37341457176</v>
+        <v>46118.540081238425</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>323</v>
@@ -7702,11 +7702,11 @@
         <v>325</v>
       </c>
       <c r="B99" s="8">
-        <v>46112.513457696754</v>
+        <v>46112.680124363425</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46118.37427302083</v>
+        <v>46118.540939687504</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>326</v>
@@ -7765,11 +7765,11 @@
         <v>328</v>
       </c>
       <c r="B100" s="5">
-        <v>46112.51346640046</v>
+        <v>46112.68013306713</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.384298125005</v>
+        <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>212</v>
@@ -7818,11 +7818,11 @@
         <v>331</v>
       </c>
       <c r="B101" s="8">
-        <v>46112.51347578704</v>
+        <v>46112.680142453704</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.384299618054</v>
+        <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>247</v>
@@ -7871,11 +7871,11 @@
         <v>334</v>
       </c>
       <c r="B102" s="5">
-        <v>46112.52029046296</v>
+        <v>46112.68695712963</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46118.37427526621</v>
+        <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>251</v>
@@ -7924,11 +7924,11 @@
         <v>336</v>
       </c>
       <c r="B103" s="8">
-        <v>46112.51348563658</v>
+        <v>46112.68015230324</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.374608032405</v>
+        <v>46118.54127469908</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>337</v>
@@ -7987,11 +7987,11 @@
         <v>339</v>
       </c>
       <c r="B104" s="5">
-        <v>46112.51349394676</v>
+        <v>46112.680160613425</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46181.566359606484</v>
+        <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>212</v>
@@ -8040,11 +8040,11 @@
         <v>342</v>
       </c>
       <c r="B105" s="8">
-        <v>46112.513505462965</v>
+        <v>46112.68017212963</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46181.566357118056</v>
+        <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>247</v>
@@ -8093,11 +8093,11 @@
         <v>345</v>
       </c>
       <c r="B106" s="5">
-        <v>46112.52114252315</v>
+        <v>46112.68780918981</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.37460988426</v>
+        <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>251</v>
@@ -8146,11 +8146,11 @@
         <v>347</v>
       </c>
       <c r="B107" s="8">
-        <v>46112.5135159375</v>
+        <v>46112.68018260416</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.37478846065</v>
+        <v>46118.54145512731</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>348</v>
@@ -8209,11 +8209,11 @@
         <v>349</v>
       </c>
       <c r="B108" s="5">
-        <v>46112.51352381945</v>
+        <v>46112.680190486106</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46181.5663616088</v>
+        <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>212</v>
@@ -8262,11 +8262,11 @@
         <v>352</v>
       </c>
       <c r="B109" s="8">
-        <v>46112.513535081016</v>
+        <v>46112.68020174769</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46181.56636039352</v>
+        <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>247</v>
@@ -8315,11 +8315,11 @@
         <v>355</v>
       </c>
       <c r="B110" s="5">
-        <v>46112.52223030092</v>
+        <v>46112.68889696759</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46118.37478960648</v>
+        <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>251</v>
@@ -8368,11 +8368,11 @@
         <v>357</v>
       </c>
       <c r="B111" s="8">
-        <v>46112.51354650463</v>
+        <v>46112.6802131713</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46118.3749275463</v>
+        <v>46118.54159421296</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>358</v>
@@ -8431,11 +8431,11 @@
         <v>359</v>
       </c>
       <c r="B112" s="5">
-        <v>46112.51355444445</v>
+        <v>46112.680221111106</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46181.566360937504</v>
+        <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>212</v>
@@ -8484,11 +8484,11 @@
         <v>361</v>
       </c>
       <c r="B113" s="8">
-        <v>46112.51356582176</v>
+        <v>46112.68023248843</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46181.56636228009</v>
+        <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>247</v>
@@ -8537,11 +8537,11 @@
         <v>363</v>
       </c>
       <c r="B114" s="5">
-        <v>46112.52445456019</v>
+        <v>46112.69112122685</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46118.374930000005</v>
+        <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>250</v>
@@ -8590,11 +8590,11 @@
         <v>365</v>
       </c>
       <c r="B115" s="8">
-        <v>46112.51357737269</v>
+        <v>46112.68024403935</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46118.37509318287</v>
+        <v>46118.54175984954</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>366</v>
@@ -8653,11 +8653,11 @@
         <v>367</v>
       </c>
       <c r="B116" s="5">
-        <v>46112.51358561343</v>
+        <v>46112.68025228009</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46181.56635783565</v>
+        <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>212</v>
@@ -8706,11 +8706,11 @@
         <v>370</v>
       </c>
       <c r="B117" s="8">
-        <v>46112.51359768519</v>
+        <v>46112.68026435185</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46181.56636282407</v>
+        <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>247</v>
@@ -8759,11 +8759,11 @@
         <v>373</v>
       </c>
       <c r="B118" s="5">
-        <v>46112.52614829861</v>
+        <v>46112.69281496528</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46118.37508619213</v>
+        <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>251</v>
@@ -8812,11 +8812,11 @@
         <v>375</v>
       </c>
       <c r="B119" s="8">
-        <v>46112.51364833333</v>
+        <v>46112.680315000005</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46118.375211990744</v>
+        <v>46118.54187865741</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>376</v>
@@ -8875,11 +8875,11 @@
         <v>377</v>
       </c>
       <c r="B120" s="5">
-        <v>46112.51365986111</v>
+        <v>46112.68032652778</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46118.375212743056</v>
+        <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>212</v>
@@ -8926,11 +8926,11 @@
         <v>379</v>
       </c>
       <c r="B121" s="8">
-        <v>46112.513669409724</v>
+        <v>46112.68033607639</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46118.375213611114</v>
+        <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>247</v>
@@ -8977,11 +8977,11 @@
         <v>381</v>
       </c>
       <c r="B122" s="5">
-        <v>46112.5270869213</v>
+        <v>46112.69375358796</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46118.37521438657</v>
+        <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>251</v>
@@ -9028,11 +9028,11 @@
         <v>383</v>
       </c>
       <c r="B123" s="8">
-        <v>46112.51367827546</v>
+        <v>46112.68034494213</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46118.375342060186</v>
+        <v>46118.54200872685</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>384</v>
@@ -9089,11 +9089,11 @@
         <v>385</v>
       </c>
       <c r="B124" s="5">
-        <v>46112.51368667824</v>
+        <v>46112.680353344906</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46118.38119788194</v>
+        <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>212</v>
@@ -9140,11 +9140,11 @@
         <v>387</v>
       </c>
       <c r="B125" s="8">
-        <v>46112.513694803245</v>
+        <v>46112.6803614699</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46118.381196145834</v>
+        <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>247</v>
@@ -9191,11 +9191,11 @@
         <v>389</v>
       </c>
       <c r="B126" s="5">
-        <v>46112.528263541666</v>
+        <v>46112.69493020834</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46118.38119685186</v>
+        <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>251</v>
@@ -9242,11 +9242,11 @@
         <v>391</v>
       </c>
       <c r="B127" s="8">
-        <v>46112.51370282407</v>
+        <v>46112.68036949074</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46118.37611902777</v>
+        <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>392</v>
@@ -9289,11 +9289,11 @@
         <v>394</v>
       </c>
       <c r="B128" s="5">
-        <v>46112.51370762731</v>
+        <v>46112.68037429398</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46118.375693090275</v>
+        <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>395</v>
@@ -9352,11 +9352,11 @@
         <v>399</v>
       </c>
       <c r="B129" s="8">
-        <v>46112.51371667824</v>
+        <v>46112.68038334491</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46118.375693738424</v>
+        <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>212</v>
@@ -9403,11 +9403,11 @@
         <v>401</v>
       </c>
       <c r="B130" s="5">
-        <v>46112.51372454861</v>
+        <v>46112.68039121528</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46118.37569451389</v>
+        <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>247</v>
@@ -9454,11 +9454,11 @@
         <v>403</v>
       </c>
       <c r="B131" s="8">
-        <v>46112.53120728009</v>
+        <v>46112.69787394676</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46118.37569533565</v>
+        <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>250</v>
@@ -9505,11 +9505,11 @@
         <v>405</v>
       </c>
       <c r="B132" s="5">
-        <v>46112.51373324074</v>
+        <v>46112.6803999074</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46118.37569619213</v>
+        <v>46118.542362858796</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>56</v>
@@ -9556,11 +9556,11 @@
         <v>407</v>
       </c>
       <c r="B133" s="8">
-        <v>46112.51374471065</v>
+        <v>46112.68041137731</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46118.37569696759</v>
+        <v>46118.54236363426</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>60</v>
@@ -9607,11 +9607,11 @@
         <v>409</v>
       </c>
       <c r="B134" s="5">
-        <v>46112.51375236111</v>
+        <v>46112.680419027776</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46118.37569774306</v>
+        <v>46118.54236440972</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>63</v>
@@ -9658,11 +9658,11 @@
         <v>411</v>
       </c>
       <c r="B135" s="8">
-        <v>46112.51376033565</v>
+        <v>46112.68042700231</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46118.37569853009</v>
+        <v>46118.54236519676</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>66</v>
@@ -9709,11 +9709,11 @@
         <v>413</v>
       </c>
       <c r="B136" s="5">
-        <v>46112.51376799769</v>
+        <v>46112.68043466435</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46118.37569929398</v>
+        <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>321</v>
@@ -9760,11 +9760,11 @@
         <v>415</v>
       </c>
       <c r="B137" s="8">
-        <v>46112.51377549769</v>
+        <v>46112.68044216435</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46118.376586956016</v>
+        <v>46118.54325362269</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>416</v>
@@ -9823,11 +9823,11 @@
         <v>419</v>
       </c>
       <c r="B138" s="5">
-        <v>46112.51378354167</v>
+        <v>46112.68045020833</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46118.376425891205</v>
+        <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>212</v>
@@ -9876,11 +9876,11 @@
         <v>421</v>
       </c>
       <c r="B139" s="8">
-        <v>46112.51379094907</v>
+        <v>46112.680457615745</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46118.37642664352</v>
+        <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>247</v>
@@ -9929,11 +9929,11 @@
         <v>423</v>
       </c>
       <c r="B140" s="5">
-        <v>46112.5326671875</v>
+        <v>46112.699333854165</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46118.376474247685</v>
+        <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>251</v>
@@ -9982,11 +9982,11 @@
         <v>425</v>
       </c>
       <c r="B141" s="8">
-        <v>46112.51379863426</v>
+        <v>46112.68046530093</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46118.376428240736</v>
+        <v>46118.54309490741</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>56</v>
@@ -10035,11 +10035,11 @@
         <v>427</v>
       </c>
       <c r="B142" s="5">
-        <v>46112.51380609954</v>
+        <v>46112.6804727662</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46118.37642912037</v>
+        <v>46118.54309578704</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>60</v>
@@ -10088,11 +10088,11 @@
         <v>429</v>
       </c>
       <c r="B143" s="8">
-        <v>46112.51385761574</v>
+        <v>46112.680524282405</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46118.3764299537</v>
+        <v>46118.54309662037</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>63</v>
@@ -10141,11 +10141,11 @@
         <v>431</v>
       </c>
       <c r="B144" s="5">
-        <v>46112.51386880787</v>
+        <v>46112.68053547454</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46118.37643081018</v>
+        <v>46118.54309747685</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10194,11 +10194,11 @@
         <v>433</v>
       </c>
       <c r="B145" s="8">
-        <v>46112.51387761574</v>
+        <v>46112.68054428241</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46118.37643179398</v>
+        <v>46118.54309846065</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>434</v>
@@ -10247,11 +10247,11 @@
         <v>436</v>
       </c>
       <c r="B146" s="5">
-        <v>46112.51388608797</v>
+        <v>46112.68055275463</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46118.37690659722</v>
+        <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>437</v>
@@ -10308,11 +10308,11 @@
         <v>439</v>
       </c>
       <c r="B147" s="8">
-        <v>46112.513897199075</v>
+        <v>46112.68056386574</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46118.37690609954</v>
+        <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>212</v>
@@ -10361,11 +10361,11 @@
         <v>441</v>
       </c>
       <c r="B148" s="5">
-        <v>46112.513905011576</v>
+        <v>46112.68057167824</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46118.37690674768</v>
+        <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>247</v>
@@ -10414,11 +10414,11 @@
         <v>443</v>
       </c>
       <c r="B149" s="8">
-        <v>46112.53368842593</v>
+        <v>46112.70035509259</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46118.43840368056</v>
+        <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>251</v>
@@ -10467,11 +10467,11 @@
         <v>444</v>
       </c>
       <c r="B150" s="5">
-        <v>46112.5139128125</v>
+        <v>46112.680579479165</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46118.37690806713</v>
+        <v>46118.5435747338</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>56</v>
@@ -10520,11 +10520,11 @@
         <v>446</v>
       </c>
       <c r="B151" s="8">
-        <v>46112.51392055556</v>
+        <v>46112.68058722222</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46118.37690870371</v>
+        <v>46118.54357537037</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10573,11 +10573,11 @@
         <v>448</v>
       </c>
       <c r="B152" s="5">
-        <v>46112.51392856482</v>
+        <v>46112.68059523148</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46118.376909328705</v>
+        <v>46118.54357599537</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10626,11 +10626,11 @@
         <v>450</v>
       </c>
       <c r="B153" s="8">
-        <v>46112.51393680555</v>
+        <v>46112.680603472225</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46118.37690994213</v>
+        <v>46118.5435766088</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10679,11 +10679,11 @@
         <v>452</v>
       </c>
       <c r="B154" s="5">
-        <v>46112.51394438658</v>
+        <v>46112.68061105324</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46118.37691060185</v>
+        <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>453</v>
@@ -10732,11 +10732,11 @@
         <v>455</v>
       </c>
       <c r="B155" s="8">
-        <v>46112.51395211805</v>
+        <v>46112.680618784725</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46118.377256736116</v>
+        <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>456</v>
@@ -10795,11 +10795,11 @@
         <v>459</v>
       </c>
       <c r="B156" s="5">
-        <v>46112.513966886574</v>
+        <v>46112.680633553246</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46118.37717853009</v>
+        <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>212</v>
@@ -10848,11 +10848,11 @@
         <v>461</v>
       </c>
       <c r="B157" s="8">
-        <v>46112.51397584491</v>
+        <v>46112.68064251158</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46118.37717936342</v>
+        <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>247</v>
@@ -10901,11 +10901,11 @@
         <v>462</v>
       </c>
       <c r="B158" s="5">
-        <v>46112.514049143516</v>
+        <v>46112.68071581019</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46118.37718408565</v>
+        <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>434</v>
@@ -10954,11 +10954,11 @@
         <v>463</v>
       </c>
       <c r="B159" s="8">
-        <v>46112.572476319445</v>
+        <v>46112.739142986116</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46118.377185335645</v>
+        <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>251</v>
@@ -11007,11 +11007,11 @@
         <v>464</v>
       </c>
       <c r="B160" s="5">
-        <v>46112.51398341435</v>
+        <v>46112.68065008102</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46118.37718614584</v>
+        <v>46118.5438528125</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>56</v>
@@ -11060,11 +11060,11 @@
         <v>465</v>
       </c>
       <c r="B161" s="8">
-        <v>46112.513990810185</v>
+        <v>46112.680657476856</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46118.377186956015</v>
+        <v>46118.54385362269</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>60</v>
@@ -11113,11 +11113,11 @@
         <v>466</v>
       </c>
       <c r="B162" s="5">
-        <v>46112.514031377315</v>
+        <v>46112.68069804399</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46118.3771878125</v>
+        <v>46118.54385447917</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>66</v>
@@ -11166,11 +11166,11 @@
         <v>467</v>
       </c>
       <c r="B163" s="8">
-        <v>46112.514040821756</v>
+        <v>46112.68070748843</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46118.37718862269</v>
+        <v>46118.54385528935</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>63</v>
@@ -11219,11 +11219,11 @@
         <v>468</v>
       </c>
       <c r="B164" s="5">
-        <v>46112.514057106484</v>
+        <v>46112.68072377315</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46118.37611855324</v>
+        <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>469</v>
@@ -11266,11 +11266,11 @@
         <v>471</v>
       </c>
       <c r="B165" s="8">
-        <v>46112.51406148148</v>
+        <v>46112.680728148145</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46118.37735388889</v>
+        <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>472</v>
@@ -11329,11 +11329,11 @@
         <v>475</v>
       </c>
       <c r="B166" s="5">
-        <v>46112.51407065972</v>
+        <v>46112.68073732639</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46118.37743908565</v>
+        <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>476</v>
@@ -11392,11 +11392,11 @@
         <v>478</v>
       </c>
       <c r="B167" s="8">
-        <v>46112.51408033565</v>
+        <v>46112.68074700232</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46118.37611855324</v>
+        <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>479</v>
@@ -11441,11 +11441,11 @@
         <v>481</v>
       </c>
       <c r="B168" s="5">
-        <v>46112.5140847338</v>
+        <v>46112.68075140046</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46118.377544710645</v>
+        <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>482</v>
@@ -11504,11 +11504,11 @@
         <v>484</v>
       </c>
       <c r="B169" s="8">
-        <v>46112.51409322917</v>
+        <v>46112.68075989583</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46118.3776578588</v>
+        <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>485</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -4732,7 +4732,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46196.654216180556</v>
+        <v>46199.16864855324</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.85708912037</v>
+        <v>46199.16870392361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>116</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="487">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -515,6 +515,9 @@
   </si>
   <si>
     <t>Generación OC materiales ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213886259305803</t>
@@ -4669,7 +4672,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.85692615741</v>
+        <v>46203.17583194445</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -4716,8 +4719,8 @@
       <c r="S46" s="6">
         <v>0</v>
       </c>
-      <c r="T46" s="11" t="s">
-        <v>53</v>
+      <c r="T46" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="U46" s="10" t="s">
         <v>54</v>
@@ -4725,7 +4728,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4768,7 +4771,7 @@
         <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4788,7 +4791,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4798,7 +4801,7 @@
         <v>46169.85689956018</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4831,7 +4834,7 @@
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4851,7 +4854,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4863,7 +4866,7 @@
         <v>46154.86774770833</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
@@ -4893,7 +4896,7 @@
         <v>120</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>120</v>
@@ -4916,7 +4919,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4928,7 +4931,7 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4955,13 +4958,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4971,7 +4974,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4983,7 +4986,7 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -5010,13 +5013,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5026,7 +5029,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5036,16 +5039,16 @@
         <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5066,7 +5069,7 @@
         <v>120</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>120</v>
@@ -5089,7 +5092,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5105,10 +5108,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5126,13 +5129,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>114</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5148,7 +5151,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5158,16 +5161,16 @@
         <v>46181.733022569446</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5185,13 +5188,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5201,7 +5204,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5213,7 +5216,7 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5243,7 +5246,7 @@
         <v>120</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5266,7 +5269,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5278,7 +5281,7 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5305,13 +5308,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5321,7 +5324,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5333,7 +5336,7 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5360,13 +5363,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5376,7 +5379,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5386,7 +5389,7 @@
         <v>46162.64351380787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5410,7 +5413,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5425,7 +5428,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5437,16 +5440,16 @@
         <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5464,13 +5467,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5490,7 +5493,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5502,16 +5505,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5529,13 +5532,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5545,7 +5548,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5557,16 +5560,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5584,13 +5587,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5600,7 +5603,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5612,16 +5615,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5639,13 +5642,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5655,7 +5658,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5667,16 +5670,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5694,13 +5697,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5720,7 +5723,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5732,16 +5735,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5759,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5775,7 +5778,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5787,16 +5790,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5814,13 +5817,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5830,7 +5833,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5842,16 +5845,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5869,13 +5872,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5885,7 +5888,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5903,10 +5906,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5924,13 +5927,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5950,7 +5953,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5962,16 +5965,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5990,7 +5993,7 @@
         <v>108</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>108</v>
@@ -6003,7 +6006,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6015,16 +6018,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6043,7 +6046,7 @@
         <v>108</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>108</v>
@@ -6056,7 +6059,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6068,16 +6071,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6096,7 +6099,7 @@
         <v>108</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>108</v>
@@ -6109,7 +6112,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6119,16 +6122,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6146,10 +6149,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6172,7 +6175,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6182,16 +6185,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6209,13 +6212,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6225,7 +6228,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6235,16 +6238,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6262,13 +6265,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6278,7 +6281,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6288,16 +6291,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6315,13 +6318,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6331,7 +6334,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6341,7 +6344,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6365,7 +6368,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6378,7 +6381,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6388,16 +6391,16 @@
         <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6413,13 +6416,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6439,7 +6442,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6449,7 +6452,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6473,7 +6476,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6486,7 +6489,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6496,16 +6499,16 @@
         <v>46177.208199479166</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6523,13 +6526,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6549,7 +6552,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6559,16 +6562,16 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6586,13 +6589,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6612,7 +6615,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6622,7 +6625,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6646,7 +6649,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6659,7 +6662,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6669,16 +6672,16 @@
         <v>46118.536602175926</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6696,13 +6699,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6722,7 +6725,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6732,16 +6735,16 @@
         <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6759,13 +6762,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6785,7 +6788,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6795,16 +6798,16 @@
         <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6822,13 +6825,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6838,7 +6841,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6848,16 +6851,16 @@
         <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6875,13 +6878,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6891,7 +6894,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6901,16 +6904,16 @@
         <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6928,13 +6931,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6944,7 +6947,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6954,16 +6957,16 @@
         <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -6981,13 +6984,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7007,7 +7010,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7017,16 +7020,16 @@
         <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7044,13 +7047,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7060,7 +7063,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7070,16 +7073,16 @@
         <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7097,13 +7100,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7113,7 +7116,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7123,16 +7126,16 @@
         <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7150,13 +7153,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7166,7 +7169,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7176,7 +7179,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7200,7 +7203,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7213,7 +7216,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7223,16 +7226,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7250,13 +7253,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>149</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7276,7 +7279,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7292,10 +7295,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7313,13 +7316,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7339,7 +7342,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7349,16 +7352,16 @@
         <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7376,13 +7379,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>131</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7402,7 +7405,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7412,16 +7415,16 @@
         <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7439,13 +7442,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>158</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7465,7 +7468,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
@@ -7475,16 +7478,16 @@
         <v>46154.867740671296</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7502,13 +7505,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7528,7 +7531,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7538,16 +7541,16 @@
         <v>46118.55096623843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7563,13 +7566,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7589,7 +7592,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7599,16 +7602,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7626,13 +7629,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7652,7 +7655,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7662,7 +7665,7 @@
         <v>46118.540081238425</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7686,7 +7689,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7699,7 +7702,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
@@ -7709,7 +7712,7 @@
         <v>46118.540939687504</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7736,13 +7739,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7762,7 +7765,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
@@ -7772,7 +7775,7 @@
         <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7799,13 +7802,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7815,7 +7818,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
@@ -7825,7 +7828,7 @@
         <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7852,13 +7855,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7868,7 +7871,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
@@ -7878,7 +7881,7 @@
         <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7905,13 +7908,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7921,7 +7924,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
@@ -7931,7 +7934,7 @@
         <v>46118.54127469908</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7958,13 +7961,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -7984,7 +7987,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
@@ -7994,7 +7997,7 @@
         <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8021,13 +8024,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8037,7 +8040,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
@@ -8047,7 +8050,7 @@
         <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8074,13 +8077,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8090,7 +8093,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
@@ -8100,7 +8103,7 @@
         <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8127,13 +8130,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8143,7 +8146,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
@@ -8153,7 +8156,7 @@
         <v>46118.54145512731</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8180,13 +8183,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8206,7 +8209,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
@@ -8216,7 +8219,7 @@
         <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8243,13 +8246,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8259,7 +8262,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
@@ -8269,7 +8272,7 @@
         <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8296,13 +8299,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8312,7 +8315,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
@@ -8322,7 +8325,7 @@
         <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8349,13 +8352,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8365,7 +8368,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
@@ -8375,7 +8378,7 @@
         <v>46118.54159421296</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8402,13 +8405,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8428,7 +8431,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
@@ -8438,7 +8441,7 @@
         <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8465,13 +8468,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8481,7 +8484,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
@@ -8491,7 +8494,7 @@
         <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8518,13 +8521,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8534,7 +8537,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
@@ -8544,7 +8547,7 @@
         <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8571,13 +8574,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8587,7 +8590,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
@@ -8597,7 +8600,7 @@
         <v>46118.54175984954</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8624,13 +8627,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8650,7 +8653,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
@@ -8660,7 +8663,7 @@
         <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8687,13 +8690,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8703,7 +8706,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
@@ -8713,7 +8716,7 @@
         <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8740,13 +8743,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8756,7 +8759,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
@@ -8766,7 +8769,7 @@
         <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8793,13 +8796,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8809,7 +8812,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
@@ -8819,7 +8822,7 @@
         <v>46118.54187865741</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8846,13 +8849,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8872,7 +8875,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
@@ -8882,7 +8885,7 @@
         <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8907,13 +8910,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8923,7 +8926,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
@@ -8933,7 +8936,7 @@
         <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8958,13 +8961,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8974,7 +8977,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
@@ -8984,7 +8987,7 @@
         <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9009,13 +9012,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9025,7 +9028,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
@@ -9035,7 +9038,7 @@
         <v>46118.54200872685</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9060,13 +9063,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9086,7 +9089,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B124" s="5">
         <v>46112.680353344906</v>
@@ -9096,7 +9099,7 @@
         <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9121,13 +9124,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9137,7 +9140,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B125" s="8">
         <v>46112.6803614699</v>
@@ -9147,7 +9150,7 @@
         <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9172,13 +9175,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9188,7 +9191,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B126" s="5">
         <v>46112.69493020834</v>
@@ -9198,7 +9201,7 @@
         <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9223,13 +9226,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9239,7 +9242,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B127" s="8">
         <v>46112.68036949074</v>
@@ -9249,7 +9252,7 @@
         <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9273,7 +9276,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9286,7 +9289,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B128" s="5">
         <v>46112.68037429398</v>
@@ -9296,16 +9299,16 @@
         <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I128" s="5">
         <v>46287</v>
@@ -9323,13 +9326,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q128" s="5">
         <v>46287</v>
@@ -9349,7 +9352,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B129" s="8">
         <v>46112.68038334491</v>
@@ -9359,16 +9362,16 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9384,13 +9387,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9400,7 +9403,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B130" s="5">
         <v>46112.68039121528</v>
@@ -9410,16 +9413,16 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9435,13 +9438,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9451,7 +9454,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B131" s="8">
         <v>46112.69787394676</v>
@@ -9461,16 +9464,16 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9486,13 +9489,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9502,7 +9505,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B132" s="5">
         <v>46112.6803999074</v>
@@ -9518,10 +9521,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9537,13 +9540,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9553,7 +9556,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B133" s="8">
         <v>46112.68041137731</v>
@@ -9569,10 +9572,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9588,13 +9591,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9604,7 +9607,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B134" s="5">
         <v>46112.680419027776</v>
@@ -9620,10 +9623,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9639,13 +9642,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9655,7 +9658,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B135" s="8">
         <v>46112.68042700231</v>
@@ -9671,10 +9674,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9690,13 +9693,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9706,7 +9709,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B136" s="5">
         <v>46112.68043466435</v>
@@ -9716,16 +9719,16 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9741,13 +9744,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9757,7 +9760,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B137" s="8">
         <v>46112.68044216435</v>
@@ -9767,7 +9770,7 @@
         <v>46118.54325362269</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9794,13 +9797,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q137" s="8">
         <v>46288</v>
@@ -9820,7 +9823,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B138" s="5">
         <v>46112.68045020833</v>
@@ -9830,7 +9833,7 @@
         <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9857,13 +9860,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9873,7 +9876,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B139" s="8">
         <v>46112.680457615745</v>
@@ -9883,7 +9886,7 @@
         <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9910,13 +9913,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9926,7 +9929,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B140" s="5">
         <v>46112.699333854165</v>
@@ -9936,7 +9939,7 @@
         <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9963,13 +9966,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9979,7 +9982,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B141" s="8">
         <v>46112.68046530093</v>
@@ -10016,13 +10019,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>56</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10032,7 +10035,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B142" s="5">
         <v>46112.6804727662</v>
@@ -10069,13 +10072,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10085,7 +10088,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B143" s="8">
         <v>46112.680524282405</v>
@@ -10122,13 +10125,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10138,7 +10141,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B144" s="5">
         <v>46112.68053547454</v>
@@ -10175,13 +10178,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10191,7 +10194,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B145" s="8">
         <v>46112.68054428241</v>
@@ -10201,7 +10204,7 @@
         <v>46118.54309846065</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10228,13 +10231,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10244,7 +10247,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B146" s="5">
         <v>46112.68055275463</v>
@@ -10254,16 +10257,16 @@
         <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10279,13 +10282,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q146" s="5">
         <v>46293</v>
@@ -10305,7 +10308,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B147" s="8">
         <v>46112.68056386574</v>
@@ -10315,16 +10318,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10342,13 +10345,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10358,7 +10361,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B148" s="5">
         <v>46112.68057167824</v>
@@ -10368,16 +10371,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10395,13 +10398,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10411,7 +10414,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B149" s="8">
         <v>46112.70035509259</v>
@@ -10421,16 +10424,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10448,13 +10451,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10464,7 +10467,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B150" s="5">
         <v>46112.680579479165</v>
@@ -10480,10 +10483,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10501,13 +10504,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10517,7 +10520,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B151" s="8">
         <v>46112.68058722222</v>
@@ -10533,10 +10536,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10554,13 +10557,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10570,7 +10573,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B152" s="5">
         <v>46112.68059523148</v>
@@ -10586,10 +10589,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10607,13 +10610,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10623,7 +10626,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B153" s="8">
         <v>46112.680603472225</v>
@@ -10639,10 +10642,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10660,13 +10663,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10676,7 +10679,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B154" s="5">
         <v>46112.68061105324</v>
@@ -10686,16 +10689,16 @@
         <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10713,13 +10716,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10729,7 +10732,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B155" s="8">
         <v>46112.680618784725</v>
@@ -10739,16 +10742,16 @@
         <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10766,13 +10769,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q155" s="8">
         <v>46294</v>
@@ -10792,7 +10795,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B156" s="5">
         <v>46112.680633553246</v>
@@ -10802,16 +10805,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10829,13 +10832,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10845,7 +10848,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B157" s="8">
         <v>46112.68064251158</v>
@@ -10855,16 +10858,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10882,13 +10885,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10898,7 +10901,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B158" s="5">
         <v>46112.68071581019</v>
@@ -10908,16 +10911,16 @@
         <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10935,13 +10938,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10951,7 +10954,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B159" s="8">
         <v>46112.739142986116</v>
@@ -10961,16 +10964,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -10988,10 +10991,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11004,7 +11007,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B160" s="5">
         <v>46112.68065008102</v>
@@ -11020,10 +11023,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11041,13 +11044,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11057,7 +11060,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B161" s="8">
         <v>46112.680657476856</v>
@@ -11073,10 +11076,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11094,13 +11097,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11110,7 +11113,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B162" s="5">
         <v>46112.68069804399</v>
@@ -11126,10 +11129,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11147,13 +11150,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11163,7 +11166,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B163" s="8">
         <v>46112.68070748843</v>
@@ -11179,10 +11182,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>
@@ -11200,13 +11203,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11216,7 +11219,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B164" s="5">
         <v>46112.68072377315</v>
@@ -11226,7 +11229,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>25</v>
@@ -11250,7 +11253,7 @@
         <v>26</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>26</v>
@@ -11263,7 +11266,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B165" s="8">
         <v>46112.680728148145</v>
@@ -11273,16 +11276,16 @@
         <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I165" s="8">
         <v>46295</v>
@@ -11300,13 +11303,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Q165" s="8">
         <v>46295</v>
@@ -11326,7 +11329,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B166" s="5">
         <v>46112.68073732639</v>
@@ -11336,16 +11339,16 @@
         <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I166" s="5">
         <v>46295</v>
@@ -11363,13 +11366,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Q166" s="5">
         <v>46295</v>
@@ -11389,7 +11392,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B167" s="8">
         <v>46112.68074700232</v>
@@ -11399,7 +11402,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>25</v>
@@ -11423,7 +11426,7 @@
         <v>26</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>26</v>
@@ -11438,7 +11441,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B168" s="5">
         <v>46112.68075140046</v>
@@ -11448,16 +11451,16 @@
         <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I168" s="5">
         <v>46295</v>
@@ -11475,13 +11478,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q168" s="5">
         <v>46295</v>
@@ -11501,7 +11504,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B169" s="8">
         <v>46112.68075989583</v>
@@ -11511,16 +11514,16 @@
         <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I169" s="8">
         <v>46304</v>
@@ -11538,13 +11541,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q169" s="8">
         <v>46304</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -2098,13 +2098,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46112.679109861114</v>
+        <v>46112.51244319444</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.67910981481</v>
+        <v>46112.51244314815</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.684899224536</v>
+        <v>46112.51823255787</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2147,13 +2147,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46112.679243356484</v>
+        <v>46112.51257668981</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.67924331018</v>
+        <v>46112.51257664352</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.67937947917</v>
+        <v>46112.5127128125</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2210,13 +2210,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46112.67925122685</v>
+        <v>46112.51258456019</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.67925120371</v>
+        <v>46112.512584537035</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.67938056713</v>
+        <v>46112.51271390046</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2273,13 +2273,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46112.67925739584</v>
+        <v>46112.512590729166</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.679257372685</v>
+        <v>46112.512590706014</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.67938130787</v>
+        <v>46112.512714641205</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2336,13 +2336,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46112.67926344907</v>
+        <v>46112.512596782406</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.6792634375</v>
+        <v>46112.51259677083</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.67938207176</v>
+        <v>46112.51271540509</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2399,13 +2399,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46112.679272511574</v>
+        <v>46112.51260584491</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.67927248843</v>
+        <v>46112.51260582176</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.679383483795</v>
+        <v>46112.51271681713</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2462,11 +2462,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46112.67911597222</v>
+        <v>46112.512449305555</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.894571122684</v>
+        <v>46134.72790445602</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2509,13 +2509,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46112.679284375</v>
+        <v>46112.51261770833</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.89456173611</v>
+        <v>46134.727895069445</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.894579768516</v>
+        <v>46134.72791310185</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2574,11 +2574,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46112.67929341435</v>
+        <v>46112.51262674769</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46112.679385428244</v>
+        <v>46112.51271876157</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2637,11 +2637,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46112.67930209491</v>
+        <v>46112.51263542824</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46112.74287908565</v>
+        <v>46112.57621241898</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2690,11 +2690,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46112.67931020833</v>
+        <v>46112.51264354167</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46112.74360094908</v>
+        <v>46112.576934282406</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2743,11 +2743,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46112.67931734954</v>
+        <v>46112.51265068287</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46112.74398168981</v>
+        <v>46112.57731502315</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2796,11 +2796,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46112.67932484954</v>
+        <v>46112.512658182866</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46112.74391716435</v>
+        <v>46112.577250497685</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2849,13 +2849,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46112.679120995366</v>
+        <v>46112.5124543287</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.74351912037</v>
+        <v>46114.576852453705</v>
       </c>
       <c r="D17" s="8">
-        <v>46118.5488546875</v>
+        <v>46118.382188020834</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2900,13 +2900,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46112.6793327662</v>
+        <v>46112.51266609954</v>
       </c>
       <c r="C18" s="5">
-        <v>46113.80815696759</v>
+        <v>46113.64149030093</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.14643453703</v>
+        <v>46113.97976787037</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2965,13 +2965,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46112.67934158565</v>
+        <v>46112.51267491898</v>
       </c>
       <c r="C19" s="8">
-        <v>46113.80818864584</v>
+        <v>46113.64152197917</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.16860619213</v>
+        <v>46121.001939525464</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -3030,13 +3030,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46112.6793505324</v>
+        <v>46112.512683865745</v>
       </c>
       <c r="C20" s="5">
-        <v>46113.808248263886</v>
+        <v>46113.64158159722</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.16860605324</v>
+        <v>46121.00193938657</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -3095,13 +3095,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46112.67936041667</v>
+        <v>46112.51269375</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.74350197917</v>
+        <v>46114.5768353125</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.16860607639</v>
+        <v>46121.00193940972</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3160,13 +3160,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46112.679370729165</v>
+        <v>46112.5127040625</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.80828232639</v>
+        <v>46113.641615659726</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.16860606481</v>
+        <v>46121.00193939815</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3225,11 +3225,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46112.6791271875</v>
+        <v>46112.51246052083</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.54559271991</v>
+        <v>46135.378926053236</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3274,13 +3274,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46112.679417754625</v>
+        <v>46112.51275108797</v>
       </c>
       <c r="C24" s="5">
-        <v>46113.80834418982</v>
+        <v>46113.64167752315</v>
       </c>
       <c r="D24" s="5">
-        <v>46116.1399068287</v>
+        <v>46115.97324016204</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3339,13 +3339,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46112.67943010417</v>
+        <v>46112.512763437495</v>
       </c>
       <c r="C25" s="8">
-        <v>46113.80835792824</v>
+        <v>46113.641691261575</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.18662815972</v>
+        <v>46123.01996149306</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3404,13 +3404,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46112.67944046296</v>
+        <v>46112.5127737963</v>
       </c>
       <c r="C26" s="5">
-        <v>46113.808378125</v>
+        <v>46113.64171145833</v>
       </c>
       <c r="D26" s="5">
-        <v>46123.186628055555</v>
+        <v>46123.01996138888</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3469,13 +3469,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46112.679452349534</v>
+        <v>46112.51278568287</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.545574386575</v>
+        <v>46135.3789077199</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.54582827546</v>
+        <v>46135.3791616088</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3534,11 +3534,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46112.67946289352</v>
+        <v>46112.51279622685</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46196.65421123843</v>
+        <v>46196.48754457176</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3597,13 +3597,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46112.679478136575</v>
+        <v>46112.512811469904</v>
       </c>
       <c r="C29" s="8">
-        <v>46113.808413645835</v>
+        <v>46113.64174697916</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.186628958334</v>
+        <v>46123.01996229167</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3662,11 +3662,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46112.67948803241</v>
+        <v>46112.512821365744</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.20103049769</v>
+        <v>46193.034363831015</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3725,13 +3725,13 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46112.67949700232</v>
+        <v>46112.51283033565</v>
       </c>
       <c r="C31" s="8">
-        <v>46113.808467152776</v>
+        <v>46113.64180048611</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.18662818287</v>
+        <v>46123.019961516206</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3790,11 +3790,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46112.67913506944</v>
+        <v>46112.512468402776</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46191.89614340277</v>
+        <v>46191.729476736116</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3837,13 +3837,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46112.679506099536</v>
+        <v>46112.51283943287</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.89613496528</v>
+        <v>46191.72946829861</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.8961546875</v>
+        <v>46191.729488020836</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -3902,13 +3902,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46112.6795156713</v>
+        <v>46112.51284900463</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.67847924768</v>
+        <v>46182.51181258102</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.678480937495</v>
+        <v>46182.51181427084</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3967,13 +3967,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46112.67952521991</v>
+        <v>46112.51285855324</v>
       </c>
       <c r="C35" s="8">
-        <v>46191.89611988426</v>
+        <v>46191.72945321759</v>
       </c>
       <c r="D35" s="8">
-        <v>46191.89612179398</v>
+        <v>46191.729455127315</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -4032,11 +4032,11 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46112.67953447917</v>
+        <v>46112.512867812504</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46196.634982337964</v>
+        <v>46196.4683156713</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4095,13 +4095,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46112.679543101855</v>
+        <v>46112.51287643518</v>
       </c>
       <c r="C37" s="8">
-        <v>46195.68274940972</v>
+        <v>46195.51608274305</v>
       </c>
       <c r="D37" s="8">
-        <v>46195.682751747685</v>
+        <v>46195.51608508102</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -4160,11 +4160,11 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46112.67955209491</v>
+        <v>46112.51288542824</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.7109980324</v>
+        <v>46195.544331365745</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -4221,11 +4221,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46112.67960491898</v>
+        <v>46112.512938252316</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.71583903935</v>
+        <v>46195.54917237269</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4284,13 +4284,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46112.679614513894</v>
+        <v>46112.51294784722</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.678226620366</v>
+        <v>46182.5115599537</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.6782279051</v>
+        <v>46182.511561238425</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4349,11 +4349,11 @@
         <v>148</v>
       </c>
       <c r="B41" s="8">
-        <v>46112.67962357639</v>
+        <v>46112.51295690972</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46195.71615581018</v>
+        <v>46195.54948914352</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -4412,11 +4412,11 @@
         <v>151</v>
       </c>
       <c r="B42" s="5">
-        <v>46112.679632581014</v>
+        <v>46112.51296591436</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.67812216435</v>
+        <v>46182.51145549769</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>152</v>
@@ -4475,13 +4475,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="8">
-        <v>46112.67964135417</v>
+        <v>46112.5129746875</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.67811483797</v>
+        <v>46182.511448171295</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.678117118056</v>
+        <v>46182.51145045139</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>155</v>
@@ -4540,11 +4540,11 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46112.67965385417</v>
+        <v>46112.512987187496</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.72350310185</v>
+        <v>46196.556836435186</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4603,13 +4603,13 @@
         <v>160</v>
       </c>
       <c r="B45" s="8">
-        <v>46112.679662372684</v>
+        <v>46112.51299570602</v>
       </c>
       <c r="C45" s="8">
-        <v>46155.8929416551</v>
+        <v>46155.726274988425</v>
       </c>
       <c r="D45" s="8">
-        <v>46182.67812403935</v>
+        <v>46182.51145737269</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>161</v>
@@ -4668,11 +4668,11 @@
         <v>163</v>
       </c>
       <c r="B46" s="5">
-        <v>46112.67967090278</v>
+        <v>46112.51300423611</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46203.17583194445</v>
+        <v>46203.00916527778</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -4731,11 +4731,11 @@
         <v>169</v>
       </c>
       <c r="B47" s="8">
-        <v>46112.679679733796</v>
+        <v>46112.51301306713</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46199.16864855324</v>
+        <v>46199.00198188657</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4794,11 +4794,11 @@
         <v>171</v>
       </c>
       <c r="B48" s="5">
-        <v>46112.679688564815</v>
+        <v>46112.51302189815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.85689956018</v>
+        <v>46169.69023289352</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4857,13 +4857,13 @@
         <v>174</v>
       </c>
       <c r="B49" s="8">
-        <v>46112.679698321765</v>
+        <v>46112.51303165509</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.86773642361</v>
+        <v>46154.70106975695</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.86774770833</v>
+        <v>46154.70108104167</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -4922,13 +4922,13 @@
         <v>177</v>
       </c>
       <c r="B50" s="5">
-        <v>46112.67970664352</v>
+        <v>46112.51303997685</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.867492777776</v>
+        <v>46154.70082611111</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.86749444444</v>
+        <v>46154.70082777778</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>178</v>
@@ -4977,13 +4977,13 @@
         <v>180</v>
       </c>
       <c r="B51" s="8">
-        <v>46112.67971469907</v>
+        <v>46112.51304803241</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.86772296297</v>
+        <v>46154.7010562963</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.86772430556</v>
+        <v>46154.701057638886</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>181</v>
@@ -5032,11 +5032,11 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46112.67972244213</v>
+        <v>46112.51305577546</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46181.733022025466</v>
+        <v>46181.566355358795</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5095,11 +5095,11 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46112.67973174769</v>
+        <v>46112.51306508102</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46199.16870392361</v>
+        <v>46199.00203725694</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>116</v>
@@ -5154,11 +5154,11 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46112.679776261575</v>
+        <v>46112.513109594904</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46181.733022569446</v>
+        <v>46181.566355902774</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -5207,13 +5207,13 @@
         <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46112.6797871875</v>
+        <v>46112.51312052083</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.69304491898</v>
+        <v>46182.52637825231</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.6930560301</v>
+        <v>46182.526389363426</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>195</v>
@@ -5272,13 +5272,13 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46112.67979498843</v>
+        <v>46112.51312832176</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.67401957176</v>
+        <v>46182.50735290509</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.6740215625</v>
+        <v>46182.50735489583</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -5327,13 +5327,13 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46112.679800983795</v>
+        <v>46112.51313431713</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.69303199074</v>
+        <v>46182.52636532407</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.69303354167</v>
+        <v>46182.526366875</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5382,11 +5382,11 @@
         <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46112.67980725694</v>
+        <v>46112.51314059028</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.64351380787</v>
+        <v>46162.4768471412</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>204</v>
@@ -5431,13 +5431,13 @@
         <v>206</v>
       </c>
       <c r="B59" s="8">
-        <v>46112.67981122685</v>
+        <v>46112.51314456019</v>
       </c>
       <c r="C59" s="8">
-        <v>46155.55032041667</v>
+        <v>46155.38365375</v>
       </c>
       <c r="D59" s="8">
-        <v>46155.55033484954</v>
+        <v>46155.38366818287</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>207</v>
@@ -5496,13 +5496,13 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.7256690162</v>
+        <v>46114.55900234954</v>
       </c>
       <c r="C60" s="5">
-        <v>46155.549498946755</v>
+        <v>46155.38283228009</v>
       </c>
       <c r="D60" s="5">
-        <v>46157.92811706019</v>
+        <v>46157.76145039352</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5551,13 +5551,13 @@
         <v>217</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.72585883102</v>
+        <v>46114.55919216435</v>
       </c>
       <c r="C61" s="8">
-        <v>46155.54951164352</v>
+        <v>46155.38284497685</v>
       </c>
       <c r="D61" s="8">
-        <v>46157.929841793986</v>
+        <v>46157.763175127315</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>218</v>
@@ -5606,13 +5606,13 @@
         <v>220</v>
       </c>
       <c r="B62" s="5">
-        <v>46114.7260297801</v>
+        <v>46114.559363113425</v>
       </c>
       <c r="C62" s="5">
-        <v>46155.54956918981</v>
+        <v>46155.38290252315</v>
       </c>
       <c r="D62" s="5">
-        <v>46155.549570648145</v>
+        <v>46155.38290398148</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>221</v>
@@ -5661,13 +5661,13 @@
         <v>223</v>
       </c>
       <c r="B63" s="8">
-        <v>46112.67982518519</v>
+        <v>46112.513158518515</v>
       </c>
       <c r="C63" s="8">
-        <v>46162.64349465277</v>
+        <v>46162.47682798612</v>
       </c>
       <c r="D63" s="8">
-        <v>46190.17747758102</v>
+        <v>46190.01081091435</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5726,13 +5726,13 @@
         <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.72944869213</v>
+        <v>46114.56278202546</v>
       </c>
       <c r="C64" s="5">
-        <v>46162.64346262731</v>
+        <v>46162.47679596065</v>
       </c>
       <c r="D64" s="5">
-        <v>46162.64346460648</v>
+        <v>46162.47679793982</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>213</v>
@@ -5781,13 +5781,13 @@
         <v>229</v>
       </c>
       <c r="B65" s="8">
-        <v>46114.72950832176</v>
+        <v>46114.56284165509</v>
       </c>
       <c r="C65" s="8">
-        <v>46162.643470509254</v>
+        <v>46162.4768038426</v>
       </c>
       <c r="D65" s="8">
-        <v>46162.643472129625</v>
+        <v>46162.47680546297</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>218</v>
@@ -5836,13 +5836,13 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.72956502315</v>
+        <v>46114.56289835648</v>
       </c>
       <c r="C66" s="5">
-        <v>46162.64348050926</v>
+        <v>46162.47681384259</v>
       </c>
       <c r="D66" s="5">
-        <v>46162.643481747684</v>
+        <v>46162.47681508102</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>221</v>
@@ -5891,13 +5891,13 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46112.6798337963</v>
+        <v>46112.513167129626</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.73301096065</v>
+        <v>46181.566344293984</v>
       </c>
       <c r="D67" s="8">
-        <v>46191.201163958336</v>
+        <v>46191.034497291665</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>108</v>
@@ -5956,13 +5956,13 @@
         <v>237</v>
       </c>
       <c r="B68" s="5">
-        <v>46114.72964204861</v>
+        <v>46114.562975381945</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.732979629625</v>
+        <v>46181.56631296297</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.73298168981</v>
+        <v>46181.56631502315</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>213</v>
@@ -6009,13 +6009,13 @@
         <v>238</v>
       </c>
       <c r="B69" s="8">
-        <v>46114.72973784722</v>
+        <v>46114.56307118056</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.7329889699</v>
+        <v>46181.566322303246</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.73299055555</v>
+        <v>46181.56632388889</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>218</v>
@@ -6062,13 +6062,13 @@
         <v>239</v>
       </c>
       <c r="B70" s="5">
-        <v>46114.72978940972</v>
+        <v>46114.56312274306</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.73299766204</v>
+        <v>46181.56633099537</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.73299902778</v>
+        <v>46181.56633236111</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>221</v>
@@ -6115,11 +6115,11 @@
         <v>240</v>
       </c>
       <c r="B71" s="8">
-        <v>46112.67984715277</v>
+        <v>46112.513180486116</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.54786293981</v>
+        <v>46118.38119627315</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>241</v>
@@ -6178,11 +6178,11 @@
         <v>245</v>
       </c>
       <c r="B72" s="5">
-        <v>46112.679854120375</v>
+        <v>46112.513187453704</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.54786737269</v>
+        <v>46118.38120070602</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>213</v>
@@ -6231,11 +6231,11 @@
         <v>247</v>
       </c>
       <c r="B73" s="8">
-        <v>46112.67986081018</v>
+        <v>46112.51319414352</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.54786818287</v>
+        <v>46118.381201516204</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>248</v>
@@ -6284,11 +6284,11 @@
         <v>250</v>
       </c>
       <c r="B74" s="5">
-        <v>46112.69527582176</v>
+        <v>46112.528609155095</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.54786895833</v>
+        <v>46118.38120229167</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>251</v>
@@ -6337,11 +6337,11 @@
         <v>254</v>
       </c>
       <c r="B75" s="8">
-        <v>46112.679867326384</v>
+        <v>46112.51320065973</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46118.55096414352</v>
+        <v>46118.38429747685</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>255</v>
@@ -6384,11 +6384,11 @@
         <v>257</v>
       </c>
       <c r="B76" s="5">
-        <v>46112.67987047454</v>
+        <v>46112.513203807874</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.55096918982</v>
+        <v>46118.38430252315</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>256</v>
@@ -6445,11 +6445,11 @@
         <v>261</v>
       </c>
       <c r="B77" s="8">
-        <v>46112.6798790162</v>
+        <v>46112.51321234954</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.74446109954</v>
+        <v>46114.57779443287</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>262</v>
@@ -6492,11 +6492,11 @@
         <v>264</v>
       </c>
       <c r="B78" s="5">
-        <v>46112.6798825463</v>
+        <v>46112.51321587963</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46177.208199479166</v>
+        <v>46177.041532812495</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>265</v>
@@ -6555,11 +6555,11 @@
         <v>269</v>
       </c>
       <c r="B79" s="8">
-        <v>46112.679890740736</v>
+        <v>46112.51322407408</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46179.167811527775</v>
+        <v>46179.00114486111</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>270</v>
@@ -6618,11 +6618,11 @@
         <v>272</v>
       </c>
       <c r="B80" s="5">
-        <v>46112.679898159724</v>
+        <v>46112.51323149305</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46118.53693787037</v>
+        <v>46118.370271203705</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>273</v>
@@ -6665,11 +6665,11 @@
         <v>275</v>
       </c>
       <c r="B81" s="8">
-        <v>46112.679901701384</v>
+        <v>46112.51323503473</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46118.536602175926</v>
+        <v>46118.369935509254</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>
@@ -6728,11 +6728,11 @@
         <v>280</v>
       </c>
       <c r="B82" s="5">
-        <v>46112.67991023148</v>
+        <v>46112.51324356481</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46118.53671</v>
+        <v>46118.37004333333</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>281</v>
@@ -6791,11 +6791,11 @@
         <v>282</v>
       </c>
       <c r="B83" s="8">
-        <v>46112.679960775466</v>
+        <v>46112.513294108794</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46181.73302506944</v>
+        <v>46181.56635840278</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>213</v>
@@ -6844,11 +6844,11 @@
         <v>285</v>
       </c>
       <c r="B84" s="5">
-        <v>46112.67997252315</v>
+        <v>46112.51330585648</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46181.73302986111</v>
+        <v>46181.56636319445</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>248</v>
@@ -6897,11 +6897,11 @@
         <v>287</v>
       </c>
       <c r="B85" s="8">
-        <v>46112.683129375</v>
+        <v>46112.51646270833</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46118.53646400463</v>
+        <v>46118.36979733796</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>251</v>
@@ -6950,11 +6950,11 @@
         <v>289</v>
       </c>
       <c r="B86" s="5">
-        <v>46112.6799821875</v>
+        <v>46112.51331552083</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.53739798611</v>
+        <v>46118.370731319446</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>290</v>
@@ -7013,11 +7013,11 @@
         <v>292</v>
       </c>
       <c r="B87" s="8">
-        <v>46112.679991655095</v>
+        <v>46112.513324988424</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46181.733025787034</v>
+        <v>46181.56635912037</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>213</v>
@@ -7066,11 +7066,11 @@
         <v>295</v>
       </c>
       <c r="B88" s="5">
-        <v>46112.68000065972</v>
+        <v>46112.513333993054</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46181.73302309027</v>
+        <v>46181.56635642362</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>248</v>
@@ -7119,11 +7119,11 @@
         <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46112.68554289352</v>
+        <v>46112.51887622685</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46118.53739997685</v>
+        <v>46118.370733310185</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>252</v>
@@ -7172,11 +7172,11 @@
         <v>300</v>
       </c>
       <c r="B90" s="5">
-        <v>46112.68000929398</v>
+        <v>46112.51334262731</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.55096842593</v>
+        <v>46118.38430175926</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>301</v>
@@ -7219,11 +7219,11 @@
         <v>303</v>
       </c>
       <c r="B91" s="8">
-        <v>46112.68001403935</v>
+        <v>46112.51334737269</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.19835885416</v>
+        <v>46185.0316921875</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>304</v>
@@ -7282,11 +7282,11 @@
         <v>306</v>
       </c>
       <c r="B92" s="5">
-        <v>46112.68002373843</v>
+        <v>46112.51335707176</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46118.551773541665</v>
+        <v>46118.385106875</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>57</v>
@@ -7345,11 +7345,11 @@
         <v>308</v>
       </c>
       <c r="B93" s="8">
-        <v>46112.680037453705</v>
+        <v>46112.51337078704</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46191.89613979167</v>
+        <v>46191.729473125</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>309</v>
@@ -7408,11 +7408,11 @@
         <v>311</v>
       </c>
       <c r="B94" s="5">
-        <v>46112.680046574074</v>
+        <v>46112.51337990741</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46112.680270150464</v>
+        <v>46112.51360348379</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>312</v>
@@ -7471,11 +7471,11 @@
         <v>314</v>
       </c>
       <c r="B95" s="8">
-        <v>46112.68005998843</v>
+        <v>46112.51339332176</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46154.867740671296</v>
+        <v>46154.701074004624</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>315</v>
@@ -7534,11 +7534,11 @@
         <v>317</v>
       </c>
       <c r="B96" s="5">
-        <v>46112.68006824074</v>
+        <v>46112.51340157408</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46118.55096623843</v>
+        <v>46118.38429957176</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>318</v>
@@ -7595,11 +7595,11 @@
         <v>320</v>
       </c>
       <c r="B97" s="8">
-        <v>46112.6800780787</v>
+        <v>46112.51341141204</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46183.18919873843</v>
+        <v>46183.02253207176</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>321</v>
@@ -7658,11 +7658,11 @@
         <v>323</v>
       </c>
       <c r="B98" s="5">
-        <v>46112.68011818287</v>
+        <v>46112.513451516206</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46118.540081238425</v>
+        <v>46118.37341457176</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>324</v>
@@ -7705,11 +7705,11 @@
         <v>326</v>
       </c>
       <c r="B99" s="8">
-        <v>46112.680124363425</v>
+        <v>46112.513457696754</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46118.540939687504</v>
+        <v>46118.37427302083</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>327</v>
@@ -7768,11 +7768,11 @@
         <v>329</v>
       </c>
       <c r="B100" s="5">
-        <v>46112.68013306713</v>
+        <v>46112.51346640046</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.55096479166</v>
+        <v>46118.384298125005</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>213</v>
@@ -7821,11 +7821,11 @@
         <v>332</v>
       </c>
       <c r="B101" s="8">
-        <v>46112.680142453704</v>
+        <v>46112.51347578704</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.55096628472</v>
+        <v>46118.384299618054</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>248</v>
@@ -7874,11 +7874,11 @@
         <v>335</v>
       </c>
       <c r="B102" s="5">
-        <v>46112.68695712963</v>
+        <v>46112.52029046296</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46118.54094193287</v>
+        <v>46118.37427526621</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>252</v>
@@ -7927,11 +7927,11 @@
         <v>337</v>
       </c>
       <c r="B103" s="8">
-        <v>46112.68015230324</v>
+        <v>46112.51348563658</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.54127469908</v>
+        <v>46118.374608032405</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>338</v>
@@ -7990,11 +7990,11 @@
         <v>340</v>
       </c>
       <c r="B104" s="5">
-        <v>46112.680160613425</v>
+        <v>46112.51349394676</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46181.73302627315</v>
+        <v>46181.566359606484</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>213</v>
@@ -8043,11 +8043,11 @@
         <v>343</v>
       </c>
       <c r="B105" s="8">
-        <v>46112.68017212963</v>
+        <v>46112.513505462965</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46181.73302378472</v>
+        <v>46181.566357118056</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>248</v>
@@ -8096,11 +8096,11 @@
         <v>346</v>
       </c>
       <c r="B106" s="5">
-        <v>46112.68780918981</v>
+        <v>46112.52114252315</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.541276550925</v>
+        <v>46118.37460988426</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>252</v>
@@ -8149,11 +8149,11 @@
         <v>348</v>
       </c>
       <c r="B107" s="8">
-        <v>46112.68018260416</v>
+        <v>46112.5135159375</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.54145512731</v>
+        <v>46118.37478846065</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>349</v>
@@ -8212,11 +8212,11 @@
         <v>350</v>
       </c>
       <c r="B108" s="5">
-        <v>46112.680190486106</v>
+        <v>46112.51352381945</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46181.73302827546</v>
+        <v>46181.5663616088</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>213</v>
@@ -8265,11 +8265,11 @@
         <v>353</v>
       </c>
       <c r="B109" s="8">
-        <v>46112.68020174769</v>
+        <v>46112.513535081016</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46181.73302706018</v>
+        <v>46181.56636039352</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>248</v>
@@ -8318,11 +8318,11 @@
         <v>356</v>
       </c>
       <c r="B110" s="5">
-        <v>46112.68889696759</v>
+        <v>46112.52223030092</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46118.541456273146</v>
+        <v>46118.37478960648</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>252</v>
@@ -8371,11 +8371,11 @@
         <v>358</v>
       </c>
       <c r="B111" s="8">
-        <v>46112.6802131713</v>
+        <v>46112.51354650463</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46118.54159421296</v>
+        <v>46118.3749275463</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>359</v>
@@ -8434,11 +8434,11 @@
         <v>360</v>
       </c>
       <c r="B112" s="5">
-        <v>46112.680221111106</v>
+        <v>46112.51355444445</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46181.73302760417</v>
+        <v>46181.566360937504</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>213</v>
@@ -8487,11 +8487,11 @@
         <v>362</v>
       </c>
       <c r="B113" s="8">
-        <v>46112.68023248843</v>
+        <v>46112.51356582176</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46181.733028946765</v>
+        <v>46181.56636228009</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>248</v>
@@ -8540,11 +8540,11 @@
         <v>364</v>
       </c>
       <c r="B114" s="5">
-        <v>46112.69112122685</v>
+        <v>46112.52445456019</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46118.54159666666</v>
+        <v>46118.374930000005</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>251</v>
@@ -8593,11 +8593,11 @@
         <v>366</v>
       </c>
       <c r="B115" s="8">
-        <v>46112.68024403935</v>
+        <v>46112.51357737269</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46118.54175984954</v>
+        <v>46118.37509318287</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>367</v>
@@ -8656,11 +8656,11 @@
         <v>368</v>
       </c>
       <c r="B116" s="5">
-        <v>46112.68025228009</v>
+        <v>46112.51358561343</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46181.73302450232</v>
+        <v>46181.56635783565</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>213</v>
@@ -8709,11 +8709,11 @@
         <v>371</v>
       </c>
       <c r="B117" s="8">
-        <v>46112.68026435185</v>
+        <v>46112.51359768519</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46181.733029490744</v>
+        <v>46181.56636282407</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>248</v>
@@ -8762,11 +8762,11 @@
         <v>374</v>
       </c>
       <c r="B118" s="5">
-        <v>46112.69281496528</v>
+        <v>46112.52614829861</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46118.5417528588</v>
+        <v>46118.37508619213</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>252</v>
@@ -8815,11 +8815,11 @@
         <v>376</v>
       </c>
       <c r="B119" s="8">
-        <v>46112.680315000005</v>
+        <v>46112.51364833333</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46118.54187865741</v>
+        <v>46118.375211990744</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>377</v>
@@ -8878,11 +8878,11 @@
         <v>378</v>
       </c>
       <c r="B120" s="5">
-        <v>46112.68032652778</v>
+        <v>46112.51365986111</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46118.54187940972</v>
+        <v>46118.375212743056</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>213</v>
@@ -8929,11 +8929,11 @@
         <v>380</v>
       </c>
       <c r="B121" s="8">
-        <v>46112.68033607639</v>
+        <v>46112.513669409724</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46118.54188027778</v>
+        <v>46118.375213611114</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>248</v>
@@ -8980,11 +8980,11 @@
         <v>382</v>
       </c>
       <c r="B122" s="5">
-        <v>46112.69375358796</v>
+        <v>46112.5270869213</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46118.54188105324</v>
+        <v>46118.37521438657</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>252</v>
@@ -9031,11 +9031,11 @@
         <v>384</v>
       </c>
       <c r="B123" s="8">
-        <v>46112.68034494213</v>
+        <v>46112.51367827546</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46118.54200872685</v>
+        <v>46118.375342060186</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>385</v>
@@ -9092,11 +9092,11 @@
         <v>386</v>
       </c>
       <c r="B124" s="5">
-        <v>46112.680353344906</v>
+        <v>46112.51368667824</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46118.547864548615</v>
+        <v>46118.38119788194</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>213</v>
@@ -9143,11 +9143,11 @@
         <v>388</v>
       </c>
       <c r="B125" s="8">
-        <v>46112.6803614699</v>
+        <v>46112.513694803245</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46118.5478628125</v>
+        <v>46118.381196145834</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>248</v>
@@ -9194,11 +9194,11 @@
         <v>390</v>
       </c>
       <c r="B126" s="5">
-        <v>46112.69493020834</v>
+        <v>46112.528263541666</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46118.54786351851</v>
+        <v>46118.38119685186</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>252</v>
@@ -9245,11 +9245,11 @@
         <v>392</v>
       </c>
       <c r="B127" s="8">
-        <v>46112.68036949074</v>
+        <v>46112.51370282407</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46118.542785694444</v>
+        <v>46118.37611902777</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>393</v>
@@ -9292,11 +9292,11 @@
         <v>395</v>
       </c>
       <c r="B128" s="5">
-        <v>46112.68037429398</v>
+        <v>46112.51370762731</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46118.542359756946</v>
+        <v>46118.375693090275</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>396</v>
@@ -9355,11 +9355,11 @@
         <v>400</v>
       </c>
       <c r="B129" s="8">
-        <v>46112.68038334491</v>
+        <v>46112.51371667824</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46118.54236040509</v>
+        <v>46118.375693738424</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>213</v>
@@ -9406,11 +9406,11 @@
         <v>402</v>
       </c>
       <c r="B130" s="5">
-        <v>46112.68039121528</v>
+        <v>46112.51372454861</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46118.54236118056</v>
+        <v>46118.37569451389</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>248</v>
@@ -9457,11 +9457,11 @@
         <v>404</v>
       </c>
       <c r="B131" s="8">
-        <v>46112.69787394676</v>
+        <v>46112.53120728009</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46118.542362002314</v>
+        <v>46118.37569533565</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>251</v>
@@ -9508,11 +9508,11 @@
         <v>406</v>
       </c>
       <c r="B132" s="5">
-        <v>46112.6803999074</v>
+        <v>46112.51373324074</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46118.542362858796</v>
+        <v>46118.37569619213</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>56</v>
@@ -9559,11 +9559,11 @@
         <v>408</v>
       </c>
       <c r="B133" s="8">
-        <v>46112.68041137731</v>
+        <v>46112.51374471065</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46118.54236363426</v>
+        <v>46118.37569696759</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>60</v>
@@ -9610,11 +9610,11 @@
         <v>410</v>
       </c>
       <c r="B134" s="5">
-        <v>46112.680419027776</v>
+        <v>46112.51375236111</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46118.54236440972</v>
+        <v>46118.37569774306</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>63</v>
@@ -9661,11 +9661,11 @@
         <v>412</v>
       </c>
       <c r="B135" s="8">
-        <v>46112.68042700231</v>
+        <v>46112.51376033565</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46118.54236519676</v>
+        <v>46118.37569853009</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>66</v>
@@ -9712,11 +9712,11 @@
         <v>414</v>
       </c>
       <c r="B136" s="5">
-        <v>46112.68043466435</v>
+        <v>46112.51376799769</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46118.542365960646</v>
+        <v>46118.37569929398</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>322</v>
@@ -9763,11 +9763,11 @@
         <v>416</v>
       </c>
       <c r="B137" s="8">
-        <v>46112.68044216435</v>
+        <v>46112.51377549769</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46118.54325362269</v>
+        <v>46118.376586956016</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>417</v>
@@ -9826,11 +9826,11 @@
         <v>420</v>
       </c>
       <c r="B138" s="5">
-        <v>46112.68045020833</v>
+        <v>46112.51378354167</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46118.54309255787</v>
+        <v>46118.376425891205</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>213</v>
@@ -9879,11 +9879,11 @@
         <v>422</v>
       </c>
       <c r="B139" s="8">
-        <v>46112.680457615745</v>
+        <v>46112.51379094907</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46118.54309331019</v>
+        <v>46118.37642664352</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>248</v>
@@ -9932,11 +9932,11 @@
         <v>424</v>
       </c>
       <c r="B140" s="5">
-        <v>46112.699333854165</v>
+        <v>46112.5326671875</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46118.54314091435</v>
+        <v>46118.376474247685</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>252</v>
@@ -9985,11 +9985,11 @@
         <v>426</v>
       </c>
       <c r="B141" s="8">
-        <v>46112.68046530093</v>
+        <v>46112.51379863426</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46118.54309490741</v>
+        <v>46118.376428240736</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>56</v>
@@ -10038,11 +10038,11 @@
         <v>428</v>
       </c>
       <c r="B142" s="5">
-        <v>46112.6804727662</v>
+        <v>46112.51380609954</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46118.54309578704</v>
+        <v>46118.37642912037</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>60</v>
@@ -10091,11 +10091,11 @@
         <v>430</v>
       </c>
       <c r="B143" s="8">
-        <v>46112.680524282405</v>
+        <v>46112.51385761574</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46118.54309662037</v>
+        <v>46118.3764299537</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>63</v>
@@ -10144,11 +10144,11 @@
         <v>432</v>
       </c>
       <c r="B144" s="5">
-        <v>46112.68053547454</v>
+        <v>46112.51386880787</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46118.54309747685</v>
+        <v>46118.37643081018</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10197,11 +10197,11 @@
         <v>434</v>
       </c>
       <c r="B145" s="8">
-        <v>46112.68054428241</v>
+        <v>46112.51387761574</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46118.54309846065</v>
+        <v>46118.37643179398</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>435</v>
@@ -10250,11 +10250,11 @@
         <v>437</v>
       </c>
       <c r="B146" s="5">
-        <v>46112.68055275463</v>
+        <v>46112.51388608797</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46118.54357326389</v>
+        <v>46118.37690659722</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>438</v>
@@ -10311,11 +10311,11 @@
         <v>440</v>
       </c>
       <c r="B147" s="8">
-        <v>46112.68056386574</v>
+        <v>46112.513897199075</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46118.543572766204</v>
+        <v>46118.37690609954</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>213</v>
@@ -10364,11 +10364,11 @@
         <v>442</v>
       </c>
       <c r="B148" s="5">
-        <v>46112.68057167824</v>
+        <v>46112.513905011576</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46118.543573414354</v>
+        <v>46118.37690674768</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>248</v>
@@ -10417,11 +10417,11 @@
         <v>444</v>
       </c>
       <c r="B149" s="8">
-        <v>46112.70035509259</v>
+        <v>46112.53368842593</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46118.60507034722</v>
+        <v>46118.43840368056</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>252</v>
@@ -10470,11 +10470,11 @@
         <v>445</v>
       </c>
       <c r="B150" s="5">
-        <v>46112.680579479165</v>
+        <v>46112.5139128125</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46118.5435747338</v>
+        <v>46118.37690806713</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>56</v>
@@ -10523,11 +10523,11 @@
         <v>447</v>
       </c>
       <c r="B151" s="8">
-        <v>46112.68058722222</v>
+        <v>46112.51392055556</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46118.54357537037</v>
+        <v>46118.37690870371</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10576,11 +10576,11 @@
         <v>449</v>
       </c>
       <c r="B152" s="5">
-        <v>46112.68059523148</v>
+        <v>46112.51392856482</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46118.54357599537</v>
+        <v>46118.376909328705</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10629,11 +10629,11 @@
         <v>451</v>
       </c>
       <c r="B153" s="8">
-        <v>46112.680603472225</v>
+        <v>46112.51393680555</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46118.5435766088</v>
+        <v>46118.37690994213</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10682,11 +10682,11 @@
         <v>453</v>
       </c>
       <c r="B154" s="5">
-        <v>46112.68061105324</v>
+        <v>46112.51394438658</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46118.543577268516</v>
+        <v>46118.37691060185</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>454</v>
@@ -10735,11 +10735,11 @@
         <v>456</v>
       </c>
       <c r="B155" s="8">
-        <v>46112.680618784725</v>
+        <v>46112.51395211805</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46118.54392340277</v>
+        <v>46118.377256736116</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>457</v>
@@ -10798,11 +10798,11 @@
         <v>460</v>
       </c>
       <c r="B156" s="5">
-        <v>46112.680633553246</v>
+        <v>46112.513966886574</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46118.543845196764</v>
+        <v>46118.37717853009</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>213</v>
@@ -10851,11 +10851,11 @@
         <v>462</v>
       </c>
       <c r="B157" s="8">
-        <v>46112.68064251158</v>
+        <v>46112.51397584491</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46118.543846030094</v>
+        <v>46118.37717936342</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>248</v>
@@ -10904,11 +10904,11 @@
         <v>463</v>
       </c>
       <c r="B158" s="5">
-        <v>46112.68071581019</v>
+        <v>46112.514049143516</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46118.543850752314</v>
+        <v>46118.37718408565</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>435</v>
@@ -10957,11 +10957,11 @@
         <v>464</v>
       </c>
       <c r="B159" s="8">
-        <v>46112.739142986116</v>
+        <v>46112.572476319445</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46118.543852002316</v>
+        <v>46118.377185335645</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>252</v>
@@ -11010,11 +11010,11 @@
         <v>465</v>
       </c>
       <c r="B160" s="5">
-        <v>46112.68065008102</v>
+        <v>46112.51398341435</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46118.5438528125</v>
+        <v>46118.37718614584</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>56</v>
@@ -11063,11 +11063,11 @@
         <v>466</v>
       </c>
       <c r="B161" s="8">
-        <v>46112.680657476856</v>
+        <v>46112.513990810185</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46118.54385362269</v>
+        <v>46118.377186956015</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>60</v>
@@ -11116,11 +11116,11 @@
         <v>467</v>
       </c>
       <c r="B162" s="5">
-        <v>46112.68069804399</v>
+        <v>46112.514031377315</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46118.54385447917</v>
+        <v>46118.3771878125</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>66</v>
@@ -11169,11 +11169,11 @@
         <v>468</v>
       </c>
       <c r="B163" s="8">
-        <v>46112.68070748843</v>
+        <v>46112.514040821756</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46118.54385528935</v>
+        <v>46118.37718862269</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>63</v>
@@ -11222,11 +11222,11 @@
         <v>469</v>
       </c>
       <c r="B164" s="5">
-        <v>46112.68072377315</v>
+        <v>46112.514057106484</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46118.54278521991</v>
+        <v>46118.37611855324</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>470</v>
@@ -11269,11 +11269,11 @@
         <v>472</v>
       </c>
       <c r="B165" s="8">
-        <v>46112.680728148145</v>
+        <v>46112.51406148148</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46118.54402055556</v>
+        <v>46118.37735388889</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>473</v>
@@ -11332,11 +11332,11 @@
         <v>476</v>
       </c>
       <c r="B166" s="5">
-        <v>46112.68073732639</v>
+        <v>46112.51407065972</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46118.54410575231</v>
+        <v>46118.37743908565</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>477</v>
@@ -11395,11 +11395,11 @@
         <v>479</v>
       </c>
       <c r="B167" s="8">
-        <v>46112.68074700232</v>
+        <v>46112.51408033565</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46118.54278521991</v>
+        <v>46118.37611855324</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>480</v>
@@ -11444,11 +11444,11 @@
         <v>482</v>
       </c>
       <c r="B168" s="5">
-        <v>46112.68075140046</v>
+        <v>46112.5140847338</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46118.54421137732</v>
+        <v>46118.377544710645</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>483</v>
@@ -11507,11 +11507,11 @@
         <v>485</v>
       </c>
       <c r="B169" s="8">
-        <v>46112.68075989583</v>
+        <v>46112.51409322917</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46118.544324525465</v>
+        <v>46118.3776578588</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>486</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -2098,13 +2098,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46112.51244319444</v>
+        <v>46112.679109861114</v>
       </c>
       <c r="C4" s="5">
-        <v>46112.51244314815</v>
+        <v>46112.67910981481</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.51823255787</v>
+        <v>46112.684899224536</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2147,13 +2147,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46112.51257668981</v>
+        <v>46112.679243356484</v>
       </c>
       <c r="C5" s="8">
-        <v>46112.51257664352</v>
+        <v>46112.67924331018</v>
       </c>
       <c r="D5" s="8">
-        <v>46112.5127128125</v>
+        <v>46112.67937947917</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2210,13 +2210,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46112.51258456019</v>
+        <v>46112.67925122685</v>
       </c>
       <c r="C6" s="5">
-        <v>46112.512584537035</v>
+        <v>46112.67925120371</v>
       </c>
       <c r="D6" s="5">
-        <v>46112.51271390046</v>
+        <v>46112.67938056713</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2273,13 +2273,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8">
-        <v>46112.512590729166</v>
+        <v>46112.67925739584</v>
       </c>
       <c r="C7" s="8">
-        <v>46112.512590706014</v>
+        <v>46112.679257372685</v>
       </c>
       <c r="D7" s="8">
-        <v>46112.512714641205</v>
+        <v>46112.67938130787</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>36</v>
@@ -2336,13 +2336,13 @@
         <v>37</v>
       </c>
       <c r="B8" s="5">
-        <v>46112.512596782406</v>
+        <v>46112.67926344907</v>
       </c>
       <c r="C8" s="5">
-        <v>46112.51259677083</v>
+        <v>46112.6792634375</v>
       </c>
       <c r="D8" s="5">
-        <v>46112.51271540509</v>
+        <v>46112.67938207176</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>38</v>
@@ -2399,13 +2399,13 @@
         <v>40</v>
       </c>
       <c r="B9" s="8">
-        <v>46112.51260584491</v>
+        <v>46112.679272511574</v>
       </c>
       <c r="C9" s="8">
-        <v>46112.51260582176</v>
+        <v>46112.67927248843</v>
       </c>
       <c r="D9" s="8">
-        <v>46112.51271681713</v>
+        <v>46112.679383483795</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>41</v>
@@ -2462,11 +2462,11 @@
         <v>42</v>
       </c>
       <c r="B10" s="5">
-        <v>46112.512449305555</v>
+        <v>46112.67911597222</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46134.72790445602</v>
+        <v>46134.894571122684</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>43</v>
@@ -2509,13 +2509,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="8">
-        <v>46112.51261770833</v>
+        <v>46112.679284375</v>
       </c>
       <c r="C11" s="8">
-        <v>46134.727895069445</v>
+        <v>46134.89456173611</v>
       </c>
       <c r="D11" s="8">
-        <v>46134.72791310185</v>
+        <v>46134.894579768516</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>46</v>
@@ -2574,11 +2574,11 @@
         <v>50</v>
       </c>
       <c r="B12" s="5">
-        <v>46112.51262674769</v>
+        <v>46112.67929341435</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46112.51271876157</v>
+        <v>46112.679385428244</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2637,11 +2637,11 @@
         <v>55</v>
       </c>
       <c r="B13" s="8">
-        <v>46112.51263542824</v>
+        <v>46112.67930209491</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46112.57621241898</v>
+        <v>46112.74287908565</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2690,11 +2690,11 @@
         <v>59</v>
       </c>
       <c r="B14" s="5">
-        <v>46112.51264354167</v>
+        <v>46112.67931020833</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46112.576934282406</v>
+        <v>46112.74360094908</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2743,11 +2743,11 @@
         <v>62</v>
       </c>
       <c r="B15" s="8">
-        <v>46112.51265068287</v>
+        <v>46112.67931734954</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46112.57731502315</v>
+        <v>46112.74398168981</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2796,11 +2796,11 @@
         <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46112.512658182866</v>
+        <v>46112.67932484954</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46112.577250497685</v>
+        <v>46112.74391716435</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -2849,13 +2849,13 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46112.5124543287</v>
+        <v>46112.679120995366</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.576852453705</v>
+        <v>46114.74351912037</v>
       </c>
       <c r="D17" s="8">
-        <v>46118.382188020834</v>
+        <v>46118.5488546875</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>69</v>
@@ -2900,13 +2900,13 @@
         <v>71</v>
       </c>
       <c r="B18" s="5">
-        <v>46112.51266609954</v>
+        <v>46112.6793327662</v>
       </c>
       <c r="C18" s="5">
-        <v>46113.64149030093</v>
+        <v>46113.80815696759</v>
       </c>
       <c r="D18" s="5">
-        <v>46113.97976787037</v>
+        <v>46114.14643453703</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>72</v>
@@ -2965,13 +2965,13 @@
         <v>74</v>
       </c>
       <c r="B19" s="8">
-        <v>46112.51267491898</v>
+        <v>46112.67934158565</v>
       </c>
       <c r="C19" s="8">
-        <v>46113.64152197917</v>
+        <v>46113.80818864584</v>
       </c>
       <c r="D19" s="8">
-        <v>46121.001939525464</v>
+        <v>46121.16860619213</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>75</v>
@@ -3030,13 +3030,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="5">
-        <v>46112.512683865745</v>
+        <v>46112.6793505324</v>
       </c>
       <c r="C20" s="5">
-        <v>46113.64158159722</v>
+        <v>46113.808248263886</v>
       </c>
       <c r="D20" s="5">
-        <v>46121.00193938657</v>
+        <v>46121.16860605324</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -3095,13 +3095,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46112.51269375</v>
+        <v>46112.67936041667</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.5768353125</v>
+        <v>46114.74350197917</v>
       </c>
       <c r="D21" s="8">
-        <v>46121.00193940972</v>
+        <v>46121.16860607639</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3160,13 +3160,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46112.5127040625</v>
+        <v>46112.679370729165</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.641615659726</v>
+        <v>46113.80828232639</v>
       </c>
       <c r="D22" s="5">
-        <v>46121.00193939815</v>
+        <v>46121.16860606481</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3225,11 +3225,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46112.51246052083</v>
+        <v>46112.6791271875</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46135.378926053236</v>
+        <v>46135.54559271991</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3274,13 +3274,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46112.51275108797</v>
+        <v>46112.679417754625</v>
       </c>
       <c r="C24" s="5">
-        <v>46113.64167752315</v>
+        <v>46113.80834418982</v>
       </c>
       <c r="D24" s="5">
-        <v>46115.97324016204</v>
+        <v>46116.1399068287</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3339,13 +3339,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46112.512763437495</v>
+        <v>46112.67943010417</v>
       </c>
       <c r="C25" s="8">
-        <v>46113.641691261575</v>
+        <v>46113.80835792824</v>
       </c>
       <c r="D25" s="8">
-        <v>46123.01996149306</v>
+        <v>46123.18662815972</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3404,13 +3404,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46112.5127737963</v>
+        <v>46112.67944046296</v>
       </c>
       <c r="C26" s="5">
-        <v>46113.64171145833</v>
+        <v>46113.808378125</v>
       </c>
       <c r="D26" s="5">
-        <v>46123.01996138888</v>
+        <v>46123.186628055555</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3469,13 +3469,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46112.51278568287</v>
+        <v>46112.679452349534</v>
       </c>
       <c r="C27" s="8">
-        <v>46135.3789077199</v>
+        <v>46135.545574386575</v>
       </c>
       <c r="D27" s="8">
-        <v>46135.3791616088</v>
+        <v>46135.54582827546</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3534,11 +3534,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46112.51279622685</v>
+        <v>46112.67946289352</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46196.48754457176</v>
+        <v>46196.65421123843</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3597,13 +3597,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46112.512811469904</v>
+        <v>46112.679478136575</v>
       </c>
       <c r="C29" s="8">
-        <v>46113.64174697916</v>
+        <v>46113.808413645835</v>
       </c>
       <c r="D29" s="8">
-        <v>46123.01996229167</v>
+        <v>46123.186628958334</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3662,11 +3662,11 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46112.512821365744</v>
+        <v>46112.67948803241</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.034363831015</v>
+        <v>46193.20103049769</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3725,13 +3725,13 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46112.51283033565</v>
+        <v>46112.67949700232</v>
       </c>
       <c r="C31" s="8">
-        <v>46113.64180048611</v>
+        <v>46113.808467152776</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.019961516206</v>
+        <v>46123.18662818287</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>
@@ -3790,11 +3790,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46112.512468402776</v>
+        <v>46112.67913506944</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46191.729476736116</v>
+        <v>46191.89614340277</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3837,13 +3837,13 @@
         <v>122</v>
       </c>
       <c r="B33" s="8">
-        <v>46112.51283943287</v>
+        <v>46112.679506099536</v>
       </c>
       <c r="C33" s="8">
-        <v>46191.72946829861</v>
+        <v>46191.89613496528</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.729488020836</v>
+        <v>46191.8961546875</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>123</v>
@@ -3902,13 +3902,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46112.51284900463</v>
+        <v>46112.6795156713</v>
       </c>
       <c r="C34" s="5">
-        <v>46182.51181258102</v>
+        <v>46182.67847924768</v>
       </c>
       <c r="D34" s="5">
-        <v>46182.51181427084</v>
+        <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3967,13 +3967,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46112.51285855324</v>
+        <v>46112.67952521991</v>
       </c>
       <c r="C35" s="8">
-        <v>46191.72945321759</v>
+        <v>46191.89611988426</v>
       </c>
       <c r="D35" s="8">
-        <v>46191.729455127315</v>
+        <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -4032,11 +4032,11 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46112.512867812504</v>
+        <v>46112.67953447917</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46196.4683156713</v>
+        <v>46196.634982337964</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4095,13 +4095,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46112.51287643518</v>
+        <v>46112.679543101855</v>
       </c>
       <c r="C37" s="8">
-        <v>46195.51608274305</v>
+        <v>46195.68274940972</v>
       </c>
       <c r="D37" s="8">
-        <v>46195.51608508102</v>
+        <v>46195.682751747685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -4160,11 +4160,11 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46112.51288542824</v>
+        <v>46112.67955209491</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.544331365745</v>
+        <v>46195.7109980324</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -4221,11 +4221,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46112.512938252316</v>
+        <v>46112.67960491898</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.54917237269</v>
+        <v>46195.71583903935</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4284,13 +4284,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46112.51294784722</v>
+        <v>46112.679614513894</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.5115599537</v>
+        <v>46182.678226620366</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.511561238425</v>
+        <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4349,11 +4349,11 @@
         <v>148</v>
       </c>
       <c r="B41" s="8">
-        <v>46112.51295690972</v>
+        <v>46112.67962357639</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46195.54948914352</v>
+        <v>46195.71615581018</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -4412,11 +4412,11 @@
         <v>151</v>
       </c>
       <c r="B42" s="5">
-        <v>46112.51296591436</v>
+        <v>46112.679632581014</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.51145549769</v>
+        <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>152</v>
@@ -4475,13 +4475,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="8">
-        <v>46112.5129746875</v>
+        <v>46112.67964135417</v>
       </c>
       <c r="C43" s="8">
-        <v>46182.511448171295</v>
+        <v>46182.67811483797</v>
       </c>
       <c r="D43" s="8">
-        <v>46182.51145045139</v>
+        <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>155</v>
@@ -4540,11 +4540,11 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46112.512987187496</v>
+        <v>46112.67965385417</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.556836435186</v>
+        <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -4603,13 +4603,13 @@
         <v>160</v>
       </c>
       <c r="B45" s="8">
-        <v>46112.51299570602</v>
+        <v>46112.679662372684</v>
       </c>
       <c r="C45" s="8">
-        <v>46155.726274988425</v>
+        <v>46155.8929416551</v>
       </c>
       <c r="D45" s="8">
-        <v>46182.51145737269</v>
+        <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>161</v>
@@ -4668,11 +4668,11 @@
         <v>163</v>
       </c>
       <c r="B46" s="5">
-        <v>46112.51300423611</v>
+        <v>46112.67967090278</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46203.00916527778</v>
+        <v>46203.17583194445</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -4731,11 +4731,11 @@
         <v>169</v>
       </c>
       <c r="B47" s="8">
-        <v>46112.51301306713</v>
+        <v>46112.679679733796</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46199.00198188657</v>
+        <v>46199.16864855324</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>109</v>
@@ -4794,11 +4794,11 @@
         <v>171</v>
       </c>
       <c r="B48" s="5">
-        <v>46112.51302189815</v>
+        <v>46112.679688564815</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.69023289352</v>
+        <v>46169.85689956018</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4857,13 +4857,13 @@
         <v>174</v>
       </c>
       <c r="B49" s="8">
-        <v>46112.51303165509</v>
+        <v>46112.679698321765</v>
       </c>
       <c r="C49" s="8">
-        <v>46154.70106975695</v>
+        <v>46154.86773642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.70108104167</v>
+        <v>46154.86774770833</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -4922,13 +4922,13 @@
         <v>177</v>
       </c>
       <c r="B50" s="5">
-        <v>46112.51303997685</v>
+        <v>46112.67970664352</v>
       </c>
       <c r="C50" s="5">
-        <v>46154.70082611111</v>
+        <v>46154.867492777776</v>
       </c>
       <c r="D50" s="5">
-        <v>46154.70082777778</v>
+        <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>178</v>
@@ -4977,13 +4977,13 @@
         <v>180</v>
       </c>
       <c r="B51" s="8">
-        <v>46112.51304803241</v>
+        <v>46112.67971469907</v>
       </c>
       <c r="C51" s="8">
-        <v>46154.7010562963</v>
+        <v>46154.86772296297</v>
       </c>
       <c r="D51" s="8">
-        <v>46154.701057638886</v>
+        <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>181</v>
@@ -5032,11 +5032,11 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46112.51305577546</v>
+        <v>46112.67972244213</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46181.566355358795</v>
+        <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5095,11 +5095,11 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46112.51306508102</v>
+        <v>46112.67973174769</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46199.00203725694</v>
+        <v>46199.16870392361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>116</v>
@@ -5154,11 +5154,11 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46112.513109594904</v>
+        <v>46112.679776261575</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46181.566355902774</v>
+        <v>46181.733022569446</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -5207,13 +5207,13 @@
         <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46112.51312052083</v>
+        <v>46112.6797871875</v>
       </c>
       <c r="C55" s="8">
-        <v>46182.52637825231</v>
+        <v>46182.69304491898</v>
       </c>
       <c r="D55" s="8">
-        <v>46182.526389363426</v>
+        <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>195</v>
@@ -5272,13 +5272,13 @@
         <v>197</v>
       </c>
       <c r="B56" s="5">
-        <v>46112.51312832176</v>
+        <v>46112.67979498843</v>
       </c>
       <c r="C56" s="5">
-        <v>46182.50735290509</v>
+        <v>46182.67401957176</v>
       </c>
       <c r="D56" s="5">
-        <v>46182.50735489583</v>
+        <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>198</v>
@@ -5327,13 +5327,13 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46112.51313431713</v>
+        <v>46112.679800983795</v>
       </c>
       <c r="C57" s="8">
-        <v>46182.52636532407</v>
+        <v>46182.69303199074</v>
       </c>
       <c r="D57" s="8">
-        <v>46182.526366875</v>
+        <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5382,11 +5382,11 @@
         <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46112.51314059028</v>
+        <v>46112.67980725694</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46162.4768471412</v>
+        <v>46162.64351380787</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>204</v>
@@ -5431,13 +5431,13 @@
         <v>206</v>
       </c>
       <c r="B59" s="8">
-        <v>46112.51314456019</v>
+        <v>46112.67981122685</v>
       </c>
       <c r="C59" s="8">
-        <v>46155.38365375</v>
+        <v>46155.55032041667</v>
       </c>
       <c r="D59" s="8">
-        <v>46155.38366818287</v>
+        <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>207</v>
@@ -5496,13 +5496,13 @@
         <v>212</v>
       </c>
       <c r="B60" s="5">
-        <v>46114.55900234954</v>
+        <v>46114.7256690162</v>
       </c>
       <c r="C60" s="5">
-        <v>46155.38283228009</v>
+        <v>46155.549498946755</v>
       </c>
       <c r="D60" s="5">
-        <v>46157.76145039352</v>
+        <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5551,13 +5551,13 @@
         <v>217</v>
       </c>
       <c r="B61" s="8">
-        <v>46114.55919216435</v>
+        <v>46114.72585883102</v>
       </c>
       <c r="C61" s="8">
-        <v>46155.38284497685</v>
+        <v>46155.54951164352</v>
       </c>
       <c r="D61" s="8">
-        <v>46157.763175127315</v>
+        <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>218</v>
@@ -5606,13 +5606,13 @@
         <v>220</v>
       </c>
       <c r="B62" s="5">
-        <v>46114.559363113425</v>
+        <v>46114.7260297801</v>
       </c>
       <c r="C62" s="5">
-        <v>46155.38290252315</v>
+        <v>46155.54956918981</v>
       </c>
       <c r="D62" s="5">
-        <v>46155.38290398148</v>
+        <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>221</v>
@@ -5661,13 +5661,13 @@
         <v>223</v>
       </c>
       <c r="B63" s="8">
-        <v>46112.513158518515</v>
+        <v>46112.67982518519</v>
       </c>
       <c r="C63" s="8">
-        <v>46162.47682798612</v>
+        <v>46162.64349465277</v>
       </c>
       <c r="D63" s="8">
-        <v>46190.01081091435</v>
+        <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>224</v>
@@ -5726,13 +5726,13 @@
         <v>226</v>
       </c>
       <c r="B64" s="5">
-        <v>46114.56278202546</v>
+        <v>46114.72944869213</v>
       </c>
       <c r="C64" s="5">
-        <v>46162.47679596065</v>
+        <v>46162.64346262731</v>
       </c>
       <c r="D64" s="5">
-        <v>46162.47679793982</v>
+        <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>213</v>
@@ -5781,13 +5781,13 @@
         <v>229</v>
       </c>
       <c r="B65" s="8">
-        <v>46114.56284165509</v>
+        <v>46114.72950832176</v>
       </c>
       <c r="C65" s="8">
-        <v>46162.4768038426</v>
+        <v>46162.643470509254</v>
       </c>
       <c r="D65" s="8">
-        <v>46162.47680546297</v>
+        <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>218</v>
@@ -5836,13 +5836,13 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46114.56289835648</v>
+        <v>46114.72956502315</v>
       </c>
       <c r="C66" s="5">
-        <v>46162.47681384259</v>
+        <v>46162.64348050926</v>
       </c>
       <c r="D66" s="5">
-        <v>46162.47681508102</v>
+        <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>221</v>
@@ -5891,13 +5891,13 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46112.513167129626</v>
+        <v>46112.6798337963</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.566344293984</v>
+        <v>46181.73301096065</v>
       </c>
       <c r="D67" s="8">
-        <v>46191.034497291665</v>
+        <v>46191.201163958336</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>108</v>
@@ -5956,13 +5956,13 @@
         <v>237</v>
       </c>
       <c r="B68" s="5">
-        <v>46114.562975381945</v>
+        <v>46114.72964204861</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.56631296297</v>
+        <v>46181.732979629625</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.56631502315</v>
+        <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>213</v>
@@ -6009,13 +6009,13 @@
         <v>238</v>
       </c>
       <c r="B69" s="8">
-        <v>46114.56307118056</v>
+        <v>46114.72973784722</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.566322303246</v>
+        <v>46181.7329889699</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.56632388889</v>
+        <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>218</v>
@@ -6062,13 +6062,13 @@
         <v>239</v>
       </c>
       <c r="B70" s="5">
-        <v>46114.56312274306</v>
+        <v>46114.72978940972</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.56633099537</v>
+        <v>46181.73299766204</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.56633236111</v>
+        <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>221</v>
@@ -6115,11 +6115,11 @@
         <v>240</v>
       </c>
       <c r="B71" s="8">
-        <v>46112.513180486116</v>
+        <v>46112.67984715277</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.38119627315</v>
+        <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>241</v>
@@ -6178,11 +6178,11 @@
         <v>245</v>
       </c>
       <c r="B72" s="5">
-        <v>46112.513187453704</v>
+        <v>46112.679854120375</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46118.38120070602</v>
+        <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>213</v>
@@ -6231,11 +6231,11 @@
         <v>247</v>
       </c>
       <c r="B73" s="8">
-        <v>46112.51319414352</v>
+        <v>46112.67986081018</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46118.381201516204</v>
+        <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>248</v>
@@ -6284,11 +6284,11 @@
         <v>250</v>
       </c>
       <c r="B74" s="5">
-        <v>46112.528609155095</v>
+        <v>46112.69527582176</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46118.38120229167</v>
+        <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>251</v>
@@ -6337,11 +6337,11 @@
         <v>254</v>
       </c>
       <c r="B75" s="8">
-        <v>46112.51320065973</v>
+        <v>46112.679867326384</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46118.38429747685</v>
+        <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>255</v>
@@ -6384,11 +6384,11 @@
         <v>257</v>
       </c>
       <c r="B76" s="5">
-        <v>46112.513203807874</v>
+        <v>46112.67987047454</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.38430252315</v>
+        <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>256</v>
@@ -6445,11 +6445,11 @@
         <v>261</v>
       </c>
       <c r="B77" s="8">
-        <v>46112.51321234954</v>
+        <v>46112.6798790162</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.57779443287</v>
+        <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>262</v>
@@ -6492,11 +6492,11 @@
         <v>264</v>
       </c>
       <c r="B78" s="5">
-        <v>46112.51321587963</v>
+        <v>46112.6798825463</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46177.041532812495</v>
+        <v>46177.208199479166</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>265</v>
@@ -6555,11 +6555,11 @@
         <v>269</v>
       </c>
       <c r="B79" s="8">
-        <v>46112.51322407408</v>
+        <v>46112.679890740736</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46179.00114486111</v>
+        <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>270</v>
@@ -6618,11 +6618,11 @@
         <v>272</v>
       </c>
       <c r="B80" s="5">
-        <v>46112.51323149305</v>
+        <v>46112.679898159724</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46118.370271203705</v>
+        <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>273</v>
@@ -6665,11 +6665,11 @@
         <v>275</v>
       </c>
       <c r="B81" s="8">
-        <v>46112.51323503473</v>
+        <v>46112.679901701384</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46118.369935509254</v>
+        <v>46118.536602175926</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>
@@ -6728,11 +6728,11 @@
         <v>280</v>
       </c>
       <c r="B82" s="5">
-        <v>46112.51324356481</v>
+        <v>46112.67991023148</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46118.37004333333</v>
+        <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>281</v>
@@ -6791,11 +6791,11 @@
         <v>282</v>
       </c>
       <c r="B83" s="8">
-        <v>46112.513294108794</v>
+        <v>46112.679960775466</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46181.56635840278</v>
+        <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>213</v>
@@ -6844,11 +6844,11 @@
         <v>285</v>
       </c>
       <c r="B84" s="5">
-        <v>46112.51330585648</v>
+        <v>46112.67997252315</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46181.56636319445</v>
+        <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>248</v>
@@ -6897,11 +6897,11 @@
         <v>287</v>
       </c>
       <c r="B85" s="8">
-        <v>46112.51646270833</v>
+        <v>46112.683129375</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46118.36979733796</v>
+        <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>251</v>
@@ -6950,11 +6950,11 @@
         <v>289</v>
       </c>
       <c r="B86" s="5">
-        <v>46112.51331552083</v>
+        <v>46112.6799821875</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.370731319446</v>
+        <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>290</v>
@@ -7013,11 +7013,11 @@
         <v>292</v>
       </c>
       <c r="B87" s="8">
-        <v>46112.513324988424</v>
+        <v>46112.679991655095</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46181.56635912037</v>
+        <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>213</v>
@@ -7066,11 +7066,11 @@
         <v>295</v>
       </c>
       <c r="B88" s="5">
-        <v>46112.513333993054</v>
+        <v>46112.68000065972</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46181.56635642362</v>
+        <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>248</v>
@@ -7119,11 +7119,11 @@
         <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46112.51887622685</v>
+        <v>46112.68554289352</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46118.370733310185</v>
+        <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>252</v>
@@ -7172,11 +7172,11 @@
         <v>300</v>
       </c>
       <c r="B90" s="5">
-        <v>46112.51334262731</v>
+        <v>46112.68000929398</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46118.38430175926</v>
+        <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>301</v>
@@ -7219,11 +7219,11 @@
         <v>303</v>
       </c>
       <c r="B91" s="8">
-        <v>46112.51334737269</v>
+        <v>46112.68001403935</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46185.0316921875</v>
+        <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>304</v>
@@ -7282,11 +7282,11 @@
         <v>306</v>
       </c>
       <c r="B92" s="5">
-        <v>46112.51335707176</v>
+        <v>46112.68002373843</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46118.385106875</v>
+        <v>46118.551773541665</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>57</v>
@@ -7345,11 +7345,11 @@
         <v>308</v>
       </c>
       <c r="B93" s="8">
-        <v>46112.51337078704</v>
+        <v>46112.680037453705</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46191.729473125</v>
+        <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>309</v>
@@ -7408,11 +7408,11 @@
         <v>311</v>
       </c>
       <c r="B94" s="5">
-        <v>46112.51337990741</v>
+        <v>46112.680046574074</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46112.51360348379</v>
+        <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>312</v>
@@ -7471,11 +7471,11 @@
         <v>314</v>
       </c>
       <c r="B95" s="8">
-        <v>46112.51339332176</v>
+        <v>46112.68005998843</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46154.701074004624</v>
+        <v>46154.867740671296</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>315</v>
@@ -7534,11 +7534,11 @@
         <v>317</v>
       </c>
       <c r="B96" s="5">
-        <v>46112.51340157408</v>
+        <v>46112.68006824074</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46118.38429957176</v>
+        <v>46118.55096623843</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>318</v>
@@ -7595,11 +7595,11 @@
         <v>320</v>
       </c>
       <c r="B97" s="8">
-        <v>46112.51341141204</v>
+        <v>46112.6800780787</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46183.02253207176</v>
+        <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>321</v>
@@ -7658,11 +7658,11 @@
         <v>323</v>
       </c>
       <c r="B98" s="5">
-        <v>46112.513451516206</v>
+        <v>46112.68011818287</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46118.37341457176</v>
+        <v>46118.540081238425</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>324</v>
@@ -7705,11 +7705,11 @@
         <v>326</v>
       </c>
       <c r="B99" s="8">
-        <v>46112.513457696754</v>
+        <v>46112.680124363425</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46118.37427302083</v>
+        <v>46118.540939687504</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>327</v>
@@ -7768,11 +7768,11 @@
         <v>329</v>
       </c>
       <c r="B100" s="5">
-        <v>46112.51346640046</v>
+        <v>46112.68013306713</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.384298125005</v>
+        <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>213</v>
@@ -7821,11 +7821,11 @@
         <v>332</v>
       </c>
       <c r="B101" s="8">
-        <v>46112.51347578704</v>
+        <v>46112.680142453704</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.384299618054</v>
+        <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>248</v>
@@ -7874,11 +7874,11 @@
         <v>335</v>
       </c>
       <c r="B102" s="5">
-        <v>46112.52029046296</v>
+        <v>46112.68695712963</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46118.37427526621</v>
+        <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>252</v>
@@ -7927,11 +7927,11 @@
         <v>337</v>
       </c>
       <c r="B103" s="8">
-        <v>46112.51348563658</v>
+        <v>46112.68015230324</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.374608032405</v>
+        <v>46118.54127469908</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>338</v>
@@ -7990,11 +7990,11 @@
         <v>340</v>
       </c>
       <c r="B104" s="5">
-        <v>46112.51349394676</v>
+        <v>46112.680160613425</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46181.566359606484</v>
+        <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>213</v>
@@ -8043,11 +8043,11 @@
         <v>343</v>
       </c>
       <c r="B105" s="8">
-        <v>46112.513505462965</v>
+        <v>46112.68017212963</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46181.566357118056</v>
+        <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>248</v>
@@ -8096,11 +8096,11 @@
         <v>346</v>
       </c>
       <c r="B106" s="5">
-        <v>46112.52114252315</v>
+        <v>46112.68780918981</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.37460988426</v>
+        <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>252</v>
@@ -8149,11 +8149,11 @@
         <v>348</v>
       </c>
       <c r="B107" s="8">
-        <v>46112.5135159375</v>
+        <v>46112.68018260416</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.37478846065</v>
+        <v>46118.54145512731</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>349</v>
@@ -8212,11 +8212,11 @@
         <v>350</v>
       </c>
       <c r="B108" s="5">
-        <v>46112.51352381945</v>
+        <v>46112.680190486106</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46181.5663616088</v>
+        <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>213</v>
@@ -8265,11 +8265,11 @@
         <v>353</v>
       </c>
       <c r="B109" s="8">
-        <v>46112.513535081016</v>
+        <v>46112.68020174769</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46181.56636039352</v>
+        <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>248</v>
@@ -8318,11 +8318,11 @@
         <v>356</v>
       </c>
       <c r="B110" s="5">
-        <v>46112.52223030092</v>
+        <v>46112.68889696759</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46118.37478960648</v>
+        <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>252</v>
@@ -8371,11 +8371,11 @@
         <v>358</v>
       </c>
       <c r="B111" s="8">
-        <v>46112.51354650463</v>
+        <v>46112.6802131713</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46118.3749275463</v>
+        <v>46118.54159421296</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>359</v>
@@ -8434,11 +8434,11 @@
         <v>360</v>
       </c>
       <c r="B112" s="5">
-        <v>46112.51355444445</v>
+        <v>46112.680221111106</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46181.566360937504</v>
+        <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>213</v>
@@ -8487,11 +8487,11 @@
         <v>362</v>
       </c>
       <c r="B113" s="8">
-        <v>46112.51356582176</v>
+        <v>46112.68023248843</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46181.56636228009</v>
+        <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>248</v>
@@ -8540,11 +8540,11 @@
         <v>364</v>
       </c>
       <c r="B114" s="5">
-        <v>46112.52445456019</v>
+        <v>46112.69112122685</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46118.374930000005</v>
+        <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>251</v>
@@ -8593,11 +8593,11 @@
         <v>366</v>
       </c>
       <c r="B115" s="8">
-        <v>46112.51357737269</v>
+        <v>46112.68024403935</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46118.37509318287</v>
+        <v>46118.54175984954</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>367</v>
@@ -8656,11 +8656,11 @@
         <v>368</v>
       </c>
       <c r="B116" s="5">
-        <v>46112.51358561343</v>
+        <v>46112.68025228009</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46181.56635783565</v>
+        <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>213</v>
@@ -8709,11 +8709,11 @@
         <v>371</v>
       </c>
       <c r="B117" s="8">
-        <v>46112.51359768519</v>
+        <v>46112.68026435185</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46181.56636282407</v>
+        <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>248</v>
@@ -8762,11 +8762,11 @@
         <v>374</v>
       </c>
       <c r="B118" s="5">
-        <v>46112.52614829861</v>
+        <v>46112.69281496528</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46118.37508619213</v>
+        <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>252</v>
@@ -8815,11 +8815,11 @@
         <v>376</v>
       </c>
       <c r="B119" s="8">
-        <v>46112.51364833333</v>
+        <v>46112.680315000005</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46118.375211990744</v>
+        <v>46118.54187865741</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>377</v>
@@ -8878,11 +8878,11 @@
         <v>378</v>
       </c>
       <c r="B120" s="5">
-        <v>46112.51365986111</v>
+        <v>46112.68032652778</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46118.375212743056</v>
+        <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>213</v>
@@ -8929,11 +8929,11 @@
         <v>380</v>
       </c>
       <c r="B121" s="8">
-        <v>46112.513669409724</v>
+        <v>46112.68033607639</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46118.375213611114</v>
+        <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>248</v>
@@ -8980,11 +8980,11 @@
         <v>382</v>
       </c>
       <c r="B122" s="5">
-        <v>46112.5270869213</v>
+        <v>46112.69375358796</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46118.37521438657</v>
+        <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>252</v>
@@ -9031,11 +9031,11 @@
         <v>384</v>
       </c>
       <c r="B123" s="8">
-        <v>46112.51367827546</v>
+        <v>46112.68034494213</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46118.375342060186</v>
+        <v>46118.54200872685</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>385</v>
@@ -9092,11 +9092,11 @@
         <v>386</v>
       </c>
       <c r="B124" s="5">
-        <v>46112.51368667824</v>
+        <v>46112.680353344906</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46118.38119788194</v>
+        <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>213</v>
@@ -9143,11 +9143,11 @@
         <v>388</v>
       </c>
       <c r="B125" s="8">
-        <v>46112.513694803245</v>
+        <v>46112.6803614699</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46118.381196145834</v>
+        <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>248</v>
@@ -9194,11 +9194,11 @@
         <v>390</v>
       </c>
       <c r="B126" s="5">
-        <v>46112.528263541666</v>
+        <v>46112.69493020834</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46118.38119685186</v>
+        <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>252</v>
@@ -9245,11 +9245,11 @@
         <v>392</v>
       </c>
       <c r="B127" s="8">
-        <v>46112.51370282407</v>
+        <v>46112.68036949074</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46118.37611902777</v>
+        <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>393</v>
@@ -9292,11 +9292,11 @@
         <v>395</v>
       </c>
       <c r="B128" s="5">
-        <v>46112.51370762731</v>
+        <v>46112.68037429398</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46118.375693090275</v>
+        <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>396</v>
@@ -9355,11 +9355,11 @@
         <v>400</v>
       </c>
       <c r="B129" s="8">
-        <v>46112.51371667824</v>
+        <v>46112.68038334491</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46118.375693738424</v>
+        <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>213</v>
@@ -9406,11 +9406,11 @@
         <v>402</v>
       </c>
       <c r="B130" s="5">
-        <v>46112.51372454861</v>
+        <v>46112.68039121528</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46118.37569451389</v>
+        <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>248</v>
@@ -9457,11 +9457,11 @@
         <v>404</v>
       </c>
       <c r="B131" s="8">
-        <v>46112.53120728009</v>
+        <v>46112.69787394676</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46118.37569533565</v>
+        <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>251</v>
@@ -9508,11 +9508,11 @@
         <v>406</v>
       </c>
       <c r="B132" s="5">
-        <v>46112.51373324074</v>
+        <v>46112.6803999074</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46118.37569619213</v>
+        <v>46118.542362858796</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>56</v>
@@ -9559,11 +9559,11 @@
         <v>408</v>
       </c>
       <c r="B133" s="8">
-        <v>46112.51374471065</v>
+        <v>46112.68041137731</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46118.37569696759</v>
+        <v>46118.54236363426</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>60</v>
@@ -9610,11 +9610,11 @@
         <v>410</v>
       </c>
       <c r="B134" s="5">
-        <v>46112.51375236111</v>
+        <v>46112.680419027776</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46118.37569774306</v>
+        <v>46118.54236440972</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>63</v>
@@ -9661,11 +9661,11 @@
         <v>412</v>
       </c>
       <c r="B135" s="8">
-        <v>46112.51376033565</v>
+        <v>46112.68042700231</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46118.37569853009</v>
+        <v>46118.54236519676</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>66</v>
@@ -9712,11 +9712,11 @@
         <v>414</v>
       </c>
       <c r="B136" s="5">
-        <v>46112.51376799769</v>
+        <v>46112.68043466435</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46118.37569929398</v>
+        <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>322</v>
@@ -9763,11 +9763,11 @@
         <v>416</v>
       </c>
       <c r="B137" s="8">
-        <v>46112.51377549769</v>
+        <v>46112.68044216435</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46118.376586956016</v>
+        <v>46118.54325362269</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>417</v>
@@ -9826,11 +9826,11 @@
         <v>420</v>
       </c>
       <c r="B138" s="5">
-        <v>46112.51378354167</v>
+        <v>46112.68045020833</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46118.376425891205</v>
+        <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>213</v>
@@ -9879,11 +9879,11 @@
         <v>422</v>
       </c>
       <c r="B139" s="8">
-        <v>46112.51379094907</v>
+        <v>46112.680457615745</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46118.37642664352</v>
+        <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>248</v>
@@ -9932,11 +9932,11 @@
         <v>424</v>
       </c>
       <c r="B140" s="5">
-        <v>46112.5326671875</v>
+        <v>46112.699333854165</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46118.376474247685</v>
+        <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>252</v>
@@ -9985,11 +9985,11 @@
         <v>426</v>
       </c>
       <c r="B141" s="8">
-        <v>46112.51379863426</v>
+        <v>46112.68046530093</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46118.376428240736</v>
+        <v>46118.54309490741</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>56</v>
@@ -10038,11 +10038,11 @@
         <v>428</v>
       </c>
       <c r="B142" s="5">
-        <v>46112.51380609954</v>
+        <v>46112.6804727662</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46118.37642912037</v>
+        <v>46118.54309578704</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>60</v>
@@ -10091,11 +10091,11 @@
         <v>430</v>
       </c>
       <c r="B143" s="8">
-        <v>46112.51385761574</v>
+        <v>46112.680524282405</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46118.3764299537</v>
+        <v>46118.54309662037</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>63</v>
@@ -10144,11 +10144,11 @@
         <v>432</v>
       </c>
       <c r="B144" s="5">
-        <v>46112.51386880787</v>
+        <v>46112.68053547454</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46118.37643081018</v>
+        <v>46118.54309747685</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10197,11 +10197,11 @@
         <v>434</v>
       </c>
       <c r="B145" s="8">
-        <v>46112.51387761574</v>
+        <v>46112.68054428241</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46118.37643179398</v>
+        <v>46118.54309846065</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>435</v>
@@ -10250,11 +10250,11 @@
         <v>437</v>
       </c>
       <c r="B146" s="5">
-        <v>46112.51388608797</v>
+        <v>46112.68055275463</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46118.37690659722</v>
+        <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>438</v>
@@ -10311,11 +10311,11 @@
         <v>440</v>
       </c>
       <c r="B147" s="8">
-        <v>46112.513897199075</v>
+        <v>46112.68056386574</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46118.37690609954</v>
+        <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>213</v>
@@ -10364,11 +10364,11 @@
         <v>442</v>
       </c>
       <c r="B148" s="5">
-        <v>46112.513905011576</v>
+        <v>46112.68057167824</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46118.37690674768</v>
+        <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>248</v>
@@ -10417,11 +10417,11 @@
         <v>444</v>
       </c>
       <c r="B149" s="8">
-        <v>46112.53368842593</v>
+        <v>46112.70035509259</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46118.43840368056</v>
+        <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>252</v>
@@ -10470,11 +10470,11 @@
         <v>445</v>
       </c>
       <c r="B150" s="5">
-        <v>46112.5139128125</v>
+        <v>46112.680579479165</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46118.37690806713</v>
+        <v>46118.5435747338</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>56</v>
@@ -10523,11 +10523,11 @@
         <v>447</v>
       </c>
       <c r="B151" s="8">
-        <v>46112.51392055556</v>
+        <v>46112.68058722222</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46118.37690870371</v>
+        <v>46118.54357537037</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>60</v>
@@ -10576,11 +10576,11 @@
         <v>449</v>
       </c>
       <c r="B152" s="5">
-        <v>46112.51392856482</v>
+        <v>46112.68059523148</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46118.376909328705</v>
+        <v>46118.54357599537</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>63</v>
@@ -10629,11 +10629,11 @@
         <v>451</v>
       </c>
       <c r="B153" s="8">
-        <v>46112.51393680555</v>
+        <v>46112.680603472225</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46118.37690994213</v>
+        <v>46118.5435766088</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>66</v>
@@ -10682,11 +10682,11 @@
         <v>453</v>
       </c>
       <c r="B154" s="5">
-        <v>46112.51394438658</v>
+        <v>46112.68061105324</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46118.37691060185</v>
+        <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>454</v>
@@ -10735,11 +10735,11 @@
         <v>456</v>
       </c>
       <c r="B155" s="8">
-        <v>46112.51395211805</v>
+        <v>46112.680618784725</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46118.377256736116</v>
+        <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>457</v>
@@ -10798,11 +10798,11 @@
         <v>460</v>
       </c>
       <c r="B156" s="5">
-        <v>46112.513966886574</v>
+        <v>46112.680633553246</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46118.37717853009</v>
+        <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>213</v>
@@ -10851,11 +10851,11 @@
         <v>462</v>
       </c>
       <c r="B157" s="8">
-        <v>46112.51397584491</v>
+        <v>46112.68064251158</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46118.37717936342</v>
+        <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>248</v>
@@ -10904,11 +10904,11 @@
         <v>463</v>
       </c>
       <c r="B158" s="5">
-        <v>46112.514049143516</v>
+        <v>46112.68071581019</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46118.37718408565</v>
+        <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>435</v>
@@ -10957,11 +10957,11 @@
         <v>464</v>
       </c>
       <c r="B159" s="8">
-        <v>46112.572476319445</v>
+        <v>46112.739142986116</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46118.377185335645</v>
+        <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>252</v>
@@ -11010,11 +11010,11 @@
         <v>465</v>
       </c>
       <c r="B160" s="5">
-        <v>46112.51398341435</v>
+        <v>46112.68065008102</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46118.37718614584</v>
+        <v>46118.5438528125</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>56</v>
@@ -11063,11 +11063,11 @@
         <v>466</v>
       </c>
       <c r="B161" s="8">
-        <v>46112.513990810185</v>
+        <v>46112.680657476856</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46118.377186956015</v>
+        <v>46118.54385362269</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>60</v>
@@ -11116,11 +11116,11 @@
         <v>467</v>
       </c>
       <c r="B162" s="5">
-        <v>46112.514031377315</v>
+        <v>46112.68069804399</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46118.3771878125</v>
+        <v>46118.54385447917</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>66</v>
@@ -11169,11 +11169,11 @@
         <v>468</v>
       </c>
       <c r="B163" s="8">
-        <v>46112.514040821756</v>
+        <v>46112.68070748843</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46118.37718862269</v>
+        <v>46118.54385528935</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>63</v>
@@ -11222,11 +11222,11 @@
         <v>469</v>
       </c>
       <c r="B164" s="5">
-        <v>46112.514057106484</v>
+        <v>46112.68072377315</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46118.37611855324</v>
+        <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>470</v>
@@ -11269,11 +11269,11 @@
         <v>472</v>
       </c>
       <c r="B165" s="8">
-        <v>46112.51406148148</v>
+        <v>46112.680728148145</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46118.37735388889</v>
+        <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>473</v>
@@ -11332,11 +11332,11 @@
         <v>476</v>
       </c>
       <c r="B166" s="5">
-        <v>46112.51407065972</v>
+        <v>46112.68073732639</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46118.37743908565</v>
+        <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>477</v>
@@ -11395,11 +11395,11 @@
         <v>479</v>
       </c>
       <c r="B167" s="8">
-        <v>46112.51408033565</v>
+        <v>46112.68074700232</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46118.37611855324</v>
+        <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>480</v>
@@ -11444,11 +11444,11 @@
         <v>482</v>
       </c>
       <c r="B168" s="5">
-        <v>46112.5140847338</v>
+        <v>46112.68075140046</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46118.377544710645</v>
+        <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>483</v>
@@ -11507,11 +11507,11 @@
         <v>485</v>
       </c>
       <c r="B169" s="8">
-        <v>46112.51409322917</v>
+        <v>46112.68075989583</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46118.3776578588</v>
+        <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>486</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46196.65421123843</v>
+        <v>46206.5765590625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46193.20103049769</v>
+        <v>46206.57737820601</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46206.5765590625</v>
+        <v>46209.580220902775</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46206.57737820601</v>
+        <v>46209.586068969904</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46209.580220902775</v>
+        <v>46209.65185336806</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46209.65185336806</v>
+        <v>46210.55840188658</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46203.17583194445</v>
+        <v>46210.168728425924</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>164</v>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.85689956018</v>
+        <v>46210.168730335645</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -5384,9 +5384,11 @@
       <c r="B58" s="5">
         <v>46112.67980725694</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46210.52998074074</v>
+      </c>
       <c r="D58" s="5">
-        <v>46162.64351380787</v>
+        <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>204</v>
@@ -5420,10 +5422,12 @@
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
+      <c r="S58" s="6">
+        <v>1</v>
+      </c>
       <c r="T58" s="6"/>
-      <c r="U58" s="12" t="s">
-        <v>90</v>
+      <c r="U58" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46210.55840188658</v>
+        <v>46210.57522067129</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46210.57522067129</v>
+        <v>46210.62912240741</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3583,7 +3583,7 @@
         <v>46192</v>
       </c>
       <c r="S28" s="6">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="T28" s="10" t="s">
         <v>31</v>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46209.586068969904</v>
+        <v>46210.62940358796</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3711,7 +3711,7 @@
         <v>46192</v>
       </c>
       <c r="S30" s="6">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="T30" s="10" t="s">
         <v>31</v>
@@ -3731,7 +3731,7 @@
         <v>46113.808467152776</v>
       </c>
       <c r="D31" s="8">
-        <v>46123.18662818287</v>
+        <v>46210.62933210648</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>86</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3538,7 +3538,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46210.62912240741</v>
+        <v>46210.663940405095</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -250,7 +250,7 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,Propuesta Sensores,Analisis de costeo,Propuesta Fabricacion Externa  ot 4294 - 4296 - 4297,Planos preliminar,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
+    <t>Ingenieria Jefe de proyecto:,Propuesta Sensores,Analisis de costeo,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297,Planos preliminar,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
   </si>
   <si>
     <t>1213886181447052</t>
@@ -355,7 +355,7 @@
     <t>1213886181474407</t>
   </si>
   <si>
-    <t>Propuesta Fabricacion Externa  ot 4294 - 4296 - 4297</t>
+    <t>Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
   </si>
   <si>
     <t>Ingenieria Detalle,Check Planos</t>
@@ -721,7 +721,7 @@
     <t>1213886181537550</t>
   </si>
   <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297,Propuesta Fabricacion Externa  ot 4294 - 4296 - 4297</t>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
   </si>
   <si>
     <t>1213910573903658</t>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46210.62940358796</v>
+        <v>46210.672841631946</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -283,667 +283,667 @@
     <t>Propuesta Sensores,propuesta motor,propuesta rodete,propuesta tableros,propuesta tableros,propuesta alabes,propuesta alabes</t>
   </si>
   <si>
+    <t>1213886181428729</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Generación OC motor  ot 4294 - 4296 - 4297,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1213886259261835</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4294 - 4296 - 4297,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1213886380480795</t>
+  </si>
+  <si>
+    <t>propuesta rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886259267316</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1213886259270650</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
+    <t>Generación OC materiales ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886181474378</t>
+  </si>
+  <si>
+    <t>Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>1213886181474407</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Check Planos</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886380494178</t>
+  </si>
+  <si>
+    <t>Atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
+  </si>
+  <si>
+    <t>1213881596172406</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301,Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:,Rodete  ot 4294 - 4296 - 4297,Sensores,Alabe  ot 4294 - 4296 - 4297,Motor  ot 4294 - 4296 - 4297,Fabricacion Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886380496282</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4294 - 4296 - 4297,Fabricación Alabe  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886304257151</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4294 - 4296 - 4297,Fabricación Alabe  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886304258305</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4294 - 4296 - 4297,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1213886259285160</t>
+  </si>
+  <si>
+    <t>Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301,Fabricación Tablero OT 4298 - 4299 -4300 -4301</t>
+  </si>
+  <si>
+    <t>1213886259285184</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301</t>
+  </si>
+  <si>
+    <t>Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301,Fabricación Tablero OT 4298 - 4299 -4300 -4301</t>
+  </si>
+  <si>
+    <t>1213886181494787</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero OT 4298 - 4299 -4300 -4301</t>
+  </si>
+  <si>
+    <t>Recepcion Tableros y componentes electricos ,Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301</t>
+  </si>
+  <si>
+    <t>1213886181476571</t>
+  </si>
+  <si>
+    <t>Rodete  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete  ot 4294 - 4296 - 4297,Fabricación Rodete  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886304275911</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Rodete  ot 4294 - 4296 - 4297,Fabricación Rodete  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213902113444391</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Rodete  ot 4294 - 4296 - 4297,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1213902113445572</t>
+  </si>
+  <si>
+    <t>Motor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Generación OC motor  ot 4294 - 4296 - 4297,Fabricación motor  ot 4294 - 4296 - 4297,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886181511076</t>
+  </si>
+  <si>
+    <t>Generación OC motor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Motor  ot 4294 - 4296 - 4297,Fabricación motor  ot 4294 - 4296 - 4297,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886259298291</t>
+  </si>
+  <si>
+    <t>Fabricación motor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Motor  ot 4294 - 4296 - 4297,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213886304284601</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Motor  ot 4294 - 4296 - 4297,OT 4297 ZVR1-14-25/4,OT 4280 ZVN 1-9-63/2,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886259305779</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1213886259305803</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886259307144</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:</t>
+  </si>
+  <si>
+    <t>1213886430624337</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores,Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>1213886304289396</t>
+  </si>
+  <si>
+    <t>Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores,Sensores</t>
+  </si>
+  <si>
+    <t>1213886259313572</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>Sensores,Recepción Sensores</t>
+  </si>
+  <si>
+    <t>1213886259313596</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Check Planos</t>
+  </si>
+  <si>
+    <t>1213902113454390</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886430614804</t>
+  </si>
+  <si>
+    <t>Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297,Check Planos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Control de calidad Fabricación externa</t>
+  </si>
+  <si>
+    <t>1213886259324444</t>
+  </si>
+  <si>
+    <t>Atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>Propuesta Atenuadores ,Fabricacion atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
+  </si>
+  <si>
+    <t>1213886259326766</t>
+  </si>
+  <si>
+    <t>Generacion oc Atenuador  ot 4295</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4295,Atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>1213886259328934</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>Atenuadores,Atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>1213886259328954</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1213902113471352</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213899500210915</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213899500210916</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213899500210917</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886304303088</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213910573903655</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213910573903656</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR 1-14-34/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213910573903657</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR1-14-25/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886181537550</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213910573903658</t>
+  </si>
+  <si>
+    <t>1213910573903659</t>
+  </si>
+  <si>
+    <t>1213910573903660</t>
+  </si>
+  <si>
+    <t>1213886259337472</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886259341627</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886259341647</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213881596172439</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213902113480432</t>
+  </si>
+  <si>
+    <t>Control de calidad</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa</t>
+  </si>
+  <si>
+    <t>1213902113480444</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213902113485641</t>
+  </si>
+  <si>
+    <t>Bodega</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213886181542206</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213886181542236</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>Bodega,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1213902113596084</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Armado,Control de calidad Armado,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1213902113601428</t>
+  </si>
+  <si>
+    <t>Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,Caldereria,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886181546547</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1213886304313737</t>
+  </si>
+  <si>
+    <t>Preparacion materiales,Check Planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213902113612855</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Armado</t>
+  </si>
+  <si>
+    <t>1213881596172409</t>
+  </si>
+  <si>
+    <t>Armado,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886380584527</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886380584552</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886304333912</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886305136215</t>
+  </si>
+  <si>
+    <t>OT  4297 ZVR 1-14-25/4,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213886259370468</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion Tableros y componentes electricos ,Recepcion motor,Recepcion Rodete,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213902113620466</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,Bodega:</t>
+  </si>
+  <si>
+    <t>1213886380596164</t>
+  </si>
+  <si>
+    <t>OT 4299- TABLERO PLC,OT 4300- TABLERO BOTONERA,OT 4301-COMPONENTES TABLERO COMPUERTAS,Bodega:,OT 4298- TABLERO VDF ABB ACS880-17</t>
+  </si>
+  <si>
+    <t>1213886181569524</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213886181428729</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Generación OC motor  ot 4294 - 4296 - 4297,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1213886259261835</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4294 - 4296 - 4297,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1213886380480795</t>
-  </si>
-  <si>
-    <t>propuesta rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886259267316</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1213886259270650</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
-  </si>
-  <si>
-    <t>Generación OC materiales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886181474378</t>
-  </si>
-  <si>
-    <t>Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>1213886181474407</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Check Planos</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886380494178</t>
-  </si>
-  <si>
-    <t>Atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
-  </si>
-  <si>
-    <t>1213881596172406</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301,Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:,Rodete  ot 4294 - 4296 - 4297,Sensores,Alabe  ot 4294 - 4296 - 4297,Motor  ot 4294 - 4296 - 4297,Fabricacion Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886380496282</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4294 - 4296 - 4297,Fabricación Alabe  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886304257151</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4294 - 4296 - 4297,Fabricación Alabe  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886304258305</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4294 - 4296 - 4297,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1213886259285160</t>
-  </si>
-  <si>
-    <t>Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301,Fabricación Tablero OT 4298 - 4299 -4300 -4301</t>
-  </si>
-  <si>
-    <t>1213886259285184</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301</t>
-  </si>
-  <si>
-    <t>Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301,Fabricación Tablero OT 4298 - 4299 -4300 -4301</t>
-  </si>
-  <si>
-    <t>1213886181494787</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero OT 4298 - 4299 -4300 -4301</t>
-  </si>
-  <si>
-    <t>Recepcion Tableros y componentes electricos ,Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301</t>
-  </si>
-  <si>
-    <t>1213886181476571</t>
-  </si>
-  <si>
-    <t>Rodete  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete  ot 4294 - 4296 - 4297,Fabricación Rodete  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886304275911</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Rodete  ot 4294 - 4296 - 4297,Fabricación Rodete  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213902113444391</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Rodete  ot 4294 - 4296 - 4297,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1213902113445572</t>
-  </si>
-  <si>
-    <t>Motor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Generación OC motor  ot 4294 - 4296 - 4297,Fabricación motor  ot 4294 - 4296 - 4297,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886181511076</t>
-  </si>
-  <si>
-    <t>Generación OC motor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Motor  ot 4294 - 4296 - 4297,Fabricación motor  ot 4294 - 4296 - 4297,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886259298291</t>
-  </si>
-  <si>
-    <t>Fabricación motor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Motor  ot 4294 - 4296 - 4297,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213886304284601</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Motor  ot 4294 - 4296 - 4297,OT 4297 ZVR1-14-25/4,OT 4280 ZVN 1-9-63/2,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886259305779</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1213886259305803</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886259307144</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:</t>
-  </si>
-  <si>
-    <t>1213886430624337</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores,Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>1213886304289396</t>
-  </si>
-  <si>
-    <t>Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores,Sensores</t>
-  </si>
-  <si>
-    <t>1213886259313572</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>Sensores,Recepción Sensores</t>
-  </si>
-  <si>
-    <t>1213886259313596</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Check Planos</t>
-  </si>
-  <si>
-    <t>1213902113454390</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886430614804</t>
-  </si>
-  <si>
-    <t>Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297,Check Planos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Control de calidad Fabricación externa</t>
-  </si>
-  <si>
-    <t>1213886259324444</t>
-  </si>
-  <si>
-    <t>Atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>Propuesta Atenuadores ,Fabricacion atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
-  </si>
-  <si>
-    <t>1213886259326766</t>
-  </si>
-  <si>
-    <t>Generacion oc Atenuador  ot 4295</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4295,Atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>1213886259328934</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>Atenuadores,Atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>1213886259328954</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1213902113471352</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213899500210915</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213899500210916</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213899500210917</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886304303088</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213910573903655</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213910573903656</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR 1-14-34/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213910573903657</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR1-14-25/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886181537550</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213910573903658</t>
-  </si>
-  <si>
-    <t>1213910573903659</t>
-  </si>
-  <si>
-    <t>1213910573903660</t>
-  </si>
-  <si>
-    <t>1213886259337472</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886259341627</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886259341647</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213881596172439</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213902113480432</t>
-  </si>
-  <si>
-    <t>Control de calidad</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa</t>
-  </si>
-  <si>
-    <t>1213902113480444</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213902113485641</t>
-  </si>
-  <si>
-    <t>Bodega</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213886181542206</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213886181542236</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Bodega,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1213902113596084</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Armado,Control de calidad Armado,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1213902113601428</t>
-  </si>
-  <si>
-    <t>Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,Caldereria,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886181546547</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1213886304313737</t>
-  </si>
-  <si>
-    <t>Preparacion materiales,Check Planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213902113612855</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Armado</t>
-  </si>
-  <si>
-    <t>1213881596172409</t>
-  </si>
-  <si>
-    <t>Armado,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886380584527</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886380584552</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886304333912</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886305136215</t>
-  </si>
-  <si>
-    <t>OT  4297 ZVR 1-14-25/4,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213886259370468</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion Tableros y componentes electricos ,Recepcion motor,Recepcion Rodete,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213902113620466</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,Bodega:</t>
-  </si>
-  <si>
-    <t>1213886380596164</t>
-  </si>
-  <si>
-    <t>OT 4299- TABLERO PLC,OT 4300- TABLERO BOTONERA,OT 4301-COMPONENTES TABLERO COMPUERTAS,Bodega:,OT 4298- TABLERO VDF ABB ACS880-17</t>
-  </si>
-  <si>
-    <t>1213886181569524</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
   </si>
   <si>
     <t>1213886304340554</t>
@@ -3227,9 +3227,11 @@
       <c r="B23" s="8">
         <v>46112.6791271875</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="8">
+        <v>46210.70046141204</v>
+      </c>
       <c r="D23" s="8">
-        <v>46135.54559271991</v>
+        <v>46210.70047322917</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3263,15 +3265,17 @@
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
+      <c r="S23" s="9">
+        <v>1</v>
+      </c>
       <c r="T23" s="9"/>
-      <c r="U23" s="12" t="s">
-        <v>90</v>
+      <c r="U23" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" s="5">
         <v>46112.679417754625</v>
@@ -3283,7 +3287,7 @@
         <v>46116.1399068287</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3316,7 +3320,7 @@
         <v>72</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q24" s="5">
         <v>46114</v>
@@ -3336,7 +3340,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="8">
         <v>46112.67943010417</v>
@@ -3348,7 +3352,7 @@
         <v>46123.18662815972</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3381,7 +3385,7 @@
         <v>75</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="8">
         <v>46121</v>
@@ -3401,7 +3405,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46112.67944046296</v>
@@ -3413,16 +3417,16 @@
         <v>46123.186628055555</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="H26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -3446,7 +3450,7 @@
         <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3466,7 +3470,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8">
         <v>46112.679452349534</v>
@@ -3478,7 +3482,7 @@
         <v>46135.54582827546</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3511,7 +3515,7 @@
         <v>46</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="8">
         <v>46121</v>
@@ -3531,26 +3535,28 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46112.67946289352</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46210.70001560185</v>
+      </c>
       <c r="D28" s="5">
-        <v>46210.663940405095</v>
+        <v>46210.7000328588</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46191</v>
@@ -3571,10 +3577,10 @@
         <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P28" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="Q28" s="5">
         <v>46191</v>
@@ -3583,7 +3589,7 @@
         <v>46192</v>
       </c>
       <c r="S28" s="6">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="T28" s="10" t="s">
         <v>31</v>
@@ -3594,7 +3600,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B29" s="8">
         <v>46112.679478136575</v>
@@ -3606,7 +3612,7 @@
         <v>46123.186628958334</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3639,7 +3645,7 @@
         <v>78</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3659,26 +3665,28 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5">
         <v>46112.67948803241</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46210.700444421294</v>
+      </c>
       <c r="D30" s="5">
-        <v>46210.672841631946</v>
+        <v>46210.700462465276</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I30" s="5">
         <v>46191</v>
@@ -3699,10 +3707,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P30" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3711,18 +3719,18 @@
         <v>46192</v>
       </c>
       <c r="S30" s="6">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="T30" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>90</v>
+      <c r="U30" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46112.67949700232</v>
@@ -3767,7 +3775,7 @@
         <v>85</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3787,7 +3795,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46112.67913506944</v>
@@ -3797,7 +3805,7 @@
         <v>46191.89614340277</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3821,7 +3829,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3834,7 +3842,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B33" s="8">
         <v>46112.679506099536</v>
@@ -3846,16 +3854,16 @@
         <v>46191.8961546875</v>
       </c>
       <c r="E33" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3873,13 +3881,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3899,7 +3907,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46112.6795156713</v>
@@ -3911,16 +3919,16 @@
         <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3938,13 +3946,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3964,7 +3972,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46112.67952521991</v>
@@ -3976,16 +3984,16 @@
         <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -4003,13 +4011,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -4029,7 +4037,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46112.67953447917</v>
@@ -4039,16 +4047,16 @@
         <v>46196.634982337964</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -4066,13 +4074,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -4092,7 +4100,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46112.679543101855</v>
@@ -4104,16 +4112,16 @@
         <v>46195.682751747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -4131,13 +4139,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4157,7 +4165,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46112.67955209491</v>
@@ -4167,16 +4175,16 @@
         <v>46195.7109980324</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4194,13 +4202,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4218,7 +4226,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46112.67960491898</v>
@@ -4228,16 +4236,16 @@
         <v>46195.71583903935</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4255,13 +4263,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4281,7 +4289,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46112.679614513894</v>
@@ -4293,16 +4301,16 @@
         <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4320,13 +4328,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4346,7 +4354,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46112.67962357639</v>
@@ -4356,16 +4364,16 @@
         <v>46195.71615581018</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4383,13 +4391,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4409,7 +4417,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46112.679632581014</v>
@@ -4419,16 +4427,16 @@
         <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4446,13 +4454,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4472,7 +4480,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46112.67964135417</v>
@@ -4484,16 +4492,16 @@
         <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4511,13 +4519,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4537,7 +4545,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46112.67965385417</v>
@@ -4547,16 +4555,16 @@
         <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4574,13 +4582,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4600,7 +4608,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="8">
         <v>46112.679662372684</v>
@@ -4612,16 +4620,16 @@
         <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4639,13 +4647,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4665,7 +4673,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46112.67967090278</v>
@@ -4675,16 +4683,16 @@
         <v>46210.168728425924</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4702,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4720,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U46" s="10" t="s">
         <v>54</v>
@@ -4728,26 +4736,26 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46199.16864855324</v>
+        <v>46210.700024143516</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4765,13 +4773,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4791,7 +4799,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4801,16 +4809,16 @@
         <v>46210.168730335645</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4828,13 +4836,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4854,7 +4862,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4866,16 +4874,16 @@
         <v>46154.86774770833</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4893,13 +4901,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4919,7 +4927,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4931,16 +4939,16 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4958,13 +4966,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4974,7 +4982,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4986,16 +4994,16 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -5013,13 +5021,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5029,7 +5037,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5039,16 +5047,16 @@
         <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5066,13 +5074,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -5092,26 +5100,26 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46199.16870392361</v>
+        <v>46210.700450081014</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5129,13 +5137,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5151,7 +5159,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5161,16 +5169,16 @@
         <v>46181.733022569446</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5188,13 +5196,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5204,7 +5212,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5216,16 +5224,16 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5243,10 +5251,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5269,7 +5277,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5281,16 +5289,16 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5308,13 +5316,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5324,7 +5332,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5336,16 +5344,16 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5363,13 +5371,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5379,7 +5387,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5391,7 +5399,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5415,7 +5423,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5432,7 +5440,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5444,16 +5452,16 @@
         <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5471,13 +5479,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5497,7 +5505,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5509,16 +5517,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5536,13 +5544,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5552,7 +5560,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5564,16 +5572,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5591,13 +5599,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5607,7 +5615,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5619,16 +5627,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5646,13 +5654,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5662,7 +5670,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5674,16 +5682,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5701,13 +5709,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5727,7 +5735,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5739,16 +5747,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5766,13 +5774,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5782,7 +5790,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5794,16 +5802,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5821,13 +5829,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5837,7 +5845,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5849,16 +5857,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5876,13 +5884,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5892,7 +5900,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5904,16 +5912,16 @@
         <v>46191.201163958336</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5931,13 +5939,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5957,7 +5965,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5969,16 +5977,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5994,13 +6002,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6010,7 +6018,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6022,16 +6030,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6047,13 +6055,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6063,7 +6071,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6075,16 +6083,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6100,13 +6108,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6116,7 +6124,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6126,16 +6134,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6153,10 +6161,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6179,7 +6187,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6189,16 +6197,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>243</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6216,13 +6224,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6232,7 +6240,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6242,16 +6250,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>243</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6269,13 +6277,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6285,7 +6293,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6295,16 +6303,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>243</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6322,13 +6330,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6338,7 +6346,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6348,7 +6356,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6372,7 +6380,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6385,7 +6393,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6395,16 +6403,16 @@
         <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6420,13 +6428,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6446,7 +6454,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6456,7 +6464,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6480,7 +6488,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6493,7 +6501,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6503,16 +6511,16 @@
         <v>46177.208199479166</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6530,13 +6538,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6556,7 +6564,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6566,16 +6574,16 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>259</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6593,13 +6601,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6619,7 +6627,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6629,7 +6637,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6653,7 +6661,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6666,7 +6674,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6676,16 +6684,16 @@
         <v>46118.536602175926</v>
       </c>
       <c r="E81" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6703,13 +6711,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6729,7 +6737,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6739,16 +6747,16 @@
         <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6766,13 +6774,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6792,7 +6800,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6802,16 +6810,16 @@
         <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6829,13 +6837,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6845,7 +6853,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6855,16 +6863,16 @@
         <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6882,13 +6890,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6898,7 +6906,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6908,16 +6916,16 @@
         <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6935,13 +6943,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6951,7 +6959,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6961,16 +6969,16 @@
         <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -6988,13 +6996,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7014,7 +7022,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7024,16 +7032,16 @@
         <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>259</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7051,13 +7059,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O87" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="P87" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>294</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7067,7 +7075,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7077,16 +7085,16 @@
         <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>258</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>259</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7104,13 +7112,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>296</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>297</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7120,7 +7128,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7130,16 +7138,16 @@
         <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>258</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>259</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7157,13 +7165,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7173,7 +7181,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7183,7 +7191,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7207,7 +7215,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7220,7 +7228,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7230,16 +7238,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7257,13 +7265,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7283,7 +7291,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7299,10 +7307,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7320,13 +7328,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7346,7 +7354,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7356,16 +7364,16 @@
         <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7383,13 +7391,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7404,7 +7412,7 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>90</v>
+        <v>310</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7425,10 +7433,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7446,10 +7454,10 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>313</v>
@@ -7488,10 +7496,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7509,10 +7517,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>316</v>
@@ -7530,7 +7538,7 @@
         <v>53</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>90</v>
+        <v>310</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7551,10 +7559,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7570,10 +7578,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>319</v>
@@ -7612,10 +7620,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7633,10 +7641,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>322</v>
@@ -7654,7 +7662,7 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>90</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7722,10 +7730,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I99" s="8">
         <v>46248</v>
@@ -7779,16 +7787,16 @@
         <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I100" s="5">
         <v>46248</v>
@@ -7832,16 +7840,16 @@
         <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I101" s="8">
         <v>46248</v>
@@ -7885,16 +7893,16 @@
         <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I102" s="5">
         <v>46248</v>
@@ -7915,7 +7923,7 @@
         <v>327</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>336</v>
@@ -7944,10 +7952,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I103" s="8">
         <v>46268</v>
@@ -8001,16 +8009,16 @@
         <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I104" s="5">
         <v>46268</v>
@@ -8054,16 +8062,16 @@
         <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I105" s="8">
         <v>46268</v>
@@ -8107,16 +8115,16 @@
         <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I106" s="5">
         <v>46268</v>
@@ -8137,7 +8145,7 @@
         <v>338</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>347</v>
@@ -8166,10 +8174,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I107" s="8">
         <v>46272</v>
@@ -8223,16 +8231,16 @@
         <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I108" s="5">
         <v>46272</v>
@@ -8276,16 +8284,16 @@
         <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I109" s="8">
         <v>46272</v>
@@ -8329,16 +8337,16 @@
         <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I110" s="5">
         <v>46272</v>
@@ -8359,7 +8367,7 @@
         <v>349</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>357</v>
@@ -8388,10 +8396,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I111" s="8">
         <v>46274</v>
@@ -8412,7 +8420,7 @@
         <v>324</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>324</v>
@@ -8445,16 +8453,16 @@
         <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I112" s="5">
         <v>46274</v>
@@ -8498,16 +8506,16 @@
         <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I113" s="8">
         <v>46274</v>
@@ -8551,16 +8559,16 @@
         <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I114" s="5">
         <v>46274</v>
@@ -8581,7 +8589,7 @@
         <v>359</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>365</v>
@@ -8610,10 +8618,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I115" s="8">
         <v>46276</v>
@@ -8667,16 +8675,16 @@
         <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I116" s="5">
         <v>46276</v>
@@ -8720,16 +8728,16 @@
         <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I117" s="8">
         <v>46276</v>
@@ -8773,16 +8781,16 @@
         <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I118" s="5">
         <v>46276</v>
@@ -8803,7 +8811,7 @@
         <v>367</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>375</v>
@@ -8832,10 +8840,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I119" s="8">
         <v>46280</v>
@@ -8889,16 +8897,16 @@
         <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8917,7 +8925,7 @@
         <v>377</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>379</v>
@@ -8940,16 +8948,16 @@
         <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8968,7 +8976,7 @@
         <v>377</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>381</v>
@@ -8991,16 +8999,16 @@
         <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -9019,7 +9027,7 @@
         <v>377</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>383</v>
@@ -9048,10 +9056,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -9103,16 +9111,16 @@
         <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -9131,7 +9139,7 @@
         <v>385</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>387</v>
@@ -9154,16 +9162,16 @@
         <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -9182,7 +9190,7 @@
         <v>385</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>389</v>
@@ -9205,16 +9213,16 @@
         <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -9233,7 +9241,7 @@
         <v>385</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>391</v>
@@ -9366,7 +9374,7 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9394,7 +9402,7 @@
         <v>396</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>401</v>
@@ -9417,7 +9425,7 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9445,7 +9453,7 @@
         <v>396</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>403</v>
@@ -9468,7 +9476,7 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9496,7 +9504,7 @@
         <v>396</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>405</v>
@@ -9780,10 +9788,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I137" s="8">
         <v>46288</v>
@@ -9837,16 +9845,16 @@
         <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I138" s="5">
         <v>46288</v>
@@ -9867,7 +9875,7 @@
         <v>417</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>421</v>
@@ -9890,16 +9898,16 @@
         <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I139" s="8">
         <v>46288</v>
@@ -9920,7 +9928,7 @@
         <v>417</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>423</v>
@@ -9943,16 +9951,16 @@
         <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I140" s="5">
         <v>46288</v>
@@ -9973,7 +9981,7 @@
         <v>417</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>425</v>
@@ -10002,10 +10010,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I141" s="8">
         <v>46288</v>
@@ -10055,10 +10063,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I142" s="5">
         <v>46288</v>
@@ -10108,10 +10116,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I143" s="8">
         <v>46288</v>
@@ -10161,10 +10169,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I144" s="5">
         <v>46288</v>
@@ -10214,10 +10222,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I145" s="8">
         <v>46288</v>
@@ -10267,10 +10275,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10322,16 +10330,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10352,7 +10360,7 @@
         <v>438</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>441</v>
@@ -10375,16 +10383,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10405,7 +10413,7 @@
         <v>438</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>443</v>
@@ -10428,16 +10436,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10458,10 +10466,10 @@
         <v>438</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10487,10 +10495,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10540,10 +10548,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10593,10 +10601,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10646,10 +10654,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10699,10 +10707,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10752,10 +10760,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10809,16 +10817,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10839,7 +10847,7 @@
         <v>457</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>461</v>
@@ -10862,16 +10870,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10892,7 +10900,7 @@
         <v>457</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>457</v>
@@ -10921,10 +10929,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10968,16 +10976,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H159" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -10998,7 +11006,7 @@
         <v>457</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11027,10 +11035,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11080,10 +11088,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H161" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11133,10 +11141,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11186,10 +11194,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="H163" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="486">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -512,9 +512,6 @@
   </si>
   <si>
     <t>Generación OC materiales ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213886259305803</t>
@@ -4680,7 +4677,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46210.168728425924</v>
+        <v>46211.172818969906</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4727,8 +4724,8 @@
       <c r="S46" s="6">
         <v>0</v>
       </c>
-      <c r="T46" s="12" t="s">
-        <v>167</v>
+      <c r="T46" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U46" s="10" t="s">
         <v>54</v>
@@ -4736,7 +4733,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4779,7 +4776,7 @@
         <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4799,7 +4796,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4809,7 +4806,7 @@
         <v>46210.168730335645</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4842,7 +4839,7 @@
         <v>108</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4862,7 +4859,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4874,7 +4871,7 @@
         <v>46154.86774770833</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
@@ -4904,7 +4901,7 @@
         <v>119</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>119</v>
@@ -4927,7 +4924,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4939,7 +4936,7 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4966,13 +4963,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>110</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4982,7 +4979,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4994,7 +4991,7 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -5021,13 +5018,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5037,7 +5034,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5047,16 +5044,16 @@
         <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5077,7 +5074,7 @@
         <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>119</v>
@@ -5100,7 +5097,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5116,10 +5113,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5137,13 +5134,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>113</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5159,7 +5156,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5169,16 +5166,16 @@
         <v>46181.733022569446</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5196,13 +5193,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5212,7 +5209,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5224,7 +5221,7 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5254,7 +5251,7 @@
         <v>119</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5277,7 +5274,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5289,7 +5286,7 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5316,13 +5313,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5332,7 +5329,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5344,7 +5341,7 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5371,13 +5368,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5387,7 +5384,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5399,7 +5396,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5423,7 +5420,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5440,7 +5437,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5452,16 +5449,16 @@
         <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>208</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5479,13 +5476,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5505,7 +5502,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5517,16 +5514,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5544,13 +5541,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5560,7 +5557,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5572,16 +5569,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5599,13 +5596,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5615,7 +5612,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5627,16 +5624,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5654,13 +5651,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5670,7 +5667,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5682,16 +5679,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>207</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>208</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5709,13 +5706,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5735,7 +5732,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5747,16 +5744,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5774,13 +5771,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5790,7 +5787,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5802,16 +5799,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5829,13 +5826,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5845,7 +5842,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5857,16 +5854,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5884,13 +5881,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5900,7 +5897,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5918,10 +5915,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5939,13 +5936,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5965,7 +5962,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5977,16 +5974,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -6005,7 +6002,7 @@
         <v>107</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>107</v>
@@ -6018,7 +6015,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6030,16 +6027,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6058,7 +6055,7 @@
         <v>107</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>107</v>
@@ -6071,7 +6068,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6083,16 +6080,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6111,7 +6108,7 @@
         <v>107</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>107</v>
@@ -6124,7 +6121,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6134,16 +6131,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6161,10 +6158,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6187,7 +6184,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6197,16 +6194,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6224,13 +6221,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6240,7 +6237,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6250,16 +6247,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6277,13 +6274,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6293,7 +6290,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6303,16 +6300,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6330,13 +6327,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6346,7 +6343,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6356,7 +6353,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6380,7 +6377,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6393,7 +6390,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6403,16 +6400,16 @@
         <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6428,13 +6425,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6454,7 +6451,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6464,7 +6461,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6488,7 +6485,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6501,7 +6498,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6511,16 +6508,16 @@
         <v>46177.208199479166</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6538,13 +6535,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6564,7 +6561,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6574,16 +6571,16 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6601,13 +6598,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6627,7 +6624,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6637,7 +6634,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6661,7 +6658,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6674,7 +6671,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6684,16 +6681,16 @@
         <v>46118.536602175926</v>
       </c>
       <c r="E81" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6711,13 +6708,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6737,7 +6734,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6747,16 +6744,16 @@
         <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6774,13 +6771,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6800,7 +6797,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6810,16 +6807,16 @@
         <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6837,13 +6834,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>283</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6853,7 +6850,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6863,16 +6860,16 @@
         <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6890,13 +6887,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6906,7 +6903,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6916,16 +6913,16 @@
         <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6943,13 +6940,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6959,7 +6956,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6969,16 +6966,16 @@
         <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -6996,13 +6993,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7022,7 +7019,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7032,16 +7029,16 @@
         <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7059,13 +7056,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O87" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="P87" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7075,7 +7072,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7085,16 +7082,16 @@
         <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7112,13 +7109,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7128,7 +7125,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7138,16 +7135,16 @@
         <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7165,13 +7162,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7181,7 +7178,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7191,7 +7188,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7215,7 +7212,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7228,7 +7225,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7238,16 +7235,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7265,13 +7262,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>148</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7291,7 +7288,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7307,10 +7304,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7328,13 +7325,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7354,7 +7351,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7364,16 +7361,16 @@
         <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7391,13 +7388,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>130</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7412,12 +7409,12 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7427,16 +7424,16 @@
         <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7454,13 +7451,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>157</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7480,7 +7477,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
@@ -7490,16 +7487,16 @@
         <v>46154.867740671296</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7517,13 +7514,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7538,12 +7535,12 @@
         <v>53</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7553,16 +7550,16 @@
         <v>46118.55096623843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7578,13 +7575,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7604,7 +7601,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7614,16 +7611,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7641,13 +7638,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7662,12 +7659,12 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7677,7 +7674,7 @@
         <v>46118.540081238425</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7701,7 +7698,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7714,7 +7711,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
@@ -7724,7 +7721,7 @@
         <v>46118.540939687504</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7751,13 +7748,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7777,7 +7774,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
@@ -7787,7 +7784,7 @@
         <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7814,13 +7811,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>331</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7830,7 +7827,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
@@ -7840,7 +7837,7 @@
         <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7867,13 +7864,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>333</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>334</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7883,7 +7880,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
@@ -7893,7 +7890,7 @@
         <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7920,13 +7917,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7936,7 +7933,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
@@ -7946,7 +7943,7 @@
         <v>46118.54127469908</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7973,13 +7970,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -7999,7 +7996,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
@@ -8009,7 +8006,7 @@
         <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8036,13 +8033,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>341</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>342</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8052,7 +8049,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
@@ -8062,7 +8059,7 @@
         <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8089,13 +8086,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O105" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="P105" s="9" t="s">
         <v>344</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>345</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8105,7 +8102,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
@@ -8115,7 +8112,7 @@
         <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8142,13 +8139,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8158,7 +8155,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
@@ -8168,7 +8165,7 @@
         <v>46118.54145512731</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8195,13 +8192,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8221,7 +8218,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
@@ -8231,7 +8228,7 @@
         <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8258,13 +8255,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O108" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8274,7 +8271,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
@@ -8284,7 +8281,7 @@
         <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8311,13 +8308,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O109" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="P109" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="P109" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8327,7 +8324,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
@@ -8337,7 +8334,7 @@
         <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8364,13 +8361,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8380,7 +8377,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
@@ -8390,7 +8387,7 @@
         <v>46118.54159421296</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8417,13 +8414,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8443,7 +8440,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
@@ -8453,7 +8450,7 @@
         <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8480,13 +8477,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8496,7 +8493,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
@@ -8506,7 +8503,7 @@
         <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8533,13 +8530,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8549,7 +8546,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
@@ -8559,7 +8556,7 @@
         <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8586,13 +8583,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8602,7 +8599,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
@@ -8612,7 +8609,7 @@
         <v>46118.54175984954</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8639,13 +8636,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8665,7 +8662,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
@@ -8675,7 +8672,7 @@
         <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8702,13 +8699,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O116" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="P116" s="6" t="s">
         <v>369</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>370</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8718,7 +8715,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
@@ -8728,7 +8725,7 @@
         <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8755,13 +8752,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O117" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="P117" s="9" t="s">
         <v>372</v>
-      </c>
-      <c r="P117" s="9" t="s">
-        <v>373</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8771,7 +8768,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
@@ -8781,7 +8778,7 @@
         <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8808,13 +8805,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8824,7 +8821,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
@@ -8834,7 +8831,7 @@
         <v>46118.54187865741</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8861,13 +8858,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8887,7 +8884,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
@@ -8897,7 +8894,7 @@
         <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8922,13 +8919,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8938,7 +8935,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
@@ -8948,7 +8945,7 @@
         <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8973,13 +8970,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8989,7 +8986,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
@@ -8999,7 +8996,7 @@
         <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9024,13 +9021,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9040,7 +9037,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
@@ -9050,7 +9047,7 @@
         <v>46118.54200872685</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9075,13 +9072,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9101,7 +9098,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B124" s="5">
         <v>46112.680353344906</v>
@@ -9111,7 +9108,7 @@
         <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9136,13 +9133,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9152,7 +9149,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B125" s="8">
         <v>46112.6803614699</v>
@@ -9162,7 +9159,7 @@
         <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9187,13 +9184,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9203,7 +9200,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B126" s="5">
         <v>46112.69493020834</v>
@@ -9213,7 +9210,7 @@
         <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9238,13 +9235,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9254,7 +9251,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B127" s="8">
         <v>46112.68036949074</v>
@@ -9264,7 +9261,7 @@
         <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9288,7 +9285,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9301,7 +9298,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B128" s="5">
         <v>46112.68037429398</v>
@@ -9311,16 +9308,16 @@
         <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G128" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="F128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G128" s="6" t="s">
+      <c r="H128" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I128" s="5">
         <v>46287</v>
@@ -9338,13 +9335,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q128" s="5">
         <v>46287</v>
@@ -9364,7 +9361,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B129" s="8">
         <v>46112.68038334491</v>
@@ -9374,16 +9371,16 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H129" s="9" t="s">
         <v>397</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>398</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9399,13 +9396,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9415,7 +9412,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B130" s="5">
         <v>46112.68039121528</v>
@@ -9425,16 +9422,16 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9450,13 +9447,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9466,7 +9463,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B131" s="8">
         <v>46112.69787394676</v>
@@ -9476,16 +9473,16 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>397</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>398</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9501,13 +9498,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9517,7 +9514,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B132" s="5">
         <v>46112.6803999074</v>
@@ -9533,10 +9530,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9552,13 +9549,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9568,7 +9565,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B133" s="8">
         <v>46112.68041137731</v>
@@ -9584,10 +9581,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>397</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>398</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9603,13 +9600,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9619,7 +9616,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B134" s="5">
         <v>46112.680419027776</v>
@@ -9635,10 +9632,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9654,13 +9651,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9670,7 +9667,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B135" s="8">
         <v>46112.68042700231</v>
@@ -9686,10 +9683,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>397</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>398</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9705,13 +9702,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9721,7 +9718,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B136" s="5">
         <v>46112.68043466435</v>
@@ -9731,16 +9728,16 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9756,13 +9753,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9772,7 +9769,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B137" s="8">
         <v>46112.68044216435</v>
@@ -9782,7 +9779,7 @@
         <v>46118.54325362269</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9809,13 +9806,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O137" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="P137" s="9" t="s">
         <v>418</v>
-      </c>
-      <c r="P137" s="9" t="s">
-        <v>419</v>
       </c>
       <c r="Q137" s="8">
         <v>46288</v>
@@ -9835,7 +9832,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B138" s="5">
         <v>46112.68045020833</v>
@@ -9845,7 +9842,7 @@
         <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9872,13 +9869,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9888,7 +9885,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B139" s="8">
         <v>46112.680457615745</v>
@@ -9898,7 +9895,7 @@
         <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9925,13 +9922,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9941,7 +9938,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B140" s="5">
         <v>46112.699333854165</v>
@@ -9951,7 +9948,7 @@
         <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9978,13 +9975,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9994,7 +9991,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B141" s="8">
         <v>46112.68046530093</v>
@@ -10031,13 +10028,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>56</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10047,7 +10044,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B142" s="5">
         <v>46112.6804727662</v>
@@ -10084,13 +10081,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10100,7 +10097,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B143" s="8">
         <v>46112.680524282405</v>
@@ -10137,13 +10134,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10153,7 +10150,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B144" s="5">
         <v>46112.68053547454</v>
@@ -10190,13 +10187,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10206,7 +10203,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B145" s="8">
         <v>46112.68054428241</v>
@@ -10216,7 +10213,7 @@
         <v>46118.54309846065</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10243,13 +10240,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10259,7 +10256,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B146" s="5">
         <v>46112.68055275463</v>
@@ -10269,16 +10266,16 @@
         <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10294,13 +10291,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q146" s="5">
         <v>46293</v>
@@ -10320,7 +10317,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B147" s="8">
         <v>46112.68056386574</v>
@@ -10330,16 +10327,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10357,13 +10354,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10373,7 +10370,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B148" s="5">
         <v>46112.68057167824</v>
@@ -10383,16 +10380,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10410,13 +10407,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10426,7 +10423,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B149" s="8">
         <v>46112.70035509259</v>
@@ -10436,16 +10433,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10463,13 +10460,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10479,7 +10476,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B150" s="5">
         <v>46112.680579479165</v>
@@ -10495,10 +10492,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10516,13 +10513,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10532,7 +10529,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B151" s="8">
         <v>46112.68058722222</v>
@@ -10548,10 +10545,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10569,13 +10566,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10585,7 +10582,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B152" s="5">
         <v>46112.68059523148</v>
@@ -10601,10 +10598,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10622,13 +10619,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10638,7 +10635,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B153" s="8">
         <v>46112.680603472225</v>
@@ -10654,10 +10651,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10675,13 +10672,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10691,7 +10688,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B154" s="5">
         <v>46112.68061105324</v>
@@ -10701,16 +10698,16 @@
         <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10728,13 +10725,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10744,7 +10741,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B155" s="8">
         <v>46112.680618784725</v>
@@ -10754,16 +10751,16 @@
         <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10781,13 +10778,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O155" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="P155" s="9" t="s">
         <v>458</v>
-      </c>
-      <c r="P155" s="9" t="s">
-        <v>459</v>
       </c>
       <c r="Q155" s="8">
         <v>46294</v>
@@ -10807,7 +10804,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B156" s="5">
         <v>46112.680633553246</v>
@@ -10817,16 +10814,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10844,13 +10841,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10860,7 +10857,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B157" s="8">
         <v>46112.68064251158</v>
@@ -10870,16 +10867,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10897,13 +10894,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10913,7 +10910,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B158" s="5">
         <v>46112.68071581019</v>
@@ -10923,16 +10920,16 @@
         <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10950,13 +10947,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10966,7 +10963,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B159" s="8">
         <v>46112.739142986116</v>
@@ -10976,16 +10973,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H159" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -11003,10 +11000,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11019,7 +11016,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B160" s="5">
         <v>46112.68065008102</v>
@@ -11035,10 +11032,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11056,13 +11053,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11072,7 +11069,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B161" s="8">
         <v>46112.680657476856</v>
@@ -11088,10 +11085,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H161" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11109,13 +11106,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11125,7 +11122,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B162" s="5">
         <v>46112.68069804399</v>
@@ -11141,10 +11138,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11162,13 +11159,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11178,7 +11175,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B163" s="8">
         <v>46112.68070748843</v>
@@ -11194,10 +11191,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H163" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>
@@ -11215,13 +11212,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11231,7 +11228,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B164" s="5">
         <v>46112.68072377315</v>
@@ -11241,7 +11238,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>25</v>
@@ -11265,7 +11262,7 @@
         <v>26</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>26</v>
@@ -11278,7 +11275,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B165" s="8">
         <v>46112.680728148145</v>
@@ -11288,16 +11285,16 @@
         <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="F165" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G165" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="F165" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G165" s="9" t="s">
+      <c r="H165" s="9" t="s">
         <v>474</v>
-      </c>
-      <c r="H165" s="9" t="s">
-        <v>475</v>
       </c>
       <c r="I165" s="8">
         <v>46295</v>
@@ -11315,13 +11312,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Q165" s="8">
         <v>46295</v>
@@ -11341,7 +11338,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B166" s="5">
         <v>46112.68073732639</v>
@@ -11351,16 +11348,16 @@
         <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="H166" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="H166" s="6" t="s">
-        <v>475</v>
       </c>
       <c r="I166" s="5">
         <v>46295</v>
@@ -11378,13 +11375,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Q166" s="5">
         <v>46295</v>
@@ -11404,7 +11401,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B167" s="8">
         <v>46112.68074700232</v>
@@ -11414,7 +11411,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>25</v>
@@ -11438,7 +11435,7 @@
         <v>26</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>26</v>
@@ -11453,7 +11450,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B168" s="5">
         <v>46112.68075140046</v>
@@ -11463,16 +11460,16 @@
         <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="H168" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>475</v>
       </c>
       <c r="I168" s="5">
         <v>46295</v>
@@ -11490,13 +11487,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Q168" s="5">
         <v>46295</v>
@@ -11516,7 +11513,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B169" s="8">
         <v>46112.68075989583</v>
@@ -11526,16 +11523,16 @@
         <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="H169" s="9" t="s">
         <v>474</v>
-      </c>
-      <c r="H169" s="9" t="s">
-        <v>475</v>
       </c>
       <c r="I169" s="8">
         <v>46304</v>
@@ -11553,13 +11550,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q169" s="8">
         <v>46304</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -814,6 +814,9 @@
     <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213886181542236</t>
   </si>
   <si>
@@ -938,9 +941,6 @@
   </si>
   <si>
     <t>Bodega:,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213886304340554</t>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46191.89614340277</v>
+        <v>46211.83114751158</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -4675,9 +4675,11 @@
       <c r="B46" s="5">
         <v>46112.67967090278</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46211.83114178241</v>
+      </c>
       <c r="D46" s="5">
-        <v>46211.172818969906</v>
+        <v>46211.831143738425</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4722,13 +4724,13 @@
         <v>46210</v>
       </c>
       <c r="S46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U46" s="10" t="s">
-        <v>54</v>
+      <c r="U46" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4738,9 +4740,11 @@
       <c r="B47" s="8">
         <v>46112.679679733796</v>
       </c>
-      <c r="C47" s="9"/>
+      <c r="C47" s="8">
+        <v>46211.828743680555</v>
+      </c>
       <c r="D47" s="8">
-        <v>46210.700024143516</v>
+        <v>46211.828745949075</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>108</v>
@@ -4801,9 +4805,11 @@
       <c r="B48" s="5">
         <v>46112.679688564815</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46211.83092953704</v>
+      </c>
       <c r="D48" s="5">
-        <v>46210.168730335645</v>
+        <v>46211.83093092593</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>170</v>
@@ -5163,7 +5169,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46181.733022569446</v>
+        <v>46211.83093851852</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -6505,7 +6511,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46177.208199479166</v>
+        <v>46211.830947395836</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>263</v>
@@ -6555,13 +6561,13 @@
       <c r="T78" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U78" s="10" t="s">
-        <v>54</v>
+      <c r="U78" s="12" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6571,7 +6577,7 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6604,7 +6610,7 @@
         <v>263</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6624,7 +6630,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6634,7 +6640,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6658,7 +6664,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6671,7 +6677,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6681,16 +6687,16 @@
         <v>46118.536602175926</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6708,13 +6714,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6734,7 +6740,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6744,16 +6750,16 @@
         <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6771,13 +6777,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>242</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6797,7 +6803,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6813,10 +6819,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6834,13 +6840,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6850,7 +6856,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6866,10 +6872,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6887,13 +6893,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6903,7 +6909,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6919,10 +6925,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6940,13 +6946,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6956,7 +6962,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6966,7 +6972,7 @@
         <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6993,13 +6999,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7019,7 +7025,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7056,13 +7062,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7072,7 +7078,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7109,13 +7115,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7125,7 +7131,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7162,13 +7168,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>249</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7178,7 +7184,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7188,7 +7194,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7212,7 +7218,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7225,7 +7231,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7235,7 +7241,7 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7262,13 +7268,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>148</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7288,7 +7294,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7325,13 +7331,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7351,7 +7357,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7361,7 +7367,7 @@
         <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7388,13 +7394,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>130</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7409,7 +7415,7 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7451,7 +7457,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>157</v>
@@ -7514,7 +7520,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>179</v>
@@ -7535,7 +7541,7 @@
         <v>53</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7575,7 +7581,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>254</v>
@@ -7638,7 +7644,7 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>199</v>
@@ -7659,7 +7665,7 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -10272,10 +10278,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10333,10 +10339,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10386,10 +10392,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10439,10 +10445,10 @@
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10492,10 +10498,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10545,10 +10551,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10598,10 +10604,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10651,10 +10657,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10704,10 +10710,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10757,10 +10763,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10820,10 +10826,10 @@
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10873,10 +10879,10 @@
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10926,10 +10932,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10979,10 +10985,10 @@
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -11032,10 +11038,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11085,10 +11091,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11138,10 +11144,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11191,10 +11197,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="487">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -536,6 +536,9 @@
   </si>
   <si>
     <t>Fabricacion Sensores,Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213886304289396</t>
@@ -4874,7 +4877,7 @@
         <v>46154.86773642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46154.86774770833</v>
+        <v>46212.191994189816</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>173</v>
@@ -4921,8 +4924,8 @@
       <c r="S49" s="9">
         <v>1</v>
       </c>
-      <c r="T49" s="11" t="s">
-        <v>53</v>
+      <c r="T49" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U49" s="11" t="s">
         <v>32</v>
@@ -4930,7 +4933,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4942,7 +4945,7 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4975,7 +4978,7 @@
         <v>110</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4985,7 +4988,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4997,7 +5000,7 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -5027,10 +5030,10 @@
         <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5040,7 +5043,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5050,16 +5053,16 @@
         <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5080,7 +5083,7 @@
         <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>119</v>
@@ -5103,7 +5106,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5119,10 +5122,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5140,13 +5143,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>113</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5162,7 +5165,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5172,16 +5175,16 @@
         <v>46211.83093851852</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5199,13 +5202,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5215,7 +5218,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5227,7 +5230,7 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5257,7 +5260,7 @@
         <v>119</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5280,7 +5283,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5292,7 +5295,7 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5319,13 +5322,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5335,7 +5338,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5347,7 +5350,7 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5374,13 +5377,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5390,7 +5393,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5402,7 +5405,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5426,7 +5429,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5443,7 +5446,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5455,16 +5458,16 @@
         <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5482,13 +5485,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5508,7 +5511,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5520,16 +5523,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5547,13 +5550,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5563,7 +5566,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5575,16 +5578,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5602,13 +5605,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5618,7 +5621,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5630,16 +5633,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5657,13 +5660,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5673,7 +5676,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5685,16 +5688,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5712,13 +5715,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5738,7 +5741,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5750,16 +5753,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5777,13 +5780,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5793,7 +5796,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5805,16 +5808,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5832,13 +5835,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5848,7 +5851,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5860,16 +5863,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5887,13 +5890,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5903,7 +5906,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5921,10 +5924,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5942,13 +5945,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5968,7 +5971,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5980,16 +5983,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -6008,7 +6011,7 @@
         <v>107</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>107</v>
@@ -6021,7 +6024,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6033,16 +6036,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6061,7 +6064,7 @@
         <v>107</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>107</v>
@@ -6074,7 +6077,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6086,16 +6089,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6114,7 +6117,7 @@
         <v>107</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>107</v>
@@ -6127,7 +6130,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6137,16 +6140,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6164,10 +6167,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6190,7 +6193,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6200,16 +6203,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6227,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6243,7 +6246,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6253,16 +6256,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6280,13 +6283,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6296,7 +6299,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6306,16 +6309,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6333,13 +6336,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6349,7 +6352,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6359,7 +6362,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6383,7 +6386,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6396,7 +6399,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6406,16 +6409,16 @@
         <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6431,13 +6434,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6457,7 +6460,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6467,7 +6470,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6491,7 +6494,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6504,7 +6507,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6514,16 +6517,16 @@
         <v>46211.830947395836</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6541,13 +6544,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>170</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6562,12 +6565,12 @@
         <v>31</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6577,16 +6580,16 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6604,13 +6607,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6630,7 +6633,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6640,7 +6643,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6664,7 +6667,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6677,7 +6680,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6687,16 +6690,16 @@
         <v>46118.536602175926</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6714,13 +6717,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6740,7 +6743,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6750,16 +6753,16 @@
         <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6777,13 +6780,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6803,7 +6806,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6813,16 +6816,16 @@
         <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6840,13 +6843,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6856,7 +6859,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6866,16 +6869,16 @@
         <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6893,13 +6896,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6909,7 +6912,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6919,16 +6922,16 @@
         <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6946,13 +6949,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6962,7 +6965,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6972,16 +6975,16 @@
         <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -6999,13 +7002,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7025,7 +7028,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7035,16 +7038,16 @@
         <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7062,13 +7065,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7078,7 +7081,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7088,16 +7091,16 @@
         <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7115,13 +7118,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7131,7 +7134,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7141,16 +7144,16 @@
         <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7168,13 +7171,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7184,7 +7187,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7194,7 +7197,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7218,7 +7221,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7231,7 +7234,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7241,16 +7244,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7268,13 +7271,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>148</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7294,7 +7297,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7310,10 +7313,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7331,13 +7334,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7357,7 +7360,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7367,16 +7370,16 @@
         <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7394,13 +7397,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>130</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7415,12 +7418,12 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7430,16 +7433,16 @@
         <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7457,13 +7460,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>157</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7483,7 +7486,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
@@ -7493,16 +7496,16 @@
         <v>46154.867740671296</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7520,13 +7523,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7541,12 +7544,12 @@
         <v>53</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7556,16 +7559,16 @@
         <v>46118.55096623843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7581,13 +7584,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7607,7 +7610,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7617,16 +7620,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7644,13 +7647,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7665,12 +7668,12 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7680,7 +7683,7 @@
         <v>46118.540081238425</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7704,7 +7707,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7717,7 +7720,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
@@ -7727,7 +7730,7 @@
         <v>46118.540939687504</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7754,13 +7757,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7780,7 +7783,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
@@ -7790,7 +7793,7 @@
         <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7817,13 +7820,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7833,7 +7836,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
@@ -7843,7 +7846,7 @@
         <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7870,13 +7873,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7886,7 +7889,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
@@ -7896,7 +7899,7 @@
         <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7923,13 +7926,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7939,7 +7942,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
@@ -7949,7 +7952,7 @@
         <v>46118.54127469908</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7976,13 +7979,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -8002,7 +8005,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
@@ -8012,7 +8015,7 @@
         <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8039,13 +8042,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8055,7 +8058,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
@@ -8065,7 +8068,7 @@
         <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8092,13 +8095,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8108,7 +8111,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
@@ -8118,7 +8121,7 @@
         <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8145,13 +8148,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8161,7 +8164,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
@@ -8171,7 +8174,7 @@
         <v>46118.54145512731</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8198,13 +8201,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8224,7 +8227,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
@@ -8234,7 +8237,7 @@
         <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8261,13 +8264,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8277,7 +8280,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
@@ -8287,7 +8290,7 @@
         <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8314,13 +8317,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8330,7 +8333,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
@@ -8340,7 +8343,7 @@
         <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8367,13 +8370,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8383,7 +8386,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
@@ -8393,7 +8396,7 @@
         <v>46118.54159421296</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8420,13 +8423,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8446,7 +8449,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
@@ -8456,7 +8459,7 @@
         <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8483,13 +8486,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8499,7 +8502,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
@@ -8509,7 +8512,7 @@
         <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8536,13 +8539,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8552,7 +8555,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
@@ -8562,7 +8565,7 @@
         <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8589,13 +8592,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8605,7 +8608,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
@@ -8615,7 +8618,7 @@
         <v>46118.54175984954</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8642,13 +8645,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8668,7 +8671,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
@@ -8678,7 +8681,7 @@
         <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8705,13 +8708,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8721,7 +8724,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
@@ -8731,7 +8734,7 @@
         <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8758,13 +8761,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8774,7 +8777,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
@@ -8784,7 +8787,7 @@
         <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8811,13 +8814,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8827,7 +8830,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
@@ -8837,7 +8840,7 @@
         <v>46118.54187865741</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8864,13 +8867,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8890,7 +8893,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
@@ -8900,7 +8903,7 @@
         <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8925,13 +8928,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8941,7 +8944,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
@@ -8951,7 +8954,7 @@
         <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8976,13 +8979,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8992,7 +8995,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
@@ -9002,7 +9005,7 @@
         <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9027,13 +9030,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9043,7 +9046,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
@@ -9053,7 +9056,7 @@
         <v>46118.54200872685</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9078,13 +9081,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9104,7 +9107,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B124" s="5">
         <v>46112.680353344906</v>
@@ -9114,7 +9117,7 @@
         <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9139,13 +9142,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9155,7 +9158,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B125" s="8">
         <v>46112.6803614699</v>
@@ -9165,7 +9168,7 @@
         <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9190,13 +9193,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9206,7 +9209,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B126" s="5">
         <v>46112.69493020834</v>
@@ -9216,7 +9219,7 @@
         <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9241,13 +9244,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9257,7 +9260,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B127" s="8">
         <v>46112.68036949074</v>
@@ -9267,7 +9270,7 @@
         <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9291,7 +9294,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9304,7 +9307,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B128" s="5">
         <v>46112.68037429398</v>
@@ -9314,16 +9317,16 @@
         <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I128" s="5">
         <v>46287</v>
@@ -9341,13 +9344,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q128" s="5">
         <v>46287</v>
@@ -9367,7 +9370,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B129" s="8">
         <v>46112.68038334491</v>
@@ -9377,16 +9380,16 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9402,13 +9405,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9418,7 +9421,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B130" s="5">
         <v>46112.68039121528</v>
@@ -9428,16 +9431,16 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9453,13 +9456,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9469,7 +9472,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B131" s="8">
         <v>46112.69787394676</v>
@@ -9479,16 +9482,16 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9504,13 +9507,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9520,7 +9523,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B132" s="5">
         <v>46112.6803999074</v>
@@ -9536,10 +9539,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9555,13 +9558,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9571,7 +9574,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B133" s="8">
         <v>46112.68041137731</v>
@@ -9587,10 +9590,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9606,13 +9609,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9622,7 +9625,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B134" s="5">
         <v>46112.680419027776</v>
@@ -9638,10 +9641,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9657,13 +9660,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9673,7 +9676,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B135" s="8">
         <v>46112.68042700231</v>
@@ -9689,10 +9692,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9708,13 +9711,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9724,7 +9727,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B136" s="5">
         <v>46112.68043466435</v>
@@ -9734,16 +9737,16 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9759,13 +9762,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9775,7 +9778,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B137" s="8">
         <v>46112.68044216435</v>
@@ -9785,7 +9788,7 @@
         <v>46118.54325362269</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9812,13 +9815,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q137" s="8">
         <v>46288</v>
@@ -9838,7 +9841,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B138" s="5">
         <v>46112.68045020833</v>
@@ -9848,7 +9851,7 @@
         <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9875,13 +9878,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9891,7 +9894,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B139" s="8">
         <v>46112.680457615745</v>
@@ -9901,7 +9904,7 @@
         <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9928,13 +9931,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9944,7 +9947,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B140" s="5">
         <v>46112.699333854165</v>
@@ -9954,7 +9957,7 @@
         <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9981,13 +9984,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9997,7 +10000,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B141" s="8">
         <v>46112.68046530093</v>
@@ -10034,13 +10037,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>56</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10050,7 +10053,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B142" s="5">
         <v>46112.6804727662</v>
@@ -10087,13 +10090,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10103,7 +10106,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B143" s="8">
         <v>46112.680524282405</v>
@@ -10140,13 +10143,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10156,7 +10159,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B144" s="5">
         <v>46112.68053547454</v>
@@ -10193,13 +10196,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10209,7 +10212,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B145" s="8">
         <v>46112.68054428241</v>
@@ -10219,7 +10222,7 @@
         <v>46118.54309846065</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10246,13 +10249,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10262,7 +10265,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B146" s="5">
         <v>46112.68055275463</v>
@@ -10272,16 +10275,16 @@
         <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10297,13 +10300,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q146" s="5">
         <v>46293</v>
@@ -10323,7 +10326,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B147" s="8">
         <v>46112.68056386574</v>
@@ -10333,16 +10336,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10360,13 +10363,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10376,7 +10379,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B148" s="5">
         <v>46112.68057167824</v>
@@ -10386,16 +10389,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10413,13 +10416,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10429,7 +10432,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B149" s="8">
         <v>46112.70035509259</v>
@@ -10439,16 +10442,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10466,13 +10469,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10482,7 +10485,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B150" s="5">
         <v>46112.680579479165</v>
@@ -10498,10 +10501,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10519,13 +10522,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10535,7 +10538,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B151" s="8">
         <v>46112.68058722222</v>
@@ -10551,10 +10554,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10572,13 +10575,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10588,7 +10591,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B152" s="5">
         <v>46112.68059523148</v>
@@ -10604,10 +10607,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10625,13 +10628,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10641,7 +10644,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B153" s="8">
         <v>46112.680603472225</v>
@@ -10657,10 +10660,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10678,13 +10681,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10694,7 +10697,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B154" s="5">
         <v>46112.68061105324</v>
@@ -10704,16 +10707,16 @@
         <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10731,13 +10734,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10747,7 +10750,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B155" s="8">
         <v>46112.680618784725</v>
@@ -10757,16 +10760,16 @@
         <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10784,13 +10787,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q155" s="8">
         <v>46294</v>
@@ -10810,7 +10813,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B156" s="5">
         <v>46112.680633553246</v>
@@ -10820,16 +10823,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10847,13 +10850,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10863,7 +10866,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B157" s="8">
         <v>46112.68064251158</v>
@@ -10873,16 +10876,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10900,13 +10903,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10916,7 +10919,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B158" s="5">
         <v>46112.68071581019</v>
@@ -10926,16 +10929,16 @@
         <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10953,13 +10956,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10969,7 +10972,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B159" s="8">
         <v>46112.739142986116</v>
@@ -10979,16 +10982,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -11006,10 +11009,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11022,7 +11025,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B160" s="5">
         <v>46112.68065008102</v>
@@ -11038,10 +11041,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11059,13 +11062,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11075,7 +11078,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B161" s="8">
         <v>46112.680657476856</v>
@@ -11091,10 +11094,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11112,13 +11115,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11128,7 +11131,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B162" s="5">
         <v>46112.68069804399</v>
@@ -11144,10 +11147,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11165,13 +11168,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11181,7 +11184,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B163" s="8">
         <v>46112.68070748843</v>
@@ -11197,10 +11200,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>
@@ -11218,13 +11221,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11234,7 +11237,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B164" s="5">
         <v>46112.68072377315</v>
@@ -11244,7 +11247,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>25</v>
@@ -11268,7 +11271,7 @@
         <v>26</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>26</v>
@@ -11281,7 +11284,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B165" s="8">
         <v>46112.680728148145</v>
@@ -11291,16 +11294,16 @@
         <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I165" s="8">
         <v>46295</v>
@@ -11318,13 +11321,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Q165" s="8">
         <v>46295</v>
@@ -11344,7 +11347,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B166" s="5">
         <v>46112.68073732639</v>
@@ -11354,16 +11357,16 @@
         <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I166" s="5">
         <v>46295</v>
@@ -11381,13 +11384,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Q166" s="5">
         <v>46295</v>
@@ -11407,7 +11410,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B167" s="8">
         <v>46112.68074700232</v>
@@ -11417,7 +11420,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>25</v>
@@ -11441,7 +11444,7 @@
         <v>26</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>26</v>
@@ -11456,7 +11459,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B168" s="5">
         <v>46112.68075140046</v>
@@ -11466,16 +11469,16 @@
         <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I168" s="5">
         <v>46295</v>
@@ -11493,13 +11496,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q168" s="5">
         <v>46295</v>
@@ -11519,7 +11522,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B169" s="8">
         <v>46112.68075989583</v>
@@ -11529,16 +11532,16 @@
         <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I169" s="8">
         <v>46304</v>
@@ -11556,13 +11559,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q169" s="8">
         <v>46304</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -7493,7 +7493,7 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46154.867740671296</v>
+        <v>46216.18165557871</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>315</v>
@@ -7540,8 +7540,8 @@
       <c r="S95" s="9">
         <v>0</v>
       </c>
-      <c r="T95" s="11" t="s">
-        <v>53</v>
+      <c r="T95" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U95" s="12" t="s">
         <v>268</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6687,7 +6687,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46118.536602175926</v>
+        <v>46218.16744653935</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>
@@ -6734,8 +6734,8 @@
       <c r="S81" s="9">
         <v>0</v>
       </c>
-      <c r="T81" s="11" t="s">
-        <v>53</v>
+      <c r="T81" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="U81" s="10" t="s">
         <v>54</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="484">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -307,9 +307,6 @@
     <t>propuesta rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete  ot 4294 - 4296 - 4297</t>
   </si>
   <si>
@@ -326,12 +323,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Check Planos</t>
@@ -3423,11 +3414,9 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H26" s="6"/>
       <c r="I26" s="5">
         <v>46121</v>
       </c>
@@ -3450,7 +3439,7 @@
         <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3470,7 +3459,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="8">
         <v>46112.679452349534</v>
@@ -3482,7 +3471,7 @@
         <v>46135.54582827546</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3515,7 +3504,7 @@
         <v>46</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q27" s="8">
         <v>46121</v>
@@ -3535,7 +3524,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="5">
         <v>46112.67946289352</v>
@@ -3547,17 +3536,15 @@
         <v>46210.7000328588</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>106</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H28" s="6"/>
       <c r="I28" s="5">
         <v>46191</v>
       </c>
@@ -3577,10 +3564,10 @@
         <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q28" s="5">
         <v>46191</v>
@@ -3600,7 +3587,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B29" s="8">
         <v>46112.679478136575</v>
@@ -3612,7 +3599,7 @@
         <v>46123.186628958334</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3645,7 +3632,7 @@
         <v>78</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3665,7 +3652,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46112.67948803241</v>
@@ -3677,17 +3664,15 @@
         <v>46210.700462465276</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>106</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H30" s="6"/>
       <c r="I30" s="5">
         <v>46191</v>
       </c>
@@ -3707,10 +3692,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3730,7 +3715,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B31" s="8">
         <v>46112.67949700232</v>
@@ -3775,7 +3760,7 @@
         <v>85</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3795,7 +3780,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46112.67913506944</v>
@@ -3805,7 +3790,7 @@
         <v>46211.83114751158</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3829,7 +3814,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3842,7 +3827,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B33" s="8">
         <v>46112.679506099536</v>
@@ -3854,16 +3839,16 @@
         <v>46191.8961546875</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3881,13 +3866,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3907,7 +3892,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46112.6795156713</v>
@@ -3919,16 +3904,16 @@
         <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3946,13 +3931,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3972,7 +3957,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B35" s="8">
         <v>46112.67952521991</v>
@@ -3984,16 +3969,16 @@
         <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -4011,13 +3996,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -4037,7 +4022,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B36" s="5">
         <v>46112.67953447917</v>
@@ -4047,16 +4032,16 @@
         <v>46196.634982337964</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -4074,13 +4059,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -4100,7 +4085,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B37" s="8">
         <v>46112.679543101855</v>
@@ -4112,16 +4097,16 @@
         <v>46195.682751747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -4139,13 +4124,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4165,7 +4150,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B38" s="5">
         <v>46112.67955209491</v>
@@ -4175,16 +4160,16 @@
         <v>46195.7109980324</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4202,13 +4187,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="O38" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="O38" s="6" t="s">
-        <v>136</v>
-      </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4226,7 +4211,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B39" s="8">
         <v>46112.67960491898</v>
@@ -4236,16 +4221,16 @@
         <v>46195.71583903935</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4263,13 +4248,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4289,7 +4274,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B40" s="5">
         <v>46112.679614513894</v>
@@ -4301,16 +4286,16 @@
         <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4328,13 +4313,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4354,7 +4339,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B41" s="8">
         <v>46112.67962357639</v>
@@ -4364,16 +4349,16 @@
         <v>46195.71615581018</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4391,13 +4376,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="O41" s="9" t="s">
-        <v>145</v>
-      </c>
       <c r="P41" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4417,7 +4402,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B42" s="5">
         <v>46112.679632581014</v>
@@ -4427,16 +4412,16 @@
         <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4454,13 +4439,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4480,7 +4465,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B43" s="8">
         <v>46112.67964135417</v>
@@ -4492,16 +4477,16 @@
         <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4519,13 +4504,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4545,7 +4530,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B44" s="5">
         <v>46112.67965385417</v>
@@ -4555,16 +4540,16 @@
         <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4582,13 +4567,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="O44" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="O44" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4608,7 +4593,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B45" s="8">
         <v>46112.679662372684</v>
@@ -4620,16 +4605,16 @@
         <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4647,13 +4632,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="O45" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="O45" s="9" t="s">
-        <v>154</v>
-      </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4673,7 +4658,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B46" s="5">
         <v>46112.67967090278</v>
@@ -4685,16 +4670,16 @@
         <v>46211.831143738425</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4712,13 +4697,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4738,7 +4723,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4750,16 +4735,16 @@
         <v>46211.828745949075</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4777,13 +4762,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4803,7 +4788,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4815,16 +4800,16 @@
         <v>46211.83093092593</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4842,13 +4827,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4868,7 +4853,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4880,16 +4865,16 @@
         <v>46212.191994189816</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4907,13 +4892,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4925,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="T49" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U49" s="11" t="s">
         <v>32</v>
@@ -4933,7 +4918,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4945,16 +4930,16 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4972,13 +4957,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4988,7 +4973,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -5000,16 +4985,16 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -5027,13 +5012,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5043,7 +5028,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5053,16 +5038,16 @@
         <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5080,13 +5065,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -5106,7 +5091,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5116,16 +5101,16 @@
         <v>46210.700450081014</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5143,13 +5128,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5165,7 +5150,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5175,16 +5160,16 @@
         <v>46211.83093851852</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5202,13 +5187,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5218,7 +5203,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5230,16 +5215,16 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5257,10 +5242,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5283,7 +5268,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5295,16 +5280,16 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5322,13 +5307,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5338,7 +5323,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5350,16 +5335,16 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5377,13 +5362,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="O57" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="O57" s="9" t="s">
-        <v>197</v>
-      </c>
       <c r="P57" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5393,7 +5378,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5405,7 +5390,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5429,7 +5414,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5446,7 +5431,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5458,16 +5443,16 @@
         <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5485,13 +5470,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5511,7 +5496,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5523,16 +5508,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5550,13 +5535,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5566,7 +5551,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5578,16 +5563,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5605,13 +5590,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5621,7 +5606,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5633,16 +5618,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5660,13 +5645,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5676,7 +5661,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5688,16 +5673,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5715,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5741,7 +5726,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5753,16 +5738,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5780,13 +5765,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="O64" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="O64" s="6" t="s">
-        <v>226</v>
-      </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5796,7 +5781,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5808,16 +5793,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5835,13 +5820,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5851,7 +5836,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5863,16 +5848,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5890,13 +5875,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5906,7 +5891,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5918,16 +5903,16 @@
         <v>46191.201163958336</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5945,13 +5930,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5971,7 +5956,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5983,16 +5968,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -6008,13 +5993,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6024,7 +6009,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6036,16 +6021,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6061,13 +6046,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6077,7 +6062,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6089,16 +6074,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6114,13 +6099,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6130,7 +6115,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6140,16 +6125,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6167,10 +6152,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6193,7 +6178,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6203,16 +6188,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6230,13 +6215,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6246,7 +6231,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6256,16 +6241,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6283,13 +6268,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6299,7 +6284,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6309,16 +6294,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6336,13 +6321,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6352,7 +6337,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6362,7 +6347,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6386,7 +6371,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6399,7 +6384,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6409,16 +6394,16 @@
         <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>255</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>258</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6434,13 +6419,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6460,7 +6445,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6470,7 +6455,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6494,7 +6479,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6507,7 +6492,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6517,16 +6502,16 @@
         <v>46211.830947395836</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6544,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6565,12 +6550,12 @@
         <v>31</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6580,16 +6565,16 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6607,13 +6592,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="O79" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="O79" s="9" t="s">
-        <v>264</v>
-      </c>
       <c r="P79" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6633,7 +6618,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6643,7 +6628,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6667,7 +6652,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6680,7 +6665,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6690,16 +6675,16 @@
         <v>46218.16744653935</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6717,13 +6702,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6735,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="T81" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U81" s="10" t="s">
         <v>54</v>
@@ -6743,7 +6728,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6753,16 +6738,16 @@
         <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6780,13 +6765,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6806,7 +6791,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6816,16 +6801,16 @@
         <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6843,13 +6828,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="O83" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>281</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6859,7 +6844,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6869,16 +6854,16 @@
         <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6896,13 +6881,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6912,7 +6897,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6922,16 +6907,16 @@
         <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6949,13 +6934,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6965,7 +6950,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6975,16 +6960,16 @@
         <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -7002,13 +6987,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7028,7 +7013,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7038,16 +7023,16 @@
         <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7065,13 +7050,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="O87" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="O87" s="9" t="s">
-        <v>293</v>
-      </c>
       <c r="P87" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7081,7 +7066,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7091,16 +7076,16 @@
         <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7118,13 +7103,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7134,7 +7119,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7144,16 +7129,16 @@
         <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7171,13 +7156,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7187,7 +7172,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7197,7 +7182,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7221,7 +7206,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7234,7 +7219,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7244,16 +7229,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7271,13 +7256,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7297,7 +7282,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7313,10 +7298,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7334,13 +7319,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7360,7 +7345,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7370,16 +7355,16 @@
         <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7397,13 +7382,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7418,12 +7403,12 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7433,16 +7418,16 @@
         <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7460,13 +7445,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7486,7 +7471,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
@@ -7496,16 +7481,16 @@
         <v>46216.18165557871</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7523,13 +7508,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7541,15 +7526,15 @@
         <v>0</v>
       </c>
       <c r="T95" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7559,16 +7544,16 @@
         <v>46118.55096623843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7584,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7610,7 +7595,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7620,16 +7605,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7647,13 +7632,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7668,12 +7653,12 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7683,7 +7668,7 @@
         <v>46118.540081238425</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7707,7 +7692,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7720,7 +7705,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
@@ -7730,17 +7715,15 @@
         <v>46118.540939687504</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="9"/>
       <c r="I99" s="8">
         <v>46248</v>
       </c>
@@ -7757,13 +7740,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7783,7 +7766,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
@@ -7793,17 +7776,15 @@
         <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="5">
         <v>46248</v>
       </c>
@@ -7820,13 +7801,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="O100" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="O100" s="6" t="s">
-        <v>330</v>
-      </c>
       <c r="P100" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7836,7 +7817,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
@@ -7846,17 +7827,15 @@
         <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="9"/>
       <c r="I101" s="8">
         <v>46248</v>
       </c>
@@ -7873,13 +7852,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7889,7 +7868,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
@@ -7899,17 +7878,15 @@
         <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
       <c r="I102" s="5">
         <v>46248</v>
       </c>
@@ -7926,13 +7903,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7942,7 +7919,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
@@ -7952,17 +7929,15 @@
         <v>46118.54127469908</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="9"/>
       <c r="I103" s="8">
         <v>46268</v>
       </c>
@@ -7979,13 +7954,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -8005,7 +7980,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
@@ -8015,17 +7990,15 @@
         <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H104" s="6"/>
       <c r="I104" s="5">
         <v>46268</v>
       </c>
@@ -8042,13 +8015,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="O104" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="O104" s="6" t="s">
-        <v>341</v>
-      </c>
       <c r="P104" s="6" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8058,7 +8031,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
@@ -8068,17 +8041,15 @@
         <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="9"/>
       <c r="I105" s="8">
         <v>46268</v>
       </c>
@@ -8095,13 +8066,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8111,7 +8082,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
@@ -8121,17 +8092,15 @@
         <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
       <c r="I106" s="5">
         <v>46268</v>
       </c>
@@ -8148,13 +8117,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8164,7 +8133,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
@@ -8174,17 +8143,15 @@
         <v>46118.54145512731</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H107" s="9"/>
       <c r="I107" s="8">
         <v>46272</v>
       </c>
@@ -8201,13 +8168,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8227,7 +8194,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
@@ -8237,17 +8204,15 @@
         <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="5">
         <v>46272</v>
       </c>
@@ -8264,13 +8229,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>349</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8280,7 +8245,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
@@ -8290,17 +8255,15 @@
         <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="9"/>
       <c r="I109" s="8">
         <v>46272</v>
       </c>
@@ -8317,13 +8280,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8333,7 +8296,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
@@ -8343,17 +8306,15 @@
         <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H110" s="6"/>
       <c r="I110" s="5">
         <v>46272</v>
       </c>
@@ -8370,13 +8331,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8386,7 +8347,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
@@ -8396,17 +8357,15 @@
         <v>46118.54159421296</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="9"/>
       <c r="I111" s="8">
         <v>46274</v>
       </c>
@@ -8423,13 +8382,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8449,7 +8408,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
@@ -8459,17 +8418,15 @@
         <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="5">
         <v>46274</v>
       </c>
@@ -8486,13 +8443,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8502,7 +8459,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
@@ -8512,17 +8469,15 @@
         <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H113" s="9"/>
       <c r="I113" s="8">
         <v>46274</v>
       </c>
@@ -8539,13 +8494,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8555,7 +8510,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
@@ -8565,17 +8520,15 @@
         <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H114" s="6"/>
       <c r="I114" s="5">
         <v>46274</v>
       </c>
@@ -8592,13 +8545,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8608,7 +8561,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
@@ -8618,17 +8571,15 @@
         <v>46118.54175984954</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H115" s="9"/>
       <c r="I115" s="8">
         <v>46276</v>
       </c>
@@ -8645,13 +8596,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8671,7 +8622,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
@@ -8681,17 +8632,15 @@
         <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H116" s="6"/>
       <c r="I116" s="5">
         <v>46276</v>
       </c>
@@ -8708,13 +8657,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="O116" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="P116" s="6" t="s">
         <v>367</v>
-      </c>
-      <c r="O116" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>370</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8724,7 +8673,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
@@ -8734,17 +8683,15 @@
         <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H117" s="9"/>
       <c r="I117" s="8">
         <v>46276</v>
       </c>
@@ -8761,13 +8708,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8777,7 +8724,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
@@ -8787,17 +8734,15 @@
         <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H118" s="6"/>
       <c r="I118" s="5">
         <v>46276</v>
       </c>
@@ -8814,13 +8759,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8830,7 +8775,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
@@ -8840,17 +8785,15 @@
         <v>46118.54187865741</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="9"/>
       <c r="I119" s="8">
         <v>46280</v>
       </c>
@@ -8867,13 +8810,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8893,7 +8836,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
@@ -8903,17 +8846,15 @@
         <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H120" s="6"/>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
         <v>46280</v>
@@ -8928,13 +8869,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8944,7 +8885,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
@@ -8954,17 +8895,15 @@
         <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="9"/>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
         <v>46280</v>
@@ -8979,13 +8918,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8995,7 +8934,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
@@ -9005,17 +8944,15 @@
         <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
         <v>46280</v>
@@ -9030,13 +8967,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9046,7 +8983,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
@@ -9056,17 +8993,15 @@
         <v>46118.54200872685</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="9"/>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
         <v>46286</v>
@@ -9081,13 +9016,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9107,7 +9042,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B124" s="5">
         <v>46112.680353344906</v>
@@ -9117,17 +9052,15 @@
         <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
         <v>46286</v>
@@ -9142,13 +9075,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9158,7 +9091,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B125" s="8">
         <v>46112.6803614699</v>
@@ -9168,17 +9101,15 @@
         <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H125" s="9"/>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
         <v>46286</v>
@@ -9193,13 +9124,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9209,7 +9140,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B126" s="5">
         <v>46112.69493020834</v>
@@ -9219,17 +9150,15 @@
         <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
         <v>46286</v>
@@ -9244,13 +9173,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9260,7 +9189,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B127" s="8">
         <v>46112.68036949074</v>
@@ -9270,7 +9199,7 @@
         <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9294,7 +9223,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9307,7 +9236,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B128" s="5">
         <v>46112.68037429398</v>
@@ -9317,16 +9246,16 @@
         <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I128" s="5">
         <v>46287</v>
@@ -9344,13 +9273,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="Q128" s="5">
         <v>46287</v>
@@ -9370,7 +9299,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B129" s="8">
         <v>46112.68038334491</v>
@@ -9380,16 +9309,16 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9405,13 +9334,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9421,7 +9350,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B130" s="5">
         <v>46112.68039121528</v>
@@ -9431,16 +9360,16 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9456,13 +9385,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9472,7 +9401,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B131" s="8">
         <v>46112.69787394676</v>
@@ -9482,16 +9411,16 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9507,13 +9436,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9523,7 +9452,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B132" s="5">
         <v>46112.6803999074</v>
@@ -9539,10 +9468,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9558,13 +9487,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9574,7 +9503,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B133" s="8">
         <v>46112.68041137731</v>
@@ -9590,10 +9519,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9609,13 +9538,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9625,7 +9554,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B134" s="5">
         <v>46112.680419027776</v>
@@ -9641,10 +9570,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9660,13 +9589,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9676,7 +9605,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B135" s="8">
         <v>46112.68042700231</v>
@@ -9692,10 +9621,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9711,13 +9640,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9727,7 +9656,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B136" s="5">
         <v>46112.68043466435</v>
@@ -9737,16 +9666,16 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9762,13 +9691,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9778,7 +9707,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B137" s="8">
         <v>46112.68044216435</v>
@@ -9788,17 +9717,15 @@
         <v>46118.54325362269</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H137" s="9"/>
       <c r="I137" s="8">
         <v>46288</v>
       </c>
@@ -9815,13 +9742,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="Q137" s="8">
         <v>46288</v>
@@ -9841,7 +9768,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B138" s="5">
         <v>46112.68045020833</v>
@@ -9851,17 +9778,15 @@
         <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H138" s="6"/>
       <c r="I138" s="5">
         <v>46288</v>
       </c>
@@ -9878,13 +9803,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9894,7 +9819,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B139" s="8">
         <v>46112.680457615745</v>
@@ -9904,17 +9829,15 @@
         <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H139" s="9"/>
       <c r="I139" s="8">
         <v>46288</v>
       </c>
@@ -9931,13 +9854,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9947,7 +9870,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B140" s="5">
         <v>46112.699333854165</v>
@@ -9957,17 +9880,15 @@
         <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H140" s="6"/>
       <c r="I140" s="5">
         <v>46288</v>
       </c>
@@ -9984,13 +9905,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10000,7 +9921,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B141" s="8">
         <v>46112.68046530093</v>
@@ -10016,11 +9937,9 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H141" s="9"/>
       <c r="I141" s="8">
         <v>46288</v>
       </c>
@@ -10037,13 +9956,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>56</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10053,7 +9972,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B142" s="5">
         <v>46112.6804727662</v>
@@ -10069,11 +9988,9 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H142" s="6"/>
       <c r="I142" s="5">
         <v>46288</v>
       </c>
@@ -10090,13 +10007,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10106,7 +10023,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B143" s="8">
         <v>46112.680524282405</v>
@@ -10122,11 +10039,9 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H143" s="9"/>
       <c r="I143" s="8">
         <v>46288</v>
       </c>
@@ -10143,13 +10058,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10159,7 +10074,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B144" s="5">
         <v>46112.68053547454</v>
@@ -10175,11 +10090,9 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H144" s="6"/>
       <c r="I144" s="5">
         <v>46288</v>
       </c>
@@ -10196,13 +10109,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10212,7 +10125,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B145" s="8">
         <v>46112.68054428241</v>
@@ -10222,17 +10135,15 @@
         <v>46118.54309846065</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H145" s="9"/>
       <c r="I145" s="8">
         <v>46288</v>
       </c>
@@ -10249,13 +10160,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10265,7 +10176,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B146" s="5">
         <v>46112.68055275463</v>
@@ -10275,16 +10186,16 @@
         <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10300,13 +10211,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="Q146" s="5">
         <v>46293</v>
@@ -10326,7 +10237,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B147" s="8">
         <v>46112.68056386574</v>
@@ -10336,16 +10247,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10363,13 +10274,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="O147" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="P147" s="9" t="s">
         <v>438</v>
-      </c>
-      <c r="O147" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="P147" s="9" t="s">
-        <v>441</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10379,7 +10290,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B148" s="5">
         <v>46112.68057167824</v>
@@ -10389,16 +10300,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10416,13 +10327,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10432,7 +10343,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B149" s="8">
         <v>46112.70035509259</v>
@@ -10442,16 +10353,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10469,13 +10380,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10485,7 +10396,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B150" s="5">
         <v>46112.680579479165</v>
@@ -10501,10 +10412,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10522,13 +10433,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10538,7 +10449,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B151" s="8">
         <v>46112.68058722222</v>
@@ -10554,10 +10465,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10575,13 +10486,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10591,7 +10502,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B152" s="5">
         <v>46112.68059523148</v>
@@ -10607,10 +10518,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10628,13 +10539,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10644,7 +10555,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B153" s="8">
         <v>46112.680603472225</v>
@@ -10660,10 +10571,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10681,13 +10592,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10697,7 +10608,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B154" s="5">
         <v>46112.68061105324</v>
@@ -10707,16 +10618,16 @@
         <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10734,13 +10645,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10750,7 +10661,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B155" s="8">
         <v>46112.680618784725</v>
@@ -10760,16 +10671,16 @@
         <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10787,13 +10698,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="Q155" s="8">
         <v>46294</v>
@@ -10813,7 +10724,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B156" s="5">
         <v>46112.680633553246</v>
@@ -10823,16 +10734,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10850,13 +10761,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10866,7 +10777,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B157" s="8">
         <v>46112.68064251158</v>
@@ -10876,16 +10787,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10903,13 +10814,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10919,7 +10830,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B158" s="5">
         <v>46112.68071581019</v>
@@ -10929,16 +10840,16 @@
         <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10956,13 +10867,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O158" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="P158" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="P158" s="6" t="s">
-        <v>457</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10972,7 +10883,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B159" s="8">
         <v>46112.739142986116</v>
@@ -10982,16 +10893,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -11009,10 +10920,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11025,7 +10936,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B160" s="5">
         <v>46112.68065008102</v>
@@ -11041,10 +10952,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11062,13 +10973,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11078,7 +10989,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B161" s="8">
         <v>46112.680657476856</v>
@@ -11094,10 +11005,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11115,13 +11026,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11131,7 +11042,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B162" s="5">
         <v>46112.68069804399</v>
@@ -11147,10 +11058,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11168,13 +11079,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11184,7 +11095,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B163" s="8">
         <v>46112.68070748843</v>
@@ -11200,10 +11111,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>
@@ -11221,13 +11132,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11237,7 +11148,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B164" s="5">
         <v>46112.68072377315</v>
@@ -11247,7 +11158,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>25</v>
@@ -11271,7 +11182,7 @@
         <v>26</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>26</v>
@@ -11284,7 +11195,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B165" s="8">
         <v>46112.680728148145</v>
@@ -11294,16 +11205,16 @@
         <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I165" s="8">
         <v>46295</v>
@@ -11321,13 +11232,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="Q165" s="8">
         <v>46295</v>
@@ -11347,7 +11258,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B166" s="5">
         <v>46112.68073732639</v>
@@ -11357,16 +11268,16 @@
         <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I166" s="5">
         <v>46295</v>
@@ -11384,13 +11295,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="Q166" s="5">
         <v>46295</v>
@@ -11410,7 +11321,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B167" s="8">
         <v>46112.68074700232</v>
@@ -11420,7 +11331,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>25</v>
@@ -11444,7 +11355,7 @@
         <v>26</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>26</v>
@@ -11459,7 +11370,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B168" s="5">
         <v>46112.68075140046</v>
@@ -11469,16 +11380,16 @@
         <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I168" s="5">
         <v>46295</v>
@@ -11496,13 +11407,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="Q168" s="5">
         <v>46295</v>
@@ -11522,7 +11433,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B169" s="8">
         <v>46112.68075989583</v>
@@ -11532,16 +11443,16 @@
         <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="I169" s="8">
         <v>46304</v>
@@ -11559,13 +11470,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="O169" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="O169" s="9" t="s">
-        <v>483</v>
-      </c>
       <c r="P169" s="9" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="Q169" s="8">
         <v>46304</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -529,319 +529,319 @@
     <t>Fabricacion Sensores,Generacion OC Sensor</t>
   </si>
   <si>
+    <t>1213886304289396</t>
+  </si>
+  <si>
+    <t>Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores,Sensores</t>
+  </si>
+  <si>
+    <t>1213886259313572</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>Sensores,Recepción Sensores</t>
+  </si>
+  <si>
+    <t>1213886259313596</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Check Planos</t>
+  </si>
+  <si>
+    <t>1213902113454390</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886430614804</t>
+  </si>
+  <si>
+    <t>Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297,Check Planos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Control de calidad Fabricación externa</t>
+  </si>
+  <si>
+    <t>1213886259324444</t>
+  </si>
+  <si>
+    <t>Atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>Propuesta Atenuadores ,Fabricacion atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
+  </si>
+  <si>
+    <t>1213886259326766</t>
+  </si>
+  <si>
+    <t>Generacion oc Atenuador  ot 4295</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4295,Atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>1213886259328934</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>Atenuadores,Atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>1213886259328954</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1213902113471352</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213899500210915</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213899500210916</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213899500210917</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886304303088</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213910573903655</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213910573903656</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR 1-14-34/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213910573903657</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR1-14-25/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886181537550</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213910573903658</t>
+  </si>
+  <si>
+    <t>1213910573903659</t>
+  </si>
+  <si>
+    <t>1213910573903660</t>
+  </si>
+  <si>
+    <t>1213886259337472</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886259341627</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886259341647</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213881596172439</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213902113480432</t>
+  </si>
+  <si>
+    <t>Control de calidad</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa</t>
+  </si>
+  <si>
+    <t>1213902113480444</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213902113485641</t>
+  </si>
+  <si>
+    <t>Bodega</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213886181542206</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213886181542236</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>Bodega,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1213902113596084</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Armado,Control de calidad Armado,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1213902113601428</t>
+  </si>
+  <si>
+    <t>Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,Caldereria,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213886304289396</t>
-  </si>
-  <si>
-    <t>Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores,Sensores</t>
-  </si>
-  <si>
-    <t>1213886259313572</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>Sensores,Recepción Sensores</t>
-  </si>
-  <si>
-    <t>1213886259313596</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Check Planos</t>
-  </si>
-  <si>
-    <t>1213902113454390</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886430614804</t>
-  </si>
-  <si>
-    <t>Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297,Check Planos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Control de calidad Fabricación externa</t>
-  </si>
-  <si>
-    <t>1213886259324444</t>
-  </si>
-  <si>
-    <t>Atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>Propuesta Atenuadores ,Fabricacion atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
-  </si>
-  <si>
-    <t>1213886259326766</t>
-  </si>
-  <si>
-    <t>Generacion oc Atenuador  ot 4295</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4295,Atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>1213886259328934</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>Atenuadores,Atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>1213886259328954</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1213902113471352</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213899500210915</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213899500210916</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213899500210917</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886304303088</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213910573903655</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213910573903656</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR 1-14-34/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213910573903657</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR1-14-25/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886181537550</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213910573903658</t>
-  </si>
-  <si>
-    <t>1213910573903659</t>
-  </si>
-  <si>
-    <t>1213910573903660</t>
-  </si>
-  <si>
-    <t>1213886259337472</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886259341627</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886259341647</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213881596172439</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213902113480432</t>
-  </si>
-  <si>
-    <t>Control de calidad</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa</t>
-  </si>
-  <si>
-    <t>1213902113480444</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213902113485641</t>
-  </si>
-  <si>
-    <t>Bodega</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213886181542206</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213886181542236</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Bodega,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1213902113596084</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Armado,Control de calidad Armado,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1213902113601428</t>
-  </si>
-  <si>
-    <t>Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,Caldereria,OT 4296 ZVR1-14-34/4</t>
   </si>
   <si>
     <t>1213886181546547</t>
@@ -4862,7 +4862,7 @@
         <v>46154.86773642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46212.191994189816</v>
+        <v>46220.18905753472</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>170</v>
@@ -4909,8 +4909,8 @@
       <c r="S49" s="9">
         <v>1</v>
       </c>
-      <c r="T49" s="12" t="s">
-        <v>172</v>
+      <c r="T49" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U49" s="11" t="s">
         <v>32</v>
@@ -4918,7 +4918,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4930,7 +4930,7 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4963,7 +4963,7 @@
         <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4973,7 +4973,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4985,7 +4985,7 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -5015,10 +5015,10 @@
         <v>170</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5028,7 +5028,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5038,16 +5038,16 @@
         <v>46181.733022025466</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5068,7 +5068,7 @@
         <v>116</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>116</v>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5107,10 +5107,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>181</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>182</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5128,13 +5128,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>110</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5150,7 +5150,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5160,16 +5160,16 @@
         <v>46211.83093851852</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5187,13 +5187,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5215,7 +5215,7 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5245,7 +5245,7 @@
         <v>116</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5268,7 +5268,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5280,7 +5280,7 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5307,13 +5307,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5323,7 +5323,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5335,7 +5335,7 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5362,13 +5362,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5390,7 +5390,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5414,7 +5414,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5431,7 +5431,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5443,16 +5443,16 @@
         <v>46155.55033484954</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>205</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5470,13 +5470,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5496,7 +5496,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5508,16 +5508,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5535,13 +5535,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5551,7 +5551,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5563,16 +5563,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5590,13 +5590,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5606,7 +5606,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5618,16 +5618,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5645,13 +5645,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5673,16 +5673,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>205</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5700,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5726,7 +5726,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5738,16 +5738,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5765,13 +5765,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5781,7 +5781,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5793,16 +5793,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5820,13 +5820,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5836,7 +5836,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5848,16 +5848,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5875,13 +5875,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5891,7 +5891,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5909,10 +5909,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5930,13 +5930,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5968,16 +5968,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5996,7 +5996,7 @@
         <v>104</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>104</v>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6021,16 +6021,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>210</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>211</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6049,7 +6049,7 @@
         <v>104</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>104</v>
@@ -6062,7 +6062,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6074,16 +6074,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6102,7 +6102,7 @@
         <v>104</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>104</v>
@@ -6115,7 +6115,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6125,16 +6125,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6152,10 +6152,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6178,7 +6178,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6188,16 +6188,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6215,13 +6215,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6231,7 +6231,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6241,16 +6241,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6268,13 +6268,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>244</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>245</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6284,7 +6284,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6294,16 +6294,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6321,13 +6321,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6347,7 +6347,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6371,7 +6371,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6394,16 +6394,16 @@
         <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6419,13 +6419,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6445,7 +6445,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6455,7 +6455,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6479,7 +6479,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6502,16 +6502,16 @@
         <v>46211.830947395836</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6529,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>167</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6550,12 +6550,12 @@
         <v>31</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6565,16 +6565,16 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6592,13 +6592,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6628,7 +6628,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6652,7 +6652,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6675,16 +6675,16 @@
         <v>46218.16744653935</v>
       </c>
       <c r="E81" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6702,13 +6702,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="T81" s="12" t="s">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="U81" s="10" t="s">
         <v>54</v>
@@ -6744,10 +6744,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6765,13 +6765,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6801,16 +6801,16 @@
         <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6854,16 +6854,16 @@
         <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6907,16 +6907,16 @@
         <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6937,7 +6937,7 @@
         <v>278</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>285</v>
@@ -6966,10 +6966,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -6987,13 +6987,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>288</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7023,16 +7023,16 @@
         <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7076,16 +7076,16 @@
         <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7129,16 +7129,16 @@
         <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7159,7 +7159,7 @@
         <v>287</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>296</v>
@@ -7235,10 +7235,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7298,10 +7298,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7361,10 +7361,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7403,7 +7403,7 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7424,10 +7424,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7487,10 +7487,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7511,7 +7511,7 @@
         <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>313</v>
@@ -7526,10 +7526,10 @@
         <v>0</v>
       </c>
       <c r="T95" s="12" t="s">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7550,10 +7550,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7572,7 +7572,7 @@
         <v>298</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>316</v>
@@ -7611,10 +7611,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7635,7 +7635,7 @@
         <v>298</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>319</v>
@@ -7653,7 +7653,7 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7776,7 +7776,7 @@
         <v>46118.55096479166</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7827,7 +7827,7 @@
         <v>46118.55096628472</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7878,7 +7878,7 @@
         <v>46118.54094193287</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7906,7 +7906,7 @@
         <v>324</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>333</v>
@@ -7990,7 +7990,7 @@
         <v>46181.73302627315</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8041,7 +8041,7 @@
         <v>46181.73302378472</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8092,7 +8092,7 @@
         <v>46118.541276550925</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8120,7 +8120,7 @@
         <v>335</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>344</v>
@@ -8204,7 +8204,7 @@
         <v>46181.73302827546</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8255,7 +8255,7 @@
         <v>46181.73302706018</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8306,7 +8306,7 @@
         <v>46118.541456273146</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8334,7 +8334,7 @@
         <v>346</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>354</v>
@@ -8385,7 +8385,7 @@
         <v>321</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>321</v>
@@ -8418,7 +8418,7 @@
         <v>46181.73302760417</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8469,7 +8469,7 @@
         <v>46181.733028946765</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8520,7 +8520,7 @@
         <v>46118.54159666666</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8548,7 +8548,7 @@
         <v>356</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>362</v>
@@ -8632,7 +8632,7 @@
         <v>46181.73302450232</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8683,7 +8683,7 @@
         <v>46181.733029490744</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8734,7 +8734,7 @@
         <v>46118.5417528588</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8762,7 +8762,7 @@
         <v>364</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>372</v>
@@ -8846,7 +8846,7 @@
         <v>46118.54187940972</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8872,7 +8872,7 @@
         <v>374</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>376</v>
@@ -8895,7 +8895,7 @@
         <v>46118.54188027778</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8921,7 +8921,7 @@
         <v>374</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>378</v>
@@ -8944,7 +8944,7 @@
         <v>46118.54188105324</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8970,7 +8970,7 @@
         <v>374</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>380</v>
@@ -9052,7 +9052,7 @@
         <v>46118.547864548615</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9078,7 +9078,7 @@
         <v>382</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>384</v>
@@ -9101,7 +9101,7 @@
         <v>46118.5478628125</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9127,7 +9127,7 @@
         <v>382</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>386</v>
@@ -9150,7 +9150,7 @@
         <v>46118.54786351851</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9176,7 +9176,7 @@
         <v>382</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>388</v>
@@ -9309,7 +9309,7 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9337,7 +9337,7 @@
         <v>393</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>398</v>
@@ -9360,7 +9360,7 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9388,7 +9388,7 @@
         <v>393</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>400</v>
@@ -9411,7 +9411,7 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9439,7 +9439,7 @@
         <v>393</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>402</v>
@@ -9778,7 +9778,7 @@
         <v>46118.54309255787</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9806,7 +9806,7 @@
         <v>414</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>418</v>
@@ -9829,7 +9829,7 @@
         <v>46118.54309331019</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9857,7 +9857,7 @@
         <v>414</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>420</v>
@@ -9880,7 +9880,7 @@
         <v>46118.54314091435</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9908,7 +9908,7 @@
         <v>414</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>422</v>
@@ -10192,10 +10192,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10247,16 +10247,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10277,7 +10277,7 @@
         <v>435</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>438</v>
@@ -10300,16 +10300,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10330,7 +10330,7 @@
         <v>435</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>440</v>
@@ -10353,16 +10353,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10383,10 +10383,10 @@
         <v>435</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10412,10 +10412,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10465,10 +10465,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10518,10 +10518,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10571,10 +10571,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10624,10 +10624,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10677,10 +10677,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10734,16 +10734,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10764,7 +10764,7 @@
         <v>454</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>458</v>
@@ -10787,16 +10787,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10817,7 +10817,7 @@
         <v>454</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>454</v>
@@ -10846,10 +10846,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10893,16 +10893,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H159" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -10923,7 +10923,7 @@
         <v>454</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -10952,10 +10952,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11005,10 +11005,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H161" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11058,10 +11058,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11111,10 +11111,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H163" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -5440,7 +5440,7 @@
         <v>46155.55032041667</v>
       </c>
       <c r="D59" s="8">
-        <v>46155.55033484954</v>
+        <v>46222.150650462965</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>202</v>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46118.540081238425</v>
+        <v>46221.897785625</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>321</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="485">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -307,6 +307,9 @@
     <t>propuesta rodete</t>
   </si>
   <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
     <t>Propuesta compras:,Generación OC Rodete  ot 4294 - 4296 - 4297</t>
   </si>
   <si>
@@ -562,6 +565,9 @@
     <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Check Planos</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213902113454390</t>
   </si>
   <si>
@@ -839,9 +845,6 @@
   </si>
   <si>
     <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,Caldereria,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213886181546547</t>
@@ -3405,7 +3408,7 @@
         <v>46113.808378125</v>
       </c>
       <c r="D26" s="5">
-        <v>46123.186628055555</v>
+        <v>46223.59623494213</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>97</v>
@@ -3414,9 +3417,11 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I26" s="5">
         <v>46121</v>
       </c>
@@ -3439,7 +3444,7 @@
         <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3459,7 +3464,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8">
         <v>46112.679452349534</v>
@@ -3471,7 +3476,7 @@
         <v>46135.54582827546</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3504,7 +3509,7 @@
         <v>46</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="8">
         <v>46121</v>
@@ -3524,7 +3529,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46112.67946289352</v>
@@ -3533,18 +3538,20 @@
         <v>46210.70001560185</v>
       </c>
       <c r="D28" s="5">
-        <v>46210.7000328588</v>
+        <v>46223.596228703704</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I28" s="5">
         <v>46191</v>
       </c>
@@ -3564,10 +3571,10 @@
         <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q28" s="5">
         <v>46191</v>
@@ -3587,7 +3594,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="8">
         <v>46112.679478136575</v>
@@ -3599,7 +3606,7 @@
         <v>46123.186628958334</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3632,7 +3639,7 @@
         <v>78</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3652,7 +3659,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5">
         <v>46112.67948803241</v>
@@ -3661,18 +3668,20 @@
         <v>46210.700444421294</v>
       </c>
       <c r="D30" s="5">
-        <v>46210.700462465276</v>
+        <v>46223.596223217595</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I30" s="5">
         <v>46191</v>
       </c>
@@ -3692,10 +3701,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3715,7 +3724,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="8">
         <v>46112.67949700232</v>
@@ -3760,7 +3769,7 @@
         <v>85</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3780,7 +3789,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46112.67913506944</v>
@@ -3790,7 +3799,7 @@
         <v>46211.83114751158</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3814,7 +3823,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3827,7 +3836,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" s="8">
         <v>46112.679506099536</v>
@@ -3839,16 +3848,16 @@
         <v>46191.8961546875</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3866,13 +3875,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3892,7 +3901,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46112.6795156713</v>
@@ -3904,16 +3913,16 @@
         <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3931,13 +3940,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3957,7 +3966,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="8">
         <v>46112.67952521991</v>
@@ -3969,16 +3978,16 @@
         <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -3996,13 +4005,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -4022,7 +4031,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46112.67953447917</v>
@@ -4032,16 +4041,16 @@
         <v>46196.634982337964</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -4059,13 +4068,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -4085,7 +4094,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="8">
         <v>46112.679543101855</v>
@@ -4097,16 +4106,16 @@
         <v>46195.682751747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -4124,13 +4133,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4150,7 +4159,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" s="5">
         <v>46112.67955209491</v>
@@ -4160,16 +4169,16 @@
         <v>46195.7109980324</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4187,13 +4196,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4211,7 +4220,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>46112.67960491898</v>
@@ -4221,16 +4230,16 @@
         <v>46195.71583903935</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4248,13 +4257,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4274,7 +4283,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" s="5">
         <v>46112.679614513894</v>
@@ -4286,16 +4295,16 @@
         <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4313,13 +4322,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4339,7 +4348,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" s="8">
         <v>46112.67962357639</v>
@@ -4349,16 +4358,16 @@
         <v>46195.71615581018</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4376,13 +4385,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4402,7 +4411,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" s="5">
         <v>46112.679632581014</v>
@@ -4412,16 +4421,16 @@
         <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4439,13 +4448,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4465,7 +4474,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" s="8">
         <v>46112.67964135417</v>
@@ -4477,16 +4486,16 @@
         <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4504,13 +4513,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4530,7 +4539,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" s="5">
         <v>46112.67965385417</v>
@@ -4540,16 +4549,16 @@
         <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4567,13 +4576,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4593,7 +4602,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B45" s="8">
         <v>46112.679662372684</v>
@@ -4605,16 +4614,16 @@
         <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4632,13 +4641,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4658,7 +4667,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B46" s="5">
         <v>46112.67967090278</v>
@@ -4670,16 +4679,16 @@
         <v>46211.831143738425</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4697,13 +4706,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4723,7 +4732,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4735,16 +4744,16 @@
         <v>46211.828745949075</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4762,13 +4771,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4788,7 +4797,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4800,16 +4809,16 @@
         <v>46211.83093092593</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4827,13 +4836,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4853,7 +4862,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4865,16 +4874,16 @@
         <v>46220.18905753472</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4892,13 +4901,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4918,7 +4927,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4930,16 +4939,16 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4957,13 +4966,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4973,7 +4982,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4985,16 +4994,16 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -5012,13 +5021,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5028,26 +5037,26 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46181.733022025466</v>
+        <v>46223.16987143518</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5065,13 +5074,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -5082,8 +5091,8 @@
       <c r="S52" s="6">
         <v>0</v>
       </c>
-      <c r="T52" s="11" t="s">
-        <v>53</v>
+      <c r="T52" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>54</v>
@@ -5091,7 +5100,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5101,16 +5110,16 @@
         <v>46210.700450081014</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5128,13 +5137,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5150,7 +5159,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5160,16 +5169,16 @@
         <v>46211.83093851852</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5187,13 +5196,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5203,7 +5212,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5215,16 +5224,16 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5242,10 +5251,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5268,7 +5277,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5280,16 +5289,16 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5307,13 +5316,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5323,7 +5332,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5335,16 +5344,16 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5362,13 +5371,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5378,7 +5387,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5390,7 +5399,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5414,7 +5423,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5431,7 +5440,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5443,16 +5452,16 @@
         <v>46222.150650462965</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5470,13 +5479,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5496,7 +5505,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5508,16 +5517,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5535,13 +5544,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5551,7 +5560,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5563,16 +5572,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5590,13 +5599,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5606,7 +5615,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5618,16 +5627,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5645,13 +5654,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5661,7 +5670,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5673,16 +5682,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5700,13 +5709,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5726,7 +5735,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5738,16 +5747,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5765,13 +5774,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5781,7 +5790,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5793,16 +5802,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5820,13 +5829,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5836,7 +5845,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5848,16 +5857,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5875,13 +5884,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5891,7 +5900,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5903,16 +5912,16 @@
         <v>46191.201163958336</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5930,13 +5939,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5956,7 +5965,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5968,16 +5977,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5993,13 +6002,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6009,7 +6018,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6021,16 +6030,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6046,13 +6055,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6062,7 +6071,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6074,16 +6083,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6099,13 +6108,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6115,7 +6124,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6125,16 +6134,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6152,10 +6161,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6178,7 +6187,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6188,16 +6197,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6215,13 +6224,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6231,7 +6240,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6241,16 +6250,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6268,13 +6277,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6284,7 +6293,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6294,16 +6303,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6321,13 +6330,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6337,7 +6346,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6347,7 +6356,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6371,7 +6380,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6384,7 +6393,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6394,16 +6403,16 @@
         <v>46118.55096918982</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6419,13 +6428,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6445,7 +6454,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6455,7 +6464,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6479,7 +6488,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6492,7 +6501,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6502,16 +6511,16 @@
         <v>46211.830947395836</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6529,13 +6538,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6550,12 +6559,12 @@
         <v>31</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6565,16 +6574,16 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6592,13 +6601,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6618,7 +6627,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6628,7 +6637,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6652,7 +6661,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6665,7 +6674,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6675,16 +6684,16 @@
         <v>46218.16744653935</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6702,13 +6711,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6720,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="T81" s="12" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="U81" s="10" t="s">
         <v>54</v>
@@ -6728,7 +6737,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6738,16 +6747,16 @@
         <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6765,13 +6774,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6791,7 +6800,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6801,16 +6810,16 @@
         <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6828,13 +6837,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6844,7 +6853,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6854,16 +6863,16 @@
         <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6881,13 +6890,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6897,7 +6906,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6907,16 +6916,16 @@
         <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6934,13 +6943,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6950,7 +6959,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6960,16 +6969,16 @@
         <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -6987,13 +6996,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7013,7 +7022,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7023,16 +7032,16 @@
         <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7050,13 +7059,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7066,7 +7075,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7076,16 +7085,16 @@
         <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7103,13 +7112,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7119,7 +7128,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7129,16 +7138,16 @@
         <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7156,13 +7165,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7172,7 +7181,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7182,7 +7191,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7206,7 +7215,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7219,7 +7228,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7229,16 +7238,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7256,13 +7265,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7282,7 +7291,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7298,10 +7307,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7319,13 +7328,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7345,7 +7354,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7355,16 +7364,16 @@
         <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7382,13 +7391,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7403,12 +7412,12 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7418,16 +7427,16 @@
         <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7445,13 +7454,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7471,26 +7480,26 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46216.18165557871</v>
+        <v>46223.16801311343</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7508,13 +7517,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7526,15 +7535,15 @@
         <v>0</v>
       </c>
       <c r="T95" s="12" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7544,16 +7553,16 @@
         <v>46118.55096623843</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7569,13 +7578,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7595,7 +7604,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7605,16 +7614,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7632,13 +7641,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7653,12 +7662,12 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7668,7 +7677,7 @@
         <v>46221.897785625</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7692,7 +7701,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7705,25 +7714,27 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46118.540939687504</v>
+        <v>46223.60165059028</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I99" s="8">
         <v>46248</v>
       </c>
@@ -7740,13 +7751,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7766,25 +7777,27 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46118.55096479166</v>
+        <v>46223.59635119213</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I100" s="5">
         <v>46248</v>
       </c>
@@ -7801,13 +7814,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7817,25 +7830,27 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46118.55096628472</v>
+        <v>46223.59635047454</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I101" s="8">
         <v>46248</v>
       </c>
@@ -7852,13 +7867,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7868,25 +7883,27 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46118.54094193287</v>
+        <v>46223.59634974537</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I102" s="5">
         <v>46248</v>
       </c>
@@ -7903,13 +7920,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7919,25 +7936,27 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46118.54127469908</v>
+        <v>46223.60164991899</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I103" s="8">
         <v>46268</v>
       </c>
@@ -7954,13 +7973,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -7980,25 +7999,27 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46181.73302627315</v>
+        <v>46223.59661136574</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I104" s="5">
         <v>46268</v>
       </c>
@@ -8015,13 +8036,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8031,25 +8052,27 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46181.73302378472</v>
+        <v>46223.59661070602</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I105" s="8">
         <v>46268</v>
       </c>
@@ -8066,13 +8089,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8082,25 +8105,27 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46118.541276550925</v>
+        <v>46223.59661008102</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I106" s="5">
         <v>46268</v>
       </c>
@@ -8117,13 +8142,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8133,25 +8158,27 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46118.54145512731</v>
+        <v>46223.60164922454</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I107" s="8">
         <v>46272</v>
       </c>
@@ -8168,13 +8195,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8194,25 +8221,27 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46181.73302827546</v>
+        <v>46223.59850755787</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I108" s="5">
         <v>46272</v>
       </c>
@@ -8229,13 +8258,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8245,25 +8274,27 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46181.73302706018</v>
+        <v>46223.598506875</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I109" s="8">
         <v>46272</v>
       </c>
@@ -8280,13 +8311,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8296,25 +8327,27 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46118.541456273146</v>
+        <v>46223.59850623843</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I110" s="5">
         <v>46272</v>
       </c>
@@ -8331,13 +8364,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8347,25 +8380,27 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46118.54159421296</v>
+        <v>46223.60164861111</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I111" s="8">
         <v>46274</v>
       </c>
@@ -8382,13 +8417,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8408,25 +8443,27 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46181.73302760417</v>
+        <v>46223.59859461806</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I112" s="5">
         <v>46274</v>
       </c>
@@ -8443,13 +8480,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8459,25 +8496,27 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46181.733028946765</v>
+        <v>46223.598594027775</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I113" s="8">
         <v>46274</v>
       </c>
@@ -8494,13 +8533,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8510,25 +8549,27 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46118.54159666666</v>
+        <v>46223.598593414354</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I114" s="5">
         <v>46274</v>
       </c>
@@ -8545,13 +8586,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8561,25 +8602,27 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46118.54175984954</v>
+        <v>46223.60164790509</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I115" s="8">
         <v>46276</v>
       </c>
@@ -8596,13 +8639,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8622,25 +8665,27 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46181.73302450232</v>
+        <v>46223.59868443287</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H116" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I116" s="5">
         <v>46276</v>
       </c>
@@ -8657,13 +8702,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8673,25 +8718,27 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46181.733029490744</v>
+        <v>46223.59868380787</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I117" s="8">
         <v>46276</v>
       </c>
@@ -8708,13 +8755,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8724,25 +8771,27 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46118.5417528588</v>
+        <v>46223.59868314815</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I118" s="5">
         <v>46276</v>
       </c>
@@ -8759,13 +8808,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8775,25 +8824,27 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46118.54187865741</v>
+        <v>46223.60164731482</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I119" s="8">
         <v>46280</v>
       </c>
@@ -8810,13 +8861,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8836,25 +8887,27 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46118.54187940972</v>
+        <v>46223.598781168985</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
         <v>46280</v>
@@ -8869,13 +8922,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8885,25 +8938,27 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46118.54188027778</v>
+        <v>46223.59878049769</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
         <v>46280</v>
@@ -8918,13 +8973,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8934,25 +8989,27 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46118.54188105324</v>
+        <v>46223.598779803244</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
         <v>46280</v>
@@ -8967,13 +9024,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8983,25 +9040,27 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46118.54200872685</v>
+        <v>46223.60164671297</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
         <v>46286</v>
@@ -9016,13 +9075,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9042,25 +9101,27 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B124" s="5">
         <v>46112.680353344906</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46118.547864548615</v>
+        <v>46223.59886346065</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
         <v>46286</v>
@@ -9075,13 +9136,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9091,25 +9152,27 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B125" s="8">
         <v>46112.6803614699</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46118.5478628125</v>
+        <v>46223.59886280092</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
         <v>46286</v>
@@ -9124,13 +9187,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9140,25 +9203,27 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B126" s="5">
         <v>46112.69493020834</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46118.54786351851</v>
+        <v>46223.59886211806</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
         <v>46286</v>
@@ -9173,13 +9238,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9189,7 +9254,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B127" s="8">
         <v>46112.68036949074</v>
@@ -9199,7 +9264,7 @@
         <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9223,7 +9288,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9236,7 +9301,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B128" s="5">
         <v>46112.68037429398</v>
@@ -9246,16 +9311,16 @@
         <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I128" s="5">
         <v>46287</v>
@@ -9273,13 +9338,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q128" s="5">
         <v>46287</v>
@@ -9299,7 +9364,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B129" s="8">
         <v>46112.68038334491</v>
@@ -9309,16 +9374,16 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9334,13 +9399,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9350,7 +9415,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B130" s="5">
         <v>46112.68039121528</v>
@@ -9360,16 +9425,16 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9385,13 +9450,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9401,7 +9466,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B131" s="8">
         <v>46112.69787394676</v>
@@ -9411,16 +9476,16 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9436,13 +9501,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9452,7 +9517,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B132" s="5">
         <v>46112.6803999074</v>
@@ -9468,10 +9533,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9487,13 +9552,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9503,7 +9568,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B133" s="8">
         <v>46112.68041137731</v>
@@ -9519,10 +9584,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9538,13 +9603,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9554,7 +9619,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B134" s="5">
         <v>46112.680419027776</v>
@@ -9570,10 +9635,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9589,13 +9654,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9605,7 +9670,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B135" s="8">
         <v>46112.68042700231</v>
@@ -9621,10 +9686,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9640,13 +9705,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9656,7 +9721,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B136" s="5">
         <v>46112.68043466435</v>
@@ -9666,16 +9731,16 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9691,13 +9756,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9707,25 +9772,27 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B137" s="8">
         <v>46112.68044216435</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46118.54325362269</v>
+        <v>46223.601863715274</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H137" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I137" s="8">
         <v>46288</v>
       </c>
@@ -9742,13 +9809,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q137" s="8">
         <v>46288</v>
@@ -9768,25 +9835,27 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B138" s="5">
         <v>46112.68045020833</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46118.54309255787</v>
+        <v>46223.60177635417</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H138" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I138" s="5">
         <v>46288</v>
       </c>
@@ -9803,13 +9872,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9819,25 +9888,27 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B139" s="8">
         <v>46112.680457615745</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46118.54309331019</v>
+        <v>46223.601775636576</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H139" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I139" s="8">
         <v>46288</v>
       </c>
@@ -9854,13 +9925,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9870,25 +9941,27 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B140" s="5">
         <v>46112.699333854165</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46118.54314091435</v>
+        <v>46223.601775</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H140" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I140" s="5">
         <v>46288</v>
       </c>
@@ -9905,13 +9978,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9921,14 +9994,14 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B141" s="8">
         <v>46112.68046530093</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46118.54309490741</v>
+        <v>46223.60177436343</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>56</v>
@@ -9937,9 +10010,11 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H141" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I141" s="8">
         <v>46288</v>
       </c>
@@ -9956,13 +10031,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>56</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9972,14 +10047,14 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B142" s="5">
         <v>46112.6804727662</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46118.54309578704</v>
+        <v>46223.60177366898</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>60</v>
@@ -9988,9 +10063,11 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H142" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I142" s="5">
         <v>46288</v>
       </c>
@@ -10007,13 +10084,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10023,14 +10100,14 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B143" s="8">
         <v>46112.680524282405</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46118.54309662037</v>
+        <v>46223.60177299769</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>63</v>
@@ -10039,9 +10116,11 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H143" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I143" s="8">
         <v>46288</v>
       </c>
@@ -10058,13 +10137,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10074,14 +10153,14 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B144" s="5">
         <v>46112.68053547454</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46118.54309747685</v>
+        <v>46223.60177233796</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>66</v>
@@ -10090,9 +10169,11 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H144" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I144" s="5">
         <v>46288</v>
       </c>
@@ -10109,13 +10190,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10125,25 +10206,27 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B145" s="8">
         <v>46112.68054428241</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46118.54309846065</v>
+        <v>46223.60177167824</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H145" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I145" s="8">
         <v>46288</v>
       </c>
@@ -10160,13 +10243,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10176,7 +10259,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B146" s="5">
         <v>46112.68055275463</v>
@@ -10186,16 +10269,16 @@
         <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10211,13 +10294,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q146" s="5">
         <v>46293</v>
@@ -10237,7 +10320,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B147" s="8">
         <v>46112.68056386574</v>
@@ -10247,16 +10330,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10274,13 +10357,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10290,7 +10373,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B148" s="5">
         <v>46112.68057167824</v>
@@ -10300,16 +10383,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10327,13 +10410,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10343,7 +10426,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B149" s="8">
         <v>46112.70035509259</v>
@@ -10353,16 +10436,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10380,13 +10463,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10396,7 +10479,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B150" s="5">
         <v>46112.680579479165</v>
@@ -10412,10 +10495,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10433,13 +10516,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10449,7 +10532,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B151" s="8">
         <v>46112.68058722222</v>
@@ -10465,10 +10548,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10486,13 +10569,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10502,7 +10585,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B152" s="5">
         <v>46112.68059523148</v>
@@ -10518,10 +10601,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10539,13 +10622,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10555,7 +10638,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B153" s="8">
         <v>46112.680603472225</v>
@@ -10571,10 +10654,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10592,13 +10675,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10608,7 +10691,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B154" s="5">
         <v>46112.68061105324</v>
@@ -10618,16 +10701,16 @@
         <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10645,13 +10728,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10661,7 +10744,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B155" s="8">
         <v>46112.680618784725</v>
@@ -10671,16 +10754,16 @@
         <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10698,13 +10781,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q155" s="8">
         <v>46294</v>
@@ -10724,7 +10807,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B156" s="5">
         <v>46112.680633553246</v>
@@ -10734,16 +10817,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10761,13 +10844,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10777,7 +10860,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B157" s="8">
         <v>46112.68064251158</v>
@@ -10787,16 +10870,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10814,13 +10897,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10830,7 +10913,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B158" s="5">
         <v>46112.68071581019</v>
@@ -10840,16 +10923,16 @@
         <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10867,13 +10950,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10883,7 +10966,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B159" s="8">
         <v>46112.739142986116</v>
@@ -10893,16 +10976,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -10920,10 +11003,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -10936,7 +11019,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B160" s="5">
         <v>46112.68065008102</v>
@@ -10952,10 +11035,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -10973,13 +11056,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10989,7 +11072,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B161" s="8">
         <v>46112.680657476856</v>
@@ -11005,10 +11088,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11026,13 +11109,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11042,7 +11125,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B162" s="5">
         <v>46112.68069804399</v>
@@ -11058,10 +11141,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11079,13 +11162,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11095,7 +11178,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B163" s="8">
         <v>46112.68070748843</v>
@@ -11111,10 +11194,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>
@@ -11132,13 +11215,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11148,7 +11231,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B164" s="5">
         <v>46112.68072377315</v>
@@ -11158,7 +11241,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>25</v>
@@ -11182,7 +11265,7 @@
         <v>26</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>26</v>
@@ -11195,7 +11278,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B165" s="8">
         <v>46112.680728148145</v>
@@ -11205,16 +11288,16 @@
         <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I165" s="8">
         <v>46295</v>
@@ -11232,13 +11315,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q165" s="8">
         <v>46295</v>
@@ -11258,7 +11341,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B166" s="5">
         <v>46112.68073732639</v>
@@ -11268,16 +11351,16 @@
         <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I166" s="5">
         <v>46295</v>
@@ -11295,13 +11378,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q166" s="5">
         <v>46295</v>
@@ -11321,7 +11404,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B167" s="8">
         <v>46112.68074700232</v>
@@ -11331,7 +11414,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>25</v>
@@ -11355,7 +11438,7 @@
         <v>26</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>26</v>
@@ -11370,7 +11453,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B168" s="5">
         <v>46112.68075140046</v>
@@ -11380,16 +11463,16 @@
         <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I168" s="5">
         <v>46295</v>
@@ -11407,13 +11490,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Q168" s="5">
         <v>46295</v>
@@ -11433,7 +11516,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B169" s="8">
         <v>46112.68075989583</v>
@@ -11443,16 +11526,16 @@
         <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I169" s="8">
         <v>46304</v>
@@ -11470,13 +11553,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Q169" s="8">
         <v>46304</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6400,7 +6400,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46118.55096918982</v>
+        <v>46224.181076203706</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>253</v>
@@ -6445,8 +6445,8 @@
       <c r="S76" s="6">
         <v>0</v>
       </c>
-      <c r="T76" s="11" t="s">
-        <v>53</v>
+      <c r="T76" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="U76" s="11" t="s">
         <v>32</v>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46223.16801311343</v>
+        <v>46224.16695678241</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>313</v>
@@ -7534,8 +7534,8 @@
       <c r="S95" s="9">
         <v>0</v>
       </c>
-      <c r="T95" s="12" t="s">
-        <v>184</v>
+      <c r="T95" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U95" s="12" t="s">
         <v>266</v>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46118.55096623843</v>
+        <v>46224.181076319444</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>316</v>
@@ -7595,8 +7595,8 @@
       <c r="S96" s="6">
         <v>0</v>
       </c>
-      <c r="T96" s="11" t="s">
-        <v>53</v>
+      <c r="T96" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="U96" s="10" t="s">
         <v>54</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6681,7 +6681,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46218.16744653935</v>
+        <v>46225.16763715278</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>274</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="486">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>propuesta rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -3420,7 +3423,7 @@
         <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -3444,7 +3447,7 @@
         <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3464,7 +3467,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="8">
         <v>46112.679452349534</v>
@@ -3476,7 +3479,7 @@
         <v>46135.54582827546</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3509,7 +3512,7 @@
         <v>46</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="8">
         <v>46121</v>
@@ -3529,7 +3532,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46112.67946289352</v>
@@ -3541,7 +3544,7 @@
         <v>46223.596228703704</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3550,7 +3553,7 @@
         <v>98</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46191</v>
@@ -3571,10 +3574,10 @@
         <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q28" s="5">
         <v>46191</v>
@@ -3594,7 +3597,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" s="8">
         <v>46112.679478136575</v>
@@ -3606,7 +3609,7 @@
         <v>46123.186628958334</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3639,7 +3642,7 @@
         <v>78</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3659,7 +3662,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5">
         <v>46112.67948803241</v>
@@ -3671,7 +3674,7 @@
         <v>46223.596223217595</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3680,7 +3683,7 @@
         <v>98</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46191</v>
@@ -3701,10 +3704,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3724,7 +3727,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" s="8">
         <v>46112.67949700232</v>
@@ -3769,7 +3772,7 @@
         <v>85</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3789,7 +3792,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46112.67913506944</v>
@@ -3799,7 +3802,7 @@
         <v>46211.83114751158</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3823,7 +3826,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3836,7 +3839,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="8">
         <v>46112.679506099536</v>
@@ -3848,16 +3851,16 @@
         <v>46191.8961546875</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3875,13 +3878,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3901,7 +3904,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46112.6795156713</v>
@@ -3913,16 +3916,16 @@
         <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3940,13 +3943,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3966,7 +3969,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="8">
         <v>46112.67952521991</v>
@@ -3978,16 +3981,16 @@
         <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -4005,13 +4008,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -4031,7 +4034,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46112.67953447917</v>
@@ -4041,16 +4044,16 @@
         <v>46196.634982337964</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -4068,13 +4071,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -4094,7 +4097,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46112.679543101855</v>
@@ -4106,16 +4109,16 @@
         <v>46195.682751747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -4133,13 +4136,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4159,7 +4162,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46112.67955209491</v>
@@ -4169,16 +4172,16 @@
         <v>46195.7109980324</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4196,13 +4199,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4220,7 +4223,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B39" s="8">
         <v>46112.67960491898</v>
@@ -4230,16 +4233,16 @@
         <v>46195.71583903935</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4257,13 +4260,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4283,7 +4286,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B40" s="5">
         <v>46112.679614513894</v>
@@ -4295,16 +4298,16 @@
         <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4322,13 +4325,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4348,7 +4351,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B41" s="8">
         <v>46112.67962357639</v>
@@ -4358,16 +4361,16 @@
         <v>46195.71615581018</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4385,13 +4388,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4411,7 +4414,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46112.679632581014</v>
@@ -4421,16 +4424,16 @@
         <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4448,13 +4451,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4474,7 +4477,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46112.67964135417</v>
@@ -4486,16 +4489,16 @@
         <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4513,13 +4516,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4539,7 +4542,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46112.67965385417</v>
@@ -4549,16 +4552,16 @@
         <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4576,13 +4579,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4602,7 +4605,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8">
         <v>46112.679662372684</v>
@@ -4614,16 +4617,16 @@
         <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4641,13 +4644,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4667,7 +4670,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46112.67967090278</v>
@@ -4679,16 +4682,16 @@
         <v>46211.831143738425</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4706,13 +4709,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4732,7 +4735,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4744,16 +4747,16 @@
         <v>46211.828745949075</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4771,13 +4774,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4797,7 +4800,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4809,16 +4812,16 @@
         <v>46211.83093092593</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4836,13 +4839,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4862,7 +4865,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4874,16 +4877,16 @@
         <v>46220.18905753472</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4901,13 +4904,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4927,7 +4930,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4939,16 +4942,16 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4966,13 +4969,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4982,7 +4985,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4994,16 +4997,16 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -5021,13 +5024,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5037,7 +5040,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5047,16 +5050,16 @@
         <v>46223.16987143518</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5074,13 +5077,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -5092,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>54</v>
@@ -5100,7 +5103,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5110,16 +5113,16 @@
         <v>46210.700450081014</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5137,13 +5140,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5159,7 +5162,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5169,16 +5172,16 @@
         <v>46211.83093851852</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5196,13 +5199,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5212,7 +5215,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5224,16 +5227,16 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5251,10 +5254,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5277,7 +5280,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5289,16 +5292,16 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5316,13 +5319,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5332,7 +5335,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5344,16 +5347,16 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5371,13 +5374,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5387,7 +5390,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5399,7 +5402,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5423,7 +5426,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5440,7 +5443,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5452,16 +5455,16 @@
         <v>46222.150650462965</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5479,13 +5482,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5505,7 +5508,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5517,16 +5520,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5544,13 +5547,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5560,7 +5563,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5572,16 +5575,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5599,13 +5602,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>78</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5615,7 +5618,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5627,16 +5630,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5654,13 +5657,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5670,7 +5673,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5682,16 +5685,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5709,13 +5712,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5735,7 +5738,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5747,16 +5750,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5774,13 +5777,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5790,7 +5793,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5802,16 +5805,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5829,13 +5832,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5845,7 +5848,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5857,16 +5860,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5884,13 +5887,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5900,7 +5903,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5912,16 +5915,16 @@
         <v>46191.201163958336</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5939,13 +5942,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5965,7 +5968,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5977,16 +5980,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -6002,13 +6005,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6018,7 +6021,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6030,16 +6033,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6055,13 +6058,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6071,7 +6074,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6083,16 +6086,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6108,13 +6111,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6124,7 +6127,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6134,16 +6137,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6161,10 +6164,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6187,7 +6190,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6197,16 +6200,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6224,13 +6227,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6240,7 +6243,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6250,16 +6253,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6277,13 +6280,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6293,7 +6296,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6303,16 +6306,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6330,13 +6333,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6346,7 +6349,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6356,7 +6359,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6380,7 +6383,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6393,7 +6396,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6403,16 +6406,16 @@
         <v>46224.181076203706</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6428,13 +6431,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6446,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U76" s="11" t="s">
         <v>32</v>
@@ -6454,7 +6457,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6464,7 +6467,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6488,7 +6491,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6501,7 +6504,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6511,16 +6514,16 @@
         <v>46211.830947395836</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6538,13 +6541,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6559,12 +6562,12 @@
         <v>31</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6574,16 +6577,16 @@
         <v>46179.167811527775</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6601,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6627,7 +6630,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6637,7 +6640,7 @@
         <v>46118.53693787037</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6661,7 +6664,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6674,7 +6677,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6684,16 +6687,16 @@
         <v>46225.16763715278</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6711,13 +6714,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6729,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="T81" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U81" s="10" t="s">
         <v>54</v>
@@ -6737,7 +6740,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6747,16 +6750,16 @@
         <v>46118.53671</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6774,13 +6777,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6800,7 +6803,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6810,16 +6813,16 @@
         <v>46181.73302506944</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6837,13 +6840,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6853,7 +6856,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6863,16 +6866,16 @@
         <v>46181.73302986111</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6890,13 +6893,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6906,7 +6909,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6916,16 +6919,16 @@
         <v>46118.53646400463</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6943,13 +6946,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6959,7 +6962,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6969,16 +6972,16 @@
         <v>46118.53739798611</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -6996,13 +6999,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7022,7 +7025,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7032,16 +7035,16 @@
         <v>46181.733025787034</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7059,13 +7062,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7075,7 +7078,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7085,16 +7088,16 @@
         <v>46181.73302309027</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7112,13 +7115,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7128,7 +7131,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7138,16 +7141,16 @@
         <v>46118.53739997685</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7165,13 +7168,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7181,7 +7184,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7191,7 +7194,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7215,7 +7218,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7228,7 +7231,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7238,16 +7241,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7265,13 +7268,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7291,7 +7294,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7307,10 +7310,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7328,13 +7331,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7354,7 +7357,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7364,16 +7367,16 @@
         <v>46191.89613979167</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7391,13 +7394,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7412,12 +7415,12 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7427,16 +7430,16 @@
         <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7454,13 +7457,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7480,7 +7483,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
@@ -7490,16 +7493,16 @@
         <v>46224.16695678241</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7517,13 +7520,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7538,12 +7541,12 @@
         <v>31</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7553,16 +7556,16 @@
         <v>46224.181076319444</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7578,13 +7581,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7596,7 +7599,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U96" s="10" t="s">
         <v>54</v>
@@ -7604,7 +7607,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7614,16 +7617,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7641,13 +7644,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7662,12 +7665,12 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7677,7 +7680,7 @@
         <v>46221.897785625</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7701,7 +7704,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7714,7 +7717,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
@@ -7724,7 +7727,7 @@
         <v>46223.60165059028</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7733,7 +7736,7 @@
         <v>98</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I99" s="8">
         <v>46248</v>
@@ -7751,13 +7754,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7777,7 +7780,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
@@ -7787,7 +7790,7 @@
         <v>46223.59635119213</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7796,7 +7799,7 @@
         <v>98</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I100" s="5">
         <v>46248</v>
@@ -7814,13 +7817,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7830,7 +7833,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
@@ -7840,7 +7843,7 @@
         <v>46223.59635047454</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7849,7 +7852,7 @@
         <v>98</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I101" s="8">
         <v>46248</v>
@@ -7867,13 +7870,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7883,7 +7886,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
@@ -7893,7 +7896,7 @@
         <v>46223.59634974537</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7902,7 +7905,7 @@
         <v>98</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I102" s="5">
         <v>46248</v>
@@ -7920,13 +7923,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7936,7 +7939,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
@@ -7946,7 +7949,7 @@
         <v>46223.60164991899</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7955,7 +7958,7 @@
         <v>98</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I103" s="8">
         <v>46268</v>
@@ -7973,13 +7976,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -7999,7 +8002,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
@@ -8009,7 +8012,7 @@
         <v>46223.59661136574</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8018,7 +8021,7 @@
         <v>98</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I104" s="5">
         <v>46268</v>
@@ -8036,13 +8039,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8052,7 +8055,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
@@ -8062,7 +8065,7 @@
         <v>46223.59661070602</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8071,7 +8074,7 @@
         <v>98</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I105" s="8">
         <v>46268</v>
@@ -8089,13 +8092,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8105,7 +8108,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
@@ -8115,7 +8118,7 @@
         <v>46223.59661008102</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8124,7 +8127,7 @@
         <v>98</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I106" s="5">
         <v>46268</v>
@@ -8142,13 +8145,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8158,7 +8161,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
@@ -8168,7 +8171,7 @@
         <v>46223.60164922454</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8177,7 +8180,7 @@
         <v>98</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I107" s="8">
         <v>46272</v>
@@ -8195,13 +8198,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8221,7 +8224,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
@@ -8231,7 +8234,7 @@
         <v>46223.59850755787</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8240,7 +8243,7 @@
         <v>98</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I108" s="5">
         <v>46272</v>
@@ -8258,13 +8261,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8274,7 +8277,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
@@ -8284,7 +8287,7 @@
         <v>46223.598506875</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8293,7 +8296,7 @@
         <v>98</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I109" s="8">
         <v>46272</v>
@@ -8311,13 +8314,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8327,7 +8330,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
@@ -8337,7 +8340,7 @@
         <v>46223.59850623843</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8346,7 +8349,7 @@
         <v>98</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I110" s="5">
         <v>46272</v>
@@ -8364,13 +8367,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8380,7 +8383,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
@@ -8390,7 +8393,7 @@
         <v>46223.60164861111</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8399,7 +8402,7 @@
         <v>98</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I111" s="8">
         <v>46274</v>
@@ -8417,13 +8420,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8443,7 +8446,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
@@ -8453,7 +8456,7 @@
         <v>46223.59859461806</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8462,7 +8465,7 @@
         <v>98</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I112" s="5">
         <v>46274</v>
@@ -8480,13 +8483,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8496,7 +8499,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
@@ -8506,7 +8509,7 @@
         <v>46223.598594027775</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8515,7 +8518,7 @@
         <v>98</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I113" s="8">
         <v>46274</v>
@@ -8533,13 +8536,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8549,7 +8552,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
@@ -8559,7 +8562,7 @@
         <v>46223.598593414354</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8568,7 +8571,7 @@
         <v>98</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I114" s="5">
         <v>46274</v>
@@ -8586,13 +8589,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8602,7 +8605,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
@@ -8612,7 +8615,7 @@
         <v>46223.60164790509</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8621,7 +8624,7 @@
         <v>98</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I115" s="8">
         <v>46276</v>
@@ -8639,13 +8642,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8665,7 +8668,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
@@ -8675,7 +8678,7 @@
         <v>46223.59868443287</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8684,7 +8687,7 @@
         <v>98</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I116" s="5">
         <v>46276</v>
@@ -8702,13 +8705,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8718,7 +8721,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
@@ -8728,7 +8731,7 @@
         <v>46223.59868380787</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8737,7 +8740,7 @@
         <v>98</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I117" s="8">
         <v>46276</v>
@@ -8755,13 +8758,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8771,7 +8774,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
@@ -8781,7 +8784,7 @@
         <v>46223.59868314815</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8790,7 +8793,7 @@
         <v>98</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I118" s="5">
         <v>46276</v>
@@ -8808,13 +8811,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8824,7 +8827,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
@@ -8834,7 +8837,7 @@
         <v>46223.60164731482</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8843,7 +8846,7 @@
         <v>98</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I119" s="8">
         <v>46280</v>
@@ -8861,13 +8864,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8887,7 +8890,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
@@ -8897,7 +8900,7 @@
         <v>46223.598781168985</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8906,7 +8909,7 @@
         <v>98</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8922,13 +8925,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8938,7 +8941,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
@@ -8948,7 +8951,7 @@
         <v>46223.59878049769</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8957,7 +8960,7 @@
         <v>98</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8973,13 +8976,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8989,7 +8992,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
@@ -8999,7 +9002,7 @@
         <v>46223.598779803244</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9008,7 +9011,7 @@
         <v>98</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -9024,13 +9027,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9040,7 +9043,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
@@ -9050,7 +9053,7 @@
         <v>46223.60164671297</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9059,7 +9062,7 @@
         <v>98</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -9075,13 +9078,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9101,7 +9104,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B124" s="5">
         <v>46112.680353344906</v>
@@ -9111,7 +9114,7 @@
         <v>46223.59886346065</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9120,7 +9123,7 @@
         <v>98</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -9136,13 +9139,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9152,7 +9155,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B125" s="8">
         <v>46112.6803614699</v>
@@ -9162,7 +9165,7 @@
         <v>46223.59886280092</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9171,7 +9174,7 @@
         <v>98</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -9187,13 +9190,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9203,7 +9206,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B126" s="5">
         <v>46112.69493020834</v>
@@ -9213,7 +9216,7 @@
         <v>46223.59886211806</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9222,7 +9225,7 @@
         <v>98</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -9238,13 +9241,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9254,7 +9257,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B127" s="8">
         <v>46112.68036949074</v>
@@ -9264,7 +9267,7 @@
         <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9288,7 +9291,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9301,7 +9304,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B128" s="5">
         <v>46112.68037429398</v>
@@ -9311,16 +9314,16 @@
         <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I128" s="5">
         <v>46287</v>
@@ -9338,13 +9341,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q128" s="5">
         <v>46287</v>
@@ -9364,7 +9367,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B129" s="8">
         <v>46112.68038334491</v>
@@ -9374,16 +9377,16 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9399,13 +9402,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9415,7 +9418,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B130" s="5">
         <v>46112.68039121528</v>
@@ -9425,16 +9428,16 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9450,13 +9453,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9466,7 +9469,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B131" s="8">
         <v>46112.69787394676</v>
@@ -9476,16 +9479,16 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9501,13 +9504,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9517,7 +9520,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B132" s="5">
         <v>46112.6803999074</v>
@@ -9533,10 +9536,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9552,13 +9555,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9568,7 +9571,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B133" s="8">
         <v>46112.68041137731</v>
@@ -9584,10 +9587,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9603,13 +9606,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9619,7 +9622,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B134" s="5">
         <v>46112.680419027776</v>
@@ -9635,10 +9638,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9654,13 +9657,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9670,7 +9673,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B135" s="8">
         <v>46112.68042700231</v>
@@ -9686,10 +9689,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9705,13 +9708,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9721,7 +9724,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B136" s="5">
         <v>46112.68043466435</v>
@@ -9731,16 +9734,16 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9756,13 +9759,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9772,7 +9775,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B137" s="8">
         <v>46112.68044216435</v>
@@ -9782,7 +9785,7 @@
         <v>46223.601863715274</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9791,7 +9794,7 @@
         <v>98</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I137" s="8">
         <v>46288</v>
@@ -9809,13 +9812,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q137" s="8">
         <v>46288</v>
@@ -9835,7 +9838,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B138" s="5">
         <v>46112.68045020833</v>
@@ -9845,7 +9848,7 @@
         <v>46223.60177635417</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9854,7 +9857,7 @@
         <v>98</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I138" s="5">
         <v>46288</v>
@@ -9872,13 +9875,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9888,7 +9891,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B139" s="8">
         <v>46112.680457615745</v>
@@ -9898,7 +9901,7 @@
         <v>46223.601775636576</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9907,7 +9910,7 @@
         <v>98</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I139" s="8">
         <v>46288</v>
@@ -9925,13 +9928,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9941,7 +9944,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B140" s="5">
         <v>46112.699333854165</v>
@@ -9951,7 +9954,7 @@
         <v>46223.601775</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9960,7 +9963,7 @@
         <v>98</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I140" s="5">
         <v>46288</v>
@@ -9978,13 +9981,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9994,7 +9997,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B141" s="8">
         <v>46112.68046530093</v>
@@ -10013,7 +10016,7 @@
         <v>98</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I141" s="8">
         <v>46288</v>
@@ -10031,13 +10034,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>56</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10047,7 +10050,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B142" s="5">
         <v>46112.6804727662</v>
@@ -10066,7 +10069,7 @@
         <v>98</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I142" s="5">
         <v>46288</v>
@@ -10084,13 +10087,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10100,7 +10103,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B143" s="8">
         <v>46112.680524282405</v>
@@ -10119,7 +10122,7 @@
         <v>98</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I143" s="8">
         <v>46288</v>
@@ -10137,13 +10140,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10153,7 +10156,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B144" s="5">
         <v>46112.68053547454</v>
@@ -10172,7 +10175,7 @@
         <v>98</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I144" s="5">
         <v>46288</v>
@@ -10190,13 +10193,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10206,7 +10209,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B145" s="8">
         <v>46112.68054428241</v>
@@ -10216,7 +10219,7 @@
         <v>46223.60177167824</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10225,7 +10228,7 @@
         <v>98</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I145" s="8">
         <v>46288</v>
@@ -10243,13 +10246,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10259,7 +10262,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B146" s="5">
         <v>46112.68055275463</v>
@@ -10269,16 +10272,16 @@
         <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10294,13 +10297,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q146" s="5">
         <v>46293</v>
@@ -10320,7 +10323,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B147" s="8">
         <v>46112.68056386574</v>
@@ -10330,16 +10333,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10357,13 +10360,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10373,7 +10376,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B148" s="5">
         <v>46112.68057167824</v>
@@ -10383,16 +10386,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10410,13 +10413,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10426,7 +10429,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B149" s="8">
         <v>46112.70035509259</v>
@@ -10436,16 +10439,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10463,13 +10466,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10479,7 +10482,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B150" s="5">
         <v>46112.680579479165</v>
@@ -10495,10 +10498,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10516,13 +10519,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10532,7 +10535,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B151" s="8">
         <v>46112.68058722222</v>
@@ -10548,10 +10551,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10569,13 +10572,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10585,7 +10588,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B152" s="5">
         <v>46112.68059523148</v>
@@ -10601,10 +10604,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10622,13 +10625,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10638,7 +10641,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B153" s="8">
         <v>46112.680603472225</v>
@@ -10654,10 +10657,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10675,13 +10678,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10691,7 +10694,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B154" s="5">
         <v>46112.68061105324</v>
@@ -10701,16 +10704,16 @@
         <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10728,13 +10731,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10744,7 +10747,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B155" s="8">
         <v>46112.680618784725</v>
@@ -10754,16 +10757,16 @@
         <v>46118.54392340277</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10781,13 +10784,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q155" s="8">
         <v>46294</v>
@@ -10807,7 +10810,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B156" s="5">
         <v>46112.680633553246</v>
@@ -10817,16 +10820,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10844,13 +10847,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10860,7 +10863,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B157" s="8">
         <v>46112.68064251158</v>
@@ -10870,16 +10873,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10897,13 +10900,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10913,7 +10916,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B158" s="5">
         <v>46112.68071581019</v>
@@ -10923,16 +10926,16 @@
         <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10950,13 +10953,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10966,7 +10969,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B159" s="8">
         <v>46112.739142986116</v>
@@ -10976,16 +10979,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -11003,10 +11006,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11019,7 +11022,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B160" s="5">
         <v>46112.68065008102</v>
@@ -11035,10 +11038,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11056,13 +11059,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11072,7 +11075,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B161" s="8">
         <v>46112.680657476856</v>
@@ -11088,10 +11091,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11109,13 +11112,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>60</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11125,7 +11128,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B162" s="5">
         <v>46112.68069804399</v>
@@ -11141,10 +11144,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11162,13 +11165,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11178,7 +11181,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B163" s="8">
         <v>46112.68070748843</v>
@@ -11194,10 +11197,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>
@@ -11215,13 +11218,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11231,7 +11234,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B164" s="5">
         <v>46112.68072377315</v>
@@ -11241,7 +11244,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>25</v>
@@ -11265,7 +11268,7 @@
         <v>26</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>26</v>
@@ -11278,7 +11281,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B165" s="8">
         <v>46112.680728148145</v>
@@ -11288,16 +11291,16 @@
         <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I165" s="8">
         <v>46295</v>
@@ -11315,13 +11318,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q165" s="8">
         <v>46295</v>
@@ -11341,7 +11344,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B166" s="5">
         <v>46112.68073732639</v>
@@ -11351,16 +11354,16 @@
         <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I166" s="5">
         <v>46295</v>
@@ -11378,13 +11381,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q166" s="5">
         <v>46295</v>
@@ -11404,7 +11407,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B167" s="8">
         <v>46112.68074700232</v>
@@ -11414,7 +11417,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>25</v>
@@ -11438,7 +11441,7 @@
         <v>26</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>26</v>
@@ -11453,7 +11456,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B168" s="5">
         <v>46112.68075140046</v>
@@ -11463,16 +11466,16 @@
         <v>46118.54421137732</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I168" s="5">
         <v>46295</v>
@@ -11490,13 +11493,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q168" s="5">
         <v>46295</v>
@@ -11516,7 +11519,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B169" s="8">
         <v>46112.68075989583</v>
@@ -11526,16 +11529,16 @@
         <v>46118.544324525465</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I169" s="8">
         <v>46304</v>
@@ -11553,13 +11556,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Q169" s="8">
         <v>46304</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6684,7 +6684,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46225.16763715278</v>
+        <v>46226.20781865741</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>275</v>
@@ -6731,8 +6731,8 @@
       <c r="S81" s="9">
         <v>0</v>
       </c>
-      <c r="T81" s="12" t="s">
-        <v>185</v>
+      <c r="T81" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U81" s="10" t="s">
         <v>54</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -790,6 +790,9 @@
     <t>Control de calidad,Recepcion Fabricacion externa</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213902113485641</t>
   </si>
   <si>
@@ -812,9 +815,6 @@
   </si>
   <si>
     <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213886181542236</t>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46211.83114751158</v>
+        <v>46227.61942258102</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>118</v>
@@ -5045,9 +5045,11 @@
       <c r="B52" s="5">
         <v>46112.67972244213</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46227.61941313658</v>
+      </c>
       <c r="D52" s="5">
-        <v>46223.16987143518</v>
+        <v>46227.61992457176</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>181</v>
@@ -5092,13 +5094,13 @@
         <v>46230</v>
       </c>
       <c r="S52" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="U52" s="10" t="s">
-        <v>54</v>
+      <c r="U52" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -5108,9 +5110,11 @@
       <c r="B53" s="8">
         <v>46112.67973174769</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46227.61934708334</v>
+      </c>
       <c r="D53" s="8">
-        <v>46210.700450081014</v>
+        <v>46227.61934873843</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>114</v>
@@ -5167,9 +5171,11 @@
       <c r="B54" s="5">
         <v>46112.679776261575</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46227.61939721065</v>
+      </c>
       <c r="D54" s="5">
-        <v>46211.83093851852</v>
+        <v>46227.619398842595</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -6403,7 +6409,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46224.181076203706</v>
+        <v>46227.6194165162</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>254</v>
@@ -6451,13 +6457,13 @@
       <c r="T76" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="U76" s="11" t="s">
-        <v>32</v>
+      <c r="U76" s="12" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6467,7 +6473,7 @@
         <v>46114.74446109954</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6491,7 +6497,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6504,7 +6510,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6514,16 +6520,16 @@
         <v>46211.830947395836</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6541,13 +6547,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6562,7 +6568,7 @@
         <v>31</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6604,10 +6610,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>270</v>
@@ -7247,10 +7253,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7310,10 +7316,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7373,10 +7379,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7415,7 +7421,7 @@
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7436,10 +7442,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7499,10 +7505,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7541,7 +7547,7 @@
         <v>31</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7562,10 +7568,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7623,10 +7629,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7665,7 +7671,7 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -415,6 +415,9 @@
     <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301,Fabricación Tablero OT 4298 - 4299 -4300 -4301</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213886259285184</t>
   </si>
   <si>
@@ -566,9 +569,6 @@
   </si>
   <si>
     <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Check Planos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213902113454390</t>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46196.634982337964</v>
+        <v>46231.207182708335</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>132</v>
@@ -4088,8 +4088,8 @@
       <c r="S36" s="6">
         <v>0</v>
       </c>
-      <c r="T36" s="11" t="s">
-        <v>53</v>
+      <c r="T36" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="U36" s="10" t="s">
         <v>54</v>
@@ -4097,7 +4097,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46112.679543101855</v>
@@ -4109,7 +4109,7 @@
         <v>46195.682751747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -4142,7 +4142,7 @@
         <v>102</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46112.67955209491</v>
@@ -4172,7 +4172,7 @@
         <v>46195.7109980324</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -4202,10 +4202,10 @@
         <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46112.67960491898</v>
@@ -4233,7 +4233,7 @@
         <v>46195.71583903935</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -4263,7 +4263,7 @@
         <v>118</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>118</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46112.679614513894</v>
@@ -4298,7 +4298,7 @@
         <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4325,13 +4325,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4351,7 +4351,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46112.67962357639</v>
@@ -4361,7 +4361,7 @@
         <v>46195.71615581018</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
@@ -4388,13 +4388,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46112.679632581014</v>
@@ -4424,7 +4424,7 @@
         <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4454,7 +4454,7 @@
         <v>118</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>118</v>
@@ -4477,7 +4477,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46112.67964135417</v>
@@ -4489,7 +4489,7 @@
         <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4516,13 +4516,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4542,7 +4542,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46112.67965385417</v>
@@ -4552,7 +4552,7 @@
         <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4579,13 +4579,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B45" s="8">
         <v>46112.679662372684</v>
@@ -4617,7 +4617,7 @@
         <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4644,13 +4644,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4670,7 +4670,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46112.67967090278</v>
@@ -4682,16 +4682,16 @@
         <v>46211.831143738425</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4712,7 +4712,7 @@
         <v>118</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>118</v>
@@ -4735,7 +4735,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4753,10 +4753,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4774,13 +4774,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4812,16 +4812,16 @@
         <v>46211.83093092593</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4839,13 +4839,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4877,16 +4877,16 @@
         <v>46220.18905753472</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4907,7 +4907,7 @@
         <v>118</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>118</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4942,16 +4942,16 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4969,13 +4969,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4997,16 +4997,16 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -5024,13 +5024,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5049,19 +5049,19 @@
         <v>46227.61941313658</v>
       </c>
       <c r="D52" s="5">
-        <v>46227.61992457176</v>
+        <v>46231.19795877315</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5082,7 +5082,7 @@
         <v>118</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>118</v>
@@ -5096,8 +5096,8 @@
       <c r="S52" s="6">
         <v>1</v>
       </c>
-      <c r="T52" s="12" t="s">
-        <v>185</v>
+      <c r="T52" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U52" s="11" t="s">
         <v>32</v>
@@ -5123,10 +5123,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5144,7 +5144,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>112</v>
@@ -5184,10 +5184,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5205,7 +5205,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>190</v>
@@ -6455,7 +6455,7 @@
         <v>0</v>
       </c>
       <c r="T76" s="12" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="U76" s="12" t="s">
         <v>259</v>
@@ -6550,7 +6550,7 @@
         <v>261</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>267</v>
@@ -7277,7 +7277,7 @@
         <v>300</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>304</v>
@@ -7340,7 +7340,7 @@
         <v>300</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>306</v>
@@ -7466,7 +7466,7 @@
         <v>300</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>312</v>
@@ -7529,7 +7529,7 @@
         <v>300</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>315</v>
@@ -7605,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="T96" s="12" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="U96" s="10" t="s">
         <v>54</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46227.6194165162</v>
+        <v>46232.188831238425</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>254</v>
@@ -6454,8 +6454,8 @@
       <c r="S76" s="6">
         <v>0</v>
       </c>
-      <c r="T76" s="12" t="s">
-        <v>134</v>
+      <c r="T76" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U76" s="12" t="s">
         <v>259</v>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46224.181076319444</v>
+        <v>46232.1888305787</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>317</v>
@@ -7604,8 +7604,8 @@
       <c r="S96" s="6">
         <v>0</v>
       </c>
-      <c r="T96" s="12" t="s">
-        <v>134</v>
+      <c r="T96" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U96" s="10" t="s">
         <v>54</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -7307,7 +7307,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46118.551773541665</v>
+        <v>46233.16826490741</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>57</v>
@@ -7354,8 +7354,8 @@
       <c r="S92" s="6">
         <v>0</v>
       </c>
-      <c r="T92" s="11" t="s">
-        <v>53</v>
+      <c r="T92" s="12" t="s">
+        <v>134</v>
       </c>
       <c r="U92" s="10" t="s">
         <v>54</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6643,7 +6643,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46118.53693787037</v>
+        <v>46237.53630173611</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>272</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6470,7 +6470,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.74446109954</v>
+        <v>46237.84762954861</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>261</v>
@@ -6578,9 +6578,11 @@
       <c r="B79" s="8">
         <v>46112.679890740736</v>
       </c>
-      <c r="C79" s="9"/>
+      <c r="C79" s="8">
+        <v>46237.84762318287</v>
+      </c>
       <c r="D79" s="8">
-        <v>46179.167811527775</v>
+        <v>46237.847639803236</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>
@@ -6625,13 +6627,13 @@
         <v>46178</v>
       </c>
       <c r="S79" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U79" s="10" t="s">
-        <v>54</v>
+      <c r="U79" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6690,7 +6692,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46226.20781865741</v>
+        <v>46237.847639803236</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>275</v>
@@ -6740,8 +6742,8 @@
       <c r="T81" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U81" s="10" t="s">
-        <v>54</v>
+      <c r="U81" s="12" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="486">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -586,7 +586,7 @@
     <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297,Check Planos,Planos preliminar</t>
   </si>
   <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Control de calidad Fabricación externa</t>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Control de calidad Fabricación externa  4294 - 4296 - 4297</t>
   </si>
   <si>
     <t>1213886259324444</t>
@@ -775,7 +775,7 @@
     <t>Control de calidad</t>
   </si>
   <si>
-    <t>Control de calidad Fabricación externa</t>
+    <t>Control de calidad Fabricación externa  4294 - 4296 - 4297</t>
   </si>
   <si>
     <t>1213902113480444</t>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46232.188831238425</v>
+        <v>46237.86113535879</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>254</v>
@@ -6468,9 +6468,11 @@
       <c r="B77" s="8">
         <v>46112.6798790162</v>
       </c>
-      <c r="C77" s="9"/>
+      <c r="C77" s="8">
+        <v>46237.86031974537</v>
+      </c>
       <c r="D77" s="8">
-        <v>46237.84762954861</v>
+        <v>46237.86033361111</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>261</v>
@@ -6504,9 +6506,13 @@
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
-      <c r="S77" s="9"/>
+      <c r="S77" s="9">
+        <v>1</v>
+      </c>
       <c r="T77" s="9"/>
-      <c r="U77" s="9"/>
+      <c r="U77" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
@@ -6515,9 +6521,11 @@
       <c r="B78" s="5">
         <v>46112.6798825463</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46237.86030320602</v>
+      </c>
       <c r="D78" s="5">
-        <v>46211.830947395836</v>
+        <v>46237.86031981482</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>264</v>
@@ -6562,13 +6570,13 @@
         <v>46176</v>
       </c>
       <c r="S78" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U78" s="12" t="s">
-        <v>259</v>
+      <c r="U78" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6582,7 +6590,7 @@
         <v>46237.84762318287</v>
       </c>
       <c r="D79" s="8">
-        <v>46237.847639803236</v>
+        <v>46237.86032310185</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>
@@ -6632,8 +6640,8 @@
       <c r="T79" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U79" s="11" t="s">
-        <v>32</v>
+      <c r="U79" s="12" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -388,6 +388,9 @@
     <t>Generación OC Alabe  ot 4294 - 4296 - 4297,Fabricación Alabe  ot 4294 - 4296 - 4297</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213886304257151</t>
   </si>
   <si>
@@ -413,9 +416,6 @@
   </si>
   <si>
     <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301,Fabricación Tablero OT 4298 - 4299 -4300 -4301</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213886259285184</t>
@@ -3848,7 +3848,7 @@
         <v>46191.89613496528</v>
       </c>
       <c r="D33" s="8">
-        <v>46191.8961546875</v>
+        <v>46238.20096541666</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>121</v>
@@ -3895,8 +3895,8 @@
       <c r="S33" s="9">
         <v>1</v>
       </c>
-      <c r="T33" s="11" t="s">
-        <v>53</v>
+      <c r="T33" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="U33" s="11" t="s">
         <v>32</v>
@@ -3904,7 +3904,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46112.6795156713</v>
@@ -3916,7 +3916,7 @@
         <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3949,7 +3949,7 @@
         <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46112.67952521991</v>
@@ -3981,7 +3981,7 @@
         <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -4011,10 +4011,10 @@
         <v>121</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -4034,17 +4034,17 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46112.67953447917</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46231.207182708335</v>
+        <v>46238.16768791666</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -4074,7 +4074,7 @@
         <v>118</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>118</v>
@@ -4089,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="12" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="U36" s="10" t="s">
         <v>54</v>
@@ -4136,7 +4136,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>102</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46195.7109980324</v>
+        <v>46238.167686064815</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4199,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>136</v>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46118.53671</v>
+        <v>46238.20096488426</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>280</v>
@@ -6810,8 +6810,8 @@
       <c r="S82" s="6">
         <v>0</v>
       </c>
-      <c r="T82" s="11" t="s">
-        <v>53</v>
+      <c r="T82" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="U82" s="10" t="s">
         <v>54</v>
@@ -7365,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="12" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="U92" s="10" t="s">
         <v>54</v>
@@ -7413,7 +7413,7 @@
         <v>300</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>309</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -4041,7 +4041,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46238.16768791666</v>
+        <v>46239.19380061343</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>133</v>
@@ -4088,8 +4088,8 @@
       <c r="S36" s="6">
         <v>0</v>
       </c>
-      <c r="T36" s="12" t="s">
-        <v>125</v>
+      <c r="T36" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U36" s="10" t="s">
         <v>54</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46237.86113535879</v>
+        <v>46239.167648125</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>254</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46232.1888305787</v>
+        <v>46239.16765043982</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>317</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -172,232 +172,232 @@
     <t>OT 4300- TABLERO BOTONERA,OT 4301-COMPONENTES TABLERO COMPUERTAS,OT 4299- TABLERO PLC,OT 4298- TABLERO VDF ABB ACS880-17</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1213886430561132</t>
+  </si>
+  <si>
+    <t>OT 4298- TABLERO VDF ABB ACS880-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Tableros y componentes electricos </t>
+  </si>
+  <si>
+    <t>OT 4298- TABLERO VDF ABB ACS880-17,Revisión tableros pruebas</t>
+  </si>
+  <si>
+    <t>1213886380443185</t>
+  </si>
+  <si>
+    <t>OT 4299- TABLERO PLC</t>
+  </si>
+  <si>
+    <t>OT 4299- TABLERO PLC,Revisión tableros pruebas</t>
+  </si>
+  <si>
+    <t>1213886380443205</t>
+  </si>
+  <si>
+    <t>OT 4300- TABLERO BOTONERA</t>
+  </si>
+  <si>
+    <t>Revisión tableros pruebas,OT 4300- TABLERO BOTONERA</t>
+  </si>
+  <si>
+    <t>1213886181433136</t>
+  </si>
+  <si>
+    <t>OT 4301-COMPONENTES TABLERO COMPUERTAS</t>
+  </si>
+  <si>
+    <t>Revisión tableros pruebas,OT 4301-COMPONENTES TABLERO COMPUERTAS</t>
+  </si>
+  <si>
+    <t>1213881596172402</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Analisis de costeo,Ingenieria Basica Motor,Ingenieria basica nucleo Rodete</t>
+  </si>
+  <si>
+    <t>1213886430565726</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,propuesta motor,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>1213886430566983</t>
+  </si>
+  <si>
+    <t>Ingenieria basica nucleo Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,propuesta alabes,propuesta rodete,Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>1213886430567012</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Propuesta Sensores,Analisis de costeo,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297,Planos preliminar,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886181447052</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica nucleo Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213886181449313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria Atenuador </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Atenuadores </t>
+  </si>
+  <si>
+    <t>1213881596172404</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>Propuesta Sensores,propuesta motor,propuesta rodete,propuesta tableros,propuesta tableros,propuesta alabes,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213886181428729</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Generación OC motor  ot 4294 - 4296 - 4297,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1213886259261835</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4294 - 4296 - 4297,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1213886380480795</t>
+  </si>
+  <si>
+    <t>propuesta rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886259267316</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1213886259270650</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
+    <t>Generación OC materiales ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886181474378</t>
+  </si>
+  <si>
+    <t>Propuesta Sensores</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>1213886181474407</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Check Planos</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886380494178</t>
+  </si>
+  <si>
+    <t>Atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
+  </si>
+  <si>
+    <t>1213881596172406</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301,Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:,Rodete  ot 4294 - 4296 - 4297,Sensores,Alabe  ot 4294 - 4296 - 4297,Motor  ot 4294 - 4296 - 4297,Fabricacion Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886380496282</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4294 - 4296 - 4297,Fabricación Alabe  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886304257151</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4294 - 4296 - 4297,Fabricación Alabe  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213886430561132</t>
-  </si>
-  <si>
-    <t>OT 4298- TABLERO VDF ABB ACS880-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Tableros y componentes electricos </t>
-  </si>
-  <si>
-    <t>OT 4298- TABLERO VDF ABB ACS880-17,Revisión tableros pruebas</t>
-  </si>
-  <si>
-    <t>1213886380443185</t>
-  </si>
-  <si>
-    <t>OT 4299- TABLERO PLC</t>
-  </si>
-  <si>
-    <t>OT 4299- TABLERO PLC,Revisión tableros pruebas</t>
-  </si>
-  <si>
-    <t>1213886380443205</t>
-  </si>
-  <si>
-    <t>OT 4300- TABLERO BOTONERA</t>
-  </si>
-  <si>
-    <t>Revisión tableros pruebas,OT 4300- TABLERO BOTONERA</t>
-  </si>
-  <si>
-    <t>1213886181433136</t>
-  </si>
-  <si>
-    <t>OT 4301-COMPONENTES TABLERO COMPUERTAS</t>
-  </si>
-  <si>
-    <t>Revisión tableros pruebas,OT 4301-COMPONENTES TABLERO COMPUERTAS</t>
-  </si>
-  <si>
-    <t>1213881596172402</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Analisis de costeo,Ingenieria Basica Motor,Ingenieria basica nucleo Rodete</t>
-  </si>
-  <si>
-    <t>1213886430565726</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,propuesta motor,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1213886430566983</t>
-  </si>
-  <si>
-    <t>Ingenieria basica nucleo Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,propuesta alabes,propuesta rodete,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1213886430567012</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Propuesta Sensores,Analisis de costeo,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297,Planos preliminar,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886181447052</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica nucleo Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213886181449313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria Atenuador </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Atenuadores </t>
-  </si>
-  <si>
-    <t>1213881596172404</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Propuesta Sensores,propuesta motor,propuesta rodete,propuesta tableros,propuesta tableros,propuesta alabes,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213886181428729</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Generación OC motor  ot 4294 - 4296 - 4297,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1213886259261835</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4294 - 4296 - 4297,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1213886380480795</t>
-  </si>
-  <si>
-    <t>propuesta rodete</t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886259267316</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros OT 4298 - 4299 -4300 -4301,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1213886259270650</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
-  </si>
-  <si>
-    <t>Generación OC materiales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886181474378</t>
-  </si>
-  <si>
-    <t>Propuesta Sensores</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>1213886181474407</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Check Planos</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886380494178</t>
-  </si>
-  <si>
-    <t>Atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
-  </si>
-  <si>
-    <t>1213881596172406</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Tablero y componentes electricos  OT 4298 - 4299 -4300 -4301,Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:,Rodete  ot 4294 - 4296 - 4297,Sensores,Alabe  ot 4294 - 4296 - 4297,Motor  ot 4294 - 4296 - 4297,Fabricacion Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886380496282</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4294 - 4296 - 4297,Fabricación Alabe  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1213886304257151</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4294 - 4296 - 4297,Fabricación Alabe  ot 4294 - 4296 - 4297</t>
   </si>
   <si>
     <t>1213886304258305</t>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46112.679385428244</v>
+        <v>46240.18768121528</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2622,7 +2622,7 @@
       <c r="S12" s="6">
         <v>0</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="T12" s="12" t="s">
         <v>53</v>
       </c>
       <c r="U12" s="10" t="s">
@@ -3896,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="U33" s="11" t="s">
         <v>32</v>
@@ -3904,7 +3904,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46112.6795156713</v>
@@ -3916,7 +3916,7 @@
         <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3949,7 +3949,7 @@
         <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>54</v>
@@ -4011,7 +4011,7 @@
         <v>121</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>131</v>
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U35" s="10" t="s">
         <v>54</v>
@@ -4154,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>54</v>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="S38" s="6"/>
       <c r="T38" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>54</v>
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>54</v>
@@ -4406,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>54</v>
@@ -4469,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>54</v>
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>54</v>
@@ -4597,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>54</v>
@@ -4662,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U45" s="10" t="s">
         <v>54</v>
@@ -4792,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="T47" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U47" s="10" t="s">
         <v>54</v>
@@ -4857,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U48" s="10" t="s">
         <v>54</v>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="T53" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U53" s="10" t="s">
         <v>54</v>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>54</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="T82" s="12" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="U82" s="10" t="s">
         <v>54</v>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46118.53739798611</v>
+        <v>46240.18768153935</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>289</v>
@@ -7032,7 +7032,7 @@
       <c r="S86" s="6">
         <v>0</v>
       </c>
-      <c r="T86" s="11" t="s">
+      <c r="T86" s="12" t="s">
         <v>53</v>
       </c>
       <c r="U86" s="10" t="s">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46233.16826490741</v>
+        <v>46240.16753766204</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>57</v>
@@ -7365,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="12" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="U92" s="10" t="s">
         <v>54</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46191.89613979167</v>
+        <v>46240.18768105324</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>308</v>
@@ -7427,7 +7427,7 @@
       <c r="S93" s="9">
         <v>0</v>
       </c>
-      <c r="T93" s="11" t="s">
+      <c r="T93" s="12" t="s">
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U94" s="10" t="s">
         <v>54</v>
@@ -7788,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="T99" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U99" s="10" t="s">
         <v>54</v>
@@ -8010,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="T103" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U103" s="10" t="s">
         <v>54</v>
@@ -8232,7 +8232,7 @@
         <v>0</v>
       </c>
       <c r="T107" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U107" s="10" t="s">
         <v>54</v>
@@ -8454,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="T111" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U111" s="10" t="s">
         <v>54</v>
@@ -8676,7 +8676,7 @@
         <v>0</v>
       </c>
       <c r="T115" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U115" s="10" t="s">
         <v>54</v>
@@ -8898,7 +8898,7 @@
         <v>0</v>
       </c>
       <c r="T119" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U119" s="10" t="s">
         <v>54</v>
@@ -9112,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="T123" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U123" s="10" t="s">
         <v>54</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="T128" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U128" s="10" t="s">
         <v>54</v>
@@ -9846,7 +9846,7 @@
         <v>0</v>
       </c>
       <c r="T137" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U137" s="10" t="s">
         <v>54</v>
@@ -10331,7 +10331,7 @@
         <v>0</v>
       </c>
       <c r="T146" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U146" s="10" t="s">
         <v>54</v>
@@ -10818,7 +10818,7 @@
         <v>0</v>
       </c>
       <c r="T155" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U155" s="10" t="s">
         <v>54</v>
@@ -11352,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="T165" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U165" s="10" t="s">
         <v>54</v>
@@ -11415,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="T166" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U166" s="10" t="s">
         <v>54</v>
@@ -11527,7 +11527,7 @@
         <v>0</v>
       </c>
       <c r="T168" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U168" s="10" t="s">
         <v>54</v>
@@ -11590,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="T169" s="11" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="U169" s="10" t="s">
         <v>54</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="478">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -1387,7 +1387,7 @@
     <t>OT 4299- TABLERO PLC,OT 4301-COMPONENTES TABLERO COMPUERTAS,OT 4300- TABLERO BOTONERA,OT 4289 ATENUADORES 3,95X3,97X1,5M,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4298- TABLERO VDF ABB ACS880-17</t>
   </si>
   <si>
-    <t>Gestion,Logistica:,Instalación Componentes,Costos</t>
+    <t>Gestion,Logistica:,Costos</t>
   </si>
   <si>
     <t>1213886259509170</t>
@@ -1445,30 +1445,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213886380747240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta en marcha </t>
-  </si>
-  <si>
-    <t>Instalación Componentes,Pruebas instalacion componentes</t>
-  </si>
-  <si>
-    <t>1213886380747253</t>
-  </si>
-  <si>
-    <t>Instalación Componentes</t>
-  </si>
-  <si>
-    <t>Puesta en marcha ,Pruebas instalacion componentes</t>
-  </si>
-  <si>
-    <t>1213886304509621</t>
-  </si>
-  <si>
-    <t>Pruebas instalacion componentes</t>
   </si>
 </sst>
 </file>
@@ -1992,7 +1968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U169"/>
+  <dimension ref="A1:U166"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -10770,7 +10746,7 @@
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46118.54392340277</v>
+        <v>46240.71854427083</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>456</v>
@@ -11418,181 +11394,6 @@
         <v>128</v>
       </c>
       <c r="U166" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A167" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="B167" s="8">
-        <v>46112.68074700232</v>
-      </c>
-      <c r="C167" s="9"/>
-      <c r="D167" s="8">
-        <v>46118.54278521991</v>
-      </c>
-      <c r="E167" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="F167" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G167" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H167" s="9"/>
-      <c r="I167" s="9"/>
-      <c r="J167" s="9"/>
-      <c r="K167" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L167" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M167" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N167" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O167" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="P167" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q167" s="9"/>
-      <c r="R167" s="9"/>
-      <c r="S167" s="9"/>
-      <c r="T167" s="9"/>
-      <c r="U167" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A168" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="B168" s="5">
-        <v>46112.68075140046</v>
-      </c>
-      <c r="C168" s="6"/>
-      <c r="D168" s="5">
-        <v>46118.54421137732</v>
-      </c>
-      <c r="E168" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="F168" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G168" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="I168" s="5">
-        <v>46295</v>
-      </c>
-      <c r="J168" s="5">
-        <v>46303</v>
-      </c>
-      <c r="K168" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L168" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M168" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N168" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="O168" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="P168" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q168" s="5">
-        <v>46295</v>
-      </c>
-      <c r="R168" s="5">
-        <v>46303</v>
-      </c>
-      <c r="S168" s="6">
-        <v>0</v>
-      </c>
-      <c r="T168" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="U168" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A169" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="B169" s="8">
-        <v>46112.68075989583</v>
-      </c>
-      <c r="C169" s="9"/>
-      <c r="D169" s="8">
-        <v>46118.544324525465</v>
-      </c>
-      <c r="E169" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="F169" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G169" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="H169" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="I169" s="8">
-        <v>46304</v>
-      </c>
-      <c r="J169" s="8">
-        <v>46314</v>
-      </c>
-      <c r="K169" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L169" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M169" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N169" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="O169" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="P169" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="Q169" s="8">
-        <v>46304</v>
-      </c>
-      <c r="R169" s="8">
-        <v>46314</v>
-      </c>
-      <c r="S169" s="9">
-        <v>0</v>
-      </c>
-      <c r="T169" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="U169" s="10" t="s">
         <v>54</v>
       </c>
     </row>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46240.16753766204</v>
+        <v>46241.18076869213</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>57</v>
@@ -7340,8 +7340,8 @@
       <c r="S92" s="6">
         <v>0</v>
       </c>
-      <c r="T92" s="12" t="s">
-        <v>53</v>
+      <c r="T92" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U92" s="10" t="s">
         <v>54</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46238.20096488426</v>
+        <v>46245.16745018518</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>280</v>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46181.73302506944</v>
+        <v>46245.167452037036</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>211</v>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46181.73302986111</v>
+        <v>46245.16746935185</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>246</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46118.53646400463</v>
+        <v>46245.167439108794</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>249</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -3824,7 +3824,7 @@
         <v>46191.89613496528</v>
       </c>
       <c r="D33" s="8">
-        <v>46238.20096541666</v>
+        <v>46246.182907951385</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>121</v>
@@ -3871,8 +3871,8 @@
       <c r="S33" s="9">
         <v>1</v>
       </c>
-      <c r="T33" s="12" t="s">
-        <v>53</v>
+      <c r="T33" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U33" s="11" t="s">
         <v>32</v>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46245.16745018518</v>
+        <v>46246.18290778935</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>280</v>
@@ -6786,8 +6786,8 @@
       <c r="S82" s="6">
         <v>0</v>
       </c>
-      <c r="T82" s="12" t="s">
-        <v>53</v>
+      <c r="T82" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U82" s="10" t="s">
         <v>54</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46240.18768121528</v>
+        <v>46247.16739545139</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46112.74287908565</v>
+        <v>46247.16739662037</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>56</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46112.74360094908</v>
+        <v>46247.167390428236</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>60</v>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46112.74398168981</v>
+        <v>46247.16739166666</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46112.74391716435</v>
+        <v>46247.16738465278</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>66</v>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46240.18768153935</v>
+        <v>46247.167392881944</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>289</v>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46181.733025787034</v>
+        <v>46247.16739427083</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>211</v>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46181.73302309027</v>
+        <v>46247.16738799769</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>246</v>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46118.53739997685</v>
+        <v>46247.16738921296</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>250</v>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46240.18768105324</v>
+        <v>46247.16738605324</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>308</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="477">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -170,9 +170,6 @@
   </si>
   <si>
     <t>OT 4300- TABLERO BOTONERA,OT 4301-COMPONENTES TABLERO COMPUERTAS,OT 4299- TABLERO PLC,OT 4298- TABLERO VDF ABB ACS880-17</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -2551,7 +2548,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46247.16739545139</v>
+        <v>46248.18939621528</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>51</v>
@@ -2598,16 +2595,16 @@
       <c r="S12" s="6">
         <v>0</v>
       </c>
-      <c r="T12" s="12" t="s">
+      <c r="T12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U12" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="U12" s="10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="8">
         <v>46112.67930209491</v>
@@ -2617,7 +2614,7 @@
         <v>46247.16739662037</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -2647,10 +2644,10 @@
         <v>51</v>
       </c>
       <c r="O13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P13" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2660,7 +2657,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="5">
         <v>46112.67931020833</v>
@@ -2670,7 +2667,7 @@
         <v>46247.167390428236</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2700,10 +2697,10 @@
         <v>51</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2713,7 +2710,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="8">
         <v>46112.67931734954</v>
@@ -2723,7 +2720,7 @@
         <v>46247.16739166666</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2753,10 +2750,10 @@
         <v>51</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -2766,7 +2763,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5">
         <v>46112.67932484954</v>
@@ -2776,7 +2773,7 @@
         <v>46247.16738465278</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2806,10 +2803,10 @@
         <v>51</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -2819,7 +2816,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="8">
         <v>46112.679120995366</v>
@@ -2831,7 +2828,7 @@
         <v>46118.5488546875</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>25</v>
@@ -2855,7 +2852,7 @@
         <v>26</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P17" s="9" t="s">
         <v>26</v>
@@ -2870,7 +2867,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="5">
         <v>46112.6793327662</v>
@@ -2882,7 +2879,7 @@
         <v>46114.14643453703</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2909,13 +2906,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="5">
         <v>46112</v>
@@ -2935,7 +2932,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" s="8">
         <v>46112.67934158565</v>
@@ -2947,7 +2944,7 @@
         <v>46121.16860619213</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2974,13 +2971,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>38</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q19" s="8">
         <v>46112</v>
@@ -3000,7 +2997,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" s="5">
         <v>46112.6793505324</v>
@@ -3012,7 +3009,7 @@
         <v>46121.16860605324</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3039,13 +3036,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q20" s="5">
         <v>46112</v>
@@ -3065,7 +3062,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" s="8">
         <v>46112.67936041667</v>
@@ -3077,7 +3074,7 @@
         <v>46121.16860607639</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -3104,13 +3101,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="P21" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="Q21" s="8">
         <v>46112</v>
@@ -3130,7 +3127,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B22" s="5">
         <v>46112.679370729165</v>
@@ -3142,7 +3139,7 @@
         <v>46121.16860606481</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -3169,13 +3166,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q22" s="5">
         <v>46112</v>
@@ -3195,7 +3192,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="8">
         <v>46112.6791271875</v>
@@ -3207,7 +3204,7 @@
         <v>46210.70047322917</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>25</v>
@@ -3231,7 +3228,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>26</v>
@@ -3248,7 +3245,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B24" s="5">
         <v>46112.679417754625</v>
@@ -3260,7 +3257,7 @@
         <v>46116.1399068287</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3287,13 +3284,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q24" s="5">
         <v>46114</v>
@@ -3313,7 +3310,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" s="8">
         <v>46112.67943010417</v>
@@ -3325,7 +3322,7 @@
         <v>46123.18662815972</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3352,13 +3349,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q25" s="8">
         <v>46121</v>
@@ -3378,7 +3375,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B26" s="5">
         <v>46112.67944046296</v>
@@ -3390,16 +3387,16 @@
         <v>46223.59623494213</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46121</v>
@@ -3417,13 +3414,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46121</v>
@@ -3443,7 +3440,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8">
         <v>46112.679452349534</v>
@@ -3455,7 +3452,7 @@
         <v>46135.54582827546</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3482,13 +3479,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>46</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="8">
         <v>46121</v>
@@ -3508,7 +3505,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46112.67946289352</v>
@@ -3520,16 +3517,16 @@
         <v>46223.596228703704</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46191</v>
@@ -3547,13 +3544,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P28" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="Q28" s="5">
         <v>46191</v>
@@ -3573,7 +3570,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="8">
         <v>46112.679478136575</v>
@@ -3585,7 +3582,7 @@
         <v>46123.186628958334</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3612,13 +3609,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q29" s="8">
         <v>46121</v>
@@ -3638,7 +3635,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5">
         <v>46112.67948803241</v>
@@ -3650,16 +3647,16 @@
         <v>46223.596223217595</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46191</v>
@@ -3677,13 +3674,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O30" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="P30" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="Q30" s="5">
         <v>46191</v>
@@ -3703,7 +3700,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B31" s="8">
         <v>46112.67949700232</v>
@@ -3715,7 +3712,7 @@
         <v>46210.62933210648</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3742,13 +3739,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="8">
         <v>46121</v>
@@ -3768,7 +3765,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46112.67913506944</v>
@@ -3778,7 +3775,7 @@
         <v>46227.61942258102</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3802,7 +3799,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3815,7 +3812,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B33" s="8">
         <v>46112.679506099536</v>
@@ -3827,16 +3824,16 @@
         <v>46246.182907951385</v>
       </c>
       <c r="E33" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I33" s="8">
         <v>46125</v>
@@ -3854,13 +3851,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q33" s="8">
         <v>46125</v>
@@ -3880,7 +3877,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46112.6795156713</v>
@@ -3892,16 +3889,16 @@
         <v>46182.678480937495</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I34" s="5">
         <v>46125</v>
@@ -3919,13 +3916,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="5">
         <v>45985</v>
@@ -3937,15 +3934,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B35" s="8">
         <v>46112.67952521991</v>
@@ -3957,16 +3954,16 @@
         <v>46191.89612179398</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I35" s="8">
         <v>46127</v>
@@ -3984,13 +3981,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q35" s="8">
         <v>45987</v>
@@ -4002,15 +3999,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46112.67953447917</v>
@@ -4020,16 +4017,16 @@
         <v>46239.19380061343</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I36" s="5">
         <v>46125</v>
@@ -4047,13 +4044,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q36" s="5">
         <v>46125</v>
@@ -4068,12 +4065,12 @@
         <v>31</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46112.679543101855</v>
@@ -4085,16 +4082,16 @@
         <v>46195.682751747685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I37" s="8">
         <v>46125</v>
@@ -4112,13 +4109,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="8">
         <v>45979</v>
@@ -4130,15 +4127,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46112.67955209491</v>
@@ -4148,16 +4145,16 @@
         <v>46238.167686064815</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I38" s="5">
         <v>46134</v>
@@ -4175,13 +4172,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q38" s="5">
         <v>45988</v>
@@ -4191,15 +4188,15 @@
       </c>
       <c r="S38" s="6"/>
       <c r="T38" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B39" s="8">
         <v>46112.67960491898</v>
@@ -4209,16 +4206,16 @@
         <v>46195.71583903935</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I39" s="8">
         <v>46125</v>
@@ -4236,13 +4233,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q39" s="8">
         <v>46125</v>
@@ -4257,12 +4254,12 @@
         <v>31</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B40" s="5">
         <v>46112.679614513894</v>
@@ -4274,16 +4271,16 @@
         <v>46182.6782279051</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I40" s="5">
         <v>46125</v>
@@ -4301,13 +4298,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q40" s="5">
         <v>45985</v>
@@ -4319,15 +4316,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B41" s="8">
         <v>46112.67962357639</v>
@@ -4337,16 +4334,16 @@
         <v>46195.71615581018</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I41" s="8">
         <v>46127</v>
@@ -4364,13 +4361,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="8">
         <v>45987</v>
@@ -4382,15 +4379,15 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46112.679632581014</v>
@@ -4400,16 +4397,16 @@
         <v>46182.67812216435</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I42" s="5">
         <v>46118</v>
@@ -4427,13 +4424,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q42" s="5">
         <v>46118</v>
@@ -4445,15 +4442,15 @@
         <v>0</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46112.67964135417</v>
@@ -4465,16 +4462,16 @@
         <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I43" s="8">
         <v>46118</v>
@@ -4492,13 +4489,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4510,15 +4507,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46112.67965385417</v>
@@ -4528,16 +4525,16 @@
         <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I44" s="5">
         <v>46139</v>
@@ -4555,13 +4552,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4573,15 +4570,15 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8">
         <v>46112.679662372684</v>
@@ -4593,16 +4590,16 @@
         <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I45" s="8">
         <v>46139</v>
@@ -4620,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4638,15 +4635,15 @@
         <v>0</v>
       </c>
       <c r="T45" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46112.67967090278</v>
@@ -4658,16 +4655,16 @@
         <v>46211.831143738425</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4685,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q46" s="5">
         <v>46195</v>
@@ -4711,7 +4708,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4723,16 +4720,16 @@
         <v>46211.828745949075</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4750,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4768,15 +4765,15 @@
         <v>0</v>
       </c>
       <c r="T47" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4788,16 +4785,16 @@
         <v>46211.83093092593</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4815,13 +4812,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4833,15 +4830,15 @@
         <v>0</v>
       </c>
       <c r="T48" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4853,16 +4850,16 @@
         <v>46220.18905753472</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4880,13 +4877,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q49" s="8">
         <v>46125</v>
@@ -4906,7 +4903,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4918,16 +4915,16 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4945,13 +4942,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4961,7 +4958,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4973,16 +4970,16 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -5000,13 +4997,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5016,7 +5013,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5028,16 +5025,16 @@
         <v>46231.19795877315</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5055,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q52" s="5">
         <v>46195</v>
@@ -5081,7 +5078,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5093,16 +5090,16 @@
         <v>46227.61934873843</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5120,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5134,15 +5131,15 @@
         <v>0</v>
       </c>
       <c r="T53" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U53" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5154,16 +5151,16 @@
         <v>46227.619398842595</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5181,13 +5178,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5197,7 +5194,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5209,16 +5206,16 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I55" s="8">
         <v>46125</v>
@@ -5236,10 +5233,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5262,7 +5259,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5274,16 +5271,16 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -5301,13 +5298,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5317,7 +5314,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5329,16 +5326,16 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="I57" s="8">
         <v>46132</v>
@@ -5356,13 +5353,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5372,7 +5369,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5384,7 +5381,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5408,7 +5405,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5425,7 +5422,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5437,16 +5434,16 @@
         <v>46222.150650462965</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5464,13 +5461,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5490,7 +5487,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5502,16 +5499,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5529,13 +5526,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5545,7 +5542,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5557,16 +5554,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5584,13 +5581,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5600,7 +5597,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5612,16 +5609,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5639,13 +5636,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5655,7 +5652,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5667,16 +5664,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5694,13 +5691,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5720,7 +5717,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5732,16 +5729,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5759,13 +5756,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5775,7 +5772,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5787,16 +5784,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5814,13 +5811,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>229</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5830,7 +5827,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5842,16 +5839,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5869,13 +5866,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5885,7 +5882,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5897,16 +5894,16 @@
         <v>46191.201163958336</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5924,13 +5921,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5950,7 +5947,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5962,16 +5959,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5987,13 +5984,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6003,7 +6000,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6015,16 +6012,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6040,13 +6037,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6056,7 +6053,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6068,16 +6065,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6093,13 +6090,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6109,7 +6106,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6119,16 +6116,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6146,10 +6143,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6164,15 +6161,15 @@
         <v>0</v>
       </c>
       <c r="T71" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6182,16 +6179,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6209,13 +6206,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6225,7 +6222,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6235,16 +6232,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6262,13 +6259,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6278,7 +6275,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6288,16 +6285,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6315,13 +6312,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6331,7 +6328,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6341,7 +6338,7 @@
         <v>46118.55096414352</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6365,7 +6362,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6378,7 +6375,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6388,16 +6385,16 @@
         <v>46239.167648125</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6413,13 +6410,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6434,12 +6431,12 @@
         <v>31</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6451,7 +6448,7 @@
         <v>46237.86033361111</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6475,7 +6472,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6492,7 +6489,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6504,16 +6501,16 @@
         <v>46237.86031981482</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6531,13 +6528,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6557,7 +6554,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6569,16 +6566,16 @@
         <v>46237.86032310185</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6596,13 +6593,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6617,12 +6614,12 @@
         <v>31</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6632,7 +6629,7 @@
         <v>46237.53630173611</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6656,7 +6653,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6669,7 +6666,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6679,16 +6676,16 @@
         <v>46237.847639803236</v>
       </c>
       <c r="E81" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6706,13 +6703,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6727,12 +6724,12 @@
         <v>31</v>
       </c>
       <c r="U81" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6742,16 +6739,16 @@
         <v>46246.18290778935</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6769,13 +6766,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6790,12 +6787,12 @@
         <v>31</v>
       </c>
       <c r="U82" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6805,16 +6802,16 @@
         <v>46245.167452037036</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6832,13 +6829,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>283</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6848,7 +6845,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6858,16 +6855,16 @@
         <v>46245.16746935185</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6885,13 +6882,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6901,7 +6898,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6911,16 +6908,16 @@
         <v>46245.167439108794</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6938,13 +6935,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6954,26 +6951,26 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46247.167392881944</v>
+        <v>46248.18939666667</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -6991,13 +6988,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7008,16 +7005,16 @@
       <c r="S86" s="6">
         <v>0</v>
       </c>
-      <c r="T86" s="12" t="s">
+      <c r="T86" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U86" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="U86" s="10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7027,16 +7024,16 @@
         <v>46247.16739427083</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7054,13 +7051,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O87" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="P87" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7070,7 +7067,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7080,16 +7077,16 @@
         <v>46247.16738799769</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7107,13 +7104,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7123,7 +7120,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7133,16 +7130,16 @@
         <v>46247.16738921296</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7160,13 +7157,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7176,7 +7173,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7186,7 +7183,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7210,7 +7207,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7223,7 +7220,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7233,16 +7230,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7260,13 +7257,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7281,12 +7278,12 @@
         <v>31</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7296,16 +7293,16 @@
         <v>46241.18076869213</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7323,13 +7320,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7344,31 +7341,31 @@
         <v>31</v>
       </c>
       <c r="U92" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46247.16738605324</v>
+        <v>46248.18939703704</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7386,13 +7383,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7403,16 +7400,16 @@
       <c r="S93" s="9">
         <v>0</v>
       </c>
-      <c r="T93" s="12" t="s">
-        <v>53</v>
+      <c r="T93" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7422,16 +7419,16 @@
         <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7449,13 +7446,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7467,15 +7464,15 @@
         <v>0</v>
       </c>
       <c r="T94" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
@@ -7485,16 +7482,16 @@
         <v>46224.16695678241</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7512,13 +7509,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7533,12 +7530,12 @@
         <v>31</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7548,16 +7545,16 @@
         <v>46239.16765043982</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7573,13 +7570,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7594,12 +7591,12 @@
         <v>31</v>
       </c>
       <c r="U96" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7609,16 +7606,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>265</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>266</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7636,13 +7633,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7657,12 +7654,12 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7672,7 +7669,7 @@
         <v>46221.897785625</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7696,7 +7693,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7709,7 +7706,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
@@ -7719,16 +7716,16 @@
         <v>46223.60165059028</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I99" s="8">
         <v>46248</v>
@@ -7746,13 +7743,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7764,15 +7761,15 @@
         <v>0</v>
       </c>
       <c r="T99" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U99" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
@@ -7782,16 +7779,16 @@
         <v>46223.59635119213</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I100" s="5">
         <v>46248</v>
@@ -7809,13 +7806,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>329</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7825,7 +7822,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
@@ -7835,16 +7832,16 @@
         <v>46223.59635047454</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I101" s="8">
         <v>46248</v>
@@ -7862,13 +7859,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>332</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7878,7 +7875,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
@@ -7888,16 +7885,16 @@
         <v>46223.59634974537</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I102" s="5">
         <v>46248</v>
@@ -7915,13 +7912,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7931,7 +7928,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
@@ -7941,16 +7938,16 @@
         <v>46223.60164991899</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H103" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I103" s="8">
         <v>46268</v>
@@ -7968,13 +7965,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -7986,15 +7983,15 @@
         <v>0</v>
       </c>
       <c r="T103" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U103" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
@@ -8004,16 +8001,16 @@
         <v>46223.59661136574</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I104" s="5">
         <v>46268</v>
@@ -8031,13 +8028,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>341</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8047,7 +8044,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
@@ -8057,16 +8054,16 @@
         <v>46223.59661070602</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H105" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I105" s="8">
         <v>46268</v>
@@ -8084,13 +8081,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O105" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="P105" s="9" t="s">
         <v>343</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>344</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8100,7 +8097,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
@@ -8110,16 +8107,16 @@
         <v>46223.59661008102</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I106" s="5">
         <v>46268</v>
@@ -8137,13 +8134,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8153,7 +8150,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
@@ -8163,16 +8160,16 @@
         <v>46223.60164922454</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H107" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I107" s="8">
         <v>46272</v>
@@ -8190,13 +8187,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8208,15 +8205,15 @@
         <v>0</v>
       </c>
       <c r="T107" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U107" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
@@ -8226,16 +8223,16 @@
         <v>46223.59850755787</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I108" s="5">
         <v>46272</v>
@@ -8253,13 +8250,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O108" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>350</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8269,7 +8266,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
@@ -8279,16 +8276,16 @@
         <v>46223.598506875</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H109" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I109" s="8">
         <v>46272</v>
@@ -8306,13 +8303,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O109" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="P109" s="9" t="s">
         <v>353</v>
-      </c>
-      <c r="P109" s="9" t="s">
-        <v>354</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8322,7 +8319,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
@@ -8332,16 +8329,16 @@
         <v>46223.59850623843</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I110" s="5">
         <v>46272</v>
@@ -8359,13 +8356,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8375,7 +8372,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
@@ -8385,16 +8382,16 @@
         <v>46223.60164861111</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H111" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I111" s="8">
         <v>46274</v>
@@ -8412,13 +8409,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8430,15 +8427,15 @@
         <v>0</v>
       </c>
       <c r="T111" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U111" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
@@ -8448,16 +8445,16 @@
         <v>46223.59859461806</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I112" s="5">
         <v>46274</v>
@@ -8475,13 +8472,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8491,7 +8488,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
@@ -8501,16 +8498,16 @@
         <v>46223.598594027775</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H113" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I113" s="8">
         <v>46274</v>
@@ -8528,13 +8525,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8544,7 +8541,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
@@ -8554,16 +8551,16 @@
         <v>46223.598593414354</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I114" s="5">
         <v>46274</v>
@@ -8581,13 +8578,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8597,7 +8594,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
@@ -8607,16 +8604,16 @@
         <v>46223.60164790509</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H115" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I115" s="8">
         <v>46276</v>
@@ -8634,13 +8631,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8652,15 +8649,15 @@
         <v>0</v>
       </c>
       <c r="T115" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U115" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
@@ -8670,16 +8667,16 @@
         <v>46223.59868443287</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I116" s="5">
         <v>46276</v>
@@ -8697,13 +8694,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O116" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="P116" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>369</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8713,7 +8710,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
@@ -8723,16 +8720,16 @@
         <v>46223.59868380787</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H117" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I117" s="8">
         <v>46276</v>
@@ -8750,13 +8747,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O117" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="P117" s="9" t="s">
         <v>371</v>
-      </c>
-      <c r="P117" s="9" t="s">
-        <v>372</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8766,7 +8763,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
@@ -8776,16 +8773,16 @@
         <v>46223.59868314815</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I118" s="5">
         <v>46276</v>
@@ -8803,13 +8800,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8819,7 +8816,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
@@ -8829,16 +8826,16 @@
         <v>46223.60164731482</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H119" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I119" s="8">
         <v>46280</v>
@@ -8856,13 +8853,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8874,15 +8871,15 @@
         <v>0</v>
       </c>
       <c r="T119" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U119" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
@@ -8892,16 +8889,16 @@
         <v>46223.598781168985</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8917,13 +8914,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8933,7 +8930,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
@@ -8943,16 +8940,16 @@
         <v>46223.59878049769</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H121" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -8968,13 +8965,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8984,7 +8981,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
@@ -8994,16 +8991,16 @@
         <v>46223.598779803244</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="5">
@@ -9019,13 +9016,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9035,7 +9032,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
@@ -9045,16 +9042,16 @@
         <v>46223.60164671297</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H123" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -9070,13 +9067,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9088,15 +9085,15 @@
         <v>0</v>
       </c>
       <c r="T123" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U123" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B124" s="5">
         <v>46112.680353344906</v>
@@ -9106,16 +9103,16 @@
         <v>46223.59886346065</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -9131,13 +9128,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9147,7 +9144,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B125" s="8">
         <v>46112.6803614699</v>
@@ -9157,16 +9154,16 @@
         <v>46223.59886280092</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H125" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="8">
@@ -9182,13 +9179,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9198,7 +9195,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B126" s="5">
         <v>46112.69493020834</v>
@@ -9208,16 +9205,16 @@
         <v>46223.59886211806</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I126" s="6"/>
       <c r="J126" s="5">
@@ -9233,13 +9230,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9249,7 +9246,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B127" s="8">
         <v>46112.68036949074</v>
@@ -9259,7 +9256,7 @@
         <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9283,7 +9280,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9296,7 +9293,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B128" s="5">
         <v>46112.68037429398</v>
@@ -9306,16 +9303,16 @@
         <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G128" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="F128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G128" s="6" t="s">
+      <c r="H128" s="6" t="s">
         <v>396</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>397</v>
       </c>
       <c r="I128" s="5">
         <v>46287</v>
@@ -9333,13 +9330,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q128" s="5">
         <v>46287</v>
@@ -9351,15 +9348,15 @@
         <v>0</v>
       </c>
       <c r="T128" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U128" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B129" s="8">
         <v>46112.68038334491</v>
@@ -9369,16 +9366,16 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="H129" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>397</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9394,13 +9391,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9410,7 +9407,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B130" s="5">
         <v>46112.68039121528</v>
@@ -9420,16 +9417,16 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>396</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>397</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9445,13 +9442,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9461,7 +9458,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B131" s="8">
         <v>46112.69787394676</v>
@@ -9471,16 +9468,16 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>397</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9496,13 +9493,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9512,7 +9509,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B132" s="5">
         <v>46112.6803999074</v>
@@ -9522,16 +9519,16 @@
         <v>46118.542362858796</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>396</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>397</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9547,13 +9544,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9563,7 +9560,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B133" s="8">
         <v>46112.68041137731</v>
@@ -9573,16 +9570,16 @@
         <v>46118.54236363426</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>397</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9598,13 +9595,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9614,7 +9611,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B134" s="5">
         <v>46112.680419027776</v>
@@ -9624,16 +9621,16 @@
         <v>46118.54236440972</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>396</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>397</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9649,13 +9646,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9665,7 +9662,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B135" s="8">
         <v>46112.68042700231</v>
@@ -9675,16 +9672,16 @@
         <v>46118.54236519676</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>397</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9700,13 +9697,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9716,7 +9713,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B136" s="5">
         <v>46112.68043466435</v>
@@ -9726,16 +9723,16 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>396</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>397</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9751,13 +9748,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9767,7 +9764,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B137" s="8">
         <v>46112.68044216435</v>
@@ -9777,16 +9774,16 @@
         <v>46223.601863715274</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I137" s="8">
         <v>46288</v>
@@ -9804,13 +9801,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O137" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="P137" s="9" t="s">
         <v>417</v>
-      </c>
-      <c r="P137" s="9" t="s">
-        <v>418</v>
       </c>
       <c r="Q137" s="8">
         <v>46288</v>
@@ -9822,15 +9819,15 @@
         <v>0</v>
       </c>
       <c r="T137" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U137" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B138" s="5">
         <v>46112.68045020833</v>
@@ -9840,16 +9837,16 @@
         <v>46223.60177635417</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I138" s="5">
         <v>46288</v>
@@ -9867,13 +9864,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9883,7 +9880,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B139" s="8">
         <v>46112.680457615745</v>
@@ -9893,16 +9890,16 @@
         <v>46223.601775636576</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I139" s="8">
         <v>46288</v>
@@ -9920,13 +9917,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9936,7 +9933,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B140" s="5">
         <v>46112.699333854165</v>
@@ -9946,16 +9943,16 @@
         <v>46223.601775</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I140" s="5">
         <v>46288</v>
@@ -9973,13 +9970,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9989,7 +9986,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B141" s="8">
         <v>46112.68046530093</v>
@@ -9999,16 +9996,16 @@
         <v>46223.60177436343</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I141" s="8">
         <v>46288</v>
@@ -10026,13 +10023,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10042,7 +10039,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B142" s="5">
         <v>46112.6804727662</v>
@@ -10052,16 +10049,16 @@
         <v>46223.60177366898</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I142" s="5">
         <v>46288</v>
@@ -10079,13 +10076,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10095,7 +10092,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B143" s="8">
         <v>46112.680524282405</v>
@@ -10105,16 +10102,16 @@
         <v>46223.60177299769</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I143" s="8">
         <v>46288</v>
@@ -10132,13 +10129,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10148,7 +10145,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B144" s="5">
         <v>46112.68053547454</v>
@@ -10158,16 +10155,16 @@
         <v>46223.60177233796</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="I144" s="5">
         <v>46288</v>
@@ -10185,13 +10182,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10201,7 +10198,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B145" s="8">
         <v>46112.68054428241</v>
@@ -10211,16 +10208,16 @@
         <v>46223.60177167824</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="I145" s="8">
         <v>46288</v>
@@ -10238,13 +10235,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10254,7 +10251,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B146" s="5">
         <v>46112.68055275463</v>
@@ -10264,16 +10261,16 @@
         <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10289,13 +10286,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q146" s="5">
         <v>46293</v>
@@ -10307,15 +10304,15 @@
         <v>0</v>
       </c>
       <c r="T146" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U146" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B147" s="8">
         <v>46112.68056386574</v>
@@ -10325,16 +10322,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10352,13 +10349,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10368,7 +10365,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B148" s="5">
         <v>46112.68057167824</v>
@@ -10378,16 +10375,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10405,13 +10402,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10421,7 +10418,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B149" s="8">
         <v>46112.70035509259</v>
@@ -10431,16 +10428,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10458,13 +10455,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10474,7 +10471,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B150" s="5">
         <v>46112.680579479165</v>
@@ -10484,16 +10481,16 @@
         <v>46118.5435747338</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10511,13 +10508,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10527,7 +10524,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B151" s="8">
         <v>46112.68058722222</v>
@@ -10537,16 +10534,16 @@
         <v>46118.54357537037</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10564,13 +10561,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10580,7 +10577,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B152" s="5">
         <v>46112.68059523148</v>
@@ -10590,16 +10587,16 @@
         <v>46118.54357599537</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10617,13 +10614,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10633,7 +10630,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B153" s="8">
         <v>46112.680603472225</v>
@@ -10643,16 +10640,16 @@
         <v>46118.5435766088</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10670,13 +10667,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10686,7 +10683,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B154" s="5">
         <v>46112.68061105324</v>
@@ -10696,16 +10693,16 @@
         <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10723,13 +10720,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10739,7 +10736,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B155" s="8">
         <v>46112.680618784725</v>
@@ -10749,16 +10746,16 @@
         <v>46240.71854427083</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10776,13 +10773,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O155" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="P155" s="9" t="s">
         <v>457</v>
-      </c>
-      <c r="P155" s="9" t="s">
-        <v>458</v>
       </c>
       <c r="Q155" s="8">
         <v>46294</v>
@@ -10794,15 +10791,15 @@
         <v>0</v>
       </c>
       <c r="T155" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U155" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B156" s="5">
         <v>46112.680633553246</v>
@@ -10812,16 +10809,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10839,13 +10836,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10855,7 +10852,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B157" s="8">
         <v>46112.68064251158</v>
@@ -10865,16 +10862,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10892,13 +10889,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10908,7 +10905,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B158" s="5">
         <v>46112.68071581019</v>
@@ -10918,16 +10915,16 @@
         <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10945,13 +10942,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10961,7 +10958,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B159" s="8">
         <v>46112.739142986116</v>
@@ -10971,16 +10968,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H159" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -10998,10 +10995,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11014,7 +11011,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B160" s="5">
         <v>46112.68065008102</v>
@@ -11024,16 +11021,16 @@
         <v>46118.5438528125</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11051,13 +11048,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11067,7 +11064,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B161" s="8">
         <v>46112.680657476856</v>
@@ -11077,16 +11074,16 @@
         <v>46118.54385362269</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H161" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11104,13 +11101,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O161" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11120,7 +11117,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B162" s="5">
         <v>46112.68069804399</v>
@@ -11130,16 +11127,16 @@
         <v>46118.54385447917</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11157,13 +11154,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11173,7 +11170,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B163" s="8">
         <v>46112.68070748843</v>
@@ -11183,16 +11180,16 @@
         <v>46118.54385528935</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H163" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>
@@ -11210,13 +11207,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11226,7 +11223,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B164" s="5">
         <v>46112.68072377315</v>
@@ -11236,7 +11233,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>25</v>
@@ -11260,7 +11257,7 @@
         <v>26</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>26</v>
@@ -11273,7 +11270,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B165" s="8">
         <v>46112.680728148145</v>
@@ -11283,16 +11280,16 @@
         <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="F165" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G165" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="F165" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G165" s="9" t="s">
+      <c r="H165" s="9" t="s">
         <v>473</v>
-      </c>
-      <c r="H165" s="9" t="s">
-        <v>474</v>
       </c>
       <c r="I165" s="8">
         <v>46295</v>
@@ -11310,13 +11307,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Q165" s="8">
         <v>46295</v>
@@ -11328,15 +11325,15 @@
         <v>0</v>
       </c>
       <c r="T165" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U165" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B166" s="5">
         <v>46112.68073732639</v>
@@ -11346,16 +11343,16 @@
         <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="H166" s="6" t="s">
         <v>473</v>
-      </c>
-      <c r="H166" s="6" t="s">
-        <v>474</v>
       </c>
       <c r="I166" s="5">
         <v>46295</v>
@@ -11373,13 +11370,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Q166" s="5">
         <v>46295</v>
@@ -11391,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="T166" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U166" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6958,7 +6958,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46248.18939666667</v>
+        <v>46255.5535544213</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>288</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="478">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -992,6 +992,9 @@
   </si>
   <si>
     <t>OT  4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1213886430692257</t>
@@ -7713,7 +7716,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46223.60165059028</v>
+        <v>46260.17012190972</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>325</v>
@@ -7760,8 +7763,8 @@
       <c r="S99" s="9">
         <v>0</v>
       </c>
-      <c r="T99" s="11" t="s">
-        <v>127</v>
+      <c r="T99" s="12" t="s">
+        <v>327</v>
       </c>
       <c r="U99" s="10" t="s">
         <v>53</v>
@@ -7769,7 +7772,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B100" s="5">
         <v>46112.68013306713</v>
@@ -7809,10 +7812,10 @@
         <v>325</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7822,7 +7825,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B101" s="8">
         <v>46112.680142453704</v>
@@ -7862,10 +7865,10 @@
         <v>325</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7875,7 +7878,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B102" s="5">
         <v>46112.68695712963</v>
@@ -7918,7 +7921,7 @@
         <v>249</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7928,7 +7931,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B103" s="8">
         <v>46112.68015230324</v>
@@ -7938,7 +7941,7 @@
         <v>46223.60164991899</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7968,7 +7971,7 @@
         <v>322</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>322</v>
@@ -7991,7 +7994,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B104" s="5">
         <v>46112.680160613425</v>
@@ -8028,13 +8031,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8044,7 +8047,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B105" s="8">
         <v>46112.68017212963</v>
@@ -8081,13 +8084,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8097,7 +8100,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B106" s="5">
         <v>46112.68780918981</v>
@@ -8134,13 +8137,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>249</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8150,7 +8153,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B107" s="8">
         <v>46112.68018260416</v>
@@ -8160,7 +8163,7 @@
         <v>46223.60164922454</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8213,7 +8216,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B108" s="5">
         <v>46112.680190486106</v>
@@ -8250,13 +8253,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8266,7 +8269,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B109" s="8">
         <v>46112.68020174769</v>
@@ -8303,13 +8306,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8319,7 +8322,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B110" s="5">
         <v>46112.68889696759</v>
@@ -8356,13 +8359,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>249</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8372,7 +8375,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B111" s="8">
         <v>46112.6802131713</v>
@@ -8382,7 +8385,7 @@
         <v>46223.60164861111</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8435,7 +8438,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B112" s="5">
         <v>46112.680221111106</v>
@@ -8472,13 +8475,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8488,7 +8491,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B113" s="8">
         <v>46112.68023248843</v>
@@ -8525,13 +8528,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8541,7 +8544,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B114" s="5">
         <v>46112.69112122685</v>
@@ -8578,13 +8581,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>249</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8594,7 +8597,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B115" s="8">
         <v>46112.68024403935</v>
@@ -8604,7 +8607,7 @@
         <v>46223.60164790509</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8657,7 +8660,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B116" s="5">
         <v>46112.68025228009</v>
@@ -8694,13 +8697,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8710,7 +8713,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B117" s="8">
         <v>46112.68026435185</v>
@@ -8747,13 +8750,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8763,7 +8766,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B118" s="5">
         <v>46112.69281496528</v>
@@ -8800,13 +8803,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>248</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8816,7 +8819,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B119" s="8">
         <v>46112.680315000005</v>
@@ -8826,7 +8829,7 @@
         <v>46223.60164731482</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8856,7 +8859,7 @@
         <v>322</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>322</v>
@@ -8879,7 +8882,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B120" s="5">
         <v>46112.68032652778</v>
@@ -8914,13 +8917,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8930,7 +8933,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B121" s="8">
         <v>46112.68033607639</v>
@@ -8965,13 +8968,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>245</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8981,7 +8984,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B122" s="5">
         <v>46112.69375358796</v>
@@ -9016,13 +9019,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>249</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9032,7 +9035,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B123" s="8">
         <v>46112.68034494213</v>
@@ -9042,7 +9045,7 @@
         <v>46223.60164671297</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9093,7 +9096,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B124" s="5">
         <v>46112.680353344906</v>
@@ -9128,13 +9131,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9144,7 +9147,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B125" s="8">
         <v>46112.6803614699</v>
@@ -9179,13 +9182,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
         <v>245</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9195,7 +9198,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B126" s="5">
         <v>46112.69493020834</v>
@@ -9230,13 +9233,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>248</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9246,7 +9249,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B127" s="8">
         <v>46112.68036949074</v>
@@ -9256,7 +9259,7 @@
         <v>46118.542785694444</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9280,7 +9283,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9293,7 +9296,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B128" s="5">
         <v>46112.68037429398</v>
@@ -9303,16 +9306,16 @@
         <v>46118.542359756946</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I128" s="5">
         <v>46287</v>
@@ -9330,13 +9333,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q128" s="5">
         <v>46287</v>
@@ -9356,7 +9359,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B129" s="8">
         <v>46112.68038334491</v>
@@ -9372,10 +9375,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9391,13 +9394,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>210</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9407,7 +9410,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B130" s="5">
         <v>46112.68039121528</v>
@@ -9423,10 +9426,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9442,13 +9445,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>245</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9458,7 +9461,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B131" s="8">
         <v>46112.69787394676</v>
@@ -9474,10 +9477,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9493,13 +9496,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>249</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9509,7 +9512,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B132" s="5">
         <v>46112.6803999074</v>
@@ -9525,10 +9528,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9544,13 +9547,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9560,7 +9563,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B133" s="8">
         <v>46112.68041137731</v>
@@ -9576,10 +9579,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9595,13 +9598,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9611,7 +9614,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B134" s="5">
         <v>46112.680419027776</v>
@@ -9627,10 +9630,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9646,13 +9649,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9662,7 +9665,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B135" s="8">
         <v>46112.68042700231</v>
@@ -9678,10 +9681,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9697,13 +9700,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9713,7 +9716,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B136" s="5">
         <v>46112.68043466435</v>
@@ -9729,10 +9732,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9748,13 +9751,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>319</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9764,7 +9767,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B137" s="8">
         <v>46112.68044216435</v>
@@ -9774,7 +9777,7 @@
         <v>46223.601863715274</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9801,13 +9804,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q137" s="8">
         <v>46288</v>
@@ -9827,7 +9830,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B138" s="5">
         <v>46112.68045020833</v>
@@ -9864,13 +9867,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9880,7 +9883,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B139" s="8">
         <v>46112.680457615745</v>
@@ -9917,13 +9920,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O139" s="9" t="s">
         <v>245</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9933,7 +9936,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B140" s="5">
         <v>46112.699333854165</v>
@@ -9970,13 +9973,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>248</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9986,7 +9989,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B141" s="8">
         <v>46112.68046530093</v>
@@ -10023,13 +10026,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>55</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10039,7 +10042,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B142" s="5">
         <v>46112.6804727662</v>
@@ -10076,13 +10079,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10092,7 +10095,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B143" s="8">
         <v>46112.680524282405</v>
@@ -10129,13 +10132,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>62</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10145,7 +10148,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B144" s="5">
         <v>46112.68053547454</v>
@@ -10182,13 +10185,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10198,7 +10201,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B145" s="8">
         <v>46112.68054428241</v>
@@ -10208,7 +10211,7 @@
         <v>46223.60177167824</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10235,13 +10238,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O145" s="9" t="s">
         <v>320</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10251,7 +10254,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B146" s="5">
         <v>46112.68055275463</v>
@@ -10261,7 +10264,7 @@
         <v>46118.54357326389</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10286,13 +10289,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q146" s="5">
         <v>46293</v>
@@ -10312,7 +10315,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B147" s="8">
         <v>46112.68056386574</v>
@@ -10349,13 +10352,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O147" s="9" t="s">
         <v>210</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q147" s="9"/>
       <c r="R147" s="9"/>
@@ -10365,7 +10368,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B148" s="5">
         <v>46112.68057167824</v>
@@ -10402,13 +10405,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>245</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10418,7 +10421,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B149" s="8">
         <v>46112.70035509259</v>
@@ -10455,7 +10458,7 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O149" s="9" t="s">
         <v>249</v>
@@ -10471,7 +10474,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B150" s="5">
         <v>46112.680579479165</v>
@@ -10508,13 +10511,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10524,7 +10527,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B151" s="8">
         <v>46112.68058722222</v>
@@ -10561,13 +10564,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10577,7 +10580,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B152" s="5">
         <v>46112.68059523148</v>
@@ -10614,13 +10617,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10630,7 +10633,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B153" s="8">
         <v>46112.680603472225</v>
@@ -10667,13 +10670,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O153" s="9" t="s">
         <v>65</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10683,7 +10686,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B154" s="5">
         <v>46112.68061105324</v>
@@ -10693,7 +10696,7 @@
         <v>46118.543577268516</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10720,13 +10723,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10736,7 +10739,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B155" s="8">
         <v>46112.680618784725</v>
@@ -10746,7 +10749,7 @@
         <v>46240.71854427083</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -10773,13 +10776,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q155" s="8">
         <v>46294</v>
@@ -10799,7 +10802,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B156" s="5">
         <v>46112.680633553246</v>
@@ -10836,13 +10839,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10852,7 +10855,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B157" s="8">
         <v>46112.68064251158</v>
@@ -10889,13 +10892,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O157" s="9" t="s">
         <v>245</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -10905,7 +10908,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B158" s="5">
         <v>46112.68071581019</v>
@@ -10915,7 +10918,7 @@
         <v>46118.543850752314</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10942,13 +10945,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10958,7 +10961,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B159" s="8">
         <v>46112.739142986116</v>
@@ -10995,7 +10998,7 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O159" s="9" t="s">
         <v>249</v>
@@ -11011,7 +11014,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B160" s="5">
         <v>46112.68065008102</v>
@@ -11048,13 +11051,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11064,7 +11067,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B161" s="8">
         <v>46112.680657476856</v>
@@ -11101,13 +11104,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11117,7 +11120,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B162" s="5">
         <v>46112.68069804399</v>
@@ -11154,13 +11157,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>65</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11170,7 +11173,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B163" s="8">
         <v>46112.68070748843</v>
@@ -11207,13 +11210,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>62</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11223,7 +11226,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B164" s="5">
         <v>46112.68072377315</v>
@@ -11233,7 +11236,7 @@
         <v>46118.54278521991</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>25</v>
@@ -11257,7 +11260,7 @@
         <v>26</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>26</v>
@@ -11270,7 +11273,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B165" s="8">
         <v>46112.680728148145</v>
@@ -11280,16 +11283,16 @@
         <v>46118.54402055556</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I165" s="8">
         <v>46295</v>
@@ -11307,13 +11310,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q165" s="8">
         <v>46295</v>
@@ -11333,7 +11336,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B166" s="5">
         <v>46112.68073732639</v>
@@ -11343,16 +11346,16 @@
         <v>46118.54410575231</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I166" s="5">
         <v>46295</v>
@@ -11370,13 +11373,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q166" s="5">
         <v>46295</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6629,7 +6629,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46237.53630173611</v>
+        <v>46260.58241461805</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>271</v>
@@ -6674,9 +6674,11 @@
       <c r="B81" s="8">
         <v>46112.679901701384</v>
       </c>
-      <c r="C81" s="9"/>
+      <c r="C81" s="8">
+        <v>46260.582406898146</v>
+      </c>
       <c r="D81" s="8">
-        <v>46237.847639803236</v>
+        <v>46260.58243447916</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>274</v>
@@ -6721,13 +6723,13 @@
         <v>46225</v>
       </c>
       <c r="S81" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U81" s="12" t="s">
-        <v>258</v>
+      <c r="U81" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6739,7 +6741,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46246.18290778935</v>
+        <v>46260.583539328705</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>279</v>
@@ -6800,9 +6802,11 @@
       <c r="B83" s="8">
         <v>46112.679960775466</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="8">
+        <v>46260.582582256946</v>
+      </c>
       <c r="D83" s="8">
-        <v>46245.167452037036</v>
+        <v>46260.58258379629</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>210</v>
@@ -6853,9 +6857,11 @@
       <c r="B84" s="5">
         <v>46112.67997252315</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46260.58353210648</v>
+      </c>
       <c r="D84" s="5">
-        <v>46245.16746935185</v>
+        <v>46260.58353350694</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>245</v>
@@ -6908,7 +6914,7 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46245.167439108794</v>
+        <v>46260.58241299768</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>248</v>
@@ -7024,7 +7030,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46247.16739427083</v>
+        <v>46260.58258729167</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>210</v>
@@ -7077,7 +7083,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46247.16738799769</v>
+        <v>46260.583538541665</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>245</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1948" uniqueCount="478">
   <si>
     <t>50001534-ZITRON PERU METRO DE LIMA (E04-05 06-R4)</t>
   </si>
@@ -787,40 +787,40 @@
     <t>Control de calidad,Recepcion Fabricacion externa</t>
   </si>
   <si>
+    <t>1213902113485641</t>
+  </si>
+  <si>
+    <t>Bodega</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213886181542206</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213886181542236</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>Bodega,Preparacion materiales</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213902113485641</t>
-  </si>
-  <si>
-    <t>Bodega</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213886181542206</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213886181542236</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Bodega,Preparacion materiales</t>
   </si>
   <si>
     <t>1213902113596084</t>
@@ -6336,9 +6336,11 @@
       <c r="B75" s="8">
         <v>46112.679867326384</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46260.658577766204</v>
+      </c>
       <c r="D75" s="8">
-        <v>46118.55096414352</v>
+        <v>46260.658590023144</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>252</v>
@@ -6372,9 +6374,13 @@
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
-      <c r="S75" s="9"/>
+      <c r="S75" s="9">
+        <v>1</v>
+      </c>
       <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
+      <c r="U75" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
@@ -6383,9 +6389,11 @@
       <c r="B76" s="5">
         <v>46112.67987047454</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46260.65855825231</v>
+      </c>
       <c r="D76" s="5">
-        <v>46239.167648125</v>
+        <v>46260.65857824074</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>253</v>
@@ -6428,18 +6436,18 @@
         <v>46231</v>
       </c>
       <c r="S76" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U76" s="12" t="s">
-        <v>258</v>
+      <c r="U76" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6451,7 +6459,7 @@
         <v>46237.86033361111</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6475,7 +6483,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6492,7 +6500,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6504,16 +6512,16 @@
         <v>46237.86031981482</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6531,13 +6539,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6557,7 +6565,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6569,7 +6577,7 @@
         <v>46237.86032310185</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6596,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6617,7 +6625,7 @@
         <v>31</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6711,7 +6719,7 @@
         <v>271</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>277</v>
@@ -6741,7 +6749,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46260.583539328705</v>
+        <v>46260.65928364583</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>279</v>
@@ -7245,10 +7253,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7308,10 +7316,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7371,10 +7379,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7413,7 +7421,7 @@
         <v>31</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7434,10 +7442,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7497,10 +7505,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7539,7 +7547,7 @@
         <v>31</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7551,7 +7559,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46239.16765043982</v>
+        <v>46260.6585802662</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>316</v>
@@ -7560,10 +7568,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7599,8 +7607,8 @@
       <c r="T96" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U96" s="10" t="s">
-        <v>53</v>
+      <c r="U96" s="12" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7621,10 +7629,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7663,7 +7671,7 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -7952,7 +7952,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46223.60164991899</v>
+        <v>46262.17720913194</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>337</v>
@@ -7999,8 +7999,8 @@
       <c r="S103" s="9">
         <v>0</v>
       </c>
-      <c r="T103" s="11" t="s">
-        <v>127</v>
+      <c r="T103" s="12" t="s">
+        <v>327</v>
       </c>
       <c r="U103" s="10" t="s">
         <v>53</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -469,6 +469,9 @@
     <t>Generación OC motor  ot 4294 - 4296 - 4297,Fabricación motor  ot 4294 - 4296 - 4297,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213886181511076</t>
   </si>
   <si>
@@ -992,9 +995,6 @@
   </si>
   <si>
     <t>OT  4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213886430692257</t>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.67812216435</v>
+        <v>46265.205750416666</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4444,8 +4444,8 @@
       <c r="S42" s="6">
         <v>0</v>
       </c>
-      <c r="T42" s="11" t="s">
-        <v>127</v>
+      <c r="T42" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>53</v>
@@ -4453,7 +4453,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46112.67964135417</v>
@@ -4465,7 +4465,7 @@
         <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4498,7 +4498,7 @@
         <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46112.67965385417</v>
@@ -4528,7 +4528,7 @@
         <v>46196.72350310185</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4558,10 +4558,10 @@
         <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B45" s="8">
         <v>46112.679662372684</v>
@@ -4593,7 +4593,7 @@
         <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4623,10 +4623,10 @@
         <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46112.67967090278</v>
@@ -4658,16 +4658,16 @@
         <v>46211.831143738425</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4688,7 +4688,7 @@
         <v>117</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>117</v>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4729,10 +4729,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4750,13 +4750,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4788,16 +4788,16 @@
         <v>46211.83093092593</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4815,13 +4815,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4853,16 +4853,16 @@
         <v>46220.18905753472</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4883,7 +4883,7 @@
         <v>117</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>117</v>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4918,16 +4918,16 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4945,13 +4945,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4961,7 +4961,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4973,16 +4973,16 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -5000,13 +5000,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5016,7 +5016,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5028,16 +5028,16 @@
         <v>46231.19795877315</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5058,7 +5058,7 @@
         <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>117</v>
@@ -5081,7 +5081,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5099,10 +5099,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5120,13 +5120,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>111</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5154,16 +5154,16 @@
         <v>46227.619398842595</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5181,13 +5181,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5197,7 +5197,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5209,7 +5209,7 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5239,7 +5239,7 @@
         <v>117</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5274,7 +5274,7 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5301,13 +5301,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5329,7 +5329,7 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5356,13 +5356,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5384,7 +5384,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5408,7 +5408,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5437,16 +5437,16 @@
         <v>46222.150650462965</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5464,13 +5464,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5502,16 +5502,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5529,13 +5529,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5557,16 +5557,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5584,13 +5584,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5612,16 +5612,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5639,13 +5639,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5667,16 +5667,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5694,13 +5694,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5720,7 +5720,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5732,16 +5732,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5759,13 +5759,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5787,16 +5787,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5814,13 +5814,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5842,16 +5842,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5869,13 +5869,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5885,7 +5885,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5903,10 +5903,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5924,13 +5924,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5950,7 +5950,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5962,16 +5962,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5990,7 +5990,7 @@
         <v>105</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>105</v>
@@ -6003,7 +6003,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6015,16 +6015,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6043,7 +6043,7 @@
         <v>105</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>105</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6068,16 +6068,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6096,7 +6096,7 @@
         <v>105</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>105</v>
@@ -6109,7 +6109,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6119,16 +6119,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6146,10 +6146,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6182,16 +6182,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6209,13 +6209,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6235,16 +6235,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6262,13 +6262,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6288,16 +6288,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6315,13 +6315,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6343,7 +6343,7 @@
         <v>46260.658590023144</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6367,7 +6367,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6396,16 +6396,16 @@
         <v>46260.65857824074</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6421,13 +6421,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6459,7 +6459,7 @@
         <v>46237.86033361111</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6483,7 +6483,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6512,16 +6512,16 @@
         <v>46237.86031981482</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6539,13 +6539,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6577,16 +6577,16 @@
         <v>46237.86032310185</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6604,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6625,12 +6625,12 @@
         <v>31</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6640,7 +6640,7 @@
         <v>46260.58241461805</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6664,7 +6664,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6677,7 +6677,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6689,16 +6689,16 @@
         <v>46260.58243447916</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6716,13 +6716,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6752,16 +6752,16 @@
         <v>46260.65928364583</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6779,13 +6779,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6817,16 +6817,16 @@
         <v>46260.58258379629</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6844,13 +6844,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6872,16 +6872,16 @@
         <v>46260.58353350694</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6899,13 +6899,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6915,7 +6915,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6925,16 +6925,16 @@
         <v>46260.58241299768</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6952,13 +6952,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6978,16 +6978,16 @@
         <v>46255.5535544213</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -7005,13 +7005,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7031,7 +7031,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7041,16 +7041,16 @@
         <v>46260.58258729167</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7068,13 +7068,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7084,7 +7084,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7094,16 +7094,16 @@
         <v>46260.583538541665</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7121,13 +7121,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7137,7 +7137,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7147,16 +7147,16 @@
         <v>46247.16738921296</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7174,13 +7174,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7190,7 +7190,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7200,7 +7200,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7224,7 +7224,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7237,7 +7237,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7247,16 +7247,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7274,13 +7274,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7300,7 +7300,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7316,10 +7316,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7337,13 +7337,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7363,7 +7363,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7373,16 +7373,16 @@
         <v>46248.18939703704</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7400,13 +7400,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7421,12 +7421,12 @@
         <v>31</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7436,16 +7436,16 @@
         <v>46112.680270150464</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7463,13 +7463,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7489,7 +7489,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B95" s="8">
         <v>46112.68005998843</v>
@@ -7499,16 +7499,16 @@
         <v>46224.16695678241</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7526,13 +7526,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q95" s="8">
         <v>46220</v>
@@ -7547,12 +7547,12 @@
         <v>31</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B96" s="5">
         <v>46112.68006824074</v>
@@ -7562,16 +7562,16 @@
         <v>46260.6585802662</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7587,13 +7587,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q96" s="5">
         <v>46231</v>
@@ -7608,12 +7608,12 @@
         <v>31</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B97" s="8">
         <v>46112.6800780787</v>
@@ -7623,16 +7623,16 @@
         <v>46183.18919873843</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7650,13 +7650,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q97" s="8">
         <v>46181</v>
@@ -7671,12 +7671,12 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B98" s="5">
         <v>46112.68011818287</v>
@@ -7686,7 +7686,7 @@
         <v>46221.897785625</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7710,7 +7710,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7723,7 +7723,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B99" s="8">
         <v>46112.680124363425</v>
@@ -7733,7 +7733,7 @@
         <v>46260.17012190972</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7760,13 +7760,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q99" s="8">
         <v>46248</v>
@@ -7778,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="T99" s="12" t="s">
-        <v>327</v>
+        <v>152</v>
       </c>
       <c r="U99" s="10" t="s">
         <v>53</v>
@@ -7796,7 +7796,7 @@
         <v>46223.59635119213</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7823,7 +7823,7 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>329</v>
@@ -7849,7 +7849,7 @@
         <v>46223.59635047454</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7876,7 +7876,7 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O101" s="9" t="s">
         <v>332</v>
@@ -7902,7 +7902,7 @@
         <v>46223.59634974537</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7929,10 +7929,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>335</v>
@@ -7982,13 +7982,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>338</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q103" s="8">
         <v>46268</v>
@@ -8000,7 +8000,7 @@
         <v>0</v>
       </c>
       <c r="T103" s="12" t="s">
-        <v>327</v>
+        <v>152</v>
       </c>
       <c r="U103" s="10" t="s">
         <v>53</v>
@@ -8018,7 +8018,7 @@
         <v>46223.59661136574</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8071,7 +8071,7 @@
         <v>46223.59661070602</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8124,7 +8124,7 @@
         <v>46223.59661008102</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8154,7 +8154,7 @@
         <v>337</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>346</v>
@@ -8204,13 +8204,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q107" s="8">
         <v>46272</v>
@@ -8240,7 +8240,7 @@
         <v>46223.59850755787</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8293,7 +8293,7 @@
         <v>46223.598506875</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8346,7 +8346,7 @@
         <v>46223.59850623843</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8376,7 +8376,7 @@
         <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>356</v>
@@ -8426,13 +8426,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q111" s="8">
         <v>46274</v>
@@ -8462,7 +8462,7 @@
         <v>46223.59859461806</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8515,7 +8515,7 @@
         <v>46223.598594027775</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8568,7 +8568,7 @@
         <v>46223.598593414354</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8598,7 +8598,7 @@
         <v>358</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>364</v>
@@ -8648,13 +8648,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q115" s="8">
         <v>46276</v>
@@ -8684,7 +8684,7 @@
         <v>46223.59868443287</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8737,7 +8737,7 @@
         <v>46223.59868380787</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8790,7 +8790,7 @@
         <v>46223.59868314815</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8820,7 +8820,7 @@
         <v>366</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>374</v>
@@ -8870,13 +8870,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>338</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q119" s="8">
         <v>46280</v>
@@ -8906,7 +8906,7 @@
         <v>46223.598781168985</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8934,7 +8934,7 @@
         <v>376</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>378</v>
@@ -8957,7 +8957,7 @@
         <v>46223.59878049769</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8985,7 +8985,7 @@
         <v>376</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>380</v>
@@ -9008,7 +9008,7 @@
         <v>46223.598779803244</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9036,7 +9036,7 @@
         <v>376</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>382</v>
@@ -9084,13 +9084,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q123" s="8">
         <v>46286</v>
@@ -9120,7 +9120,7 @@
         <v>46223.59886346065</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9148,7 +9148,7 @@
         <v>384</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>386</v>
@@ -9171,7 +9171,7 @@
         <v>46223.59886280092</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9199,7 +9199,7 @@
         <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>388</v>
@@ -9222,7 +9222,7 @@
         <v>46223.59886211806</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9250,7 +9250,7 @@
         <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>390</v>
@@ -9383,7 +9383,7 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9411,7 +9411,7 @@
         <v>395</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>400</v>
@@ -9434,7 +9434,7 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9462,7 +9462,7 @@
         <v>395</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>402</v>
@@ -9485,7 +9485,7 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9513,7 +9513,7 @@
         <v>395</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>404</v>
@@ -9740,7 +9740,7 @@
         <v>46118.542365960646</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9768,7 +9768,7 @@
         <v>395</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>414</v>
@@ -9854,7 +9854,7 @@
         <v>46223.60177635417</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9884,7 +9884,7 @@
         <v>416</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>420</v>
@@ -9907,7 +9907,7 @@
         <v>46223.601775636576</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9937,7 +9937,7 @@
         <v>416</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>422</v>
@@ -9960,7 +9960,7 @@
         <v>46223.601775</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9990,7 +9990,7 @@
         <v>416</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>424</v>
@@ -10255,7 +10255,7 @@
         <v>416</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>435</v>
@@ -10284,10 +10284,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10339,16 +10339,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10369,7 +10369,7 @@
         <v>437</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>440</v>
@@ -10392,16 +10392,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10422,7 +10422,7 @@
         <v>437</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>442</v>
@@ -10445,16 +10445,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10475,10 +10475,10 @@
         <v>437</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10504,10 +10504,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10557,10 +10557,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10610,10 +10610,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10663,10 +10663,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10716,10 +10716,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10769,10 +10769,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10826,16 +10826,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10856,7 +10856,7 @@
         <v>456</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>460</v>
@@ -10879,16 +10879,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10909,7 +10909,7 @@
         <v>456</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>456</v>
@@ -10938,10 +10938,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10985,16 +10985,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -11015,7 +11015,7 @@
         <v>456</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11044,10 +11044,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11097,10 +11097,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11150,10 +11150,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11203,10 +11203,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46260.58241461805</v>
+        <v>46265.8665325926</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>272</v>
@@ -6973,9 +6973,11 @@
       <c r="B86" s="5">
         <v>46112.6799821875</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46265.866524791665</v>
+      </c>
       <c r="D86" s="5">
-        <v>46255.5535544213</v>
+        <v>46265.866544212964</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>289</v>
@@ -7020,13 +7022,13 @@
         <v>46247</v>
       </c>
       <c r="S86" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U86" s="10" t="s">
-        <v>53</v>
+      <c r="U86" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -8176,7 +8176,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46223.60164922454</v>
+        <v>46266.19227758102</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>348</v>
@@ -8223,8 +8223,8 @@
       <c r="S107" s="9">
         <v>0</v>
       </c>
-      <c r="T107" s="11" t="s">
-        <v>127</v>
+      <c r="T107" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U107" s="10" t="s">
         <v>53</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -7435,7 +7435,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46112.680270150464</v>
+        <v>46267.181278379634</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>311</v>
@@ -7482,8 +7482,8 @@
       <c r="S94" s="6">
         <v>0</v>
       </c>
-      <c r="T94" s="11" t="s">
-        <v>127</v>
+      <c r="T94" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U94" s="10" t="s">
         <v>53</v>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46260.17012190972</v>
+        <v>46267.16748857639</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>326</v>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46223.59635119213</v>
+        <v>46267.16749694444</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>211</v>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46223.59635047454</v>
+        <v>46267.16748722222</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>246</v>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46223.59634974537</v>
+        <v>46267.16750917824</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>250</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -7732,7 +7732,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46267.16748857639</v>
+        <v>46268.182027939816</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>326</v>
@@ -7779,8 +7779,8 @@
       <c r="S99" s="9">
         <v>0</v>
       </c>
-      <c r="T99" s="12" t="s">
-        <v>152</v>
+      <c r="T99" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U99" s="10" t="s">
         <v>53</v>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46223.60164861111</v>
+        <v>46268.196200266204</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>358</v>
@@ -8445,8 +8445,8 @@
       <c r="S111" s="9">
         <v>0</v>
       </c>
-      <c r="T111" s="11" t="s">
-        <v>127</v>
+      <c r="T111" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U111" s="10" t="s">
         <v>53</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -7954,7 +7954,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46262.17720913194</v>
+        <v>46269.16771181713</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>337</v>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46223.59661136574</v>
+        <v>46269.16771060185</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>211</v>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46223.59661070602</v>
+        <v>46269.167709421294</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>246</v>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46223.59661008102</v>
+        <v>46269.1677040625</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>250</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -7954,7 +7954,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46269.16771181713</v>
+        <v>46270.17116346065</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>337</v>
@@ -8001,8 +8001,8 @@
       <c r="S103" s="9">
         <v>0</v>
       </c>
-      <c r="T103" s="12" t="s">
-        <v>152</v>
+      <c r="T103" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U103" s="10" t="s">
         <v>53</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -4397,7 +4397,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46265.205750416666</v>
+        <v>46272.1671390625</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.72350310185</v>
+        <v>46272.16712449074</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46223.60164790509</v>
+        <v>46272.14767306713</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>366</v>
@@ -8667,8 +8667,8 @@
       <c r="S115" s="9">
         <v>0</v>
       </c>
-      <c r="T115" s="11" t="s">
-        <v>127</v>
+      <c r="T115" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="U115" s="10" t="s">
         <v>53</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -469,487 +469,487 @@
     <t>Generación OC motor  ot 4294 - 4296 - 4297,Fabricación motor  ot 4294 - 4296 - 4297,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
   </si>
   <si>
+    <t>1213886181511076</t>
+  </si>
+  <si>
+    <t>Generación OC motor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Motor  ot 4294 - 4296 - 4297,Fabricación motor  ot 4294 - 4296 - 4297,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886259298291</t>
+  </si>
+  <si>
+    <t>Fabricación motor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Motor  ot 4294 - 4296 - 4297,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213886304284601</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Motor  ot 4294 - 4296 - 4297,OT 4297 ZVR1-14-25/4,OT 4280 ZVN 1-9-63/2,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886259305779</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC materiales ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886259305803</t>
+  </si>
+  <si>
+    <t>Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886259307144</t>
+  </si>
+  <si>
+    <t>Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:</t>
+  </si>
+  <si>
+    <t>1213886430624337</t>
+  </si>
+  <si>
+    <t>Sensores</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores,Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>1213886304289396</t>
+  </si>
+  <si>
+    <t>Generacion OC Sensor</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores,Sensores</t>
+  </si>
+  <si>
+    <t>1213886259313572</t>
+  </si>
+  <si>
+    <t>Fabricacion Sensores</t>
+  </si>
+  <si>
+    <t>Sensores,Recepción Sensores</t>
+  </si>
+  <si>
+    <t>1213886259313596</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Check Planos</t>
+  </si>
+  <si>
+    <t>1213902113454390</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886430614804</t>
+  </si>
+  <si>
+    <t>Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297,Check Planos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Control de calidad Fabricación externa  4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213886259324444</t>
+  </si>
+  <si>
+    <t>Atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>Propuesta Atenuadores ,Fabricacion atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
+  </si>
+  <si>
+    <t>1213886259326766</t>
+  </si>
+  <si>
+    <t>Generacion oc Atenuador  ot 4295</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4295,Atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>1213886259328934</t>
+  </si>
+  <si>
+    <t>Fabricacion atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>Atenuadores,Atenuador ot 4295</t>
+  </si>
+  <si>
+    <t>1213886259328954</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1213902113471352</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213899500210915</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213899500210916</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213899500210917</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886304303088</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213910573903655</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213910573903656</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR 1-14-34/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4296 ZVR 1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213910573903657</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR1-14-25/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4297 ZVR1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886181537550</t>
+  </si>
+  <si>
+    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213910573903658</t>
+  </si>
+  <si>
+    <t>1213910573903659</t>
+  </si>
+  <si>
+    <t>1213910573903660</t>
+  </si>
+  <si>
+    <t>1213886259337472</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886259341627</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886259341647</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213881596172439</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213902113480432</t>
+  </si>
+  <si>
+    <t>Control de calidad</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa  4294 - 4296 - 4297</t>
+  </si>
+  <si>
+    <t>1213902113480444</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213902113485641</t>
+  </si>
+  <si>
+    <t>Bodega</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213886181542206</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213886181542236</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>Bodega,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213902113596084</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Armado,Control de calidad Armado,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1213902113601428</t>
+  </si>
+  <si>
+    <t>Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,Caldereria,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886181546547</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1213886304313737</t>
+  </si>
+  <si>
+    <t>Preparacion materiales,Check Planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213902113612855</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Armado</t>
+  </si>
+  <si>
+    <t>1213881596172409</t>
+  </si>
+  <si>
+    <t>Armado,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886380584527</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT  4297 ZVR 1-14-25/4</t>
+  </si>
+  <si>
+    <t>1213886380584552</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4294 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213886304333912</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886305136215</t>
+  </si>
+  <si>
+    <t>OT  4297 ZVR 1-14-25/4,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213886259370468</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion Tableros y componentes electricos ,Recepcion motor,Recepcion Rodete,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213902113620466</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,Bodega:</t>
+  </si>
+  <si>
+    <t>1213886380596164</t>
+  </si>
+  <si>
+    <t>OT 4299- TABLERO PLC,OT 4300- TABLERO BOTONERA,OT 4301-COMPONENTES TABLERO COMPUERTAS,Bodega:,OT 4298- TABLERO VDF ABB ACS880-17</t>
+  </si>
+  <si>
+    <t>1213886181569524</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
+    <t>1213886304340554</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>OT 4294 ZVR 1-14-42/4,Bodega:,OT 4296 ZVR1-14-34/4</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213886181511076</t>
-  </si>
-  <si>
-    <t>Generación OC motor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Motor  ot 4294 - 4296 - 4297,Fabricación motor  ot 4294 - 4296 - 4297,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886259298291</t>
-  </si>
-  <si>
-    <t>Fabricación motor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Motor  ot 4294 - 4296 - 4297,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213886304284601</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Motor  ot 4294 - 4296 - 4297,OT 4297 ZVR1-14-25/4,OT 4280 ZVN 1-9-63/2,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886259305779</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC materiales ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886259305803</t>
-  </si>
-  <si>
-    <t>Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886259307144</t>
-  </si>
-  <si>
-    <t>Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Materiales a codigo // compras locales aprovisionamientomiento  ot 4294 - 4296 - 4297:</t>
-  </si>
-  <si>
-    <t>1213886430624337</t>
-  </si>
-  <si>
-    <t>Sensores</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores,Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>1213886304289396</t>
-  </si>
-  <si>
-    <t>Generacion OC Sensor</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores,Sensores</t>
-  </si>
-  <si>
-    <t>1213886259313572</t>
-  </si>
-  <si>
-    <t>Fabricacion Sensores</t>
-  </si>
-  <si>
-    <t>Sensores,Recepción Sensores</t>
-  </si>
-  <si>
-    <t>1213886259313596</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,Check Planos</t>
-  </si>
-  <si>
-    <t>1213902113454390</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886430614804</t>
-  </si>
-  <si>
-    <t>Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion a codigo y compras locales ot 4294 - 4296 - 4297,Check Planos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Control de calidad Fabricación externa  4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213886259324444</t>
-  </si>
-  <si>
-    <t>Atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>Propuesta Atenuadores ,Fabricacion atenuador ot 4295,Generacion oc Atenuador  ot 4295</t>
-  </si>
-  <si>
-    <t>1213886259326766</t>
-  </si>
-  <si>
-    <t>Generacion oc Atenuador  ot 4295</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4295,Atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>1213886259328934</t>
-  </si>
-  <si>
-    <t>Fabricacion atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>Atenuadores,Atenuador ot 4295</t>
-  </si>
-  <si>
-    <t>1213886259328954</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1213902113471352</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213899500210915</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213899500210916</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213899500210917</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886304303088</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,OT 4296 ZVR 1-14-34/4,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213910573903655</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213910573903656</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR 1-14-34/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4296 ZVR 1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213910573903657</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR1-14-25/4,Planos motor proveedor  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4297 ZVR1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886181537550</t>
-  </si>
-  <si>
-    <t>Fabricacion Externa  ot 4294 - 4296 - 4297,Fabricacion estructura proveedor externo  ot 4294 - 4296 - 4297,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,OT 4296 ZVR1-14-34/4,propuesta compras a codigo // aprovisionamiento ot 4294 - 4296 - 4297,Propuesta Fabricación Externa  ot 4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213910573903658</t>
-  </si>
-  <si>
-    <t>1213910573903659</t>
-  </si>
-  <si>
-    <t>1213910573903660</t>
-  </si>
-  <si>
-    <t>1213886259337472</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886259341627</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886259341647</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213881596172439</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213902113480432</t>
-  </si>
-  <si>
-    <t>Control de calidad</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa  4294 - 4296 - 4297</t>
-  </si>
-  <si>
-    <t>1213902113480444</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213902113485641</t>
-  </si>
-  <si>
-    <t>Bodega</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213886181542206</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213886181542236</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Bodega,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213902113596084</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Armado,Control de calidad Armado,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1213902113601428</t>
-  </si>
-  <si>
-    <t>Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,Caldereria,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886181546547</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1213886304313737</t>
-  </si>
-  <si>
-    <t>Preparacion materiales,Check Planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213902113612855</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Armado</t>
-  </si>
-  <si>
-    <t>1213881596172409</t>
-  </si>
-  <si>
-    <t>Armado,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886380584527</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,OT  4297 ZVR 1-14-25/4</t>
-  </si>
-  <si>
-    <t>1213886380584552</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4294 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213886304333912</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886305136215</t>
-  </si>
-  <si>
-    <t>OT  4297 ZVR 1-14-25/4,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213886259370468</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion Tableros y componentes electricos ,Recepcion motor,Recepcion Rodete,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213902113620466</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4296 ZVR1-14-34/4,OT 4294 ZVR 1-14-42/4,Bodega:</t>
-  </si>
-  <si>
-    <t>1213886380596164</t>
-  </si>
-  <si>
-    <t>OT 4299- TABLERO PLC,OT 4300- TABLERO BOTONERA,OT 4301-COMPONENTES TABLERO COMPUERTAS,Bodega:,OT 4298- TABLERO VDF ABB ACS880-17</t>
-  </si>
-  <si>
-    <t>1213886181569524</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>1213886304340554</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>OT 4294 ZVR 1-14-42/4,Bodega:,OT 4296 ZVR1-14-34/4</t>
   </si>
   <si>
     <t>1213886380599685</t>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46272.1671390625</v>
+        <v>46273.12870017361</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4444,8 +4444,8 @@
       <c r="S42" s="6">
         <v>0</v>
       </c>
-      <c r="T42" s="12" t="s">
-        <v>152</v>
+      <c r="T42" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>53</v>
@@ -4453,7 +4453,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46112.67964135417</v>
@@ -4465,7 +4465,7 @@
         <v>46182.678117118056</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4498,7 +4498,7 @@
         <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q43" s="8">
         <v>45978</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46112.67965385417</v>
@@ -4528,7 +4528,7 @@
         <v>46272.16712449074</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4558,10 +4558,10 @@
         <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q44" s="5">
         <v>45999</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8">
         <v>46112.679662372684</v>
@@ -4593,7 +4593,7 @@
         <v>46182.67812403935</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4623,10 +4623,10 @@
         <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="8">
         <v>45999</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46112.67967090278</v>
@@ -4658,16 +4658,16 @@
         <v>46211.831143738425</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46195</v>
@@ -4688,7 +4688,7 @@
         <v>117</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>117</v>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46112.679679733796</v>
@@ -4729,10 +4729,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46195</v>
@@ -4750,13 +4750,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q47" s="8">
         <v>45985</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B48" s="5">
         <v>46112.679688564815</v>
@@ -4788,16 +4788,16 @@
         <v>46211.83093092593</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46202</v>
@@ -4815,13 +4815,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q48" s="5">
         <v>46007</v>
@@ -4841,7 +4841,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B49" s="8">
         <v>46112.679698321765</v>
@@ -4853,16 +4853,16 @@
         <v>46220.18905753472</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46125</v>
@@ -4883,7 +4883,7 @@
         <v>117</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>117</v>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B50" s="5">
         <v>46112.67970664352</v>
@@ -4918,16 +4918,16 @@
         <v>46154.86749444444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46125</v>
@@ -4945,13 +4945,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4961,7 +4961,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46112.67971469907</v>
@@ -4973,16 +4973,16 @@
         <v>46154.86772430556</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46135</v>
@@ -5000,13 +5000,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5016,7 +5016,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46112.67972244213</v>
@@ -5028,16 +5028,16 @@
         <v>46231.19795877315</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46195</v>
@@ -5058,7 +5058,7 @@
         <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>117</v>
@@ -5081,7 +5081,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46112.67973174769</v>
@@ -5099,10 +5099,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46195</v>
@@ -5120,13 +5120,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>111</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46112.679776261575</v>
@@ -5154,16 +5154,16 @@
         <v>46227.619398842595</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46210</v>
@@ -5181,13 +5181,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5197,7 +5197,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46112.6797871875</v>
@@ -5209,7 +5209,7 @@
         <v>46182.6930560301</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
@@ -5239,7 +5239,7 @@
         <v>117</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5262,7 +5262,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46112.67979498843</v>
@@ -5274,7 +5274,7 @@
         <v>46182.6740215625</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5301,13 +5301,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46112.679800983795</v>
@@ -5329,7 +5329,7 @@
         <v>46182.69303354167</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5356,13 +5356,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46112.67980725694</v>
@@ -5384,7 +5384,7 @@
         <v>46210.52999649306</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5408,7 +5408,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46112.67981122685</v>
@@ -5437,16 +5437,16 @@
         <v>46222.150650462965</v>
       </c>
       <c r="E59" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="I59" s="8">
         <v>46121</v>
@@ -5464,13 +5464,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="Q59" s="8">
         <v>46121</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46114.7256690162</v>
@@ -5502,16 +5502,16 @@
         <v>46157.92811706019</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I60" s="5">
         <v>46121</v>
@@ -5529,13 +5529,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B61" s="8">
         <v>46114.72585883102</v>
@@ -5557,16 +5557,16 @@
         <v>46157.929841793986</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I61" s="8">
         <v>46121</v>
@@ -5584,13 +5584,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46114.7260297801</v>
@@ -5612,16 +5612,16 @@
         <v>46155.549570648145</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I62" s="5">
         <v>46121</v>
@@ -5639,13 +5639,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46112.67982518519</v>
@@ -5667,16 +5667,16 @@
         <v>46190.17747758102</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="I63" s="8">
         <v>46183</v>
@@ -5694,13 +5694,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q63" s="8">
         <v>46183</v>
@@ -5720,7 +5720,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46114.72944869213</v>
@@ -5732,16 +5732,16 @@
         <v>46162.64346460648</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I64" s="5">
         <v>46183</v>
@@ -5759,13 +5759,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46114.72950832176</v>
@@ -5787,16 +5787,16 @@
         <v>46162.643472129625</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I65" s="8">
         <v>46183</v>
@@ -5814,13 +5814,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O65" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>229</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46114.72956502315</v>
@@ -5842,16 +5842,16 @@
         <v>46162.643481747684</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I66" s="5">
         <v>46183</v>
@@ -5869,13 +5869,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5885,7 +5885,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B67" s="8">
         <v>46112.6798337963</v>
@@ -5903,10 +5903,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I67" s="8">
         <v>46190</v>
@@ -5924,13 +5924,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q67" s="8">
         <v>46190</v>
@@ -5950,7 +5950,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46114.72964204861</v>
@@ -5962,16 +5962,16 @@
         <v>46181.73298168981</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5990,7 +5990,7 @@
         <v>105</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>105</v>
@@ -6003,7 +6003,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B69" s="8">
         <v>46114.72973784722</v>
@@ -6015,16 +6015,16 @@
         <v>46181.73299055555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -6043,7 +6043,7 @@
         <v>105</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>105</v>
@@ -6056,7 +6056,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46114.72978940972</v>
@@ -6068,16 +6068,16 @@
         <v>46181.73299902778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -6096,7 +6096,7 @@
         <v>105</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>105</v>
@@ -6109,7 +6109,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="8">
         <v>46112.67984715277</v>
@@ -6119,16 +6119,16 @@
         <v>46118.54786293981</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="I71" s="8">
         <v>46281</v>
@@ -6146,10 +6146,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6182,16 +6182,16 @@
         <v>46118.54786737269</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="I72" s="5">
         <v>46281</v>
@@ -6209,13 +6209,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6235,16 +6235,16 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>240</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="I73" s="8">
         <v>46281</v>
@@ -6262,13 +6262,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6288,16 +6288,16 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="I74" s="5">
         <v>46281</v>
@@ -6315,13 +6315,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6343,7 +6343,7 @@
         <v>46260.658590023144</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6367,7 +6367,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6396,16 +6396,16 @@
         <v>46260.65857824074</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6421,13 +6421,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6459,7 +6459,7 @@
         <v>46237.86033361111</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6483,7 +6483,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6512,16 +6512,16 @@
         <v>46237.86031981482</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6539,13 +6539,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6577,16 +6577,16 @@
         <v>46237.86032310185</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6604,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6625,12 +6625,12 @@
         <v>31</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6640,7 +6640,7 @@
         <v>46265.8665325926</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6664,7 +6664,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6677,7 +6677,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6689,16 +6689,16 @@
         <v>46260.58243447916</v>
       </c>
       <c r="E81" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
+      <c r="H81" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6716,13 +6716,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6752,16 +6752,16 @@
         <v>46260.65928364583</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6779,13 +6779,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6817,16 +6817,16 @@
         <v>46260.58258379629</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6844,13 +6844,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>283</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6872,16 +6872,16 @@
         <v>46260.58353350694</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6899,13 +6899,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6915,7 +6915,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6925,16 +6925,16 @@
         <v>46260.58241299768</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6952,13 +6952,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6980,16 +6980,16 @@
         <v>46265.866544212964</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -7007,13 +7007,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7033,7 +7033,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7043,16 +7043,16 @@
         <v>46260.58258729167</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7070,13 +7070,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O87" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="P87" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7086,7 +7086,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7096,16 +7096,16 @@
         <v>46260.583538541665</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7123,13 +7123,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7139,7 +7139,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7149,16 +7149,16 @@
         <v>46247.16738921296</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7176,13 +7176,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7202,7 +7202,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7226,7 +7226,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7239,7 +7239,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7249,16 +7249,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7276,13 +7276,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7302,7 +7302,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7318,10 +7318,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7339,13 +7339,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7365,7 +7365,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7375,16 +7375,16 @@
         <v>46248.18939703704</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7402,13 +7402,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7423,12 +7423,12 @@
         <v>31</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
@@ -7438,16 +7438,16 @@
         <v>46267.181278379634</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7465,13 +7465,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="12" t="s">
-        <v>152</v>
+        <v>312</v>
       </c>
       <c r="U94" s="10" t="s">
         <v>53</v>
@@ -7507,10 +7507,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7528,10 +7528,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>315</v>
@@ -7549,7 +7549,7 @@
         <v>31</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7570,10 +7570,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7589,10 +7589,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>318</v>
@@ -7610,7 +7610,7 @@
         <v>31</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7631,10 +7631,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7652,10 +7652,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>321</v>
@@ -7673,7 +7673,7 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7798,7 +7798,7 @@
         <v>46267.16749694444</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7851,7 +7851,7 @@
         <v>46267.16748722222</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7904,7 +7904,7 @@
         <v>46267.16750917824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7934,7 +7934,7 @@
         <v>326</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>335</v>
@@ -8020,7 +8020,7 @@
         <v>46269.16771060185</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8073,7 +8073,7 @@
         <v>46269.167709421294</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8126,7 +8126,7 @@
         <v>46269.1677040625</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8156,7 +8156,7 @@
         <v>337</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>346</v>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46266.19227758102</v>
+        <v>46273.1674925463</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>348</v>
@@ -8224,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="T107" s="12" t="s">
-        <v>152</v>
+        <v>312</v>
       </c>
       <c r="U107" s="10" t="s">
         <v>53</v>
@@ -8239,10 +8239,10 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46223.59850755787</v>
+        <v>46273.16743239583</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8292,10 +8292,10 @@
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46223.598506875</v>
+        <v>46273.1674940625</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8345,10 +8345,10 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46223.59850623843</v>
+        <v>46273.16747483796</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8378,7 +8378,7 @@
         <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>356</v>
@@ -8431,7 +8431,7 @@
         <v>323</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>323</v>
@@ -8446,7 +8446,7 @@
         <v>0</v>
       </c>
       <c r="T111" s="12" t="s">
-        <v>152</v>
+        <v>312</v>
       </c>
       <c r="U111" s="10" t="s">
         <v>53</v>
@@ -8464,7 +8464,7 @@
         <v>46223.59859461806</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8517,7 +8517,7 @@
         <v>46223.598594027775</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8570,7 +8570,7 @@
         <v>46223.598593414354</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8600,7 +8600,7 @@
         <v>358</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>364</v>
@@ -8668,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="T115" s="12" t="s">
-        <v>152</v>
+        <v>312</v>
       </c>
       <c r="U115" s="10" t="s">
         <v>53</v>
@@ -8686,7 +8686,7 @@
         <v>46223.59868443287</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8739,7 +8739,7 @@
         <v>46223.59868380787</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8792,7 +8792,7 @@
         <v>46223.59868314815</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8822,7 +8822,7 @@
         <v>366</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>374</v>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46223.60164731482</v>
+        <v>46273.15093820602</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>376</v>
@@ -8889,8 +8889,8 @@
       <c r="S119" s="9">
         <v>0</v>
       </c>
-      <c r="T119" s="11" t="s">
-        <v>127</v>
+      <c r="T119" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="U119" s="10" t="s">
         <v>53</v>
@@ -8908,7 +8908,7 @@
         <v>46223.598781168985</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8936,7 +8936,7 @@
         <v>376</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>378</v>
@@ -8959,7 +8959,7 @@
         <v>46223.59878049769</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8987,7 +8987,7 @@
         <v>376</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>380</v>
@@ -9010,7 +9010,7 @@
         <v>46223.598779803244</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9038,7 +9038,7 @@
         <v>376</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>382</v>
@@ -9122,7 +9122,7 @@
         <v>46223.59886346065</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9150,7 +9150,7 @@
         <v>384</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>386</v>
@@ -9173,7 +9173,7 @@
         <v>46223.59886280092</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9201,7 +9201,7 @@
         <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>388</v>
@@ -9224,7 +9224,7 @@
         <v>46223.59886211806</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9252,7 +9252,7 @@
         <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>390</v>
@@ -9385,7 +9385,7 @@
         <v>46118.54236040509</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9413,7 +9413,7 @@
         <v>395</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P129" s="9" t="s">
         <v>400</v>
@@ -9436,7 +9436,7 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9464,7 +9464,7 @@
         <v>395</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>402</v>
@@ -9487,7 +9487,7 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9515,7 +9515,7 @@
         <v>395</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>404</v>
@@ -9856,7 +9856,7 @@
         <v>46223.60177635417</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9886,7 +9886,7 @@
         <v>416</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>420</v>
@@ -9909,7 +9909,7 @@
         <v>46223.601775636576</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9939,7 +9939,7 @@
         <v>416</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>422</v>
@@ -9962,7 +9962,7 @@
         <v>46223.601775</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9992,7 +9992,7 @@
         <v>416</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>424</v>
@@ -10286,10 +10286,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10341,16 +10341,16 @@
         <v>46118.543572766204</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10371,7 +10371,7 @@
         <v>437</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>440</v>
@@ -10394,16 +10394,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10424,7 +10424,7 @@
         <v>437</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>442</v>
@@ -10447,16 +10447,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10477,10 +10477,10 @@
         <v>437</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10506,10 +10506,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10559,10 +10559,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H151" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10612,10 +10612,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10665,10 +10665,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10718,10 +10718,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10771,10 +10771,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10828,16 +10828,16 @@
         <v>46118.543845196764</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10858,7 +10858,7 @@
         <v>456</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>460</v>
@@ -10881,16 +10881,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10911,7 +10911,7 @@
         <v>456</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>456</v>
@@ -10940,10 +10940,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10987,16 +10987,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H159" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -11017,7 +11017,7 @@
         <v>456</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11046,10 +11046,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11099,10 +11099,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H161" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11152,10 +11152,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11205,10 +11205,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H163" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -739,6 +739,9 @@
     <t>OT 4297 ZVR 1-14-25/4,OT 4294 ZVR 1-14-42/4,OT 4296 ZVR1-14-34/4</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1213886259341627</t>
   </si>
   <si>
@@ -947,9 +950,6 @@
   </si>
   <si>
     <t>OT 4294 ZVR 1-14-42/4,Bodega:,OT 4296 ZVR1-14-34/4</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1213886380599685</t>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46118.54786293981</v>
+        <v>46274.12746957176</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>238</v>
@@ -6163,8 +6163,8 @@
       <c r="S71" s="9">
         <v>0</v>
       </c>
-      <c r="T71" s="11" t="s">
-        <v>127</v>
+      <c r="T71" s="12" t="s">
+        <v>242</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>53</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
         <v>46112.679854120375</v>
@@ -6215,7 +6215,7 @@
         <v>210</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B73" s="8">
         <v>46112.67986081018</v>
@@ -6235,7 +6235,7 @@
         <v>46118.54786818287</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -6265,10 +6265,10 @@
         <v>238</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B74" s="5">
         <v>46112.69527582176</v>
@@ -6288,7 +6288,7 @@
         <v>46118.54786895833</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6318,10 +6318,10 @@
         <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B75" s="8">
         <v>46112.679867326384</v>
@@ -6343,7 +6343,7 @@
         <v>46260.658590023144</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>25</v>
@@ -6367,7 +6367,7 @@
         <v>26</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>26</v>
@@ -6384,7 +6384,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B76" s="5">
         <v>46112.67987047454</v>
@@ -6396,16 +6396,16 @@
         <v>46260.65857824074</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6421,13 +6421,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q76" s="5">
         <v>46231</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B77" s="8">
         <v>46112.6798790162</v>
@@ -6459,7 +6459,7 @@
         <v>46237.86033361111</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6483,7 +6483,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6500,7 +6500,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B78" s="5">
         <v>46112.6798825463</v>
@@ -6512,16 +6512,16 @@
         <v>46237.86031981482</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I78" s="5">
         <v>46244</v>
@@ -6539,13 +6539,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q78" s="5">
         <v>46175</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B79" s="8">
         <v>46112.679890740736</v>
@@ -6577,16 +6577,16 @@
         <v>46237.86032310185</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I79" s="8">
         <v>46246</v>
@@ -6604,13 +6604,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q79" s="8">
         <v>46177</v>
@@ -6625,12 +6625,12 @@
         <v>31</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
         <v>46112.679898159724</v>
@@ -6640,7 +6640,7 @@
         <v>46265.8665325926</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6664,7 +6664,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6677,7 +6677,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B81" s="8">
         <v>46112.679901701384</v>
@@ -6689,16 +6689,16 @@
         <v>46260.58243447916</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I81" s="8">
         <v>46217</v>
@@ -6716,13 +6716,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="8">
         <v>46217</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46112.67991023148</v>
@@ -6752,16 +6752,16 @@
         <v>46260.65928364583</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I82" s="5">
         <v>46226</v>
@@ -6779,13 +6779,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>241</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46226</v>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46112.679960775466</v>
@@ -6823,10 +6823,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I83" s="8">
         <v>46226</v>
@@ -6844,13 +6844,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6860,7 +6860,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46112.67997252315</v>
@@ -6872,16 +6872,16 @@
         <v>46260.58353350694</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I84" s="5">
         <v>46226</v>
@@ -6899,13 +6899,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6915,7 +6915,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B85" s="8">
         <v>46112.683129375</v>
@@ -6925,16 +6925,16 @@
         <v>46260.58241299768</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I85" s="8">
         <v>46226</v>
@@ -6952,13 +6952,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46112.6799821875</v>
@@ -6980,16 +6980,16 @@
         <v>46265.866544212964</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46246</v>
@@ -7007,13 +7007,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86" s="5">
         <v>46246</v>
@@ -7033,7 +7033,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8">
         <v>46112.679991655095</v>
@@ -7049,10 +7049,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -7070,13 +7070,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7086,7 +7086,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46112.68000065972</v>
@@ -7096,16 +7096,16 @@
         <v>46260.583538541665</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46246</v>
@@ -7123,13 +7123,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7139,7 +7139,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46112.68554289352</v>
@@ -7149,16 +7149,16 @@
         <v>46247.16738921296</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46246</v>
@@ -7176,13 +7176,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B90" s="5">
         <v>46112.68000929398</v>
@@ -7202,7 +7202,7 @@
         <v>46118.55096842593</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -7226,7 +7226,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -7239,7 +7239,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B91" s="8">
         <v>46112.68001403935</v>
@@ -7249,16 +7249,16 @@
         <v>46185.19835885416</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I91" s="8">
         <v>46183</v>
@@ -7276,13 +7276,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7302,7 +7302,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B92" s="5">
         <v>46112.68002373843</v>
@@ -7318,10 +7318,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I92" s="5">
         <v>46239</v>
@@ -7339,13 +7339,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q92" s="5">
         <v>46239</v>
@@ -7365,7 +7365,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B93" s="8">
         <v>46112.680037453705</v>
@@ -7375,16 +7375,16 @@
         <v>46248.18939703704</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I93" s="8">
         <v>46246</v>
@@ -7402,13 +7402,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q93" s="8">
         <v>46246</v>
@@ -7423,31 +7423,31 @@
         <v>31</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B94" s="5">
         <v>46112.680046574074</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46267.181278379634</v>
+        <v>46274.16743396991</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I94" s="5">
         <v>46273</v>
@@ -7465,13 +7465,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>156</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q94" s="5">
         <v>46273</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="12" t="s">
-        <v>312</v>
+        <v>242</v>
       </c>
       <c r="U94" s="10" t="s">
         <v>53</v>
@@ -7507,10 +7507,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I95" s="8">
         <v>46220</v>
@@ -7528,7 +7528,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>178</v>
@@ -7549,7 +7549,7 @@
         <v>31</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7570,10 +7570,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7589,10 +7589,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>318</v>
@@ -7610,7 +7610,7 @@
         <v>31</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7631,10 +7631,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I97" s="8">
         <v>46181</v>
@@ -7652,7 +7652,7 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>198</v>
@@ -7673,7 +7673,7 @@
         <v>31</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7851,7 +7851,7 @@
         <v>46267.16748722222</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7904,7 +7904,7 @@
         <v>46267.16750917824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7934,7 +7934,7 @@
         <v>326</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>335</v>
@@ -8073,7 +8073,7 @@
         <v>46269.167709421294</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8126,7 +8126,7 @@
         <v>46269.1677040625</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8156,7 +8156,7 @@
         <v>337</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>346</v>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46273.1674925463</v>
+        <v>46274.15587163194</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>348</v>
@@ -8223,8 +8223,8 @@
       <c r="S107" s="9">
         <v>0</v>
       </c>
-      <c r="T107" s="12" t="s">
-        <v>312</v>
+      <c r="T107" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U107" s="10" t="s">
         <v>53</v>
@@ -8295,7 +8295,7 @@
         <v>46273.1674940625</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8348,7 +8348,7 @@
         <v>46273.16747483796</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8378,7 +8378,7 @@
         <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>356</v>
@@ -8446,7 +8446,7 @@
         <v>0</v>
       </c>
       <c r="T111" s="12" t="s">
-        <v>312</v>
+        <v>242</v>
       </c>
       <c r="U111" s="10" t="s">
         <v>53</v>
@@ -8517,7 +8517,7 @@
         <v>46223.598594027775</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8570,7 +8570,7 @@
         <v>46223.598593414354</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8600,7 +8600,7 @@
         <v>358</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>364</v>
@@ -8668,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="T115" s="12" t="s">
-        <v>312</v>
+        <v>242</v>
       </c>
       <c r="U115" s="10" t="s">
         <v>53</v>
@@ -8739,7 +8739,7 @@
         <v>46223.59868380787</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8792,7 +8792,7 @@
         <v>46223.59868314815</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8822,7 +8822,7 @@
         <v>366</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>374</v>
@@ -8890,7 +8890,7 @@
         <v>0</v>
       </c>
       <c r="T119" s="12" t="s">
-        <v>312</v>
+        <v>242</v>
       </c>
       <c r="U119" s="10" t="s">
         <v>53</v>
@@ -8959,7 +8959,7 @@
         <v>46223.59878049769</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8987,7 +8987,7 @@
         <v>376</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>380</v>
@@ -9010,7 +9010,7 @@
         <v>46223.598779803244</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9038,7 +9038,7 @@
         <v>376</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>382</v>
@@ -9173,7 +9173,7 @@
         <v>46223.59886280092</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9201,7 +9201,7 @@
         <v>384</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>388</v>
@@ -9224,7 +9224,7 @@
         <v>46223.59886211806</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9252,7 +9252,7 @@
         <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>390</v>
@@ -9436,7 +9436,7 @@
         <v>46118.54236118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9464,7 +9464,7 @@
         <v>395</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>402</v>
@@ -9487,7 +9487,7 @@
         <v>46118.542362002314</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9515,7 +9515,7 @@
         <v>395</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P131" s="9" t="s">
         <v>404</v>
@@ -9909,7 +9909,7 @@
         <v>46223.601775636576</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9939,7 +9939,7 @@
         <v>416</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>422</v>
@@ -9962,7 +9962,7 @@
         <v>46223.601775</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9992,7 +9992,7 @@
         <v>416</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>424</v>
@@ -10286,10 +10286,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10347,10 +10347,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I147" s="8">
         <v>46293</v>
@@ -10394,16 +10394,16 @@
         <v>46118.543573414354</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I148" s="5">
         <v>46293</v>
@@ -10424,7 +10424,7 @@
         <v>437</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>442</v>
@@ -10447,16 +10447,16 @@
         <v>46118.60507034722</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I149" s="8">
         <v>46293</v>
@@ -10477,10 +10477,10 @@
         <v>437</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10506,10 +10506,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I150" s="5">
         <v>46293</v>
@@ -10559,10 +10559,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I151" s="8">
         <v>46293</v>
@@ -10612,10 +10612,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I152" s="5">
         <v>46293</v>
@@ -10665,10 +10665,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I153" s="8">
         <v>46293</v>
@@ -10718,10 +10718,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I154" s="5">
         <v>46293</v>
@@ -10771,10 +10771,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I155" s="8">
         <v>46294</v>
@@ -10834,10 +10834,10 @@
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I156" s="5">
         <v>46294</v>
@@ -10881,16 +10881,16 @@
         <v>46118.543846030094</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I157" s="8">
         <v>46294</v>
@@ -10911,7 +10911,7 @@
         <v>456</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>456</v>
@@ -10940,10 +10940,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I158" s="5">
         <v>46294</v>
@@ -10987,16 +10987,16 @@
         <v>46118.543852002316</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I159" s="8">
         <v>46294</v>
@@ -11017,7 +11017,7 @@
         <v>456</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>26</v>
@@ -11046,10 +11046,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I160" s="5">
         <v>46294</v>
@@ -11099,10 +11099,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I161" s="8">
         <v>46294</v>
@@ -11152,10 +11152,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I162" s="5">
         <v>46294</v>
@@ -11205,10 +11205,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I163" s="8">
         <v>46294</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -7435,7 +7435,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46274.16743396991</v>
+        <v>46275.16202614583</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>311</v>
@@ -7482,8 +7482,8 @@
       <c r="S94" s="6">
         <v>0</v>
       </c>
-      <c r="T94" s="12" t="s">
-        <v>242</v>
+      <c r="T94" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U94" s="10" t="s">
         <v>53</v>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46268.196200266204</v>
+        <v>46275.16748762732</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>358</v>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46223.59859461806</v>
+        <v>46275.167486631944</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>210</v>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46223.598594027775</v>
+        <v>46275.16748549769</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>246</v>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46223.598593414354</v>
+        <v>46275.167477662035</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>249</v>

--- a/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
+++ b/data/50001534 - ZITRON PERU METRO LIMA E04-05-06-R4.xlsx
@@ -8398,7 +8398,7 @@
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46275.16748762732</v>
+        <v>46276.1559318287</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>358</v>
@@ -8445,8 +8445,8 @@
       <c r="S111" s="9">
         <v>0</v>
       </c>
-      <c r="T111" s="12" t="s">
-        <v>242</v>
+      <c r="T111" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U111" s="10" t="s">
         <v>53</v>
